--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcabf36b0134af82/바탕 화면/김인혁/김인혁_청년축구단/1. 출석부/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcabf36b0134af82/바탕 화면/김인혁_청년축구단/1. 출석부/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1131" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D52BFECD-F442-41B8-BEC8-5AC9673C18EE}"/>
+  <xr:revisionPtr revIDLastSave="1193" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC86EF0F-FC37-40DA-A20D-F39F1B20B262}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="종합Sheet" sheetId="1" r:id="rId1"/>
@@ -24,10 +24,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">개인기록Sheet!$A$3:$I$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">종합Sheet!$A$3:$CT$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">종합Sheet!$A$3:$CT$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'종합Sheet (외부)'!$A$3:$CT$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">개인기록Sheet!$A$2:$I$52</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">종합Sheet!$A$1:$L$123</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">종합Sheet!$A$1:$L$124</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'종합Sheet (외부)'!$A$1:$L$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">종합Sheet!$3:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'종합Sheet (외부)'!$3:$3</definedName>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2900" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="443">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -1669,6 +1669,14 @@
   </si>
   <si>
     <t>6Q</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출전</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최강인</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2825,10 +2833,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <a:themeElements>
@@ -3087,7 +3091,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CT124"/>
+  <dimension ref="A1:CT125"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -3099,8 +3103,9 @@
     <col min="7" max="7" width="4.3984375" style="1" customWidth="1"/>
     <col min="8" max="8" width="8.8984375" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.19921875" style="1" customWidth="1"/>
-    <col min="10" max="30" width="5.19921875" style="1" customWidth="1"/>
-    <col min="31" max="33" width="5.19921875" style="3" customWidth="1"/>
+    <col min="10" max="30" width="5.19921875" style="1" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="5.19921875" style="3" hidden="1" customWidth="1"/>
+    <col min="32" max="33" width="5.19921875" style="3" customWidth="1"/>
     <col min="34" max="59" width="5.19921875" style="1" customWidth="1"/>
     <col min="60" max="82" width="4.796875" style="1" customWidth="1"/>
     <col min="83" max="90" width="8.8984375" style="1"/>
@@ -3109,8 +3114,8 @@
   <sheetData>
     <row r="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="D1" s="53">
-        <f>COUNTIF(D4:D159,"발주")</f>
-        <v>10</v>
+        <f>COUNTIF(D4:D160,"발주")</f>
+        <v>9</v>
       </c>
       <c r="I1" s="18" t="s">
         <v>87</v>
@@ -3268,22 +3273,22 @@
     </row>
     <row r="2" spans="1:82" x14ac:dyDescent="0.25">
       <c r="D2" s="53">
-        <f>COUNTIF(D4:D159,"지급")</f>
-        <v>68</v>
+        <f>COUNTIF(D4:D160,"지급")</f>
+        <v>69</v>
       </c>
       <c r="E2" s="53">
-        <f>COUNTIF(E4:E142,"지급")</f>
+        <f>COUNTIF(E4:E143,"지급")</f>
         <v>0</v>
       </c>
       <c r="H2" s="18">
         <f>SUM(J2:AR2)/COUNTA(J2:BB2)</f>
-        <v>15.377777777777778</v>
+        <v>16.177777777777777</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>83</v>
       </c>
       <c r="J2" s="1">
-        <f t="shared" ref="J2:AO2" si="0">COUNTA(J4:J154)</f>
+        <f t="shared" ref="J2:AO2" si="0">COUNTA(J4:J155)</f>
         <v>15</v>
       </c>
       <c r="K2" s="1">
@@ -3404,14 +3409,14 @@
       </c>
       <c r="AN2" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO2" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP2" s="1">
-        <f t="shared" ref="AP2:BG2" si="1">COUNTA(AP4:AP154)</f>
+        <f t="shared" ref="AP2:BG2" si="1">COUNTA(AP4:AP155)</f>
         <v>0</v>
       </c>
       <c r="AQ2" s="1">
@@ -3601,8 +3606,12 @@
       <c r="AM3" s="4">
         <v>46261</v>
       </c>
-      <c r="AN3" s="4"/>
-      <c r="AO3" s="4"/>
+      <c r="AN3" s="4">
+        <v>46265</v>
+      </c>
+      <c r="AO3" s="4">
+        <v>46275</v>
+      </c>
       <c r="AP3" s="4"/>
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
@@ -3663,8 +3672,8 @@
         <v>37</v>
       </c>
       <c r="G4" s="2">
-        <f>RANK(H4,$H$4:$H$124,0)</f>
-        <v>4</v>
+        <f>RANK(H4,$H$4:$H$125,0)</f>
+        <v>5</v>
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
@@ -3810,16 +3819,16 @@
         <v>37</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" ref="G5:G68" si="2">RANK(H5,$H$4:$H$124,0)</f>
-        <v>57</v>
+        <f t="shared" ref="G5:G68" si="2">RANK(H5,$H$4:$H$125,0)</f>
+        <v>51</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="I5" s="6">
         <f t="shared" ref="I5:I68" si="3">(COUNTIF(J5:CD5,"출전")*1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3862,7 +3871,9 @@
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
-      <c r="AO5" s="2"/>
+      <c r="AO5" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP5" s="2"/>
       <c r="AQ5" s="2"/>
       <c r="AR5" s="2"/>
@@ -3924,7 +3935,7 @@
       </c>
       <c r="G6" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H6" s="6">
         <f>I6+개인기록Sheet!C6</f>
@@ -4028,7 +4039,7 @@
       </c>
       <c r="G7" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H7" s="6">
         <f>I7+개인기록Sheet!C7</f>
@@ -4131,7 +4142,7 @@
       </c>
       <c r="G8" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H8" s="6">
         <f>I8+개인기록Sheet!C8</f>
@@ -4234,7 +4245,7 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="2"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
@@ -4355,11 +4366,11 @@
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
-        <v>19.600000000000001</v>
+        <v>20.6</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>349</v>
@@ -4424,7 +4435,9 @@
       </c>
       <c r="AM10" s="2"/>
       <c r="AN10" s="2"/>
-      <c r="AO10" s="2"/>
+      <c r="AO10" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AP10" s="2"/>
       <c r="AQ10" s="2"/>
       <c r="AR10" s="2"/>
@@ -4486,15 +4499,15 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
-        <v>16.899999999999999</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>349</v>
@@ -4551,7 +4564,9 @@
         <v>349</v>
       </c>
       <c r="AN11" s="2"/>
-      <c r="AO11" s="2"/>
+      <c r="AO11" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP11" s="2"/>
       <c r="AQ11" s="2"/>
       <c r="AR11" s="2"/>
@@ -4614,7 +4629,7 @@
       </c>
       <c r="G12" s="2">
         <f t="shared" si="2"/>
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C12</f>
@@ -4720,7 +4735,7 @@
       </c>
       <c r="G13" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H13" s="6">
         <f>I13+개인기록Sheet!C13</f>
@@ -4824,7 +4839,7 @@
       </c>
       <c r="G14" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H14" s="6">
         <f>I14+개인기록Sheet!C14</f>
@@ -4920,7 +4935,7 @@
       </c>
       <c r="D15" s="54">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="54"/>
       <c r="F15" s="2" t="s">
@@ -4928,15 +4943,15 @@
       </c>
       <c r="G15" s="2">
         <f t="shared" si="2"/>
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6">
         <f>I15+개인기록Sheet!C15</f>
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="I15" s="6">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -4970,8 +4985,12 @@
       <c r="AK15" s="2"/>
       <c r="AL15" s="2"/>
       <c r="AM15" s="2"/>
-      <c r="AN15" s="2"/>
-      <c r="AO15" s="2"/>
+      <c r="AN15" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AO15" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AP15" s="2"/>
       <c r="AQ15" s="2"/>
       <c r="AR15" s="2"/>
@@ -5033,7 +5052,7 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
@@ -5154,7 +5173,7 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
@@ -5287,7 +5306,7 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C18</f>
@@ -5383,21 +5402,23 @@
       </c>
       <c r="D19" s="54">
         <f>COUNTA(AF19:AS19)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="54"/>
-      <c r="F19" s="60"/>
+      <c r="F19" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="G19" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C19</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -5430,7 +5451,9 @@
       <c r="AL19" s="2"/>
       <c r="AM19" s="2"/>
       <c r="AN19" s="2"/>
-      <c r="AO19" s="2"/>
+      <c r="AO19" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP19" s="2"/>
       <c r="AQ19" s="2"/>
       <c r="AR19" s="2"/>
@@ -5492,7 +5515,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="2"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
@@ -5606,7 +5629,7 @@
       </c>
       <c r="G21" s="2">
         <f t="shared" si="2"/>
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C21</f>
@@ -5825,7 +5848,7 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H23" s="6">
         <f>I23+개인기록Sheet!C23</f>
@@ -5929,7 +5952,7 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C24</f>
@@ -6032,7 +6055,7 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="2"/>
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
@@ -6137,15 +6160,15 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C26</f>
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -6187,8 +6210,12 @@
       <c r="AM26" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AN26" s="2"/>
-      <c r="AO26" s="2"/>
+      <c r="AN26" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AO26" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP26" s="2"/>
       <c r="AQ26" s="2"/>
       <c r="AR26" s="2"/>
@@ -6250,15 +6277,15 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C27</f>
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="I27" s="6">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
@@ -6311,7 +6338,9 @@
       <c r="AL27" s="2"/>
       <c r="AM27" s="2"/>
       <c r="AN27" s="2"/>
-      <c r="AO27" s="2"/>
+      <c r="AO27" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP27" s="2"/>
       <c r="AQ27" s="2"/>
       <c r="AR27" s="2"/>
@@ -6377,11 +6406,11 @@
       </c>
       <c r="H28" s="6">
         <f>I28+개인기록Sheet!C28</f>
-        <v>34.700000000000003</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="I28" s="6">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
@@ -6461,8 +6490,12 @@
       <c r="AM28" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AN28" s="2"/>
-      <c r="AO28" s="2"/>
+      <c r="AN28" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AO28" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP28" s="2"/>
       <c r="AQ28" s="2"/>
       <c r="AR28" s="2"/>
@@ -6524,15 +6557,15 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C29</f>
-        <v>11.1</v>
+        <v>13.1</v>
       </c>
       <c r="I29" s="6">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -6580,8 +6613,12 @@
       <c r="AM29" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AN29" s="2"/>
-      <c r="AO29" s="2"/>
+      <c r="AN29" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AO29" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP29" s="2"/>
       <c r="AQ29" s="2"/>
       <c r="AR29" s="2"/>
@@ -6644,7 +6681,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C30</f>
@@ -6747,7 +6784,7 @@
       </c>
       <c r="G31" s="2">
         <f t="shared" si="2"/>
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C31</f>
@@ -6856,7 +6893,7 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
@@ -6989,11 +7026,11 @@
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C33</f>
-        <v>26.8</v>
+        <v>27.8</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>349</v>
@@ -7070,7 +7107,9 @@
         <v>349</v>
       </c>
       <c r="AN33" s="2"/>
-      <c r="AO33" s="2"/>
+      <c r="AO33" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP33" s="2"/>
       <c r="AQ33" s="2"/>
       <c r="AR33" s="2"/>
@@ -7132,7 +7171,7 @@
       </c>
       <c r="G34" s="2">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H34" s="6">
         <f>I34+개인기록Sheet!C34</f>
@@ -7257,11 +7296,11 @@
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C35</f>
-        <v>19.600000000000001</v>
+        <v>20.6</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
@@ -7325,7 +7364,9 @@
         <v>349</v>
       </c>
       <c r="AM35" s="2"/>
-      <c r="AN35" s="2"/>
+      <c r="AN35" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AO35" s="2"/>
       <c r="AP35" s="2"/>
       <c r="AQ35" s="2"/>
@@ -7389,7 +7430,7 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C36</f>
@@ -7493,7 +7534,7 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C37</f>
@@ -7596,15 +7637,15 @@
       </c>
       <c r="G38" s="2">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H38" s="6">
         <f>I38+개인기록Sheet!C38</f>
-        <v>23.6</v>
+        <v>24.6</v>
       </c>
       <c r="I38" s="6">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
@@ -7671,7 +7712,9 @@
         <v>349</v>
       </c>
       <c r="AN38" s="2"/>
-      <c r="AO38" s="2"/>
+      <c r="AO38" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AP38" s="2"/>
       <c r="AQ38" s="2"/>
       <c r="AR38" s="2"/>
@@ -7733,7 +7776,7 @@
       </c>
       <c r="G39" s="2">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H39" s="6">
         <f>I39+개인기록Sheet!C39</f>
@@ -7851,7 +7894,7 @@
       </c>
       <c r="G40" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H40" s="6">
         <f>I40+개인기록Sheet!C40</f>
@@ -7954,7 +7997,7 @@
       </c>
       <c r="G41" s="2">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H41" s="6">
         <f>I41+개인기록Sheet!C41</f>
@@ -8062,7 +8105,7 @@
       </c>
       <c r="G42" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H42" s="6">
         <f>I42+개인기록Sheet!C42</f>
@@ -8166,7 +8209,7 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H43" s="6">
         <f>I43+개인기록Sheet!C43</f>
@@ -8269,7 +8312,7 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H44" s="6">
         <f>I44+개인기록Sheet!C44</f>
@@ -8380,11 +8423,11 @@
       </c>
       <c r="H45" s="6">
         <f>I45+개인기록Sheet!C45</f>
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="I45" s="6">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
@@ -8453,7 +8496,9 @@
         <v>349</v>
       </c>
       <c r="AN45" s="2"/>
-      <c r="AO45" s="2"/>
+      <c r="AO45" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AP45" s="2"/>
       <c r="AQ45" s="2"/>
       <c r="AR45" s="2"/>
@@ -8515,15 +8560,15 @@
       </c>
       <c r="G46" s="2">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H46" s="6">
         <f>I46+개인기록Sheet!C46</f>
-        <v>7.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I46" s="6">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -8569,7 +8614,9 @@
         <v>349</v>
       </c>
       <c r="AM46" s="2"/>
-      <c r="AN46" s="2"/>
+      <c r="AN46" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AO46" s="2"/>
       <c r="AP46" s="2"/>
       <c r="AQ46" s="2"/>
@@ -8624,7 +8671,7 @@
         <v>2024</v>
       </c>
       <c r="D47" s="54" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="E47" s="54"/>
       <c r="F47" s="2" t="s">
@@ -8632,7 +8679,7 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H47" s="6">
         <f>I47+개인기록Sheet!C47</f>
@@ -8744,7 +8791,7 @@
       <c r="F48" s="60"/>
       <c r="G48" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H48" s="6">
         <f>I48+개인기록Sheet!C48</f>
@@ -8847,15 +8894,15 @@
       </c>
       <c r="G49" s="2">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H49" s="6">
         <f>I49+개인기록Sheet!C49</f>
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
       <c r="I49" s="6">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
@@ -8918,7 +8965,9 @@
         <v>349</v>
       </c>
       <c r="AN49" s="2"/>
-      <c r="AO49" s="2"/>
+      <c r="AO49" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP49" s="2"/>
       <c r="AQ49" s="2"/>
       <c r="AR49" s="2"/>
@@ -8981,7 +9030,7 @@
       </c>
       <c r="G50" s="2">
         <f t="shared" si="2"/>
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H50" s="6">
         <f>I50+개인기록Sheet!C50</f>
@@ -9089,7 +9138,7 @@
       </c>
       <c r="G51" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H51" s="6">
         <f>I51+개인기록Sheet!C51</f>
@@ -9193,7 +9242,7 @@
       </c>
       <c r="G52" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H52" s="6">
         <f>I52+개인기록Sheet!C52</f>
@@ -9296,7 +9345,7 @@
       </c>
       <c r="G53" s="2">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H53" s="6">
         <f>I53+개인기록Sheet!C53</f>
@@ -9430,7 +9479,7 @@
       </c>
       <c r="G54" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H54" s="6">
         <f>I54+개인기록Sheet!C54</f>
@@ -9534,7 +9583,7 @@
       </c>
       <c r="G55" s="2">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H55" s="6">
         <f>I55+개인기록Sheet!C55</f>
@@ -9760,7 +9809,7 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H57" s="6">
         <f>I57+개인기록Sheet!C57</f>
@@ -9864,7 +9913,7 @@
       </c>
       <c r="G58" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H58" s="6">
         <f>I58+개인기록Sheet!C58</f>
@@ -9967,15 +10016,15 @@
       </c>
       <c r="G59" s="2">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H59" s="6">
         <f>I59+개인기록Sheet!C59</f>
-        <v>20.399999999999999</v>
+        <v>21.4</v>
       </c>
       <c r="I59" s="6">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
@@ -10042,7 +10091,9 @@
       </c>
       <c r="AM59" s="2"/>
       <c r="AN59" s="2"/>
-      <c r="AO59" s="2"/>
+      <c r="AO59" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP59" s="2"/>
       <c r="AQ59" s="2"/>
       <c r="AR59" s="2"/>
@@ -10108,11 +10159,11 @@
       </c>
       <c r="H60" s="6">
         <f>I60+개인기록Sheet!C60</f>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="I60" s="6">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>349</v>
@@ -10149,7 +10200,9 @@
       <c r="AL60" s="2"/>
       <c r="AM60" s="2"/>
       <c r="AN60" s="2"/>
-      <c r="AO60" s="2"/>
+      <c r="AO60" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP60" s="2"/>
       <c r="AQ60" s="2"/>
       <c r="AR60" s="2"/>
@@ -10211,7 +10264,7 @@
       </c>
       <c r="G61" s="2">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H61" s="6">
         <f>I61+개인기록Sheet!C61</f>
@@ -10331,7 +10384,7 @@
       </c>
       <c r="G62" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H62" s="6">
         <f>I62+개인기록Sheet!C62</f>
@@ -10438,11 +10491,11 @@
       </c>
       <c r="H63" s="6">
         <f>I63+개인기록Sheet!C63</f>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="I63" s="6">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
@@ -10479,7 +10532,9 @@
       <c r="AL63" s="2"/>
       <c r="AM63" s="2"/>
       <c r="AN63" s="2"/>
-      <c r="AO63" s="2"/>
+      <c r="AO63" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP63" s="2"/>
       <c r="AQ63" s="2"/>
       <c r="AR63" s="2"/>
@@ -10541,15 +10596,15 @@
       </c>
       <c r="G64" s="2">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H64" s="6">
         <f>I64+개인기록Sheet!C64</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I64" s="6">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>349</v>
@@ -10599,7 +10654,9 @@
         <v>349</v>
       </c>
       <c r="AM64" s="2"/>
-      <c r="AN64" s="2"/>
+      <c r="AN64" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AO64" s="2"/>
       <c r="AP64" s="2"/>
       <c r="AQ64" s="2"/>
@@ -10662,7 +10719,7 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H65" s="6">
         <f>I65+개인기록Sheet!C65</f>
@@ -10782,7 +10839,7 @@
       </c>
       <c r="G66" s="2">
         <f t="shared" si="2"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H66" s="6">
         <f>I66+개인기록Sheet!C66</f>
@@ -10893,7 +10950,7 @@
       </c>
       <c r="G67" s="2">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H67" s="6">
         <f>I67+개인기록Sheet!C67</f>
@@ -11013,7 +11070,7 @@
       </c>
       <c r="G68" s="2">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H68" s="6">
         <f>I68+개인기록Sheet!C68</f>
@@ -11112,15 +11169,15 @@
       <c r="E69" s="54"/>
       <c r="F69" s="60"/>
       <c r="G69" s="2">
-        <f t="shared" ref="G69:G124" si="11">RANK(H69,$H$4:$H$124,0)</f>
-        <v>90</v>
+        <f t="shared" ref="G69:G125" si="11">RANK(H69,$H$4:$H$125,0)</f>
+        <v>95</v>
       </c>
       <c r="H69" s="6">
         <f>I69+개인기록Sheet!C69</f>
         <v>0</v>
       </c>
       <c r="I69" s="6">
-        <f t="shared" ref="I69:I124" si="12">(COUNTIF(J69:CD69,"출전")*1)</f>
+        <f t="shared" ref="I69:I125" si="12">(COUNTIF(J69:CD69,"출전")*1)</f>
         <v>0</v>
       </c>
       <c r="J69" s="2"/>
@@ -11217,7 +11274,7 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" si="11"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H70" s="6">
         <f>I70+개인기록Sheet!C70</f>
@@ -11324,11 +11381,11 @@
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I71" s="6">
         <f t="shared" si="12"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
@@ -11390,7 +11447,9 @@
       </c>
       <c r="AL71" s="2"/>
       <c r="AM71" s="2"/>
-      <c r="AN71" s="2"/>
+      <c r="AN71" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AO71" s="2"/>
       <c r="AP71" s="2"/>
       <c r="AQ71" s="2"/>
@@ -11454,7 +11513,7 @@
       </c>
       <c r="G72" s="2">
         <f t="shared" si="11"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H72" s="6">
         <f>I72+개인기록Sheet!C72</f>
@@ -11565,7 +11624,7 @@
       </c>
       <c r="G73" s="2">
         <f t="shared" si="11"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H73" s="6">
         <f>I73+개인기록Sheet!C73</f>
@@ -11680,7 +11739,7 @@
       </c>
       <c r="G74" s="2">
         <f t="shared" si="11"/>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H74" s="6">
         <f>I74+개인기록Sheet!C74</f>
@@ -11798,7 +11857,7 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" si="11"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
@@ -11901,7 +11960,7 @@
       </c>
       <c r="G76" s="2">
         <f t="shared" si="11"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H76" s="6">
         <f>I76+개인기록Sheet!C76</f>
@@ -12014,15 +12073,15 @@
       </c>
       <c r="G77" s="2">
         <f t="shared" si="11"/>
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H77" s="6">
         <f>I77+개인기록Sheet!C77</f>
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="I77" s="6">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
@@ -12062,7 +12121,9 @@
       <c r="AK77" s="2"/>
       <c r="AL77" s="2"/>
       <c r="AM77" s="2"/>
-      <c r="AN77" s="2"/>
+      <c r="AN77" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AO77" s="2"/>
       <c r="AP77" s="2"/>
       <c r="AQ77" s="2"/>
@@ -12125,7 +12186,7 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" si="11"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H78" s="6">
         <f>I78+개인기록Sheet!C78</f>
@@ -12241,7 +12302,7 @@
       </c>
       <c r="G79" s="2">
         <f t="shared" si="11"/>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H79" s="6">
         <f>I79+개인기록Sheet!C79</f>
@@ -12347,7 +12408,7 @@
       </c>
       <c r="G80" s="2">
         <f t="shared" si="11"/>
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H80" s="6">
         <f>I80+개인기록Sheet!C80</f>
@@ -12454,7 +12515,7 @@
       </c>
       <c r="G81" s="2">
         <f t="shared" si="11"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H81" s="6">
         <f>I81+개인기록Sheet!C81</f>
@@ -12573,7 +12634,7 @@
       </c>
       <c r="G82" s="2">
         <f t="shared" si="11"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H82" s="6">
         <f>I82+개인기록Sheet!C82</f>
@@ -12686,15 +12747,15 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="11"/>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
-        <v>13.3</v>
+        <v>15.3</v>
       </c>
       <c r="I83" s="6">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
@@ -12746,8 +12807,12 @@
       <c r="AM83" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AN83" s="2"/>
-      <c r="AO83" s="2"/>
+      <c r="AN83" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AO83" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP83" s="2"/>
       <c r="AQ83" s="2"/>
       <c r="AR83" s="2"/>
@@ -12809,15 +12874,15 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" si="11"/>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H84" s="6">
         <f>I84+개인기록Sheet!C84</f>
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="I84" s="6">
         <f t="shared" si="12"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
@@ -12868,7 +12933,9 @@
       <c r="AL84" s="2"/>
       <c r="AM84" s="2"/>
       <c r="AN84" s="2"/>
-      <c r="AO84" s="2"/>
+      <c r="AO84" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP84" s="2"/>
       <c r="AQ84" s="2"/>
       <c r="AR84" s="2"/>
@@ -12930,15 +12997,15 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" si="11"/>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H85" s="6">
         <f>I85+개인기록Sheet!C85</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I85" s="6">
         <f t="shared" si="12"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
@@ -12989,7 +13056,9 @@
         <v>349</v>
       </c>
       <c r="AN85" s="2"/>
-      <c r="AO85" s="2"/>
+      <c r="AO85" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP85" s="2"/>
       <c r="AQ85" s="2"/>
       <c r="AR85" s="2"/>
@@ -13051,7 +13120,7 @@
       </c>
       <c r="G86" s="2">
         <f t="shared" si="11"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H86" s="6">
         <f>I86+개인기록Sheet!C86</f>
@@ -13174,7 +13243,7 @@
       </c>
       <c r="G87" s="2">
         <f t="shared" si="11"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H87" s="6">
         <f>I87+개인기록Sheet!C87</f>
@@ -13285,7 +13354,7 @@
       </c>
       <c r="G88" s="2">
         <f t="shared" si="11"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H88" s="6">
         <f>I88+개인기록Sheet!C88</f>
@@ -13402,7 +13471,7 @@
       </c>
       <c r="G89" s="2">
         <f t="shared" si="11"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H89" s="6">
         <f>I89+개인기록Sheet!C89</f>
@@ -13515,7 +13584,7 @@
       </c>
       <c r="G90" s="2">
         <f t="shared" si="11"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H90" s="6">
         <f>I90+개인기록Sheet!C90</f>
@@ -13619,7 +13688,7 @@
       </c>
       <c r="G91" s="2">
         <f t="shared" si="11"/>
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H91" s="6">
         <f>I91+개인기록Sheet!C91</f>
@@ -13728,7 +13797,7 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" si="11"/>
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H92" s="6">
         <f>I92+개인기록Sheet!C92</f>
@@ -13838,7 +13907,7 @@
       </c>
       <c r="G93" s="2">
         <f t="shared" si="11"/>
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H93" s="6">
         <f>I93+개인기록Sheet!C93</f>
@@ -13944,7 +14013,7 @@
       </c>
       <c r="G94" s="2">
         <f t="shared" si="11"/>
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H94" s="6">
         <f>I94+개인기록Sheet!C94</f>
@@ -14049,7 +14118,7 @@
       </c>
       <c r="G95" s="2">
         <f t="shared" si="11"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H95" s="6">
         <f>I95+개인기록Sheet!C95</f>
@@ -14160,7 +14229,7 @@
       </c>
       <c r="G96" s="2">
         <f t="shared" si="11"/>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H96" s="6">
         <f>I96+개인기록Sheet!C96</f>
@@ -14263,15 +14332,15 @@
       </c>
       <c r="G97" s="2">
         <f t="shared" si="11"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H97" s="6">
         <f>I97+개인기록Sheet!C97</f>
-        <v>13.7</v>
+        <v>14.7</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
@@ -14324,7 +14393,9 @@
       <c r="AL97" s="2"/>
       <c r="AM97" s="2"/>
       <c r="AN97" s="2"/>
-      <c r="AO97" s="2"/>
+      <c r="AO97" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP97" s="2"/>
       <c r="AQ97" s="2"/>
       <c r="AR97" s="2"/>
@@ -14386,15 +14457,15 @@
       </c>
       <c r="G98" s="2">
         <f t="shared" si="11"/>
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H98" s="6">
         <f>I98+개인기록Sheet!C98</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
@@ -14429,7 +14500,9 @@
       <c r="AL98" s="2"/>
       <c r="AM98" s="2"/>
       <c r="AN98" s="2"/>
-      <c r="AO98" s="2"/>
+      <c r="AO98" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP98" s="2"/>
       <c r="AQ98" s="2"/>
       <c r="AR98" s="2"/>
@@ -14484,7 +14557,7 @@
       </c>
       <c r="D99" s="54">
         <f>COUNTA(AF99:AS99)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="54"/>
       <c r="F99" s="2" t="s">
@@ -14492,15 +14565,15 @@
       </c>
       <c r="G99" s="2">
         <f t="shared" si="11"/>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H99" s="6">
         <f>I99+개인기록Sheet!C99</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" s="6">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
@@ -14533,7 +14606,9 @@
       <c r="AL99" s="2"/>
       <c r="AM99" s="2"/>
       <c r="AN99" s="2"/>
-      <c r="AO99" s="2"/>
+      <c r="AO99" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP99" s="2"/>
       <c r="AQ99" s="2"/>
       <c r="AR99" s="2"/>
@@ -14595,7 +14670,7 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" si="11"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
@@ -14721,7 +14796,7 @@
       </c>
       <c r="G101" s="2">
         <f t="shared" si="11"/>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
@@ -14826,7 +14901,7 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="11"/>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
@@ -14937,7 +15012,7 @@
       </c>
       <c r="G103" s="2">
         <f t="shared" si="11"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
@@ -15072,15 +15147,15 @@
       </c>
       <c r="G104" s="2">
         <f t="shared" si="11"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H104" s="6">
         <f>I104+개인기록Sheet!C104</f>
-        <v>16.399999999999999</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="I104" s="6">
         <f t="shared" si="12"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
@@ -15139,7 +15214,9 @@
         <v>349</v>
       </c>
       <c r="AN104" s="2"/>
-      <c r="AO104" s="2"/>
+      <c r="AO104" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP104" s="2"/>
       <c r="AQ104" s="2"/>
       <c r="AR104" s="2"/>
@@ -15201,7 +15278,7 @@
       </c>
       <c r="G105" s="2">
         <f t="shared" si="11"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
@@ -15320,7 +15397,7 @@
       </c>
       <c r="G106" s="2">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H106" s="6">
         <f>I106+개인기록Sheet!C106</f>
@@ -15602,7 +15679,7 @@
       </c>
       <c r="G108" s="2">
         <f t="shared" si="11"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H108" s="6">
         <f>I108+개인기록Sheet!C108</f>
@@ -15701,13 +15778,14 @@
         <v>106</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C109" s="57">
-        <v>2022</v>
-      </c>
-      <c r="D109" s="54" t="s">
-        <v>323</v>
+        <v>442</v>
+      </c>
+      <c r="C109" s="58">
+        <v>2026</v>
+      </c>
+      <c r="D109" s="54">
+        <f>COUNTA(AF109:AS109)</f>
+        <v>1</v>
       </c>
       <c r="E109" s="54"/>
       <c r="F109" s="2" t="s">
@@ -15715,70 +15793,50 @@
       </c>
       <c r="G109" s="2">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="H109" s="6">
         <f>I109+개인기록Sheet!C109</f>
-        <v>15.600000000000001</v>
+        <v>1</v>
       </c>
       <c r="I109" s="6">
         <f t="shared" si="12"/>
-        <v>11</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>349</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J109" s="2"/>
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
-      <c r="Q109" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="Q109" s="2"/>
       <c r="R109" s="2"/>
-      <c r="S109" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="S109" s="2"/>
       <c r="T109" s="2"/>
-      <c r="U109" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="U109" s="2"/>
       <c r="V109" s="2"/>
       <c r="W109" s="2"/>
       <c r="X109" s="2"/>
-      <c r="Y109" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="Y109" s="2"/>
       <c r="Z109" s="2"/>
       <c r="AA109" s="2"/>
-      <c r="AB109" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AC109" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AD109" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AB109" s="2"/>
+      <c r="AC109" s="2"/>
+      <c r="AD109" s="2"/>
       <c r="AE109" s="2"/>
-      <c r="AF109" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AF109" s="2"/>
       <c r="AG109" s="2"/>
       <c r="AH109" s="2"/>
       <c r="AI109" s="2"/>
-      <c r="AJ109" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AJ109" s="2"/>
       <c r="AK109" s="2"/>
       <c r="AL109" s="2"/>
-      <c r="AM109" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AM109" s="2"/>
       <c r="AN109" s="2"/>
-      <c r="AO109" s="2"/>
+      <c r="AO109" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP109" s="2"/>
       <c r="AQ109" s="2"/>
       <c r="AR109" s="2"/>
@@ -15826,14 +15884,13 @@
         <v>107</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C110" s="57">
-        <v>2021</v>
-      </c>
-      <c r="D110" s="54">
-        <f>COUNTA(AF110:AS110)</f>
-        <v>0</v>
+        <v>2022</v>
+      </c>
+      <c r="D110" s="54" t="s">
+        <v>323</v>
       </c>
       <c r="E110" s="54"/>
       <c r="F110" s="2" t="s">
@@ -15841,46 +15898,68 @@
       </c>
       <c r="G110" s="2">
         <f t="shared" si="11"/>
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="H110" s="6">
-        <f>I110+개인기록Sheet!C110</f>
-        <v>0</v>
+        <f>I110+개인기록Sheet!C109</f>
+        <v>11</v>
       </c>
       <c r="I110" s="6">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J110" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
-      <c r="Q110" s="2"/>
+      <c r="Q110" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="R110" s="2"/>
-      <c r="S110" s="2"/>
+      <c r="S110" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="T110" s="2"/>
-      <c r="U110" s="2"/>
+      <c r="U110" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="V110" s="2"/>
       <c r="W110" s="2"/>
       <c r="X110" s="2"/>
-      <c r="Y110" s="2"/>
+      <c r="Y110" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="Z110" s="2"/>
       <c r="AA110" s="2"/>
-      <c r="AB110" s="2"/>
-      <c r="AC110" s="2"/>
-      <c r="AD110" s="2"/>
+      <c r="AB110" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC110" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AD110" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AE110" s="2"/>
-      <c r="AF110" s="2"/>
+      <c r="AF110" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AG110" s="2"/>
       <c r="AH110" s="2"/>
       <c r="AI110" s="2"/>
-      <c r="AJ110" s="2"/>
+      <c r="AJ110" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AK110" s="2"/>
       <c r="AL110" s="2"/>
-      <c r="AM110" s="2"/>
+      <c r="AM110" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN110" s="2"/>
       <c r="AO110" s="2"/>
       <c r="AP110" s="2"/>
@@ -15930,13 +16009,14 @@
         <v>108</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C111" s="58">
-        <v>2025</v>
-      </c>
-      <c r="D111" s="54" t="s">
-        <v>323</v>
+        <v>96</v>
+      </c>
+      <c r="C111" s="57">
+        <v>2021</v>
+      </c>
+      <c r="D111" s="54">
+        <f>COUNTA(AF111:AS111)</f>
+        <v>0</v>
       </c>
       <c r="E111" s="54"/>
       <c r="F111" s="2" t="s">
@@ -15944,74 +16024,46 @@
       </c>
       <c r="G111" s="2">
         <f t="shared" si="11"/>
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="H111" s="6">
-        <f>I111+개인기록Sheet!C111</f>
-        <v>17.2</v>
+        <f>I111+개인기록Sheet!C110</f>
+        <v>4.6000000000000005</v>
       </c>
       <c r="I111" s="6">
         <f t="shared" si="12"/>
-        <v>14</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>349</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J111" s="2"/>
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
-      <c r="N111" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
       <c r="Q111" s="2"/>
-      <c r="R111" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="R111" s="2"/>
       <c r="S111" s="2"/>
-      <c r="T111" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="T111" s="2"/>
       <c r="U111" s="2"/>
       <c r="V111" s="2"/>
       <c r="W111" s="2"/>
       <c r="X111" s="2"/>
       <c r="Y111" s="2"/>
-      <c r="Z111" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AA111" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="Z111" s="2"/>
+      <c r="AA111" s="2"/>
       <c r="AB111" s="2"/>
-      <c r="AC111" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AC111" s="2"/>
       <c r="AD111" s="2"/>
-      <c r="AE111" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AF111" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AG111" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AH111" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AE111" s="2"/>
+      <c r="AF111" s="2"/>
+      <c r="AG111" s="2"/>
+      <c r="AH111" s="2"/>
       <c r="AI111" s="2"/>
-      <c r="AJ111" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AK111" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AJ111" s="2"/>
+      <c r="AK111" s="2"/>
       <c r="AL111" s="2"/>
-      <c r="AM111" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AM111" s="2"/>
       <c r="AN111" s="2"/>
       <c r="AO111" s="2"/>
       <c r="AP111" s="2"/>
@@ -16061,10 +16113,10 @@
         <v>109</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C112" s="57">
-        <v>2023</v>
+        <v>325</v>
+      </c>
+      <c r="C112" s="58">
+        <v>2025</v>
       </c>
       <c r="D112" s="54" t="s">
         <v>323</v>
@@ -16075,35 +16127,35 @@
       </c>
       <c r="G112" s="2">
         <f t="shared" si="11"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H112" s="6">
-        <f>I112+개인기록Sheet!C112</f>
-        <v>12.6</v>
+        <f>I112+개인기록Sheet!C111</f>
+        <v>14</v>
       </c>
       <c r="I112" s="6">
         <f t="shared" si="12"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>349</v>
       </c>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
-      <c r="M112" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="M112" s="2"/>
+      <c r="N112" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" s="2"/>
-      <c r="Q112" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="R112" s="2"/>
+      <c r="Q112" s="2"/>
+      <c r="R112" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="S112" s="2"/>
-      <c r="T112" s="2"/>
+      <c r="T112" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="U112" s="2"/>
       <c r="V112" s="2"/>
       <c r="W112" s="2"/>
@@ -16112,9 +16164,13 @@
       <c r="Z112" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AA112" s="2"/>
+      <c r="AA112" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AB112" s="2"/>
-      <c r="AC112" s="2"/>
+      <c r="AC112" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AD112" s="2"/>
       <c r="AE112" s="2" t="s">
         <v>349</v>
@@ -16136,7 +16192,9 @@
         <v>349</v>
       </c>
       <c r="AL112" s="2"/>
-      <c r="AM112" s="2"/>
+      <c r="AM112" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN112" s="2"/>
       <c r="AO112" s="2"/>
       <c r="AP112" s="2"/>
@@ -16186,10 +16244,10 @@
         <v>110</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C113" s="57" t="s">
-        <v>319</v>
+        <v>195</v>
+      </c>
+      <c r="C113" s="57">
+        <v>2023</v>
       </c>
       <c r="D113" s="54" t="s">
         <v>323</v>
@@ -16200,15 +16258,15 @@
       </c>
       <c r="G113" s="2">
         <f t="shared" si="11"/>
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H113" s="6">
-        <f>I113+개인기록Sheet!C113</f>
-        <v>11.8</v>
+        <f>I113+개인기록Sheet!C112</f>
+        <v>14.2</v>
       </c>
       <c r="I113" s="6">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>349</v>
@@ -16219,45 +16277,47 @@
         <v>349</v>
       </c>
       <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+      <c r="O113" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="P113" s="2"/>
       <c r="Q113" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="R113" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="S113" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="R113" s="2"/>
+      <c r="S113" s="2"/>
       <c r="T113" s="2"/>
       <c r="U113" s="2"/>
       <c r="V113" s="2"/>
       <c r="W113" s="2"/>
-      <c r="X113" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="Y113" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="X113" s="2"/>
+      <c r="Y113" s="2"/>
       <c r="Z113" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AA113" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AA113" s="2"/>
       <c r="AB113" s="2"/>
       <c r="AC113" s="2"/>
       <c r="AD113" s="2"/>
-      <c r="AE113" s="2"/>
+      <c r="AE113" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AF113" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="AG113" s="2"/>
-      <c r="AH113" s="2"/>
+      <c r="AG113" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AH113" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AI113" s="2"/>
-      <c r="AJ113" s="2"/>
-      <c r="AK113" s="2"/>
+      <c r="AJ113" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AK113" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AL113" s="2"/>
       <c r="AM113" s="2"/>
       <c r="AN113" s="2"/>
@@ -16309,10 +16369,10 @@
         <v>111</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C114" s="58">
-        <v>2025</v>
+        <v>67</v>
+      </c>
+      <c r="C114" s="57" t="s">
+        <v>319</v>
       </c>
       <c r="D114" s="54" t="s">
         <v>323</v>
@@ -16323,37 +16383,49 @@
       </c>
       <c r="G114" s="2">
         <f t="shared" si="11"/>
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H114" s="6">
-        <f>I114+개인기록Sheet!C114</f>
-        <v>8.6</v>
+        <f>I114+개인기록Sheet!C113</f>
+        <v>11.6</v>
       </c>
       <c r="I114" s="6">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="K114" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="K114" s="2"/>
       <c r="L114" s="2"/>
-      <c r="M114" s="2"/>
+      <c r="M114" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" s="2"/>
-      <c r="Q114" s="2"/>
-      <c r="R114" s="2"/>
-      <c r="S114" s="2"/>
+      <c r="Q114" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="R114" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="S114" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="T114" s="2"/>
       <c r="U114" s="2"/>
       <c r="V114" s="2"/>
       <c r="W114" s="2"/>
-      <c r="X114" s="2"/>
-      <c r="Y114" s="2"/>
-      <c r="Z114" s="2"/>
+      <c r="X114" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y114" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="Z114" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AA114" s="2" t="s">
         <v>349</v>
       </c>
@@ -16361,19 +16433,15 @@
       <c r="AC114" s="2"/>
       <c r="AD114" s="2"/>
       <c r="AE114" s="2"/>
-      <c r="AF114" s="2"/>
+      <c r="AF114" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AG114" s="2"/>
       <c r="AH114" s="2"/>
-      <c r="AI114" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AJ114" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AI114" s="2"/>
+      <c r="AJ114" s="2"/>
       <c r="AK114" s="2"/>
-      <c r="AL114" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AL114" s="2"/>
       <c r="AM114" s="2"/>
       <c r="AN114" s="2"/>
       <c r="AO114" s="2"/>
@@ -16424,10 +16492,10 @@
         <v>112</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C115" s="57">
-        <v>2022</v>
+        <v>306</v>
+      </c>
+      <c r="C115" s="58">
+        <v>2025</v>
       </c>
       <c r="D115" s="54" t="s">
         <v>323</v>
@@ -16438,18 +16506,22 @@
       </c>
       <c r="G115" s="2">
         <f t="shared" si="11"/>
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H115" s="6">
-        <f>I115+개인기록Sheet!C115</f>
-        <v>6.6</v>
+        <f>I115+개인기록Sheet!C114</f>
+        <v>7.8</v>
       </c>
       <c r="I115" s="6">
         <f t="shared" si="12"/>
-        <v>5</v>
-      </c>
-      <c r="J115" s="2"/>
-      <c r="K115" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
@@ -16457,21 +16529,17 @@
       <c r="P115" s="2"/>
       <c r="Q115" s="2"/>
       <c r="R115" s="2"/>
-      <c r="S115" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="S115" s="2"/>
       <c r="T115" s="2"/>
       <c r="U115" s="2"/>
       <c r="V115" s="2"/>
       <c r="W115" s="2"/>
       <c r="X115" s="2"/>
-      <c r="Y115" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="Z115" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AA115" s="2"/>
+      <c r="Y115" s="2"/>
+      <c r="Z115" s="2"/>
+      <c r="AA115" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AB115" s="2"/>
       <c r="AC115" s="2"/>
       <c r="AD115" s="2"/>
@@ -16486,7 +16554,9 @@
         <v>349</v>
       </c>
       <c r="AK115" s="2"/>
-      <c r="AL115" s="2"/>
+      <c r="AL115" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AM115" s="2"/>
       <c r="AN115" s="2"/>
       <c r="AO115" s="2"/>
@@ -16537,10 +16607,10 @@
         <v>113</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C116" s="58">
-        <v>2024</v>
+        <v>113</v>
+      </c>
+      <c r="C116" s="57">
+        <v>2022</v>
       </c>
       <c r="D116" s="54" t="s">
         <v>323</v>
@@ -16551,37 +16621,39 @@
       </c>
       <c r="G116" s="2">
         <f t="shared" si="11"/>
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="H116" s="6">
-        <f>I116+개인기록Sheet!C116</f>
-        <v>2.2000000000000002</v>
+        <f>I116+개인기록Sheet!C115</f>
+        <v>8.6</v>
       </c>
       <c r="I116" s="6">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
-      <c r="L116" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="L116" s="2"/>
       <c r="M116" s="2"/>
-      <c r="N116" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
       <c r="Q116" s="2"/>
       <c r="R116" s="2"/>
-      <c r="S116" s="2"/>
+      <c r="S116" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="T116" s="2"/>
       <c r="U116" s="2"/>
       <c r="V116" s="2"/>
       <c r="W116" s="2"/>
       <c r="X116" s="2"/>
-      <c r="Y116" s="2"/>
-      <c r="Z116" s="2"/>
+      <c r="Y116" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="Z116" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AA116" s="2"/>
       <c r="AB116" s="2"/>
       <c r="AC116" s="2"/>
@@ -16590,13 +16662,19 @@
       <c r="AF116" s="2"/>
       <c r="AG116" s="2"/>
       <c r="AH116" s="2"/>
-      <c r="AI116" s="2"/>
-      <c r="AJ116" s="2"/>
+      <c r="AI116" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AJ116" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AK116" s="2"/>
       <c r="AL116" s="2"/>
       <c r="AM116" s="2"/>
       <c r="AN116" s="2"/>
-      <c r="AO116" s="2"/>
+      <c r="AO116" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="AP116" s="2"/>
       <c r="AQ116" s="2"/>
       <c r="AR116" s="2"/>
@@ -16644,13 +16722,13 @@
         <v>114</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>371</v>
+        <v>296</v>
       </c>
       <c r="C117" s="58">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D117" s="54" t="s">
-        <v>391</v>
+        <v>323</v>
       </c>
       <c r="E117" s="54"/>
       <c r="F117" s="2" t="s">
@@ -16658,42 +16736,36 @@
       </c>
       <c r="G117" s="2">
         <f t="shared" si="11"/>
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="H117" s="6">
-        <f>I117+개인기록Sheet!C117</f>
-        <v>7.5</v>
+        <f>I117+개인기록Sheet!C116</f>
+        <v>3.6</v>
       </c>
       <c r="I117" s="6">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
-      <c r="L117" s="2"/>
+      <c r="L117" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="M117" s="2"/>
-      <c r="N117" s="2"/>
+      <c r="N117" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
       <c r="Q117" s="2"/>
       <c r="R117" s="2"/>
       <c r="S117" s="2"/>
       <c r="T117" s="2"/>
-      <c r="U117" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="V117" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="W117" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="X117" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="Y117" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="U117" s="2"/>
+      <c r="V117" s="2"/>
+      <c r="W117" s="2"/>
+      <c r="X117" s="2"/>
+      <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
       <c r="AA117" s="2"/>
       <c r="AB117" s="2"/>
@@ -16757,13 +16829,13 @@
         <v>115</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C118" s="57">
-        <v>2023</v>
+        <v>371</v>
+      </c>
+      <c r="C118" s="58">
+        <v>2026</v>
       </c>
       <c r="D118" s="54" t="s">
-        <v>323</v>
+        <v>391</v>
       </c>
       <c r="E118" s="54"/>
       <c r="F118" s="2" t="s">
@@ -16771,25 +16843,21 @@
       </c>
       <c r="G118" s="2">
         <f t="shared" si="11"/>
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="H118" s="6">
-        <f>I118+개인기록Sheet!C118</f>
-        <v>14.8</v>
+        <f>I118+개인기록Sheet!C117</f>
+        <v>5.2</v>
       </c>
       <c r="I118" s="6">
         <f t="shared" si="12"/>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
-      <c r="L118" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="L118" s="2"/>
       <c r="M118" s="2"/>
-      <c r="N118" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
       <c r="Q118" s="2"/>
@@ -16799,40 +16867,32 @@
       <c r="U118" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="V118" s="2"/>
-      <c r="W118" s="2"/>
-      <c r="X118" s="2"/>
-      <c r="Y118" s="2"/>
+      <c r="V118" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="W118" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="X118" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y118" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="Z118" s="2"/>
       <c r="AA118" s="2"/>
-      <c r="AB118" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AC118" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AD118" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AB118" s="2"/>
+      <c r="AC118" s="2"/>
+      <c r="AD118" s="2"/>
       <c r="AE118" s="2"/>
       <c r="AF118" s="2"/>
-      <c r="AG118" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AG118" s="2"/>
       <c r="AH118" s="2"/>
-      <c r="AI118" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AJ118" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AK118" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AI118" s="2"/>
+      <c r="AJ118" s="2"/>
+      <c r="AK118" s="2"/>
       <c r="AL118" s="2"/>
-      <c r="AM118" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AM118" s="2"/>
       <c r="AN118" s="2"/>
       <c r="AO118" s="2"/>
       <c r="AP118" s="2"/>
@@ -16882,13 +16942,13 @@
         <v>116</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C119" s="57">
         <v>2023</v>
       </c>
       <c r="D119" s="54" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="E119" s="54"/>
       <c r="F119" s="2" t="s">
@@ -16896,49 +16956,71 @@
       </c>
       <c r="G119" s="2">
         <f t="shared" si="11"/>
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="H119" s="6">
-        <f>I119+개인기록Sheet!C119</f>
-        <v>1.4</v>
+        <f>I119+개인기록Sheet!C118</f>
+        <v>14.5</v>
       </c>
       <c r="I119" s="6">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
-      <c r="L119" s="2"/>
+      <c r="L119" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="M119" s="2"/>
-      <c r="N119" s="2"/>
+      <c r="N119" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
       <c r="Q119" s="2"/>
       <c r="R119" s="2"/>
       <c r="S119" s="2"/>
       <c r="T119" s="2"/>
-      <c r="U119" s="2"/>
+      <c r="U119" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="V119" s="2"/>
       <c r="W119" s="2"/>
       <c r="X119" s="2"/>
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
       <c r="AA119" s="2"/>
-      <c r="AB119" s="2"/>
-      <c r="AC119" s="2"/>
-      <c r="AD119" s="2"/>
+      <c r="AB119" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AC119" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AD119" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AE119" s="2"/>
       <c r="AF119" s="2"/>
-      <c r="AG119" s="2"/>
-      <c r="AH119" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AI119" s="2"/>
-      <c r="AJ119" s="2"/>
-      <c r="AK119" s="2"/>
+      <c r="AG119" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AH119" s="2"/>
+      <c r="AI119" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AJ119" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AK119" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AL119" s="2"/>
-      <c r="AM119" s="2"/>
-      <c r="AN119" s="2"/>
+      <c r="AM119" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AN119" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AO119" s="2"/>
       <c r="AP119" s="2"/>
       <c r="AQ119" s="2"/>
@@ -16987,14 +17069,13 @@
         <v>117</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C120" s="58">
-        <v>2025</v>
-      </c>
-      <c r="D120" s="54">
-        <f>COUNTA(AF120:AS120)</f>
-        <v>1</v>
+        <v>131</v>
+      </c>
+      <c r="C120" s="57">
+        <v>2023</v>
+      </c>
+      <c r="D120" s="54" t="s">
+        <v>350</v>
       </c>
       <c r="E120" s="54"/>
       <c r="F120" s="2" t="s">
@@ -17002,15 +17083,15 @@
       </c>
       <c r="G120" s="2">
         <f t="shared" si="11"/>
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H120" s="6">
-        <f>I120+개인기록Sheet!C120</f>
-        <v>3.4</v>
+        <f>I120+개인기록Sheet!C119</f>
+        <v>4.8000000000000007</v>
       </c>
       <c r="I120" s="6">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
@@ -17019,9 +17100,7 @@
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
-      <c r="Q120" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="Q120" s="2"/>
       <c r="R120" s="2"/>
       <c r="S120" s="2"/>
       <c r="T120" s="2"/>
@@ -17031,18 +17110,16 @@
       <c r="X120" s="2"/>
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
-      <c r="AA120" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AA120" s="2"/>
       <c r="AB120" s="2"/>
       <c r="AC120" s="2"/>
       <c r="AD120" s="2"/>
       <c r="AE120" s="2"/>
-      <c r="AF120" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AF120" s="2"/>
       <c r="AG120" s="2"/>
-      <c r="AH120" s="2"/>
+      <c r="AH120" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AI120" s="2"/>
       <c r="AJ120" s="2"/>
       <c r="AK120" s="2"/>
@@ -17097,13 +17174,14 @@
         <v>118</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C121" s="57" t="s">
-        <v>319</v>
-      </c>
-      <c r="D121" s="54" t="s">
-        <v>323</v>
+        <v>315</v>
+      </c>
+      <c r="C121" s="58">
+        <v>2025</v>
+      </c>
+      <c r="D121" s="54">
+        <f>COUNTA(AF121:AS121)</f>
+        <v>1</v>
       </c>
       <c r="E121" s="54"/>
       <c r="F121" s="2" t="s">
@@ -17111,15 +17189,15 @@
       </c>
       <c r="G121" s="2">
         <f t="shared" si="11"/>
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="H121" s="6">
-        <f>I121+개인기록Sheet!C121</f>
-        <v>0</v>
+        <f>I121+개인기록Sheet!C120</f>
+        <v>3.4</v>
       </c>
       <c r="I121" s="6">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
@@ -17128,7 +17206,9 @@
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
-      <c r="Q121" s="2"/>
+      <c r="Q121" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="R121" s="2"/>
       <c r="S121" s="2"/>
       <c r="T121" s="2"/>
@@ -17138,12 +17218,16 @@
       <c r="X121" s="2"/>
       <c r="Y121" s="2"/>
       <c r="Z121" s="2"/>
-      <c r="AA121" s="2"/>
+      <c r="AA121" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AB121" s="2"/>
       <c r="AC121" s="2"/>
       <c r="AD121" s="2"/>
       <c r="AE121" s="2"/>
-      <c r="AF121" s="2"/>
+      <c r="AF121" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AG121" s="2"/>
       <c r="AH121" s="2"/>
       <c r="AI121" s="2"/>
@@ -17200,14 +17284,13 @@
         <v>119</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C122" s="58">
-        <v>2024</v>
-      </c>
-      <c r="D122" s="54">
-        <f>COUNTA(AF122:AS122)</f>
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="C122" s="57" t="s">
+        <v>319</v>
+      </c>
+      <c r="D122" s="54" t="s">
+        <v>323</v>
       </c>
       <c r="E122" s="54"/>
       <c r="F122" s="2" t="s">
@@ -17215,11 +17298,11 @@
       </c>
       <c r="G122" s="2">
         <f t="shared" si="11"/>
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H122" s="6">
-        <f>I122+개인기록Sheet!C122</f>
-        <v>0</v>
+        <f>I122+개인기록Sheet!C121</f>
+        <v>0.4</v>
       </c>
       <c r="I122" s="6">
         <f t="shared" si="12"/>
@@ -17304,13 +17387,14 @@
         <v>120</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C123" s="57" t="s">
-        <v>319</v>
-      </c>
-      <c r="D123" s="54" t="s">
-        <v>323</v>
+        <v>240</v>
+      </c>
+      <c r="C123" s="58">
+        <v>2024</v>
+      </c>
+      <c r="D123" s="54">
+        <f>COUNTA(AF123:AS123)</f>
+        <v>0</v>
       </c>
       <c r="E123" s="54"/>
       <c r="F123" s="2" t="s">
@@ -17318,62 +17402,46 @@
       </c>
       <c r="G123" s="2">
         <f t="shared" si="11"/>
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="H123" s="6">
-        <f>I123+개인기록Sheet!C123</f>
-        <v>12</v>
+        <f>I123+개인기록Sheet!C122</f>
+        <v>0</v>
       </c>
       <c r="I123" s="6">
         <f t="shared" si="12"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J123" s="2"/>
-      <c r="K123" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="K123" s="2"/>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
-      <c r="Q123" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="Q123" s="2"/>
       <c r="R123" s="2"/>
-      <c r="S123" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="S123" s="2"/>
       <c r="T123" s="2"/>
       <c r="U123" s="2"/>
       <c r="V123" s="2"/>
       <c r="W123" s="2"/>
       <c r="X123" s="2"/>
       <c r="Y123" s="2"/>
-      <c r="Z123" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="Z123" s="2"/>
       <c r="AA123" s="2"/>
       <c r="AB123" s="2"/>
-      <c r="AC123" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AC123" s="2"/>
       <c r="AD123" s="2"/>
       <c r="AE123" s="2"/>
-      <c r="AF123" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AF123" s="2"/>
       <c r="AG123" s="2"/>
       <c r="AH123" s="2"/>
-      <c r="AI123" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AI123" s="2"/>
       <c r="AJ123" s="2"/>
       <c r="AK123" s="2"/>
       <c r="AL123" s="2"/>
-      <c r="AM123" s="2" t="s">
-        <v>349</v>
-      </c>
+      <c r="AM123" s="2"/>
       <c r="AN123" s="2"/>
       <c r="AO123" s="2"/>
       <c r="AP123" s="2"/>
@@ -17423,14 +17491,13 @@
         <v>121</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C124" s="58">
-        <v>2026</v>
-      </c>
-      <c r="D124" s="54">
-        <f>COUNTA(AF124:AS124)</f>
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="C124" s="57" t="s">
+        <v>319</v>
+      </c>
+      <c r="D124" s="54" t="s">
+        <v>323</v>
       </c>
       <c r="E124" s="54"/>
       <c r="F124" s="2" t="s">
@@ -17438,39 +17505,51 @@
       </c>
       <c r="G124" s="2">
         <f t="shared" si="11"/>
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="H124" s="6">
-        <f>I124+개인기록Sheet!C124</f>
-        <v>2.6</v>
+        <f>I124+개인기록Sheet!C123</f>
+        <v>8</v>
       </c>
       <c r="I124" s="6">
         <f t="shared" si="12"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J124" s="2"/>
-      <c r="K124" s="2"/>
+      <c r="K124" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
-      <c r="Q124" s="2"/>
+      <c r="Q124" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="R124" s="2"/>
-      <c r="S124" s="2"/>
+      <c r="S124" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="T124" s="2"/>
       <c r="U124" s="2"/>
       <c r="V124" s="2"/>
       <c r="W124" s="2"/>
       <c r="X124" s="2"/>
       <c r="Y124" s="2"/>
-      <c r="Z124" s="2"/>
+      <c r="Z124" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AA124" s="2"/>
       <c r="AB124" s="2"/>
-      <c r="AC124" s="2"/>
+      <c r="AC124" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AD124" s="2"/>
       <c r="AE124" s="2"/>
-      <c r="AF124" s="2"/>
+      <c r="AF124" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AG124" s="2"/>
       <c r="AH124" s="2"/>
       <c r="AI124" s="2" t="s">
@@ -17478,10 +17557,10 @@
       </c>
       <c r="AJ124" s="2"/>
       <c r="AK124" s="2"/>
-      <c r="AL124" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="AM124" s="2"/>
+      <c r="AL124" s="2"/>
+      <c r="AM124" s="2" t="s">
+        <v>349</v>
+      </c>
       <c r="AN124" s="2"/>
       <c r="AO124" s="2"/>
       <c r="AP124" s="2"/>
@@ -17526,20 +17605,128 @@
       <c r="CC124" s="2"/>
       <c r="CD124" s="2"/>
     </row>
+    <row r="125" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <v>122</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C125" s="58">
+        <v>2026</v>
+      </c>
+      <c r="D125" s="54">
+        <f>COUNTA(AF125:AS125)</f>
+        <v>2</v>
+      </c>
+      <c r="E125" s="54"/>
+      <c r="F125" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G125" s="2">
+        <f t="shared" si="11"/>
+        <v>56</v>
+      </c>
+      <c r="H125" s="6">
+        <f>I125+개인기록Sheet!C124</f>
+        <v>6</v>
+      </c>
+      <c r="I125" s="6">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="J125" s="2"/>
+      <c r="K125" s="2"/>
+      <c r="L125" s="2"/>
+      <c r="M125" s="2"/>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" s="2"/>
+      <c r="Q125" s="2"/>
+      <c r="R125" s="2"/>
+      <c r="S125" s="2"/>
+      <c r="T125" s="2"/>
+      <c r="U125" s="2"/>
+      <c r="V125" s="2"/>
+      <c r="W125" s="2"/>
+      <c r="X125" s="2"/>
+      <c r="Y125" s="2"/>
+      <c r="Z125" s="2"/>
+      <c r="AA125" s="2"/>
+      <c r="AB125" s="2"/>
+      <c r="AC125" s="2"/>
+      <c r="AD125" s="2"/>
+      <c r="AE125" s="2"/>
+      <c r="AF125" s="2"/>
+      <c r="AG125" s="2"/>
+      <c r="AH125" s="2"/>
+      <c r="AI125" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AJ125" s="2"/>
+      <c r="AK125" s="2"/>
+      <c r="AL125" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="AM125" s="2"/>
+      <c r="AN125" s="2"/>
+      <c r="AO125" s="2"/>
+      <c r="AP125" s="2"/>
+      <c r="AQ125" s="2"/>
+      <c r="AR125" s="2"/>
+      <c r="AS125" s="2"/>
+      <c r="AT125" s="2"/>
+      <c r="AU125" s="2"/>
+      <c r="AV125" s="2"/>
+      <c r="AW125" s="2"/>
+      <c r="AX125" s="2"/>
+      <c r="AY125" s="2"/>
+      <c r="AZ125" s="2"/>
+      <c r="BA125" s="2"/>
+      <c r="BB125" s="2"/>
+      <c r="BC125" s="2"/>
+      <c r="BD125" s="2"/>
+      <c r="BE125" s="2"/>
+      <c r="BF125" s="2"/>
+      <c r="BG125" s="2"/>
+      <c r="BH125" s="2"/>
+      <c r="BI125" s="2"/>
+      <c r="BJ125" s="2"/>
+      <c r="BK125" s="2"/>
+      <c r="BL125" s="2"/>
+      <c r="BM125" s="2"/>
+      <c r="BN125" s="2"/>
+      <c r="BO125" s="2"/>
+      <c r="BP125" s="2"/>
+      <c r="BQ125" s="2"/>
+      <c r="BR125" s="2"/>
+      <c r="BS125" s="2"/>
+      <c r="BT125" s="2"/>
+      <c r="BU125" s="2"/>
+      <c r="BV125" s="2"/>
+      <c r="BW125" s="2"/>
+      <c r="BX125" s="2"/>
+      <c r="BY125" s="2"/>
+      <c r="BZ125" s="2"/>
+      <c r="CA125" s="2"/>
+      <c r="CB125" s="2"/>
+      <c r="CC125" s="2"/>
+      <c r="CD125" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="D4:E124">
+  <conditionalFormatting sqref="D4:E125">
     <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="지급">
       <formula>NOT(ISERROR(SEARCH("지급",D4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G124">
+  <conditionalFormatting sqref="G4:G125">
     <cfRule type="top10" dxfId="12" priority="948" bottom="1" rank="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H124">
+  <conditionalFormatting sqref="H4:H125">
     <cfRule type="top10" dxfId="11" priority="950" rank="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I124">
+  <conditionalFormatting sqref="I4:I125">
     <cfRule type="top10" dxfId="10" priority="952" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.39347222447395325" right="0.39347222447395325" top="0.19666667282581329" bottom="0.19666667282581329" header="0.19666667282581329" footer="0.19666667282581329"/>
@@ -26383,7 +26570,7 @@
   <sheetPr codeName="Sheet4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:CW124"/>
+  <dimension ref="A2:CW125"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -26583,7 +26770,7 @@
         <v>신재경</v>
       </c>
       <c r="C5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C5:C68" si="7">((D5+E5+G5+H5)*0.2)+(F5*0.3)</f>
         <v>0.90000000000000013</v>
       </c>
       <c r="D5" s="14">
@@ -26607,7 +26794,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I5:I68" si="8">SUM(D5:H5)</f>
         <v>4</v>
       </c>
       <c r="J5" s="15"/>
@@ -26660,7 +26847,7 @@
         <v>정효태</v>
       </c>
       <c r="C6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D6" s="14">
@@ -26684,7 +26871,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J6" s="15"/>
@@ -26737,7 +26924,7 @@
         <v>이승민</v>
       </c>
       <c r="C7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D7" s="14">
@@ -26761,7 +26948,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J7" s="15"/>
@@ -26814,7 +27001,7 @@
         <v>이정석</v>
       </c>
       <c r="C8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D8" s="14">
@@ -26838,7 +27025,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J8" s="15"/>
@@ -26891,7 +27078,7 @@
         <v>강종찬</v>
       </c>
       <c r="C9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0.8</v>
       </c>
       <c r="D9" s="14">
@@ -26915,7 +27102,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="J9" s="15"/>
@@ -26968,7 +27155,7 @@
         <v>강관석</v>
       </c>
       <c r="C10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
       <c r="D10" s="14">
@@ -26992,7 +27179,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="J10" s="15"/>
@@ -27045,7 +27232,7 @@
         <v>강기혁</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>4.9000000000000004</v>
       </c>
       <c r="D11" s="14">
@@ -27069,7 +27256,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
       <c r="J11" s="15"/>
@@ -27122,7 +27309,7 @@
         <v>강도일</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D12" s="14">
@@ -27146,7 +27333,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J12" s="15"/>
@@ -27199,7 +27386,7 @@
         <v>강일수</v>
       </c>
       <c r="C13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D13" s="14">
@@ -27223,7 +27410,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J13" s="15"/>
@@ -27271,7 +27458,7 @@
         <v>구교훈</v>
       </c>
       <c r="C14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D14" s="14">
@@ -27295,7 +27482,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J14" s="15"/>
@@ -27338,7 +27525,7 @@
         <v>권민강</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D15" s="14">
@@ -27362,7 +27549,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="J15" s="15"/>
@@ -27405,7 +27592,7 @@
         <v>김기문</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>3.5</v>
       </c>
       <c r="D16" s="14">
@@ -27429,7 +27616,7 @@
         <v>2</v>
       </c>
       <c r="I16" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="J16" s="15"/>
@@ -27472,7 +27659,7 @@
         <v>김기태</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>3.8000000000000003</v>
       </c>
       <c r="D17" s="14">
@@ -27496,7 +27683,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="J17" s="15"/>
@@ -27529,7 +27716,7 @@
         <v>김덕준</v>
       </c>
       <c r="C18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D18" s="14">
@@ -27553,7 +27740,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J18" s="15"/>
@@ -27581,7 +27768,7 @@
         <v>김도원</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D19" s="14">
@@ -27605,7 +27792,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J19" s="15"/>
@@ -27620,7 +27807,7 @@
         <v>김동인</v>
       </c>
       <c r="C20" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D20" s="14">
@@ -27644,7 +27831,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J20" s="15"/>
@@ -27659,7 +27846,7 @@
         <v>김류현</v>
       </c>
       <c r="C21" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D21" s="14">
@@ -27683,7 +27870,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J21" s="15"/>
@@ -27698,7 +27885,7 @@
         <v>김민섭</v>
       </c>
       <c r="C22" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D22" s="14">
@@ -27722,7 +27909,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J22" s="15"/>
@@ -27737,7 +27924,7 @@
         <v>김민찬</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D23" s="14">
@@ -27761,7 +27948,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J23" s="15"/>
@@ -27776,7 +27963,7 @@
         <v>김범기</v>
       </c>
       <c r="C24" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D24" s="14">
@@ -27800,7 +27987,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J24" s="15"/>
@@ -27815,7 +28002,7 @@
         <v>김병준</v>
       </c>
       <c r="C25" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D25" s="14">
@@ -27839,7 +28026,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J25" s="15"/>
@@ -27854,7 +28041,7 @@
         <v>김부건</v>
       </c>
       <c r="C26" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="D26" s="14">
@@ -27878,7 +28065,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="J26" s="15"/>
@@ -27893,7 +28080,7 @@
         <v>김성수</v>
       </c>
       <c r="C27" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>2.5</v>
       </c>
       <c r="D27" s="14">
@@ -27917,7 +28104,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="J27" s="15"/>
@@ -27932,7 +28119,7 @@
         <v>김성준</v>
       </c>
       <c r="C28" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>10.7</v>
       </c>
       <c r="D28" s="14">
@@ -27956,7 +28143,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="J28" s="15"/>
@@ -27971,7 +28158,7 @@
         <v>김송환</v>
       </c>
       <c r="C29" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>3.0999999999999996</v>
       </c>
       <c r="D29" s="14">
@@ -27995,7 +28182,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="J29" s="15"/>
@@ -28010,7 +28197,7 @@
         <v>김영태</v>
       </c>
       <c r="C30" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D30" s="14">
@@ -28034,7 +28221,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J30" s="15"/>
@@ -28049,7 +28236,7 @@
         <v>김용빈</v>
       </c>
       <c r="C31" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D31" s="14">
@@ -28073,7 +28260,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J31" s="15"/>
@@ -28088,7 +28275,7 @@
         <v>김용현</v>
       </c>
       <c r="C32" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="D32" s="14">
@@ -28112,7 +28299,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="J32" s="15"/>
@@ -28127,7 +28314,7 @@
         <v>김우인</v>
       </c>
       <c r="C33" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>4.8000000000000007</v>
       </c>
       <c r="D33" s="14">
@@ -28151,7 +28338,7 @@
         <v>12</v>
       </c>
       <c r="I33" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="J33" s="15"/>
@@ -28166,7 +28353,7 @@
         <v>김종준</v>
       </c>
       <c r="C34" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D34" s="14">
@@ -28190,7 +28377,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J34" s="15"/>
@@ -28205,7 +28392,7 @@
         <v>김종혁</v>
       </c>
       <c r="C35" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
       <c r="D35" s="14">
@@ -28229,7 +28416,7 @@
         <v>2</v>
       </c>
       <c r="I35" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="J35" s="15"/>
@@ -28244,7 +28431,7 @@
         <v>김준영</v>
       </c>
       <c r="C36" s="2">
-        <f t="shared" ref="C36:C67" si="7">((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D36" s="14">
@@ -28268,7 +28455,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="14">
-        <f t="shared" ref="I36:I67" si="8">SUM(D36:H36)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J36" s="15"/>
@@ -29492,7 +29679,7 @@
         <v>오운용</v>
       </c>
       <c r="C68" s="2">
-        <f t="shared" ref="C68:C99" si="9">((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D68" s="14">
@@ -29516,7 +29703,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="14">
-        <f t="shared" ref="I68:I99" si="10">SUM(D68:H68)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J68" s="15"/>
@@ -29531,7 +29718,7 @@
         <v>오준서</v>
       </c>
       <c r="C69" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="C69:C125" si="9">((D69+E69+G69+H69)*0.2)+(F69*0.3)</f>
         <v>0</v>
       </c>
       <c r="D69" s="14">
@@ -29555,7 +29742,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I69:I125" si="10">SUM(D69:H69)</f>
         <v>0</v>
       </c>
       <c r="J69" s="15"/>
@@ -30740,7 +30927,7 @@
         <v>전나현</v>
       </c>
       <c r="C100" s="2">
-        <f t="shared" ref="C100:C131" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
+        <f t="shared" si="9"/>
         <v>2.5</v>
       </c>
       <c r="D100" s="14">
@@ -30764,7 +30951,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="14">
-        <f t="shared" ref="I100:I131" si="12">SUM(D100:H100)</f>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J100" s="15"/>
@@ -30779,7 +30966,7 @@
         <v>전성환</v>
       </c>
       <c r="C101" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="D101" s="14">
@@ -30803,7 +30990,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J101" s="15"/>
@@ -30818,7 +31005,7 @@
         <v>전하늘</v>
       </c>
       <c r="C102" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0.7</v>
       </c>
       <c r="D102" s="14">
@@ -30842,7 +31029,7 @@
         <v>0</v>
       </c>
       <c r="I102" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J102" s="15"/>
@@ -30857,7 +31044,7 @@
         <v>정민수</v>
       </c>
       <c r="C103" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>5.2</v>
       </c>
       <c r="D103" s="14">
@@ -30881,7 +31068,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="J103" s="15"/>
@@ -30896,7 +31083,7 @@
         <v>정재명</v>
       </c>
       <c r="C104" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>3.4000000000000004</v>
       </c>
       <c r="D104" s="14">
@@ -30920,7 +31107,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>17</v>
       </c>
       <c r="J104" s="15"/>
@@ -30935,7 +31122,7 @@
         <v>정현서</v>
       </c>
       <c r="C105" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.5</v>
       </c>
       <c r="D105" s="14">
@@ -30959,7 +31146,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
     </row>
@@ -30973,7 +31160,7 @@
         <v>조진한</v>
       </c>
       <c r="C106" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>5.8000000000000007</v>
       </c>
       <c r="D106" s="14">
@@ -30997,7 +31184,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>22</v>
       </c>
     </row>
@@ -31011,7 +31198,7 @@
         <v>조현우</v>
       </c>
       <c r="C107" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="D107" s="14">
@@ -31035,7 +31222,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
     </row>
@@ -31049,7 +31236,7 @@
         <v>차승원</v>
       </c>
       <c r="C108" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="D108" s="14">
@@ -31073,7 +31260,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
     </row>
@@ -31084,19 +31271,19 @@
       </c>
       <c r="B109" s="2" t="str">
         <f>종합Sheet!B109</f>
-        <v>최령창</v>
+        <v>최강인</v>
       </c>
       <c r="C109" s="2">
-        <f t="shared" si="11"/>
-        <v>4.6000000000000005</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="D109" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B109)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E109" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B109)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F109" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B109)</f>
@@ -31104,15 +31291,15 @@
       </c>
       <c r="G109" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B109)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H109" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B109)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I109" s="14">
-        <f t="shared" si="12"/>
-        <v>23</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -31122,19 +31309,19 @@
       </c>
       <c r="B110" s="2" t="str">
         <f>종합Sheet!B110</f>
-        <v>최승훈</v>
+        <v>최령창</v>
       </c>
       <c r="C110" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>4.6000000000000005</v>
       </c>
       <c r="D110" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B110)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E110" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B110)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F110" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B110)</f>
@@ -31142,15 +31329,15 @@
       </c>
       <c r="G110" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B110)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H110" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B110)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I110" s="14">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -31160,15 +31347,15 @@
       </c>
       <c r="B111" s="2" t="str">
         <f>종합Sheet!B111</f>
-        <v>한상규</v>
+        <v>최승훈</v>
       </c>
       <c r="C111" s="2">
-        <f t="shared" si="11"/>
-        <v>3.2</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="D111" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B111)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B111)</f>
@@ -31180,15 +31367,15 @@
       </c>
       <c r="G111" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B111)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H111" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B111)</f>
         <v>0</v>
       </c>
       <c r="I111" s="14">
-        <f t="shared" si="12"/>
-        <v>16</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -31198,19 +31385,19 @@
       </c>
       <c r="B112" s="2" t="str">
         <f>종합Sheet!B112</f>
-        <v>한의현</v>
+        <v>한상규</v>
       </c>
       <c r="C112" s="2">
-        <f t="shared" si="11"/>
-        <v>1.6</v>
+        <f t="shared" si="9"/>
+        <v>3.2</v>
       </c>
       <c r="D112" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B112)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B112)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F112" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B112)</f>
@@ -31218,15 +31405,15 @@
       </c>
       <c r="G112" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B112)</f>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H112" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B112)</f>
         <v>0</v>
       </c>
       <c r="I112" s="14">
-        <f t="shared" si="12"/>
-        <v>8</v>
+        <f t="shared" si="10"/>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -31236,11 +31423,11 @@
       </c>
       <c r="B113" s="2" t="str">
         <f>종합Sheet!B113</f>
-        <v>한중희</v>
+        <v>한의현</v>
       </c>
       <c r="C113" s="2">
-        <f t="shared" si="11"/>
-        <v>1.8</v>
+        <f t="shared" si="9"/>
+        <v>1.6</v>
       </c>
       <c r="D113" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B113)</f>
@@ -31248,7 +31435,7 @@
       </c>
       <c r="E113" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B113)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F113" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B113)</f>
@@ -31256,15 +31443,15 @@
       </c>
       <c r="G113" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B113)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H113" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B113)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" s="14">
-        <f t="shared" si="12"/>
-        <v>9</v>
+        <f t="shared" si="10"/>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -31274,35 +31461,35 @@
       </c>
       <c r="B114" s="2" t="str">
         <f>종합Sheet!B114</f>
-        <v>허동혁</v>
+        <v>한중희</v>
       </c>
       <c r="C114" s="2">
-        <f t="shared" si="11"/>
-        <v>2.6</v>
+        <f t="shared" si="9"/>
+        <v>1.8</v>
       </c>
       <c r="D114" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B114)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E114" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B114)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F114" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B114)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G114" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B114)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H114" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B114)</f>
         <v>1</v>
       </c>
       <c r="I114" s="14">
-        <f t="shared" si="12"/>
-        <v>12</v>
+        <f t="shared" si="10"/>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -31312,19 +31499,19 @@
       </c>
       <c r="B115" s="2" t="str">
         <f>종합Sheet!B115</f>
-        <v>홍석준</v>
+        <v>허동혁</v>
       </c>
       <c r="C115" s="2">
-        <f t="shared" si="11"/>
-        <v>1.6</v>
+        <f t="shared" si="9"/>
+        <v>2.6</v>
       </c>
       <c r="D115" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B115)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E115" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B115)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F115" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B115)</f>
@@ -31332,15 +31519,15 @@
       </c>
       <c r="G115" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B115)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B115)</f>
         <v>1</v>
       </c>
       <c r="I115" s="14">
-        <f t="shared" si="12"/>
-        <v>7</v>
+        <f t="shared" si="10"/>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -31350,23 +31537,23 @@
       </c>
       <c r="B116" s="2" t="str">
         <f>종합Sheet!B116</f>
-        <v>홍현석</v>
+        <v>홍석준</v>
       </c>
       <c r="C116" s="2">
-        <f t="shared" si="11"/>
-        <v>0.2</v>
+        <f t="shared" si="9"/>
+        <v>1.6</v>
       </c>
       <c r="D116" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B116)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E116" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B116)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B116)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G116" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B116)</f>
@@ -31374,11 +31561,11 @@
       </c>
       <c r="H116" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B116)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" s="14">
-        <f t="shared" si="12"/>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -31388,35 +31575,35 @@
       </c>
       <c r="B117" s="2" t="str">
         <f>종합Sheet!B117</f>
-        <v>황건호</v>
+        <v>홍현석</v>
       </c>
       <c r="C117" s="2">
-        <f t="shared" si="11"/>
-        <v>2.5</v>
+        <f t="shared" si="9"/>
+        <v>0.2</v>
       </c>
       <c r="D117" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B117)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E117" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B117)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B117)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G117" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B117)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B117)</f>
         <v>0</v>
       </c>
       <c r="I117" s="14">
-        <f t="shared" si="12"/>
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -31426,35 +31613,35 @@
       </c>
       <c r="B118" s="2" t="str">
         <f>종합Sheet!B118</f>
-        <v>황석원</v>
+        <v>황건호</v>
       </c>
       <c r="C118" s="2">
-        <f t="shared" si="11"/>
-        <v>3.8000000000000003</v>
+        <f t="shared" si="9"/>
+        <v>2.5</v>
       </c>
       <c r="D118" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B118)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E118" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B118)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B118)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G118" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B118)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H118" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B118)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="14">
-        <f t="shared" si="12"/>
-        <v>18</v>
+        <f t="shared" si="10"/>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -31464,15 +31651,15 @@
       </c>
       <c r="B119" s="2" t="str">
         <f>종합Sheet!B119</f>
-        <v>황재순</v>
+        <v>황석원</v>
       </c>
       <c r="C119" s="2">
-        <f t="shared" si="11"/>
-        <v>0.4</v>
+        <f t="shared" si="9"/>
+        <v>3.8000000000000003</v>
       </c>
       <c r="D119" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B119)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E119" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B119)</f>
@@ -31480,19 +31667,19 @@
       </c>
       <c r="F119" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B119)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G119" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B119)</f>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H119" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B119)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" s="14">
-        <f t="shared" si="12"/>
-        <v>2</v>
+        <f t="shared" si="10"/>
+        <v>18</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -31502,15 +31689,15 @@
       </c>
       <c r="B120" s="2" t="str">
         <f>종합Sheet!B120</f>
-        <v>황철우</v>
+        <v>황재순</v>
       </c>
       <c r="C120" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D120" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B120)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E120" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B120)</f>
@@ -31522,14 +31709,14 @@
       </c>
       <c r="G120" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B120)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H120" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B120)</f>
         <v>0</v>
       </c>
       <c r="I120" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
     </row>
@@ -31540,15 +31727,15 @@
       </c>
       <c r="B121" s="2" t="str">
         <f>종합Sheet!B121</f>
-        <v>김민성</v>
+        <v>황철우</v>
       </c>
       <c r="C121" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>0.4</v>
       </c>
       <c r="D121" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B121)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E121" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B121)</f>
@@ -31567,8 +31754,8 @@
         <v>0</v>
       </c>
       <c r="I121" s="14">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -31578,10 +31765,10 @@
       </c>
       <c r="B122" s="2" t="str">
         <f>종합Sheet!B122</f>
-        <v>송명섭</v>
+        <v>김민성</v>
       </c>
       <c r="C122" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D122" s="14">
@@ -31605,7 +31792,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -31616,19 +31803,19 @@
       </c>
       <c r="B123" s="2" t="str">
         <f>종합Sheet!B123</f>
-        <v>최경영</v>
+        <v>송명섭</v>
       </c>
       <c r="C123" s="2">
-        <f t="shared" si="11"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="D123" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B123)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E123" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B123)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B123)</f>
@@ -31636,15 +31823,15 @@
       </c>
       <c r="G123" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B123)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H123" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B123)</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I123" s="14">
-        <f t="shared" si="12"/>
-        <v>20</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -31654,19 +31841,19 @@
       </c>
       <c r="B124" s="2" t="str">
         <f>종합Sheet!B124</f>
-        <v>박지수</v>
+        <v>최경영</v>
       </c>
       <c r="C124" s="2">
-        <f t="shared" si="11"/>
-        <v>0.60000000000000009</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="D124" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B124)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E124" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B124)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B124)</f>
@@ -31678,32 +31865,70 @@
       </c>
       <c r="H124" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B124)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I124" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <f>종합Sheet!A125</f>
+        <v>122</v>
+      </c>
+      <c r="B125" s="2" t="str">
+        <f>종합Sheet!B125</f>
+        <v>박지수</v>
+      </c>
+      <c r="C125" s="2">
+        <f t="shared" si="9"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="D125" s="14">
+        <f>COUNTIF(경기기록Sheet!$E:$H,B125)</f>
+        <v>0</v>
+      </c>
+      <c r="E125" s="14">
+        <f>COUNTIF(경기기록Sheet!$I:$L,B125)</f>
+        <v>0</v>
+      </c>
+      <c r="F125" s="14">
+        <f>COUNTIF(경기기록Sheet!$M:$P,B125)</f>
+        <v>0</v>
+      </c>
+      <c r="G125" s="14">
+        <f>COUNTIF(경기기록Sheet!$Q:$U,B125)</f>
+        <v>3</v>
+      </c>
+      <c r="H125" s="14">
+        <f>COUNTIF(경기기록Sheet!$V:$V,B125)</f>
+        <v>0</v>
+      </c>
+      <c r="I125" s="14">
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="D4:D124">
+  <conditionalFormatting sqref="D4:D125">
     <cfRule type="top10" dxfId="9" priority="953" rank="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E124">
+  <conditionalFormatting sqref="E4:E125">
     <cfRule type="top10" dxfId="8" priority="954" rank="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F124">
+  <conditionalFormatting sqref="F4:F125">
     <cfRule type="top10" dxfId="7" priority="955" rank="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G124">
+  <conditionalFormatting sqref="G4:G125">
     <cfRule type="top10" dxfId="6" priority="956" rank="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H124">
+  <conditionalFormatting sqref="H4:H125">
     <cfRule type="top10" dxfId="5" priority="957" rank="3"/>
     <cfRule type="top10" priority="958" rank="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I124">
+  <conditionalFormatting sqref="I4:I125">
     <cfRule type="top10" dxfId="4" priority="959" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.39347222447395325" right="0.39347222447395325" top="0.19666667282581329" bottom="0.19666667282581329" header="0.19666667282581329" footer="0.19666667282581329"/>
@@ -33306,15 +33531,15 @@
         <v>298</v>
       </c>
       <c r="E3" s="70">
-        <f>VLOOKUP(D3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>16</v>
+        <f>VLOOKUP(D3,종합Sheet!$B$3:$I$124,8,0)</f>
+        <v>17</v>
       </c>
       <c r="F3" s="70" t="s">
         <v>298</v>
       </c>
       <c r="G3" s="61">
-        <f>VLOOKUP(F3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>19.600000000000001</v>
+        <f>VLOOKUP(F3,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>20.6</v>
       </c>
       <c r="I3" s="95" t="s">
         <v>330</v>
@@ -33338,15 +33563,15 @@
         <v>298</v>
       </c>
       <c r="Q3" s="62">
-        <f>VLOOKUP(P3,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>16</v>
+        <f>VLOOKUP(P3,종합Sheet!$B$3:$I$124,8,0)</f>
+        <v>17</v>
       </c>
       <c r="R3" s="62" t="s">
         <v>298</v>
       </c>
       <c r="S3" s="63">
-        <f>VLOOKUP(R3,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>19.600000000000001</v>
+        <f>VLOOKUP(R3,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>20.6</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.25">
@@ -33358,14 +33583,14 @@
         <v>50</v>
       </c>
       <c r="E4" s="62">
-        <f>VLOOKUP(D4,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(D4,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>22</v>
       </c>
       <c r="F4" s="70" t="s">
         <v>224</v>
       </c>
       <c r="G4" s="61">
-        <f>VLOOKUP(F4,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(F4,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>8.1999999999999993</v>
       </c>
       <c r="I4" s="96"/>
@@ -33386,15 +33611,15 @@
         <v>221</v>
       </c>
       <c r="Q4" s="62">
-        <f>VLOOKUP(P4,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>24</v>
+        <f>VLOOKUP(P4,종합Sheet!$B$3:$I$124,8,0)</f>
+        <v>26</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>221</v>
       </c>
       <c r="S4" s="63">
-        <f>VLOOKUP(R4,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>34.700000000000003</v>
+        <f>VLOOKUP(R4,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>36.700000000000003</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
@@ -33406,15 +33631,15 @@
         <v>221</v>
       </c>
       <c r="E5" s="47">
-        <f>VLOOKUP(D5,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>24</v>
+        <f>VLOOKUP(D5,종합Sheet!$B$3:$I$124,8,0)</f>
+        <v>26</v>
       </c>
       <c r="F5" s="70" t="s">
         <v>221</v>
       </c>
       <c r="G5" s="61">
-        <f>VLOOKUP(F5,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>34.700000000000003</v>
+        <f>VLOOKUP(F5,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>36.700000000000003</v>
       </c>
       <c r="I5" s="96"/>
       <c r="J5" s="66">
@@ -33434,14 +33659,14 @@
         <v>304</v>
       </c>
       <c r="Q5" s="62">
-        <f>VLOOKUP(P5,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(P5,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>21</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>304</v>
       </c>
       <c r="S5" s="63">
-        <f>VLOOKUP(R5,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(R5,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>26.8</v>
       </c>
     </row>
@@ -33454,15 +33679,15 @@
         <v>304</v>
       </c>
       <c r="E6" s="47">
-        <f>VLOOKUP(D6,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(D6,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>21</v>
       </c>
       <c r="F6" s="70" t="s">
         <v>232</v>
       </c>
       <c r="G6" s="61">
-        <f>VLOOKUP(F6,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>18.2</v>
+        <f>VLOOKUP(F6,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>19.2</v>
       </c>
       <c r="I6" s="96"/>
       <c r="J6" s="66">
@@ -33482,14 +33707,14 @@
         <v>230</v>
       </c>
       <c r="Q6" s="69">
-        <f>VLOOKUP(P6,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(P6,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>16</v>
       </c>
       <c r="R6" s="65" t="s">
         <v>230</v>
       </c>
       <c r="S6" s="71">
-        <f>VLOOKUP(R6,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(R6,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>21.2</v>
       </c>
     </row>
@@ -33502,14 +33727,14 @@
         <v>232</v>
       </c>
       <c r="E7" s="47">
-        <f>VLOOKUP(D7,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>15</v>
+        <f>VLOOKUP(D7,종합Sheet!$B$3:$I$124,8,0)</f>
+        <v>16</v>
       </c>
       <c r="F7" s="70" t="s">
         <v>304</v>
       </c>
       <c r="G7" s="61">
-        <f>VLOOKUP(F7,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(F7,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>26.8</v>
       </c>
       <c r="I7" s="97"/>
@@ -33530,15 +33755,15 @@
         <v>322</v>
       </c>
       <c r="Q7" s="69">
-        <f>VLOOKUP(P7,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>15</v>
+        <f>VLOOKUP(P7,종합Sheet!$B$3:$I$124,8,0)</f>
+        <v>16</v>
       </c>
       <c r="R7" s="65" t="s">
         <v>322</v>
       </c>
       <c r="S7" s="71">
-        <f>VLOOKUP(R7,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>20</v>
+        <f>VLOOKUP(R7,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
@@ -33550,14 +33775,14 @@
         <v>224</v>
       </c>
       <c r="E8" s="47">
-        <f>VLOOKUP(D8,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(D8,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>7</v>
       </c>
       <c r="F8" s="62" t="s">
         <v>50</v>
       </c>
       <c r="G8" s="63">
-        <f>VLOOKUP(F8,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(F8,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>24</v>
       </c>
       <c r="N8" s="86"/>
@@ -33568,15 +33793,15 @@
         <v>316</v>
       </c>
       <c r="Q8" s="69">
-        <f>VLOOKUP(P8,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>9</v>
+        <f>VLOOKUP(P8,종합Sheet!$B$3:$I$124,8,0)</f>
+        <v>10</v>
       </c>
       <c r="R8" s="65" t="s">
         <v>316</v>
       </c>
       <c r="S8" s="71">
-        <f>VLOOKUP(R8,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>11</v>
+        <f>VLOOKUP(R8,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
@@ -33588,15 +33813,15 @@
         <v>48</v>
       </c>
       <c r="E9" s="65">
-        <f>VLOOKUP(D9,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(D9,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>7</v>
       </c>
       <c r="F9" s="70" t="s">
         <v>7</v>
       </c>
       <c r="G9" s="61">
-        <f>VLOOKUP(F9,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>13.3</v>
+        <f>VLOOKUP(F9,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>15.3</v>
       </c>
       <c r="I9" s="99" t="s">
         <v>248</v>
@@ -33616,14 +33841,14 @@
         <v>308</v>
       </c>
       <c r="Q9" s="69">
-        <f>VLOOKUP(P9,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(P9,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>10</v>
       </c>
       <c r="R9" s="65" t="s">
         <v>309</v>
       </c>
       <c r="S9" s="71">
-        <f>VLOOKUP(R9,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(R9,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -33636,14 +33861,14 @@
         <v>55</v>
       </c>
       <c r="E10" s="64">
-        <f>VLOOKUP(D10,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(D10,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>9</v>
       </c>
       <c r="F10" s="70" t="s">
         <v>53</v>
       </c>
       <c r="G10" s="61">
-        <f>VLOOKUP(F10,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(F10,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>17.600000000000001</v>
       </c>
       <c r="I10" s="95" t="s">
@@ -33666,14 +33891,14 @@
         <v>309</v>
       </c>
       <c r="Q10" s="65">
-        <f>VLOOKUP(P10,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(P10,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>0</v>
       </c>
       <c r="R10" s="65" t="s">
         <v>308</v>
       </c>
       <c r="S10" s="71">
-        <f>VLOOKUP(R10,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(R10,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>12.2</v>
       </c>
     </row>
@@ -33686,14 +33911,14 @@
         <v>7</v>
       </c>
       <c r="E11" s="65">
-        <f>VLOOKUP(D11,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>10</v>
+        <f>VLOOKUP(D11,종합Sheet!$B$3:$I$124,8,0)</f>
+        <v>12</v>
       </c>
       <c r="F11" s="70" t="s">
         <v>48</v>
       </c>
       <c r="G11" s="61">
-        <f>VLOOKUP(F11,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(F11,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>7.8</v>
       </c>
       <c r="I11" s="96"/>
@@ -33714,15 +33939,15 @@
         <v>314</v>
       </c>
       <c r="Q11" s="65">
-        <f>VLOOKUP(P11,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(P11,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>6</v>
       </c>
       <c r="R11" s="65" t="s">
         <v>314</v>
       </c>
       <c r="S11" s="71">
-        <f>VLOOKUP(R11,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>8.6</v>
+        <f>VLOOKUP(R11,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>7.8</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
@@ -33734,15 +33959,15 @@
         <v>223</v>
       </c>
       <c r="E12" s="65">
-        <f>VLOOKUP(D12,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>12</v>
+        <f>VLOOKUP(D12,종합Sheet!$B$3:$I$124,8,0)</f>
+        <v>13</v>
       </c>
       <c r="F12" s="70" t="s">
         <v>223</v>
       </c>
       <c r="G12" s="61">
-        <f>VLOOKUP(F12,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>16.899999999999999</v>
+        <f>VLOOKUP(F12,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>17.899999999999999</v>
       </c>
       <c r="I12" s="96"/>
       <c r="J12" s="66">
@@ -33762,14 +33987,14 @@
         <v>334</v>
       </c>
       <c r="Q12" s="65" t="e">
-        <f>VLOOKUP(P12,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(P12,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>#N/A</v>
       </c>
       <c r="R12" s="65" t="s">
         <v>334</v>
       </c>
       <c r="S12" s="71" t="e">
-        <f>VLOOKUP(R12,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(R12,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -33782,14 +34007,14 @@
         <v>53</v>
       </c>
       <c r="E13" s="65">
-        <f>VLOOKUP(D13,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(D13,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>13</v>
       </c>
       <c r="F13" s="70" t="s">
         <v>241</v>
       </c>
       <c r="G13" s="61">
-        <f>VLOOKUP(F13,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(F13,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>17.399999999999999</v>
       </c>
       <c r="I13" s="96"/>
@@ -33818,15 +34043,15 @@
         <v>228</v>
       </c>
       <c r="E14" s="65">
-        <f>VLOOKUP(D14,종합Sheet!$B$3:$I$123,8,0)</f>
-        <v>22</v>
+        <f>VLOOKUP(D14,종합Sheet!$B$3:$I$124,8,0)</f>
+        <v>23</v>
       </c>
       <c r="F14" s="70" t="s">
         <v>228</v>
       </c>
       <c r="G14" s="61">
-        <f>VLOOKUP(F14,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>26.8</v>
+        <f>VLOOKUP(F14,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>27.8</v>
       </c>
       <c r="I14" s="97"/>
       <c r="J14" s="66">
@@ -33854,14 +34079,14 @@
         <v>241</v>
       </c>
       <c r="E15" s="65">
-        <f>VLOOKUP(D15,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(D15,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>15</v>
       </c>
       <c r="F15" s="62" t="s">
         <v>299</v>
       </c>
       <c r="G15" s="63">
-        <f>VLOOKUP(F15,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(F15,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>12.5</v>
       </c>
       <c r="N15"/>
@@ -33880,14 +34105,14 @@
         <v>230</v>
       </c>
       <c r="E16" s="65">
-        <f>VLOOKUP(D16,종합Sheet!$B$3:$I$123,8,0)</f>
+        <f>VLOOKUP(D16,종합Sheet!$B$3:$I$124,8,0)</f>
         <v>16</v>
       </c>
       <c r="F16" s="62" t="s">
         <v>230</v>
       </c>
       <c r="G16" s="63">
-        <f>VLOOKUP(F16,종합Sheet!$B$3:$I$123,7,0)</f>
+        <f>VLOOKUP(F16,종합Sheet!$B$3:$I$124,7,0)</f>
         <v>21.2</v>
       </c>
       <c r="H16" s="37"/>
@@ -33916,8 +34141,8 @@
         <v>229</v>
       </c>
       <c r="G17" s="63">
-        <f>VLOOKUP(F17,종합Sheet!$B$3:$I$123,7,0)</f>
-        <v>12.6</v>
+        <f>VLOOKUP(F17,종합Sheet!$B$3:$I$124,7,0)</f>
+        <v>14.2</v>
       </c>
       <c r="H17" s="37"/>
       <c r="I17" s="95" t="s">
@@ -34670,15 +34895,15 @@
         <v>50</v>
       </c>
       <c r="C4" s="31" t="str">
-        <f>VLOOKUP(B4,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B4,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D4" s="2" t="str">
-        <f>VLOOKUP(B4,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B4,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E4" s="2">
-        <f>VLOOKUP(B4,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B4,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -34784,15 +35009,15 @@
         <v>39</v>
       </c>
       <c r="C5" s="31">
-        <f>VLOOKUP(B5,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B5,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2021</v>
       </c>
       <c r="D5" s="2" t="str">
-        <f>VLOOKUP(B5,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B5,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E5" s="2">
-        <f>VLOOKUP(B5,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B5,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -34902,15 +35127,15 @@
         <v>8</v>
       </c>
       <c r="C6" s="31" t="str">
-        <f>VLOOKUP(B6,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B6,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D6" s="2" t="str">
-        <f>VLOOKUP(B6,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B6,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>발주</v>
       </c>
       <c r="E6" s="2">
-        <f>VLOOKUP(B6,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B6,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -35014,15 +35239,15 @@
         <v>48</v>
       </c>
       <c r="C7" s="31" t="str">
-        <f>VLOOKUP(B7,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B7,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D7" s="2" t="str">
-        <f>VLOOKUP(B7,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B7,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E7" s="2">
-        <f>VLOOKUP(B7,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B7,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -35122,15 +35347,15 @@
         <v>109</v>
       </c>
       <c r="C8" s="31">
-        <f>VLOOKUP(B8,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B8,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2022</v>
       </c>
       <c r="D8" s="2" t="str">
-        <f>VLOOKUP(B8,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B8,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E8" s="2">
-        <f>VLOOKUP(B8,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B8,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -35240,15 +35465,15 @@
         <v>111</v>
       </c>
       <c r="C9" s="31">
-        <f>VLOOKUP(B9,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B9,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2022</v>
       </c>
       <c r="D9" s="2" t="str">
-        <f>VLOOKUP(B9,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B9,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E9" s="2">
-        <f>VLOOKUP(B9,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B9,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -35354,15 +35579,15 @@
         <v>90</v>
       </c>
       <c r="C10" s="31" t="e">
-        <f>VLOOKUP(B10,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B10,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>#N/A</v>
       </c>
       <c r="D10" s="2" t="e">
-        <f>VLOOKUP(B10,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B10,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>#N/A</v>
       </c>
       <c r="E10" s="2" t="e">
-        <f>VLOOKUP(B10,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B10,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>#N/A</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -35468,15 +35693,15 @@
         <v>133</v>
       </c>
       <c r="C11" s="31">
-        <f>VLOOKUP(B11,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B11,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2023</v>
       </c>
       <c r="D11" s="2" t="str">
-        <f>VLOOKUP(B11,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B11,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>발주</v>
       </c>
       <c r="E11" s="2">
-        <f>VLOOKUP(B11,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B11,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -35584,15 +35809,15 @@
         <v>91</v>
       </c>
       <c r="C12" s="31">
-        <f>VLOOKUP(B12,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B12,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2022</v>
       </c>
       <c r="D12" s="2" t="str">
-        <f>VLOOKUP(B12,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B12,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E12" s="2">
-        <f>VLOOKUP(B12,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B12,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -35698,15 +35923,15 @@
         <v>14</v>
       </c>
       <c r="C13" s="31" t="str">
-        <f>VLOOKUP(B13,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B13,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D13" s="2" t="str">
-        <f>VLOOKUP(B13,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B13,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E13" s="2">
-        <f>VLOOKUP(B13,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B13,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -35810,15 +36035,15 @@
         <v>134</v>
       </c>
       <c r="C14" s="31">
-        <f>VLOOKUP(B14,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B14,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2023</v>
       </c>
       <c r="D14" s="2" t="str">
-        <f>VLOOKUP(B14,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B14,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E14" s="2">
-        <f>VLOOKUP(B14,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B14,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -35920,15 +36145,15 @@
         <v>201</v>
       </c>
       <c r="C15" s="31">
-        <f>VLOOKUP(B15,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B15,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2024</v>
       </c>
       <c r="D15" s="2" t="str">
-        <f>VLOOKUP(B15,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B15,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E15" s="2">
-        <f>VLOOKUP(B15,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B15,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F15" s="2"/>
@@ -36019,15 +36244,15 @@
         <v>64</v>
       </c>
       <c r="C16" s="31" t="str">
-        <f>VLOOKUP(B16,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B16,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D16" s="2" t="str">
-        <f>VLOOKUP(B16,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B16,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E16" s="2">
-        <f>VLOOKUP(B16,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B16,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -36137,15 +36362,15 @@
         <v>161</v>
       </c>
       <c r="C17" s="31">
-        <f>VLOOKUP(B17,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B17,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2023</v>
       </c>
       <c r="D17" s="2">
-        <f>VLOOKUP(B17,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B17,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>0</v>
       </c>
       <c r="E17" s="2">
-        <f>VLOOKUP(B17,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B17,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -36247,15 +36472,15 @@
         <v>53</v>
       </c>
       <c r="C18" s="31" t="str">
-        <f>VLOOKUP(B18,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B18,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D18" s="2" t="str">
-        <f>VLOOKUP(B18,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B18,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E18" s="2">
-        <f>VLOOKUP(B18,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B18,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -36365,15 +36590,15 @@
         <v>55</v>
       </c>
       <c r="C19" s="31" t="str">
-        <f>VLOOKUP(B19,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B19,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D19" s="2" t="str">
-        <f>VLOOKUP(B19,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B19,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E19" s="2">
-        <f>VLOOKUP(B19,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B19,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -36483,15 +36708,15 @@
         <v>106</v>
       </c>
       <c r="C20" s="31">
-        <f>VLOOKUP(B20,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B20,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2022</v>
       </c>
       <c r="D20" s="2" t="str">
-        <f>VLOOKUP(B20,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B20,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E20" s="2">
-        <f>VLOOKUP(B20,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B20,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -36595,15 +36820,15 @@
         <v>118</v>
       </c>
       <c r="C21" s="31">
-        <f>VLOOKUP(B21,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B21,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2022</v>
       </c>
       <c r="D21" s="2" t="str">
-        <f>VLOOKUP(B21,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B21,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E21" s="2">
-        <f>VLOOKUP(B21,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B21,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -36707,15 +36932,15 @@
         <v>120</v>
       </c>
       <c r="C22" s="31">
-        <f>VLOOKUP(B22,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B22,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2022</v>
       </c>
       <c r="D22" s="2">
-        <f>VLOOKUP(B22,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B22,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>2</v>
       </c>
       <c r="E22" s="2">
-        <f>VLOOKUP(B22,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B22,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F22" s="2"/>
@@ -36806,15 +37031,15 @@
         <v>135</v>
       </c>
       <c r="C23" s="31">
-        <f>VLOOKUP(B23,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B23,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2023</v>
       </c>
       <c r="D23" s="2" t="str">
-        <f>VLOOKUP(B23,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B23,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E23" s="2">
-        <f>VLOOKUP(B23,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B23,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F23" s="2" t="s">
@@ -36922,15 +37147,15 @@
         <v>110</v>
       </c>
       <c r="C24" s="31">
-        <f>VLOOKUP(B24,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B24,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2022</v>
       </c>
       <c r="D24" s="2" t="str">
-        <f>VLOOKUP(B24,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B24,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E24" s="2">
-        <f>VLOOKUP(B24,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B24,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F24" s="2" t="s">
@@ -37034,15 +37259,15 @@
         <v>125</v>
       </c>
       <c r="C25" s="31">
-        <f>VLOOKUP(B25,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B25,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2023</v>
       </c>
       <c r="D25" s="2" t="str">
-        <f>VLOOKUP(B25,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B25,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E25" s="2">
-        <f>VLOOKUP(B25,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B25,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F25" s="2" t="s">
@@ -37148,15 +37373,15 @@
         <v>97</v>
       </c>
       <c r="C26" s="31">
-        <f>VLOOKUP(B26,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B26,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2021</v>
       </c>
       <c r="D26" s="2" t="str">
-        <f>VLOOKUP(B26,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B26,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E26" s="2">
-        <f>VLOOKUP(B26,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B26,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F26" s="2" t="s">
@@ -37264,15 +37489,15 @@
         <v>46</v>
       </c>
       <c r="C27" s="31" t="e">
-        <f>VLOOKUP(B27,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B27,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>#N/A</v>
       </c>
       <c r="D27" s="2" t="e">
-        <f>VLOOKUP(B27,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B27,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>#N/A</v>
       </c>
       <c r="E27" s="2" t="e">
-        <f>VLOOKUP(B27,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B27,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>#N/A</v>
       </c>
       <c r="F27" s="2" t="s">
@@ -37378,15 +37603,15 @@
         <v>75</v>
       </c>
       <c r="C28" s="31" t="str">
-        <f>VLOOKUP(B28,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B28,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D28" s="2" t="str">
-        <f>VLOOKUP(B28,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B28,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E28" s="2">
-        <f>VLOOKUP(B28,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B28,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F28" s="2" t="s">
@@ -37492,15 +37717,15 @@
         <v>178</v>
       </c>
       <c r="C29" s="31">
-        <f>VLOOKUP(B29,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B29,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2023</v>
       </c>
       <c r="D29" s="2" t="str">
-        <f>VLOOKUP(B29,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B29,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E29" s="2">
-        <f>VLOOKUP(B29,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B29,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F29" s="2" t="s">
@@ -37602,15 +37827,15 @@
         <v>7</v>
       </c>
       <c r="C30" s="31" t="str">
-        <f>VLOOKUP(B30,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B30,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D30" s="2" t="str">
-        <f>VLOOKUP(B30,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B30,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E30" s="2">
-        <f>VLOOKUP(B30,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B30,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F30" s="2" t="s">
@@ -37716,15 +37941,15 @@
         <v>5</v>
       </c>
       <c r="C31" s="31" t="str">
-        <f>VLOOKUP(B31,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B31,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D31" s="2" t="str">
-        <f>VLOOKUP(B31,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B31,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E31" s="2">
-        <f>VLOOKUP(B31,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B31,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F31" s="2" t="s">
@@ -37826,15 +38051,15 @@
         <v>123</v>
       </c>
       <c r="C32" s="31" t="e">
-        <f>VLOOKUP(B32,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B32,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>#N/A</v>
       </c>
       <c r="D32" s="2" t="e">
-        <f>VLOOKUP(B32,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B32,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>#N/A</v>
       </c>
       <c r="E32" s="2" t="e">
-        <f>VLOOKUP(B32,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B32,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>#N/A</v>
       </c>
       <c r="F32" s="2" t="s">
@@ -37942,15 +38167,15 @@
         <v>121</v>
       </c>
       <c r="C33" s="31">
-        <f>VLOOKUP(B33,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B33,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2022</v>
       </c>
       <c r="D33" s="2">
-        <f>VLOOKUP(B33,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B33,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>0</v>
       </c>
       <c r="E33" s="2">
-        <f>VLOOKUP(B33,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B33,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F33" s="2" t="s">
@@ -38052,15 +38277,15 @@
         <v>136</v>
       </c>
       <c r="C34" s="31">
-        <f>VLOOKUP(B34,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B34,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2023</v>
       </c>
       <c r="D34" s="2" t="str">
-        <f>VLOOKUP(B34,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B34,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E34" s="2">
-        <f>VLOOKUP(B34,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B34,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F34" s="2" t="s">
@@ -38162,15 +38387,15 @@
         <v>124</v>
       </c>
       <c r="C35" s="31">
-        <f>VLOOKUP(B35,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B35,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>2023</v>
       </c>
       <c r="D35" s="2" t="str">
-        <f>VLOOKUP(B35,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B35,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E35" s="2">
-        <f>VLOOKUP(B35,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B35,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F35" s="2" t="s">
@@ -38280,15 +38505,15 @@
         <v>32</v>
       </c>
       <c r="C36" s="31" t="str">
-        <f>VLOOKUP(B36,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B36,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D36" s="2" t="str">
-        <f>VLOOKUP(B36,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B36,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E36" s="2">
-        <f>VLOOKUP(B36,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B36,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F36" s="2" t="s">
@@ -38394,15 +38619,15 @@
         <v>42</v>
       </c>
       <c r="C37" s="31" t="str">
-        <f>VLOOKUP(B37,종합Sheet!$B$4:$F$135,2,0)</f>
+        <f>VLOOKUP(B37,종합Sheet!$B$4:$F$136,2,0)</f>
         <v>Origin</v>
       </c>
       <c r="D37" s="2" t="str">
-        <f>VLOOKUP(B37,종합Sheet!$B$4:$F$135,3,0)</f>
+        <f>VLOOKUP(B37,종합Sheet!$B$4:$F$136,3,0)</f>
         <v>지급</v>
       </c>
       <c r="E37" s="2">
-        <f>VLOOKUP(B37,종합Sheet!$B$4:$F$135,4,0)</f>
+        <f>VLOOKUP(B37,종합Sheet!$B$4:$F$136,4,0)</f>
         <v>0</v>
       </c>
       <c r="F37" s="2" t="s">

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcabf36b0134af82/바탕 화면/김인혁_청년축구단/1. 출석부/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1359" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B81C2ABA-216E-4B80-B9A4-6C2A98D10921}"/>
+  <xr:revisionPtr revIDLastSave="1382" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0A07B7-C4E2-4499-82D0-700F96069048}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="종합Sheet" sheetId="1" r:id="rId1"/>
@@ -2530,10 +2530,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2542,20 +2542,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2567,6 +2567,33 @@
       <font>
         <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -2627,33 +2654,6 @@
       <font>
         <color rgb="FF9C0006"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -3194,7 +3194,7 @@
     <row r="1" spans="1:82" x14ac:dyDescent="0.25">
       <c r="D1" s="53">
         <f>COUNTIF(D4:D157,"발주")</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I1" s="18" t="s">
         <v>87</v>
@@ -3353,7 +3353,7 @@
     <row r="2" spans="1:82" x14ac:dyDescent="0.25">
       <c r="D2" s="53">
         <f>COUNTIF(D4:D157,"지급")</f>
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E2" s="53">
         <f>COUNTIF(E4:E140,"지급")</f>
@@ -3754,9 +3754,9 @@
       <c r="F4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="2" t="e">
-        <f t="shared" ref="G4:G35" si="2">RANK(H4,$H$4:$H$122,0)</f>
-        <v>#REF!</v>
+      <c r="G4" s="2">
+        <f>RANK(H4,$H$4:$H$122,0)</f>
+        <v>4</v>
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
@@ -3905,9 +3905,9 @@
       <c r="F5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="2" t="e">
-        <f t="shared" si="2"/>
-        <v>#REF!</v>
+      <c r="G5" s="2">
+        <f t="shared" ref="G4:G35" si="2">RANK(H5,$H$4:$H$122,0)</f>
+        <v>53</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
@@ -4020,9 +4020,9 @@
       <c r="F6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="2" t="e">
+      <c r="G6" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="H6" s="6">
         <f>I6+개인기록Sheet!C6</f>
@@ -4117,16 +4117,16 @@
         <v>318</v>
       </c>
       <c r="D7" s="54">
-        <f>COUNTA(AF7:AS7)</f>
+        <f>COUNTA(AF7:AU7)</f>
         <v>0</v>
       </c>
       <c r="E7" s="54"/>
       <c r="F7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="2" t="e">
+      <c r="G7" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="H7" s="6">
         <f>I7+개인기록Sheet!C7</f>
@@ -4221,15 +4221,15 @@
         <v>318</v>
       </c>
       <c r="D8" s="54" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="E8" s="54"/>
       <c r="F8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="2" t="e">
+      <c r="G8" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="H8" s="6">
         <f>I8+개인기록Sheet!C8</f>
@@ -4330,9 +4330,9 @@
       <c r="F9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="2" t="e">
+      <c r="G9" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>43</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
@@ -4449,9 +4449,9 @@
       <c r="F10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="2" t="e">
+      <c r="G10" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>13</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
@@ -4586,9 +4586,9 @@
       <c r="F11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="2" t="e">
+      <c r="G11" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>14</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
@@ -4713,16 +4713,16 @@
         <v>2025</v>
       </c>
       <c r="D12" s="54">
-        <f t="shared" ref="D12:D15" si="4">COUNTA(AF12:AS12)</f>
+        <f t="shared" ref="D12:D15" si="4">COUNTA(AF12:AU12)</f>
         <v>0</v>
       </c>
       <c r="E12" s="54"/>
       <c r="F12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="2" t="e">
+      <c r="G12" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>86</v>
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C12</f>
@@ -4826,9 +4826,9 @@
       <c r="F13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="2" t="e">
+      <c r="G13" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="H13" s="6">
         <f>I13+개인기록Sheet!C13</f>
@@ -4930,9 +4930,9 @@
       <c r="F14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="2" t="e">
+      <c r="G14" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="H14" s="6">
         <f>I14+개인기록Sheet!C14</f>
@@ -5034,9 +5034,9 @@
       <c r="F15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="2" t="e">
+      <c r="G15" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>64</v>
       </c>
       <c r="H15" s="6">
         <f>I15+개인기록Sheet!C15</f>
@@ -5145,9 +5145,9 @@
       <c r="F16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="2" t="e">
+      <c r="G16" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>33</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
@@ -5266,9 +5266,9 @@
       <c r="F17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="2" t="e">
+      <c r="G17" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>15</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
@@ -5393,15 +5393,15 @@
         <v>2023</v>
       </c>
       <c r="D18" s="54" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="E18" s="54"/>
       <c r="F18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G18" s="2" t="e">
+      <c r="G18" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C18</f>
@@ -5496,16 +5496,16 @@
         <v>2026</v>
       </c>
       <c r="D19" s="54">
-        <f>COUNTA(AF19:AS19)</f>
+        <f>COUNTA(AF19:AU19)</f>
         <v>1</v>
       </c>
       <c r="E19" s="54"/>
       <c r="F19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="2" t="e">
+      <c r="G19" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>86</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C19</f>
@@ -5608,13 +5608,13 @@
       <c r="F20" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="2" t="e">
+      <c r="G20" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>60</v>
       </c>
       <c r="H20" s="6">
-        <f>I20+개인기록Sheet!C22</f>
-        <v>5</v>
+        <f>I20+개인기록Sheet!C20</f>
+        <v>5.4</v>
       </c>
       <c r="I20" s="6">
         <f t="shared" si="3"/>
@@ -5715,19 +5715,19 @@
         <v>2024</v>
       </c>
       <c r="D21" s="54">
-        <f t="shared" ref="D21:D22" si="5">COUNTA(AF21:AS21)</f>
+        <f t="shared" ref="D21:D22" si="5">COUNTA(AF21:AU21)</f>
         <v>0</v>
       </c>
       <c r="E21" s="54"/>
       <c r="F21" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G21" s="2" t="e">
+      <c r="G21" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="H21" s="6">
-        <f>I21+개인기록Sheet!C23</f>
+        <f>I21+개인기록Sheet!C21</f>
         <v>0</v>
       </c>
       <c r="I21" s="6">
@@ -5826,13 +5826,13 @@
       <c r="F22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="2" t="e">
+      <c r="G22" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="H22" s="6">
-        <f>I22+개인기록Sheet!C24</f>
-        <v>1.1000000000000001</v>
+        <f>I22+개인기록Sheet!C22</f>
+        <v>0</v>
       </c>
       <c r="I22" s="6">
         <f t="shared" si="3"/>
@@ -5929,13 +5929,13 @@
       <c r="F23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G23" s="2" t="e">
+      <c r="G23" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>86</v>
       </c>
       <c r="H23" s="6">
-        <f>I23+개인기록Sheet!C25</f>
-        <v>3.9000000000000004</v>
+        <f>I23+개인기록Sheet!C23</f>
+        <v>1</v>
       </c>
       <c r="I23" s="6">
         <f t="shared" si="3"/>
@@ -6034,13 +6034,13 @@
       <c r="F24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="2" t="e">
+      <c r="G24" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>46</v>
       </c>
       <c r="H24" s="6">
-        <f>I24+개인기록Sheet!C26</f>
-        <v>17.7</v>
+        <f>I24+개인기록Sheet!C24</f>
+        <v>8.1</v>
       </c>
       <c r="I24" s="6">
         <f t="shared" si="3"/>
@@ -6151,13 +6151,13 @@
       <c r="F25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G25" s="2" t="e">
+      <c r="G25" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>24</v>
       </c>
       <c r="H25" s="6">
-        <f>I25+개인기록Sheet!C27</f>
-        <v>15.1</v>
+        <f>I25+개인기록Sheet!C25</f>
+        <v>14.9</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="3"/>
@@ -6278,13 +6278,13 @@
       <c r="F26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="2" t="e">
+      <c r="G26" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>1</v>
       </c>
       <c r="H26" s="6">
-        <f>I26+개인기록Sheet!C28</f>
-        <v>26</v>
+        <f>I26+개인기록Sheet!C26</f>
+        <v>36.700000000000003</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="3"/>
@@ -6433,13 +6433,13 @@
       <c r="F27" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G27" s="2" t="e">
+      <c r="G27" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>31</v>
       </c>
       <c r="H27" s="6">
-        <f>I27+개인기록Sheet!C29</f>
-        <v>10</v>
+        <f>I27+개인기록Sheet!C27</f>
+        <v>13.1</v>
       </c>
       <c r="I27" s="6">
         <f t="shared" si="3"/>
@@ -6550,20 +6550,20 @@
         <v>2023</v>
       </c>
       <c r="D28" s="54">
-        <f>COUNTA(AF28:AS28)</f>
+        <f>COUNTA(AF28:AU28)</f>
         <v>0</v>
       </c>
       <c r="E28" s="54"/>
       <c r="F28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G28" s="2" t="e">
+      <c r="G28" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="H28" s="6">
-        <f>I28+개인기록Sheet!C30</f>
-        <v>4.5999999999999996</v>
+        <f>I28+개인기록Sheet!C28</f>
+        <v>0</v>
       </c>
       <c r="I28" s="6">
         <f t="shared" si="3"/>
@@ -6660,13 +6660,13 @@
       <c r="F29" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G29" s="2" t="e">
+      <c r="G29" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>74</v>
       </c>
       <c r="H29" s="6">
-        <f>I29+개인기록Sheet!C31</f>
-        <v>8.1999999999999993</v>
+        <f>I29+개인기록Sheet!C29</f>
+        <v>3</v>
       </c>
       <c r="I29" s="6">
         <f t="shared" si="3"/>
@@ -6769,13 +6769,13 @@
       <c r="F30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="2" t="e">
+      <c r="G30" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>16</v>
       </c>
       <c r="H30" s="6">
-        <f>I30+개인기록Sheet!C32</f>
-        <v>14.4</v>
+        <f>I30+개인기록Sheet!C30</f>
+        <v>18.600000000000001</v>
       </c>
       <c r="I30" s="6">
         <f t="shared" si="3"/>
@@ -6900,13 +6900,13 @@
       <c r="F31" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G31" s="2" t="e">
+      <c r="G31" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>2</v>
       </c>
       <c r="H31" s="6">
-        <f>I31+개인기록Sheet!C33</f>
-        <v>29.4</v>
+        <f>I31+개인기록Sheet!C31</f>
+        <v>30.2</v>
       </c>
       <c r="I31" s="6">
         <f t="shared" si="3"/>
@@ -7053,13 +7053,13 @@
       <c r="F32" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G32" s="2" t="e">
+      <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>38</v>
       </c>
       <c r="H32" s="6">
-        <f>I32+개인기록Sheet!C34</f>
-        <v>10</v>
+        <f>I32+개인기록Sheet!C32</f>
+        <v>10.4</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="3"/>
@@ -7176,13 +7176,13 @@
       <c r="F33" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G33" s="2" t="e">
+      <c r="G33" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>8</v>
       </c>
       <c r="H33" s="6">
-        <f>I33+개인기록Sheet!C35</f>
-        <v>24.8</v>
+        <f>I33+개인기록Sheet!C33</f>
+        <v>22.4</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="3"/>
@@ -7309,19 +7309,19 @@
         <v>2025</v>
       </c>
       <c r="D34" s="54">
-        <f t="shared" ref="D34" si="6">COUNTA(AF34:AS34)</f>
+        <f>COUNTA(AF34:AU34)</f>
         <v>0</v>
       </c>
       <c r="E34" s="54"/>
       <c r="F34" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G34" s="2" t="e">
+      <c r="G34" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="H34" s="6">
-        <f>I34+개인기록Sheet!C37</f>
+        <f>I34+개인기록Sheet!C34</f>
         <v>0</v>
       </c>
       <c r="I34" s="6">
@@ -7419,13 +7419,13 @@
       <c r="F35" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G35" s="2" t="e">
+      <c r="G35" s="2">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>5</v>
       </c>
       <c r="H35" s="6">
-        <f>I35+개인기록Sheet!C38</f>
-        <v>19.399999999999999</v>
+        <f>I35+개인기록Sheet!C35</f>
+        <v>25.8</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="3"/>
@@ -7560,13 +7560,13 @@
       <c r="F36" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G36" s="2" t="e">
-        <f t="shared" ref="G36:G67" si="7">RANK(H36,$H$4:$H$122,0)</f>
-        <v>#REF!</v>
+      <c r="G36" s="2">
+        <f t="shared" ref="G36:G67" si="6">RANK(H36,$H$4:$H$122,0)</f>
+        <v>49</v>
       </c>
       <c r="H36" s="6">
-        <f>I36+개인기록Sheet!C39</f>
-        <v>7</v>
+        <f>I36+개인기록Sheet!C36</f>
+        <v>7.6</v>
       </c>
       <c r="I36" s="6">
         <f t="shared" si="3"/>
@@ -7671,19 +7671,19 @@
         <v>2025</v>
       </c>
       <c r="D37" s="54">
-        <f>COUNTA(AF37:AS37)</f>
+        <f>COUNTA(AF37:AU37)</f>
         <v>0</v>
       </c>
       <c r="E37" s="54"/>
       <c r="F37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G37" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G37" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H37" s="6">
-        <f>I37+개인기록Sheet!C40</f>
+        <f>I37+개인기록Sheet!C37</f>
         <v>0</v>
       </c>
       <c r="I37" s="6">
@@ -7781,12 +7781,12 @@
       <c r="F38" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G38" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G38" s="2">
+        <f t="shared" si="6"/>
+        <v>77</v>
       </c>
       <c r="H38" s="6">
-        <f>I38+개인기록Sheet!C41</f>
+        <f>I38+개인기록Sheet!C38</f>
         <v>2.4</v>
       </c>
       <c r="I38" s="6">
@@ -7882,20 +7882,20 @@
         <v>318</v>
       </c>
       <c r="D39" s="54">
-        <f t="shared" ref="D39:D40" si="8">COUNTA(AF39:AS39)</f>
+        <f t="shared" ref="D39:D40" si="7">COUNTA(AF39:AU39)</f>
         <v>0</v>
       </c>
       <c r="E39" s="54"/>
       <c r="F39" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G39" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G39" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H39" s="6">
-        <f>I39+개인기록Sheet!C42</f>
-        <v>4.6000000000000005</v>
+        <f>I39+개인기록Sheet!C39</f>
+        <v>0</v>
       </c>
       <c r="I39" s="6">
         <f t="shared" si="3"/>
@@ -7986,20 +7986,20 @@
         <v>2024</v>
       </c>
       <c r="D40" s="54">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E40" s="54"/>
       <c r="F40" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G40" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G40" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H40" s="6">
-        <f>I40+개인기록Sheet!C43</f>
-        <v>0.5</v>
+        <f>I40+개인기록Sheet!C40</f>
+        <v>0</v>
       </c>
       <c r="I40" s="6">
         <f t="shared" si="3"/>
@@ -8096,13 +8096,13 @@
       <c r="F41" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G41" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G41" s="2">
+        <f t="shared" si="6"/>
+        <v>77</v>
       </c>
       <c r="H41" s="6">
-        <f>I41+개인기록Sheet!C44</f>
-        <v>4.4000000000000004</v>
+        <f>I41+개인기록Sheet!C41</f>
+        <v>2.4</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="3"/>
@@ -8203,13 +8203,13 @@
       <c r="F42" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G42" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G42" s="2">
+        <f t="shared" si="6"/>
+        <v>6</v>
       </c>
       <c r="H42" s="6">
-        <f>I42+개인기록Sheet!C45</f>
-        <v>21</v>
+        <f>I42+개인기록Sheet!C42</f>
+        <v>25.6</v>
       </c>
       <c r="I42" s="6">
         <f t="shared" si="3"/>
@@ -8342,19 +8342,19 @@
         <v>2026</v>
       </c>
       <c r="D43" s="54" t="s">
-        <v>349</v>
+        <v>226</v>
       </c>
       <c r="E43" s="54"/>
       <c r="F43" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G43" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G43" s="2">
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="H43" s="6">
-        <f>I43+개인기록Sheet!C46</f>
-        <v>12.4</v>
+        <f>I43+개인기록Sheet!C43</f>
+        <v>9.5</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="3"/>
@@ -8469,13 +8469,13 @@
       <c r="F44" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G44" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G44" s="2">
+        <f t="shared" si="6"/>
+        <v>45</v>
       </c>
       <c r="H44" s="6">
-        <f>I44+개인기록Sheet!C47</f>
-        <v>6</v>
+        <f>I44+개인기록Sheet!C44</f>
+        <v>8.4</v>
       </c>
       <c r="I44" s="6">
         <f t="shared" si="3"/>
@@ -8578,17 +8578,17 @@
         <v>2026</v>
       </c>
       <c r="D45" s="54">
-        <f>COUNTA(AF45:AS45)</f>
+        <f>COUNTA(AF45:AU45)</f>
         <v>0</v>
       </c>
       <c r="E45" s="54"/>
       <c r="F45" s="60"/>
-      <c r="G45" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G45" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H45" s="6">
-        <f>I45+개인기록Sheet!C48</f>
+        <f>I45+개인기록Sheet!C45</f>
         <v>0</v>
       </c>
       <c r="I45" s="6">
@@ -8686,13 +8686,13 @@
       <c r="F46" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G46" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G46" s="2">
+        <f t="shared" si="6"/>
+        <v>9</v>
       </c>
       <c r="H46" s="6">
-        <f>I46+개인기록Sheet!C49</f>
-        <v>18</v>
+        <f>I46+개인기록Sheet!C46</f>
+        <v>21.4</v>
       </c>
       <c r="I46" s="6">
         <f t="shared" si="3"/>
@@ -8819,20 +8819,20 @@
         <v>2022</v>
       </c>
       <c r="D47" s="54">
-        <f t="shared" ref="D47:D49" si="9">COUNTA(AF47:AS47)</f>
+        <f t="shared" ref="D47:D49" si="8">COUNTA(AF47:AU47)</f>
         <v>2</v>
       </c>
       <c r="E47" s="54"/>
       <c r="F47" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G47" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G47" s="2">
+        <f t="shared" si="6"/>
+        <v>80</v>
       </c>
       <c r="H47" s="6">
-        <f>I47+개인기록Sheet!C50</f>
-        <v>4.4000000000000004</v>
+        <f>I47+개인기록Sheet!C47</f>
+        <v>2</v>
       </c>
       <c r="I47" s="6">
         <f t="shared" si="3"/>
@@ -8927,19 +8927,19 @@
         <v>2025</v>
       </c>
       <c r="D48" s="54">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E48" s="54"/>
       <c r="F48" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G48" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G48" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H48" s="6">
-        <f>I48+개인기록Sheet!C51</f>
+        <f>I48+개인기록Sheet!C48</f>
         <v>0</v>
       </c>
       <c r="I48" s="6">
@@ -9031,20 +9031,20 @@
         <v>2022</v>
       </c>
       <c r="D49" s="54">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E49" s="54"/>
       <c r="F49" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G49" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G49" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H49" s="6">
-        <f>I49+개인기록Sheet!C52</f>
-        <v>0.4</v>
+        <f>I49+개인기록Sheet!C49</f>
+        <v>0</v>
       </c>
       <c r="I49" s="6">
         <f t="shared" si="3"/>
@@ -9141,13 +9141,13 @@
       <c r="F50" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G50" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G50" s="2">
+        <f t="shared" si="6"/>
+        <v>18</v>
       </c>
       <c r="H50" s="6">
-        <f>I50+개인기록Sheet!C53</f>
-        <v>15.4</v>
+        <f>I50+개인기록Sheet!C50</f>
+        <v>17.399999999999999</v>
       </c>
       <c r="I50" s="6">
         <f t="shared" si="3"/>
@@ -9268,19 +9268,19 @@
         <v>2023</v>
       </c>
       <c r="D51" s="54">
-        <f t="shared" ref="D51:D55" si="10">COUNTA(AF51:AS51)</f>
+        <f t="shared" ref="D51:D55" si="9">COUNTA(AF51:AU51)</f>
         <v>0</v>
       </c>
       <c r="E51" s="54"/>
       <c r="F51" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G51" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G51" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H51" s="6">
-        <f>I51+개인기록Sheet!C54</f>
+        <f>I51+개인기록Sheet!C51</f>
         <v>0</v>
       </c>
       <c r="I51" s="6">
@@ -9372,20 +9372,20 @@
         <v>2026</v>
       </c>
       <c r="D52" s="54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E52" s="54"/>
       <c r="F52" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G52" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G52" s="2">
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="H52" s="6">
-        <f>I52+개인기록Sheet!C55</f>
-        <v>5</v>
+        <f>I52+개인기록Sheet!C52</f>
+        <v>5.4</v>
       </c>
       <c r="I52" s="6">
         <f t="shared" si="3"/>
@@ -9486,20 +9486,20 @@
         <v>2026</v>
       </c>
       <c r="D53" s="54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E53" s="54"/>
       <c r="F53" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G53" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G53" s="2">
+        <f t="shared" si="6"/>
+        <v>60</v>
       </c>
       <c r="H53" s="6">
-        <f>I53+개인기록Sheet!C56</f>
-        <v>8.6</v>
+        <f>I53+개인기록Sheet!C53</f>
+        <v>5.4</v>
       </c>
       <c r="I53" s="6">
         <f t="shared" si="3"/>
@@ -9600,20 +9600,20 @@
         <v>2023</v>
       </c>
       <c r="D54" s="54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E54" s="54"/>
       <c r="F54" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G54" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G54" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H54" s="6">
-        <f>I54+개인기록Sheet!C57</f>
-        <v>0.6</v>
+        <f>I54+개인기록Sheet!C54</f>
+        <v>0</v>
       </c>
       <c r="I54" s="6">
         <f t="shared" si="3"/>
@@ -9704,20 +9704,20 @@
         <v>2022</v>
       </c>
       <c r="D55" s="54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E55" s="54"/>
       <c r="F55" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G55" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H55" s="6">
-        <f>I55+개인기록Sheet!C58</f>
-        <v>2.1</v>
+        <f>I55+개인기록Sheet!C55</f>
+        <v>0</v>
       </c>
       <c r="I55" s="6">
         <f t="shared" si="3"/>
@@ -9814,13 +9814,13 @@
       <c r="F56" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G56" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G56" s="2">
+        <f t="shared" si="6"/>
+        <v>7</v>
       </c>
       <c r="H56" s="6">
-        <f>I56+개인기록Sheet!C59</f>
-        <v>20</v>
+        <f>I56+개인기록Sheet!C56</f>
+        <v>23.6</v>
       </c>
       <c r="I56" s="6">
         <f t="shared" si="3"/>
@@ -9957,12 +9957,12 @@
       <c r="F57" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G57" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G57" s="2">
+        <f t="shared" si="6"/>
+        <v>69</v>
       </c>
       <c r="H57" s="6">
-        <f>I57+개인기록Sheet!C60</f>
+        <f>I57+개인기록Sheet!C57</f>
         <v>3.6</v>
       </c>
       <c r="I57" s="6">
@@ -10066,13 +10066,13 @@
       <c r="F58" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G58" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G58" s="2">
+        <f t="shared" si="6"/>
+        <v>37</v>
       </c>
       <c r="H58" s="6">
-        <f>I58+개인기록Sheet!C61</f>
-        <v>11</v>
+        <f>I58+개인기록Sheet!C58</f>
+        <v>11.1</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="3"/>
@@ -10181,20 +10181,20 @@
         <v>2024</v>
       </c>
       <c r="D59" s="54">
-        <f>COUNTA(AF59:AS59)</f>
+        <f>COUNTA(AF59:AU59)</f>
         <v>0</v>
       </c>
       <c r="E59" s="54"/>
       <c r="F59" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G59" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G59" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H59" s="6">
-        <f>I59+개인기록Sheet!C62</f>
-        <v>3.7</v>
+        <f>I59+개인기록Sheet!C59</f>
+        <v>0</v>
       </c>
       <c r="I59" s="6">
         <f t="shared" si="3"/>
@@ -10291,13 +10291,13 @@
       <c r="F60" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G60" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G60" s="2">
+        <f t="shared" si="6"/>
+        <v>69</v>
       </c>
       <c r="H60" s="6">
-        <f>I60+개인기록Sheet!C63</f>
-        <v>3.3</v>
+        <f>I60+개인기록Sheet!C60</f>
+        <v>3.6</v>
       </c>
       <c r="I60" s="6">
         <f t="shared" si="3"/>
@@ -10400,13 +10400,13 @@
       <c r="F61" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G61" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G61" s="2">
+        <f t="shared" si="6"/>
+        <v>34</v>
       </c>
       <c r="H61" s="6">
-        <f>I61+개인기록Sheet!C64</f>
-        <v>12.9</v>
+        <f>I61+개인기록Sheet!C61</f>
+        <v>12</v>
       </c>
       <c r="I61" s="6">
         <f t="shared" si="3"/>
@@ -10517,19 +10517,19 @@
         <v>2026</v>
       </c>
       <c r="D62" s="54" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="E62" s="54"/>
       <c r="F62" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G62" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G62" s="2">
+        <f t="shared" si="6"/>
+        <v>32</v>
       </c>
       <c r="H62" s="6">
-        <f>I62+개인기록Sheet!C65</f>
-        <v>9</v>
+        <f>I62+개인기록Sheet!C62</f>
+        <v>12.7</v>
       </c>
       <c r="I62" s="6">
         <f t="shared" si="3"/>
@@ -10638,20 +10638,20 @@
         <v>2026</v>
       </c>
       <c r="D63" s="54">
-        <f>COUNTA(AF63:AS63)</f>
+        <f>COUNTA(AF63:AU63)</f>
         <v>0</v>
       </c>
       <c r="E63" s="54"/>
       <c r="F63" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G63" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G63" s="2">
+        <f t="shared" si="6"/>
+        <v>67</v>
       </c>
       <c r="H63" s="6">
-        <f>I63+개인기록Sheet!C66</f>
-        <v>4</v>
+        <f>I63+개인기록Sheet!C63</f>
+        <v>4.3</v>
       </c>
       <c r="I63" s="6">
         <f t="shared" si="3"/>
@@ -10756,13 +10756,13 @@
       <c r="F64" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G64" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G64" s="2">
+        <f t="shared" si="6"/>
+        <v>35</v>
       </c>
       <c r="H64" s="6">
-        <f>I64+개인기록Sheet!C67</f>
-        <v>9</v>
+        <f>I64+개인기록Sheet!C64</f>
+        <v>11.9</v>
       </c>
       <c r="I64" s="6">
         <f t="shared" si="3"/>
@@ -10871,20 +10871,20 @@
         <v>318</v>
       </c>
       <c r="D65" s="54">
-        <f t="shared" ref="D65:D67" si="11">COUNTA(AF65:AS65)</f>
+        <f t="shared" ref="D65:D67" si="10">COUNTA(AF65:AU65)</f>
         <v>0</v>
       </c>
       <c r="E65" s="54"/>
       <c r="F65" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G65" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G65" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H65" s="6">
-        <f>I65+개인기록Sheet!C68</f>
-        <v>5</v>
+        <f>I65+개인기록Sheet!C65</f>
+        <v>0</v>
       </c>
       <c r="I65" s="6">
         <f t="shared" si="3"/>
@@ -10973,21 +10973,21 @@
       </c>
       <c r="C66" s="57"/>
       <c r="D66" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E66" s="54"/>
       <c r="F66" s="60"/>
-      <c r="G66" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G66" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H66" s="6">
-        <f>I66+개인기록Sheet!C69</f>
-        <v>0.4</v>
+        <f>I66+개인기록Sheet!C66</f>
+        <v>0</v>
       </c>
       <c r="I66" s="6">
-        <f t="shared" ref="I66:I122" si="12">(COUNTIF(J66:CD66,"출전")*1)</f>
+        <f t="shared" ref="I66:I122" si="11">(COUNTIF(J66:CD66,"출전")*1)</f>
         <v>0</v>
       </c>
       <c r="J66" s="2"/>
@@ -11075,23 +11075,23 @@
         <v>2025</v>
       </c>
       <c r="D67" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E67" s="54"/>
       <c r="F67" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G67" s="2" t="e">
-        <f t="shared" si="7"/>
-        <v>#REF!</v>
+      <c r="G67" s="2">
+        <f t="shared" si="6"/>
+        <v>92</v>
       </c>
       <c r="H67" s="6">
-        <f>I67+개인기록Sheet!C70</f>
-        <v>0.8</v>
+        <f>I67+개인기록Sheet!C67</f>
+        <v>0</v>
       </c>
       <c r="I67" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J67" s="2"/>
@@ -11185,16 +11185,16 @@
       <c r="F68" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G68" s="2" t="e">
-        <f t="shared" ref="G68:G99" si="13">RANK(H68,$H$4:$H$122,0)</f>
-        <v>#REF!</v>
+      <c r="G68" s="2">
+        <f t="shared" ref="G68:G99" si="12">RANK(H68,$H$4:$H$122,0)</f>
+        <v>11</v>
       </c>
       <c r="H68" s="6">
-        <f>I68+개인기록Sheet!C71</f>
-        <v>17.5</v>
+        <f>I68+개인기록Sheet!C68</f>
+        <v>21</v>
       </c>
       <c r="I68" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="J68" s="2"/>
@@ -11314,23 +11314,23 @@
         <v>2026</v>
       </c>
       <c r="D69" s="54">
-        <f>COUNTA(AF69:AS69)</f>
+        <f>COUNTA(AF69:AU69)</f>
         <v>0</v>
       </c>
       <c r="E69" s="54"/>
       <c r="F69" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G69" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G69" s="2">
+        <f t="shared" si="12"/>
+        <v>65</v>
       </c>
       <c r="H69" s="6">
-        <f>I69+개인기록Sheet!C72</f>
-        <v>4</v>
+        <f>I69+개인기록Sheet!C69</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I69" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="J69" s="2"/>
@@ -11432,16 +11432,16 @@
       <c r="F70" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G70" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G70" s="2">
+        <f t="shared" si="12"/>
+        <v>54</v>
       </c>
       <c r="H70" s="6">
-        <f>I70+개인기록Sheet!C73</f>
-        <v>7.2</v>
+        <f>I70+개인기록Sheet!C70</f>
+        <v>6.8</v>
       </c>
       <c r="I70" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="J70" s="2"/>
@@ -11547,16 +11547,16 @@
       <c r="F71" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G71" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G71" s="2">
+        <f t="shared" si="12"/>
+        <v>40</v>
       </c>
       <c r="H71" s="6">
-        <f>I71+개인기록Sheet!C74</f>
-        <v>9.6</v>
+        <f>I71+개인기록Sheet!C71</f>
+        <v>9.5</v>
       </c>
       <c r="I71" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="J71" s="2"/>
@@ -11660,23 +11660,23 @@
         <v>318</v>
       </c>
       <c r="D72" s="54">
-        <f>COUNTA(AF72:AS72)</f>
+        <f>COUNTA(AF72:AU72)</f>
         <v>0</v>
       </c>
       <c r="E72" s="54"/>
       <c r="F72" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G72" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G72" s="2">
+        <f t="shared" si="12"/>
+        <v>92</v>
       </c>
       <c r="H72" s="6">
-        <f>I72+개인기록Sheet!C75</f>
-        <v>1.1000000000000001</v>
+        <f>I72+개인기록Sheet!C72</f>
+        <v>0</v>
       </c>
       <c r="I72" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J72" s="2"/>
@@ -11770,16 +11770,16 @@
       <c r="F73" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G73" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G73" s="2">
+        <f t="shared" si="12"/>
+        <v>57</v>
       </c>
       <c r="H73" s="6">
-        <f>I73+개인기록Sheet!C76</f>
-        <v>5.6</v>
+        <f>I73+개인기록Sheet!C73</f>
+        <v>6.2</v>
       </c>
       <c r="I73" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="J73" s="2"/>
@@ -11883,16 +11883,16 @@
       <c r="F74" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G74" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G74" s="2">
+        <f t="shared" si="12"/>
+        <v>55</v>
       </c>
       <c r="H74" s="6">
-        <f>I74+개인기록Sheet!C77</f>
-        <v>5.6</v>
+        <f>I74+개인기록Sheet!C74</f>
+        <v>6.6</v>
       </c>
       <c r="I74" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="J74" s="2"/>
@@ -11990,22 +11990,22 @@
         <v>2026</v>
       </c>
       <c r="D75" s="54" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="E75" s="54"/>
       <c r="F75" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G75" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G75" s="2">
+        <f t="shared" si="12"/>
+        <v>46</v>
       </c>
       <c r="H75" s="6">
-        <f>I75+개인기록Sheet!C78</f>
-        <v>8.1999999999999993</v>
+        <f>I75+개인기록Sheet!C75</f>
+        <v>8.1</v>
       </c>
       <c r="I75" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="J75" s="2"/>
@@ -12107,23 +12107,23 @@
         <v>2025</v>
       </c>
       <c r="D76" s="54">
-        <f t="shared" ref="D76:D77" si="14">COUNTA(AF76:AS76)</f>
+        <f t="shared" ref="D76:D77" si="13">COUNTA(AF76:AU76)</f>
         <v>1</v>
       </c>
       <c r="E76" s="54"/>
       <c r="F76" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G76" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G76" s="2">
+        <f t="shared" si="12"/>
+        <v>82</v>
       </c>
       <c r="H76" s="6">
-        <f>I76+개인기록Sheet!C79</f>
-        <v>2.2000000000000002</v>
+        <f>I76+개인기록Sheet!C76</f>
+        <v>1.6</v>
       </c>
       <c r="I76" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J76" s="2"/>
@@ -12213,23 +12213,23 @@
         <v>2023</v>
       </c>
       <c r="D77" s="54">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E77" s="54"/>
       <c r="F77" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G77" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G77" s="2">
+        <f t="shared" si="12"/>
+        <v>75</v>
       </c>
       <c r="H77" s="6">
-        <f>I77+개인기록Sheet!C80</f>
-        <v>6</v>
+        <f>I77+개인기록Sheet!C77</f>
+        <v>2.6</v>
       </c>
       <c r="I77" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="J77" s="2"/>
@@ -12327,16 +12327,16 @@
       <c r="F78" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G78" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G78" s="2">
+        <f t="shared" si="12"/>
+        <v>39</v>
       </c>
       <c r="H78" s="6">
-        <f>I78+개인기록Sheet!C81</f>
-        <v>11.6</v>
+        <f>I78+개인기록Sheet!C78</f>
+        <v>10.199999999999999</v>
       </c>
       <c r="I78" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="J78" s="2"/>
@@ -12448,16 +12448,16 @@
       <c r="F79" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G79" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G79" s="2">
+        <f t="shared" si="12"/>
+        <v>52</v>
       </c>
       <c r="H79" s="6">
-        <f>I79+개인기록Sheet!C82</f>
-        <v>8.1999999999999993</v>
+        <f>I79+개인기록Sheet!C79</f>
+        <v>7.2</v>
       </c>
       <c r="I79" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="J79" s="2"/>
@@ -12563,16 +12563,16 @@
       <c r="F80" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G80" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G80" s="2">
+        <f t="shared" si="12"/>
+        <v>20</v>
       </c>
       <c r="H80" s="6">
-        <f>I80+개인기록Sheet!C83</f>
-        <v>15.4</v>
+        <f>I80+개인기록Sheet!C80</f>
+        <v>17</v>
       </c>
       <c r="I80" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
       <c r="J80" s="2"/>
@@ -12692,16 +12692,16 @@
       <c r="F81" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G81" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G81" s="2">
+        <f t="shared" si="12"/>
+        <v>25</v>
       </c>
       <c r="H81" s="6">
-        <f>I81+개인기록Sheet!C84</f>
-        <v>12.4</v>
+        <f>I81+개인기록Sheet!C81</f>
+        <v>14.6</v>
       </c>
       <c r="I81" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="J81" s="2"/>
@@ -12819,16 +12819,16 @@
       <c r="F82" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G82" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G82" s="2">
+        <f t="shared" si="12"/>
+        <v>29</v>
       </c>
       <c r="H82" s="6">
-        <f>I82+개인기록Sheet!C85</f>
-        <v>11.9</v>
+        <f>I82+개인기록Sheet!C82</f>
+        <v>13.2</v>
       </c>
       <c r="I82" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="J82" s="2"/>
@@ -12944,16 +12944,16 @@
       <c r="F83" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G83" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G83" s="2">
+        <f t="shared" si="12"/>
+        <v>28</v>
       </c>
       <c r="H83" s="6">
-        <f>I83+개인기록Sheet!C86</f>
-        <v>12.4</v>
+        <f>I83+개인기록Sheet!C83</f>
+        <v>13.4</v>
       </c>
       <c r="I83" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="J83" s="2"/>
@@ -13069,16 +13069,16 @@
       <c r="F84" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G84" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G84" s="2">
+        <f t="shared" si="12"/>
+        <v>65</v>
       </c>
       <c r="H84" s="6">
-        <f>I84+개인기록Sheet!C87</f>
-        <v>4</v>
+        <f>I84+개인기록Sheet!C84</f>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I84" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="J84" s="2"/>
@@ -13180,16 +13180,16 @@
       <c r="F85" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G85" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G85" s="2">
+        <f t="shared" si="12"/>
+        <v>48</v>
       </c>
       <c r="H85" s="6">
-        <f>I85+개인기록Sheet!C88</f>
-        <v>8</v>
+        <f>I85+개인기록Sheet!C85</f>
+        <v>7.9</v>
       </c>
       <c r="I85" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="J85" s="2"/>
@@ -13297,16 +13297,16 @@
       <c r="F86" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G86" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G86" s="2">
+        <f t="shared" si="12"/>
+        <v>56</v>
       </c>
       <c r="H86" s="6">
-        <f>I86+개인기록Sheet!C89</f>
-        <v>5.4</v>
+        <f>I86+개인기록Sheet!C86</f>
+        <v>6.4</v>
       </c>
       <c r="I86" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="J86" s="2"/>
@@ -13404,22 +13404,22 @@
         <v>318</v>
       </c>
       <c r="D87" s="54" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="E87" s="54"/>
       <c r="F87" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G87" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G87" s="2">
+        <f t="shared" si="12"/>
+        <v>92</v>
       </c>
       <c r="H87" s="6">
-        <f>I87+개인기록Sheet!C90</f>
+        <f>I87+개인기록Sheet!C87</f>
         <v>0</v>
       </c>
       <c r="I87" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J87" s="2"/>
@@ -13507,23 +13507,23 @@
         <v>2026</v>
       </c>
       <c r="D88" s="54">
-        <f>COUNTA(AF88:AS88)</f>
+        <f>COUNTA(AF88:AU88)</f>
         <v>0</v>
       </c>
       <c r="E88" s="54"/>
       <c r="F88" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G88" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G88" s="2">
+        <f t="shared" si="12"/>
+        <v>68</v>
       </c>
       <c r="H88" s="6">
-        <f>I88+개인기록Sheet!C91</f>
-        <v>3</v>
+        <f>I88+개인기록Sheet!C88</f>
+        <v>4</v>
       </c>
       <c r="I88" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="J88" s="2"/>
@@ -13623,16 +13623,16 @@
       <c r="F89" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G89" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G89" s="2">
+        <f t="shared" si="12"/>
+        <v>72</v>
       </c>
       <c r="H89" s="6">
-        <f>I89+개인기록Sheet!C92</f>
-        <v>3.8</v>
+        <f>I89+개인기록Sheet!C89</f>
+        <v>3.4</v>
       </c>
       <c r="I89" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="J89" s="2"/>
@@ -13726,23 +13726,23 @@
         <v>2024</v>
       </c>
       <c r="D90" s="54">
-        <f t="shared" ref="D90:D91" si="15">COUNTA(AF90:AS90)</f>
+        <f t="shared" ref="D90:D91" si="14">COUNTA(AF90:AU90)</f>
         <v>0</v>
       </c>
       <c r="E90" s="54"/>
       <c r="F90" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G90" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G90" s="2">
+        <f t="shared" si="12"/>
+        <v>86</v>
       </c>
       <c r="H90" s="6">
-        <f>I90+개인기록Sheet!C93</f>
+        <f>I90+개인기록Sheet!C90</f>
         <v>1</v>
       </c>
       <c r="I90" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J90" s="2"/>
@@ -13832,23 +13832,23 @@
         <v>2026</v>
       </c>
       <c r="D91" s="54">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="E91" s="54"/>
       <c r="F91" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G91" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G91" s="2">
+        <f t="shared" si="12"/>
+        <v>86</v>
       </c>
       <c r="H91" s="6">
-        <f>I91+개인기록Sheet!C94</f>
-        <v>4.9000000000000004</v>
+        <f>I91+개인기록Sheet!C91</f>
+        <v>1</v>
       </c>
       <c r="I91" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J91" s="2"/>
@@ -13944,16 +13944,16 @@
       <c r="F92" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G92" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G92" s="2">
+        <f t="shared" si="12"/>
+        <v>63</v>
       </c>
       <c r="H92" s="6">
-        <f>I92+개인기록Sheet!C95</f>
-        <v>4</v>
+        <f>I92+개인기록Sheet!C92</f>
+        <v>4.8</v>
       </c>
       <c r="I92" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="J92" s="2"/>
@@ -14055,16 +14055,16 @@
       <c r="F93" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G93" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G93" s="2">
+        <f t="shared" si="12"/>
+        <v>92</v>
       </c>
       <c r="H93" s="6">
-        <f>I93+개인기록Sheet!C96</f>
+        <f>I93+개인기록Sheet!C93</f>
         <v>0</v>
       </c>
       <c r="I93" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J93" s="2"/>
@@ -14158,16 +14158,16 @@
       <c r="F94" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G94" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G94" s="2">
+        <f t="shared" si="12"/>
+        <v>22</v>
       </c>
       <c r="H94" s="6">
-        <f>I94+개인기록Sheet!C97</f>
-        <v>14.5</v>
+        <f>I94+개인기록Sheet!C94</f>
+        <v>15.9</v>
       </c>
       <c r="I94" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="J94" s="2"/>
@@ -14279,22 +14279,22 @@
         <v>2022</v>
       </c>
       <c r="D95" s="54" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="E95" s="54"/>
       <c r="F95" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G95" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G95" s="2">
+        <f t="shared" si="12"/>
+        <v>80</v>
       </c>
       <c r="H95" s="6">
-        <f>I95+개인기록Sheet!C98</f>
-        <v>2.2000000000000002</v>
+        <f>I95+개인기록Sheet!C95</f>
+        <v>2</v>
       </c>
       <c r="I95" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="J95" s="2"/>
@@ -14386,23 +14386,23 @@
         <v>2022</v>
       </c>
       <c r="D96" s="54">
-        <f>COUNTA(AF96:AS96)</f>
+        <f>COUNTA(AF96:AU96)</f>
         <v>1</v>
       </c>
       <c r="E96" s="54"/>
       <c r="F96" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G96" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G96" s="2">
+        <f t="shared" si="12"/>
+        <v>86</v>
       </c>
       <c r="H96" s="6">
-        <f>I96+개인기록Sheet!C99</f>
-        <v>1.9000000000000001</v>
+        <f>I96+개인기록Sheet!C96</f>
+        <v>1</v>
       </c>
       <c r="I96" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J96" s="2"/>
@@ -14498,16 +14498,16 @@
       <c r="F97" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G97" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G97" s="2">
+        <f t="shared" si="12"/>
+        <v>27</v>
       </c>
       <c r="H97" s="6">
-        <f>I97+개인기록Sheet!C100</f>
-        <v>16.2</v>
+        <f>I97+개인기록Sheet!C97</f>
+        <v>13.5</v>
       </c>
       <c r="I97" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="J97" s="2"/>
@@ -14617,23 +14617,23 @@
         <v>2022</v>
       </c>
       <c r="D98" s="54">
-        <f>COUNTA(AF98:AS98)</f>
+        <f>COUNTA(AF98:AU98)</f>
         <v>0</v>
       </c>
       <c r="E98" s="54"/>
       <c r="F98" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G98" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G98" s="2">
+        <f t="shared" si="12"/>
+        <v>84</v>
       </c>
       <c r="H98" s="6">
-        <f>I98+개인기록Sheet!C101</f>
-        <v>4.5999999999999996</v>
+        <f>I98+개인기록Sheet!C98</f>
+        <v>1.2</v>
       </c>
       <c r="I98" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J98" s="2"/>
@@ -14729,16 +14729,16 @@
       <c r="F99" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G99" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#REF!</v>
+      <c r="G99" s="2">
+        <f t="shared" si="12"/>
+        <v>59</v>
       </c>
       <c r="H99" s="6">
-        <f>I99+개인기록Sheet!C102</f>
-        <v>6.5</v>
+        <f>I99+개인기록Sheet!C99</f>
+        <v>5.9</v>
       </c>
       <c r="I99" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="J99" s="2"/>
@@ -14842,16 +14842,16 @@
       <c r="F100" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G100" s="2" t="e">
-        <f t="shared" ref="G100:G131" si="16">RANK(H100,$H$4:$H$122,0)</f>
-        <v>#REF!</v>
+      <c r="G100" s="2">
+        <f t="shared" ref="G100:G122" si="15">RANK(H100,$H$4:$H$122,0)</f>
+        <v>10</v>
       </c>
       <c r="H100" s="6">
-        <f>I100+개인기록Sheet!C103</f>
-        <v>22.5</v>
+        <f>I100+개인기록Sheet!C100</f>
+        <v>21.2</v>
       </c>
       <c r="I100" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="J100" s="2"/>
@@ -14977,16 +14977,16 @@
       <c r="F101" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G101" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G101" s="2">
+        <f t="shared" si="15"/>
+        <v>16</v>
       </c>
       <c r="H101" s="6">
-        <f>I101+개인기록Sheet!C104</f>
-        <v>17.8</v>
+        <f>I101+개인기록Sheet!C101</f>
+        <v>18.600000000000001</v>
       </c>
       <c r="I101" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="J101" s="2"/>
@@ -15110,16 +15110,16 @@
       <c r="F102" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G102" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G102" s="2">
+        <f t="shared" si="15"/>
+        <v>40</v>
       </c>
       <c r="H102" s="6">
-        <f>I102+개인기록Sheet!C105</f>
-        <v>9</v>
+        <f>I102+개인기록Sheet!C102</f>
+        <v>9.5</v>
       </c>
       <c r="I102" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="J102" s="2"/>
@@ -15229,16 +15229,16 @@
       <c r="F103" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G103" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G103" s="2">
+        <f t="shared" si="15"/>
+        <v>3</v>
       </c>
       <c r="H103" s="6">
-        <f>I103+개인기록Sheet!C106</f>
-        <v>23.5</v>
+        <f>I103+개인기록Sheet!C103</f>
+        <v>29.5</v>
       </c>
       <c r="I103" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>23</v>
       </c>
       <c r="J103" s="2" t="s">
@@ -15378,16 +15378,16 @@
       <c r="F104" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G104" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G104" s="2">
+        <f t="shared" si="15"/>
+        <v>12</v>
       </c>
       <c r="H104" s="6">
-        <f>I104+개인기록Sheet!C107</f>
-        <v>22.6</v>
+        <f>I104+개인기록Sheet!C104</f>
+        <v>20.8</v>
       </c>
       <c r="I104" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="J104" s="2" t="s">
@@ -15517,16 +15517,16 @@
       <c r="F105" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G105" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G105" s="2">
+        <f t="shared" si="15"/>
+        <v>58</v>
       </c>
       <c r="H105" s="6">
-        <f>I105+개인기록Sheet!C108</f>
-        <v>5</v>
+        <f>I105+개인기록Sheet!C105</f>
+        <v>6</v>
       </c>
       <c r="I105" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="J105" s="2" t="s">
@@ -15624,23 +15624,23 @@
         <v>2026</v>
       </c>
       <c r="D106" s="54">
-        <f>COUNTA(AF106:AS106)</f>
+        <f>COUNTA(AF106:AU106)</f>
         <v>2</v>
       </c>
       <c r="E106" s="54"/>
       <c r="F106" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G106" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G106" s="2">
+        <f t="shared" si="15"/>
+        <v>76</v>
       </c>
       <c r="H106" s="6">
-        <f>I106+개인기록Sheet!C109</f>
-        <v>5.2</v>
+        <f>I106+개인기록Sheet!C106</f>
+        <v>2.5</v>
       </c>
       <c r="I106" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="J106" s="2"/>
@@ -15738,16 +15738,16 @@
       <c r="F107" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G107" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G107" s="2">
+        <f t="shared" si="15"/>
+        <v>21</v>
       </c>
       <c r="H107" s="6">
-        <f>I107+개인기록Sheet!C109</f>
-        <v>15.2</v>
+        <f>I107+개인기록Sheet!C107</f>
+        <v>16.600000000000001</v>
       </c>
       <c r="I107" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="J107" s="2" t="s">
@@ -15859,23 +15859,23 @@
         <v>2021</v>
       </c>
       <c r="D108" s="54">
-        <f>COUNTA(AF108:AS108)</f>
+        <f>COUNTA(AF108:AU108)</f>
         <v>0</v>
       </c>
       <c r="E108" s="54"/>
       <c r="F108" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G108" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G108" s="2">
+        <f t="shared" si="15"/>
+        <v>92</v>
       </c>
       <c r="H108" s="6">
-        <f>I108+개인기록Sheet!C110</f>
-        <v>2</v>
+        <f>I108+개인기록Sheet!C108</f>
+        <v>0</v>
       </c>
       <c r="I108" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J108" s="2"/>
@@ -15969,16 +15969,16 @@
       <c r="F109" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G109" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G109" s="2">
+        <f t="shared" si="15"/>
+        <v>19</v>
       </c>
       <c r="H109" s="6">
-        <f>I109+개인기록Sheet!C111</f>
-        <v>15.8</v>
+        <f>I109+개인기록Sheet!C109</f>
+        <v>17.2</v>
       </c>
       <c r="I109" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="J109" s="2" t="s">
@@ -16100,16 +16100,16 @@
       <c r="F110" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G110" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G110" s="2">
+        <f t="shared" si="15"/>
+        <v>26</v>
       </c>
       <c r="H110" s="6">
-        <f>I110+개인기록Sheet!C112</f>
-        <v>14.6</v>
+        <f>I110+개인기록Sheet!C110</f>
+        <v>14</v>
       </c>
       <c r="I110" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="J110" s="2" t="s">
@@ -16227,16 +16227,16 @@
       <c r="F111" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G111" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G111" s="2">
+        <f t="shared" si="15"/>
+        <v>36</v>
       </c>
       <c r="H111" s="6">
-        <f>I111+개인기록Sheet!C113</f>
-        <v>11.6</v>
+        <f>I111+개인기록Sheet!C111</f>
+        <v>11.8</v>
       </c>
       <c r="I111" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="J111" s="2" t="s">
@@ -16350,16 +16350,16 @@
       <c r="F112" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G112" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G112" s="2">
+        <f t="shared" si="15"/>
+        <v>44</v>
       </c>
       <c r="H112" s="6">
-        <f>I112+개인기록Sheet!C114</f>
-        <v>6.2</v>
+        <f>I112+개인기록Sheet!C112</f>
+        <v>8.6</v>
       </c>
       <c r="I112" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="J112" s="2" t="s">
@@ -16465,16 +16465,16 @@
       <c r="F113" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G113" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G113" s="2">
+        <f t="shared" si="15"/>
+        <v>49</v>
       </c>
       <c r="H113" s="6">
-        <f>I113+개인기록Sheet!C115</f>
-        <v>8.5</v>
+        <f>I113+개인기록Sheet!C113</f>
+        <v>7.6</v>
       </c>
       <c r="I113" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="J113" s="2"/>
@@ -16580,16 +16580,16 @@
       <c r="F114" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G114" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G114" s="2">
+        <f t="shared" si="15"/>
+        <v>79</v>
       </c>
       <c r="H114" s="6">
-        <f>I114+개인기록Sheet!C116</f>
-        <v>5.8000000000000007</v>
+        <f>I114+개인기록Sheet!C114</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I114" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="J114" s="2"/>
@@ -16687,16 +16687,16 @@
       <c r="F115" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G115" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G115" s="2">
+        <f t="shared" si="15"/>
+        <v>51</v>
       </c>
       <c r="H115" s="6">
-        <f>I115+개인기록Sheet!C117</f>
-        <v>5.4</v>
+        <f>I115+개인기록Sheet!C115</f>
+        <v>7.5</v>
       </c>
       <c r="I115" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="J115" s="2"/>
@@ -16800,16 +16800,16 @@
       <c r="F116" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G116" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G116" s="2">
+        <f t="shared" si="15"/>
+        <v>23</v>
       </c>
       <c r="H116" s="6">
-        <f>I116+개인기록Sheet!C118</f>
-        <v>12.4</v>
+        <f>I116+개인기록Sheet!C116</f>
+        <v>15.8</v>
       </c>
       <c r="I116" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="J116" s="2"/>
@@ -16927,16 +16927,16 @@
       <c r="F117" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G117" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G117" s="2">
+        <f t="shared" si="15"/>
+        <v>83</v>
       </c>
       <c r="H117" s="6">
-        <f>I117+개인기록Sheet!C119</f>
-        <v>1</v>
+        <f>I117+개인기록Sheet!C117</f>
+        <v>1.4</v>
       </c>
       <c r="I117" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J117" s="2"/>
@@ -17026,23 +17026,23 @@
         <v>2025</v>
       </c>
       <c r="D118" s="54">
-        <f>COUNTA(AF118:AS118)</f>
+        <f>COUNTA(AF118:AU118)</f>
         <v>1</v>
       </c>
       <c r="E118" s="54"/>
       <c r="F118" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G118" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G118" s="2">
+        <f t="shared" si="15"/>
+        <v>72</v>
       </c>
       <c r="H118" s="6">
-        <f>I118+개인기록Sheet!C120</f>
-        <v>3.2</v>
+        <f>I118+개인기록Sheet!C118</f>
+        <v>3.4</v>
       </c>
       <c r="I118" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="J118" s="2"/>
@@ -17142,16 +17142,16 @@
       <c r="F119" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G119" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G119" s="2">
+        <f t="shared" si="15"/>
+        <v>92</v>
       </c>
       <c r="H119" s="6">
-        <f>I119+개인기록Sheet!C121</f>
-        <v>4.2</v>
+        <f>I119+개인기록Sheet!C119</f>
+        <v>0</v>
       </c>
       <c r="I119" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J119" s="2"/>
@@ -17239,23 +17239,23 @@
         <v>2024</v>
       </c>
       <c r="D120" s="54">
-        <f>COUNTA(AF120:AS120)</f>
+        <f>COUNTA(AF120:AU120)</f>
         <v>1</v>
       </c>
       <c r="E120" s="54"/>
       <c r="F120" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G120" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
+      <c r="G120" s="2">
+        <f t="shared" si="15"/>
+        <v>84</v>
       </c>
       <c r="H120" s="6">
-        <f>I120+개인기록Sheet!C122</f>
-        <v>1.6</v>
+        <f>I120+개인기록Sheet!C120</f>
+        <v>1.2</v>
       </c>
       <c r="I120" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J120" s="2"/>
@@ -17351,16 +17351,16 @@
       <c r="F121" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G121" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H121" s="6" t="e">
-        <f>I121+개인기록Sheet!#REF!</f>
-        <v>#REF!</v>
+      <c r="G121" s="2">
+        <f t="shared" si="15"/>
+        <v>29</v>
+      </c>
+      <c r="H121" s="6">
+        <f>I121+개인기록Sheet!C121</f>
+        <v>13.2</v>
       </c>
       <c r="I121" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="J121" s="2"/>
@@ -17466,23 +17466,23 @@
         <v>2026</v>
       </c>
       <c r="D122" s="54">
-        <f>COUNTA(AF122:AS122)</f>
+        <f>COUNTA(AF122:AU122)</f>
         <v>3</v>
       </c>
       <c r="E122" s="54"/>
       <c r="F122" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G122" s="2" t="e">
-        <f t="shared" si="16"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H122" s="6" t="e">
-        <f>I122+개인기록Sheet!#REF!</f>
-        <v>#REF!</v>
+      <c r="G122" s="2">
+        <f t="shared" si="15"/>
+        <v>69</v>
+      </c>
+      <c r="H122" s="6">
+        <f>I122+개인기록Sheet!C122</f>
+        <v>3.6</v>
       </c>
       <c r="I122" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="J122" s="2"/>
@@ -17566,6 +17566,7 @@
       <c r="CD122" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:CT122" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:E122">
     <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="지급">
@@ -26658,70 +26659,335 @@
     </row>
   </sheetData>
   <mergeCells count="428">
-    <mergeCell ref="B312:B313"/>
-    <mergeCell ref="C312:C313"/>
-    <mergeCell ref="D312:D313"/>
-    <mergeCell ref="B314:B315"/>
-    <mergeCell ref="C314:C315"/>
-    <mergeCell ref="D314:D315"/>
-    <mergeCell ref="E307:H307"/>
-    <mergeCell ref="I307:L307"/>
-    <mergeCell ref="M307:P307"/>
-    <mergeCell ref="Q307:V307"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="C308:C309"/>
-    <mergeCell ref="D308:D309"/>
-    <mergeCell ref="B310:B311"/>
-    <mergeCell ref="C310:C311"/>
-    <mergeCell ref="D310:D311"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="C262:C263"/>
-    <mergeCell ref="D262:D263"/>
-    <mergeCell ref="B264:B265"/>
-    <mergeCell ref="C264:C265"/>
-    <mergeCell ref="D264:D265"/>
-    <mergeCell ref="E257:H257"/>
-    <mergeCell ref="I257:L257"/>
-    <mergeCell ref="M257:P257"/>
-    <mergeCell ref="Q257:V257"/>
-    <mergeCell ref="B258:B259"/>
-    <mergeCell ref="C258:C259"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="B260:B261"/>
-    <mergeCell ref="C260:C261"/>
-    <mergeCell ref="D260:D261"/>
-    <mergeCell ref="B252:B253"/>
-    <mergeCell ref="C252:C253"/>
-    <mergeCell ref="D252:D253"/>
-    <mergeCell ref="Q245:V245"/>
-    <mergeCell ref="B246:B247"/>
-    <mergeCell ref="C246:C247"/>
-    <mergeCell ref="D246:D247"/>
-    <mergeCell ref="B248:B249"/>
-    <mergeCell ref="C248:C249"/>
-    <mergeCell ref="D248:D249"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="C250:C251"/>
-    <mergeCell ref="D250:D251"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="C238:C239"/>
-    <mergeCell ref="D238:D239"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="C240:C241"/>
-    <mergeCell ref="D240:D241"/>
-    <mergeCell ref="E245:H245"/>
-    <mergeCell ref="I245:L245"/>
-    <mergeCell ref="M245:P245"/>
-    <mergeCell ref="E233:H233"/>
-    <mergeCell ref="I233:L233"/>
-    <mergeCell ref="M233:P233"/>
-    <mergeCell ref="Q233:V233"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="C234:C235"/>
-    <mergeCell ref="D234:D235"/>
-    <mergeCell ref="B236:B237"/>
-    <mergeCell ref="C236:C237"/>
-    <mergeCell ref="D236:D237"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="C300:C301"/>
+    <mergeCell ref="D300:D301"/>
+    <mergeCell ref="B302:B303"/>
+    <mergeCell ref="C302:C303"/>
+    <mergeCell ref="D302:D303"/>
+    <mergeCell ref="E295:H295"/>
+    <mergeCell ref="I295:L295"/>
+    <mergeCell ref="M295:P295"/>
+    <mergeCell ref="B288:B289"/>
+    <mergeCell ref="C288:C289"/>
+    <mergeCell ref="D288:D289"/>
+    <mergeCell ref="Q295:V295"/>
+    <mergeCell ref="B296:B297"/>
+    <mergeCell ref="C296:C297"/>
+    <mergeCell ref="D296:D297"/>
+    <mergeCell ref="B298:B299"/>
+    <mergeCell ref="C298:C299"/>
+    <mergeCell ref="D298:D299"/>
+    <mergeCell ref="B290:B291"/>
+    <mergeCell ref="C290:C291"/>
+    <mergeCell ref="D290:D291"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="C282:C283"/>
+    <mergeCell ref="D282:D283"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="C284:C285"/>
+    <mergeCell ref="D284:D285"/>
+    <mergeCell ref="B286:B287"/>
+    <mergeCell ref="C286:C287"/>
+    <mergeCell ref="D286:D287"/>
+    <mergeCell ref="C272:C273"/>
+    <mergeCell ref="D272:D273"/>
+    <mergeCell ref="E279:H279"/>
+    <mergeCell ref="I279:L279"/>
+    <mergeCell ref="M279:P279"/>
+    <mergeCell ref="Q279:V279"/>
+    <mergeCell ref="B280:B281"/>
+    <mergeCell ref="C280:C281"/>
+    <mergeCell ref="D280:D281"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="C226:C227"/>
+    <mergeCell ref="D226:D227"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="C228:C229"/>
+    <mergeCell ref="D228:D229"/>
+    <mergeCell ref="E221:H221"/>
+    <mergeCell ref="I221:L221"/>
+    <mergeCell ref="M221:P221"/>
+    <mergeCell ref="Q221:V221"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="D222:D223"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="D216:D217"/>
+    <mergeCell ref="E211:H211"/>
+    <mergeCell ref="I211:L211"/>
+    <mergeCell ref="M211:P211"/>
+    <mergeCell ref="Q211:V211"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="D212:D213"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="D214:D215"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="D198:D199"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="D206:D207"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="D200:D201"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="D202:D203"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="D204:D205"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E195:H195"/>
+    <mergeCell ref="I195:L195"/>
+    <mergeCell ref="M195:P195"/>
+    <mergeCell ref="Q195:V195"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="D196:D197"/>
+    <mergeCell ref="Q183:V183"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="D184:D185"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
+    <mergeCell ref="E183:H183"/>
+    <mergeCell ref="I183:L183"/>
+    <mergeCell ref="M183:P183"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="M113:P113"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="M77:P77"/>
+    <mergeCell ref="Q89:V89"/>
+    <mergeCell ref="M89:P89"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="Q113:V113"/>
+    <mergeCell ref="Q77:V77"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:L101"/>
+    <mergeCell ref="M101:P101"/>
+    <mergeCell ref="Q101:V101"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="Q63:V63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="Q49:V49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:V37"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="Q2:V2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="Q13:V13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="E135:H135"/>
+    <mergeCell ref="I135:L135"/>
+    <mergeCell ref="M135:P135"/>
+    <mergeCell ref="E125:H125"/>
+    <mergeCell ref="I125:L125"/>
+    <mergeCell ref="M125:P125"/>
+    <mergeCell ref="Q135:V135"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="Q125:V125"/>
+    <mergeCell ref="Q159:V159"/>
+    <mergeCell ref="Q171:V171"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="Q147:V147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="E147:H147"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="M147:P147"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="D166:D167"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
     <mergeCell ref="E159:H159"/>
     <mergeCell ref="I159:L159"/>
     <mergeCell ref="M159:P159"/>
@@ -26746,295 +27012,61 @@
     <mergeCell ref="E171:H171"/>
     <mergeCell ref="I171:L171"/>
     <mergeCell ref="M171:P171"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="D166:D167"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="Q159:V159"/>
-    <mergeCell ref="Q171:V171"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="Q147:V147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="E147:H147"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="M147:P147"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="E135:H135"/>
-    <mergeCell ref="I135:L135"/>
-    <mergeCell ref="M135:P135"/>
-    <mergeCell ref="E125:H125"/>
-    <mergeCell ref="I125:L125"/>
-    <mergeCell ref="M125:P125"/>
-    <mergeCell ref="Q135:V135"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="Q125:V125"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:L89"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="Q13:V13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:V37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="Q49:V49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="Q63:V63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="E113:H113"/>
-    <mergeCell ref="I113:L113"/>
-    <mergeCell ref="M113:P113"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="M77:P77"/>
-    <mergeCell ref="Q89:V89"/>
-    <mergeCell ref="M89:P89"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="Q113:V113"/>
-    <mergeCell ref="Q77:V77"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:L101"/>
-    <mergeCell ref="M101:P101"/>
-    <mergeCell ref="Q101:V101"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E195:H195"/>
-    <mergeCell ref="I195:L195"/>
-    <mergeCell ref="M195:P195"/>
-    <mergeCell ref="Q195:V195"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="D196:D197"/>
-    <mergeCell ref="Q183:V183"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="D184:D185"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="D190:D191"/>
-    <mergeCell ref="E183:H183"/>
-    <mergeCell ref="I183:L183"/>
-    <mergeCell ref="M183:P183"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="D198:D199"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="D206:D207"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="D200:D201"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="D202:D203"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="D204:D205"/>
-    <mergeCell ref="E211:H211"/>
-    <mergeCell ref="I211:L211"/>
-    <mergeCell ref="M211:P211"/>
-    <mergeCell ref="Q211:V211"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="D214:D215"/>
-    <mergeCell ref="Q221:V221"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="D222:D223"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="D216:D217"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="C226:C227"/>
-    <mergeCell ref="D226:D227"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="C228:C229"/>
-    <mergeCell ref="D228:D229"/>
-    <mergeCell ref="E221:H221"/>
-    <mergeCell ref="I221:L221"/>
-    <mergeCell ref="M221:P221"/>
+    <mergeCell ref="E233:H233"/>
+    <mergeCell ref="I233:L233"/>
+    <mergeCell ref="M233:P233"/>
+    <mergeCell ref="Q233:V233"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="C234:C235"/>
+    <mergeCell ref="D234:D235"/>
+    <mergeCell ref="B236:B237"/>
+    <mergeCell ref="C236:C237"/>
+    <mergeCell ref="D236:D237"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="C238:C239"/>
+    <mergeCell ref="D238:D239"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="C240:C241"/>
+    <mergeCell ref="D240:D241"/>
+    <mergeCell ref="E245:H245"/>
+    <mergeCell ref="I245:L245"/>
+    <mergeCell ref="M245:P245"/>
+    <mergeCell ref="B252:B253"/>
+    <mergeCell ref="C252:C253"/>
+    <mergeCell ref="D252:D253"/>
+    <mergeCell ref="Q245:V245"/>
+    <mergeCell ref="B246:B247"/>
+    <mergeCell ref="C246:C247"/>
+    <mergeCell ref="D246:D247"/>
+    <mergeCell ref="B248:B249"/>
+    <mergeCell ref="C248:C249"/>
+    <mergeCell ref="D248:D249"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="C250:C251"/>
+    <mergeCell ref="D250:D251"/>
+    <mergeCell ref="E257:H257"/>
+    <mergeCell ref="I257:L257"/>
+    <mergeCell ref="M257:P257"/>
+    <mergeCell ref="Q257:V257"/>
+    <mergeCell ref="B258:B259"/>
+    <mergeCell ref="C258:C259"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="B260:B261"/>
+    <mergeCell ref="C260:C261"/>
+    <mergeCell ref="D260:D261"/>
+    <mergeCell ref="Q307:V307"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="C308:C309"/>
+    <mergeCell ref="D308:D309"/>
+    <mergeCell ref="B310:B311"/>
+    <mergeCell ref="C310:C311"/>
+    <mergeCell ref="D310:D311"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="C262:C263"/>
+    <mergeCell ref="D262:D263"/>
+    <mergeCell ref="B264:B265"/>
+    <mergeCell ref="C264:C265"/>
+    <mergeCell ref="D264:D265"/>
     <mergeCell ref="B274:B275"/>
     <mergeCell ref="C274:C275"/>
     <mergeCell ref="D274:D275"/>
@@ -27046,46 +27078,15 @@
     <mergeCell ref="C270:C271"/>
     <mergeCell ref="D270:D271"/>
     <mergeCell ref="B272:B273"/>
-    <mergeCell ref="C272:C273"/>
-    <mergeCell ref="D272:D273"/>
-    <mergeCell ref="E279:H279"/>
-    <mergeCell ref="I279:L279"/>
-    <mergeCell ref="M279:P279"/>
-    <mergeCell ref="Q279:V279"/>
-    <mergeCell ref="B280:B281"/>
-    <mergeCell ref="C280:C281"/>
-    <mergeCell ref="D280:D281"/>
-    <mergeCell ref="B282:B283"/>
-    <mergeCell ref="C282:C283"/>
-    <mergeCell ref="D282:D283"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="C284:C285"/>
-    <mergeCell ref="D284:D285"/>
-    <mergeCell ref="B286:B287"/>
-    <mergeCell ref="C286:C287"/>
-    <mergeCell ref="D286:D287"/>
-    <mergeCell ref="B288:B289"/>
-    <mergeCell ref="C288:C289"/>
-    <mergeCell ref="D288:D289"/>
-    <mergeCell ref="Q295:V295"/>
-    <mergeCell ref="B296:B297"/>
-    <mergeCell ref="C296:C297"/>
-    <mergeCell ref="D296:D297"/>
-    <mergeCell ref="B298:B299"/>
-    <mergeCell ref="C298:C299"/>
-    <mergeCell ref="D298:D299"/>
-    <mergeCell ref="B290:B291"/>
-    <mergeCell ref="C290:C291"/>
-    <mergeCell ref="D290:D291"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="C300:C301"/>
-    <mergeCell ref="D300:D301"/>
-    <mergeCell ref="B302:B303"/>
-    <mergeCell ref="C302:C303"/>
-    <mergeCell ref="D302:D303"/>
-    <mergeCell ref="E295:H295"/>
-    <mergeCell ref="I295:L295"/>
-    <mergeCell ref="M295:P295"/>
+    <mergeCell ref="B312:B313"/>
+    <mergeCell ref="C312:C313"/>
+    <mergeCell ref="D312:D313"/>
+    <mergeCell ref="B314:B315"/>
+    <mergeCell ref="C314:C315"/>
+    <mergeCell ref="D314:D315"/>
+    <mergeCell ref="E307:H307"/>
+    <mergeCell ref="I307:L307"/>
+    <mergeCell ref="M307:P307"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -27221,7 +27222,7 @@
         <v>김인혁</v>
       </c>
       <c r="C4" s="2">
-        <f>((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
+        <f t="shared" ref="C4:C35" si="0">((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
         <v>2</v>
       </c>
       <c r="D4" s="14">
@@ -27245,7 +27246,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="14">
-        <f>SUM(D4:H4)</f>
+        <f t="shared" ref="I4:I35" si="1">SUM(D4:H4)</f>
         <v>10</v>
       </c>
       <c r="J4" s="15"/>
@@ -27256,35 +27257,35 @@
         <v>350</v>
       </c>
       <c r="M4" s="21">
-        <f>VLOOKUP(L4,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" ref="M4:M17" si="2">VLOOKUP(L4,$B$4:$H$133,3,FALSE)</f>
         <v>24</v>
       </c>
       <c r="N4" s="33" t="s">
         <v>350</v>
       </c>
       <c r="O4" s="22">
-        <f>VLOOKUP(N4,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" ref="O4:O15" si="3">VLOOKUP(N4,$B$4:$H$133,4,FALSE)</f>
         <v>10</v>
       </c>
       <c r="P4" s="34" t="s">
         <v>221</v>
       </c>
       <c r="Q4" s="23">
-        <f>VLOOKUP(P4,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" ref="Q4:Q16" si="4">VLOOKUP(P4,$B$4:$H$133,5,FALSE)</f>
         <v>17</v>
       </c>
       <c r="R4" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S4" s="55">
-        <f>VLOOKUP(R4,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" ref="S4:S18" si="5">VLOOKUP(R4,$B$4:$H$133,6,FALSE)</f>
         <v>23</v>
       </c>
       <c r="T4" s="36" t="s">
         <v>42</v>
       </c>
       <c r="U4" s="56">
-        <f>VLOOKUP(T4,$B$4:$H$133,7,FALSE)</f>
+        <f t="shared" ref="U4:U13" si="6">VLOOKUP(T4,$B$4:$H$133,7,FALSE)</f>
         <v>15</v>
       </c>
     </row>
@@ -27298,7 +27299,7 @@
         <v>신재경</v>
       </c>
       <c r="C5" s="2">
-        <f>((D5+E5+G5+H5)*0.2)+(F5*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="D5" s="14">
@@ -27322,7 +27323,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="14">
-        <f>SUM(D5:H5)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="J5" s="15"/>
@@ -27333,35 +27334,35 @@
         <v>223</v>
       </c>
       <c r="M5" s="21">
-        <f>VLOOKUP(L5,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="N5" s="33" t="s">
         <v>53</v>
       </c>
       <c r="O5" s="22">
-        <f>VLOOKUP(N5,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="P5" s="34" t="s">
         <v>304</v>
       </c>
       <c r="Q5" s="23">
-        <f>VLOOKUP(P5,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="R5" s="35" t="s">
         <v>230</v>
       </c>
       <c r="S5" s="55">
-        <f>VLOOKUP(R5,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="T5" s="36" t="s">
         <v>228</v>
       </c>
       <c r="U5" s="56">
-        <f>VLOOKUP(T5,$B$4:$H$133,7,FALSE)</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
     </row>
@@ -27375,7 +27376,7 @@
         <v>정효태</v>
       </c>
       <c r="C6" s="2">
-        <f>((D6+E6+G6+H6)*0.2)+(F6*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D6" s="14">
@@ -27399,7 +27400,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="14">
-        <f>SUM(D6:H6)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J6" s="15"/>
@@ -27410,35 +27411,35 @@
         <v>397</v>
       </c>
       <c r="M6" s="21">
-        <f>VLOOKUP(L6,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="N6" s="33" t="s">
         <v>356</v>
       </c>
       <c r="O6" s="22">
-        <f>VLOOKUP(N6,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="P6" s="34" t="s">
         <v>64</v>
       </c>
       <c r="Q6" s="23">
-        <f>VLOOKUP(P6,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="R6" s="35" t="s">
         <v>353</v>
       </c>
       <c r="S6" s="55">
-        <f>VLOOKUP(R6,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="T6" s="36" t="s">
         <v>220</v>
       </c>
       <c r="U6" s="56">
-        <f>VLOOKUP(T6,$B$4:$H$133,7,FALSE)</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
     </row>
@@ -27452,7 +27453,7 @@
         <v>이승민</v>
       </c>
       <c r="C7" s="2">
-        <f>((D7+E7+G7+H7)*0.2)+(F7*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D7" s="14">
@@ -27476,7 +27477,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="14">
-        <f>SUM(D7:H7)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J7" s="15"/>
@@ -27487,35 +27488,35 @@
         <v>221</v>
       </c>
       <c r="M7" s="21">
-        <f>VLOOKUP(L7,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="N7" s="33" t="s">
         <v>221</v>
       </c>
       <c r="O7" s="22">
-        <f>VLOOKUP(N7,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="P7" s="34" t="s">
         <v>298</v>
       </c>
       <c r="Q7" s="23">
-        <f>VLOOKUP(P7,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="R7" s="35" t="s">
         <v>359</v>
       </c>
       <c r="S7" s="55">
-        <f>VLOOKUP(R7,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="T7" s="36" t="s">
         <v>352</v>
       </c>
       <c r="U7" s="56">
-        <f>VLOOKUP(T7,$B$4:$H$133,7,FALSE)</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
@@ -27529,7 +27530,7 @@
         <v>이정석</v>
       </c>
       <c r="C8" s="2">
-        <f>((D8+E8+G8+H8)*0.2)+(F8*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D8" s="14">
@@ -27553,7 +27554,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <f>SUM(D8:H8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J8" s="15"/>
@@ -27564,35 +27565,35 @@
         <v>231</v>
       </c>
       <c r="M8" s="21">
-        <f>VLOOKUP(L8,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="N8" s="33" t="s">
         <v>50</v>
       </c>
       <c r="O8" s="22">
-        <f>VLOOKUP(N8,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="P8" s="34" t="s">
         <v>53</v>
       </c>
       <c r="Q8" s="23">
-        <f>VLOOKUP(P8,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="R8" s="35" t="s">
         <v>232</v>
       </c>
       <c r="S8" s="55">
-        <f>VLOOKUP(R8,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="T8" s="36" t="s">
         <v>353</v>
       </c>
       <c r="U8" s="56">
-        <f>VLOOKUP(T8,$B$4:$H$133,7,FALSE)</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
@@ -27606,7 +27607,7 @@
         <v>강종찬</v>
       </c>
       <c r="C9" s="2">
-        <f>((D9+E9+G9+H9)*0.2)+(F9*0.3)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="D9" s="14">
@@ -27630,7 +27631,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="14">
-        <f>SUM(D9:H9)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="J9" s="15"/>
@@ -27641,35 +27642,35 @@
         <v>352</v>
       </c>
       <c r="M9" s="21">
-        <f>VLOOKUP(L9,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="N9" s="33" t="s">
         <v>223</v>
       </c>
       <c r="O9" s="22">
-        <f>VLOOKUP(N9,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="P9" s="34" t="s">
         <v>7</v>
       </c>
       <c r="Q9" s="23">
-        <f>VLOOKUP(P9,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="R9" s="35" t="s">
         <v>391</v>
       </c>
       <c r="S9" s="55">
-        <f>VLOOKUP(R9,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="T9" s="36" t="s">
         <v>396</v>
       </c>
       <c r="U9" s="56">
-        <f>VLOOKUP(T9,$B$4:$H$133,7,FALSE)</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
@@ -27683,7 +27684,7 @@
         <v>강관석</v>
       </c>
       <c r="C10" s="2">
-        <f>((D10+E10+G10+H10)*0.2)+(F10*0.3)</f>
+        <f t="shared" si="0"/>
         <v>3.6</v>
       </c>
       <c r="D10" s="14">
@@ -27707,7 +27708,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="14">
-        <f>SUM(D10:H10)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="J10" s="15"/>
@@ -27718,35 +27719,35 @@
         <v>356</v>
       </c>
       <c r="M10" s="21">
-        <f>VLOOKUP(L10,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N10" s="33" t="s">
         <v>313</v>
       </c>
       <c r="O10" s="22">
-        <f>VLOOKUP(N10,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="P10" s="34" t="s">
         <v>375</v>
       </c>
       <c r="Q10" s="23">
-        <f>VLOOKUP(P10,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="R10" s="35" t="s">
         <v>62</v>
       </c>
       <c r="S10" s="55">
-        <f>VLOOKUP(R10,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="T10" s="36" t="s">
         <v>298</v>
       </c>
       <c r="U10" s="56">
-        <f>VLOOKUP(T10,$B$4:$H$133,7,FALSE)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -27760,7 +27761,7 @@
         <v>강기혁</v>
       </c>
       <c r="C11" s="2">
-        <f>((D11+E11+G11+H11)*0.2)+(F11*0.3)</f>
+        <f t="shared" si="0"/>
         <v>5.3000000000000007</v>
       </c>
       <c r="D11" s="14">
@@ -27784,7 +27785,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="14">
-        <f>SUM(D11:H11)</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="J11" s="15"/>
@@ -27795,35 +27796,35 @@
         <v>228</v>
       </c>
       <c r="M11" s="21">
-        <f>VLOOKUP(L11,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="N11" s="33" t="s">
         <v>7</v>
       </c>
       <c r="O11" s="22">
-        <f>VLOOKUP(N11,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="P11" s="34" t="s">
         <v>381</v>
       </c>
       <c r="Q11" s="23">
-        <f>VLOOKUP(P11,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="R11" s="35" t="s">
         <v>302</v>
       </c>
       <c r="S11" s="55">
-        <f>VLOOKUP(R11,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="T11" s="36" t="s">
         <v>299</v>
       </c>
       <c r="U11" s="56">
-        <f>VLOOKUP(T11,$B$4:$H$133,7,FALSE)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -27837,7 +27838,7 @@
         <v>강도일</v>
       </c>
       <c r="C12" s="2">
-        <f>((D12+E12+G12+H12)*0.2)+(F12*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D12" s="14">
@@ -27861,7 +27862,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="14">
-        <f>SUM(D12:H12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J12" s="15"/>
@@ -27872,35 +27873,35 @@
         <v>406</v>
       </c>
       <c r="M12" s="21">
-        <f>VLOOKUP(L12,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="N12" s="33" t="s">
         <v>352</v>
       </c>
       <c r="O12" s="22">
-        <f>VLOOKUP(N12,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P12" s="34" t="s">
         <v>299</v>
       </c>
       <c r="Q12" s="23">
-        <f>VLOOKUP(P12,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R12" s="35" t="s">
         <v>308</v>
       </c>
       <c r="S12" s="55">
-        <f>VLOOKUP(R12,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="T12" s="36" t="s">
         <v>360</v>
       </c>
       <c r="U12" s="56">
-        <f>VLOOKUP(T12,$B$4:$H$133,7,FALSE)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -27914,7 +27915,7 @@
         <v>강일수</v>
       </c>
       <c r="C13" s="2">
-        <f>((D13+E13+G13+H13)*0.2)+(F13*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D13" s="14">
@@ -27938,7 +27939,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="14">
-        <f>SUM(D13:H13)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J13" s="15"/>
@@ -27949,35 +27950,35 @@
         <v>304</v>
       </c>
       <c r="M13" s="21">
-        <f>VLOOKUP(L13,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="N13" s="33" t="s">
         <v>381</v>
       </c>
       <c r="O13" s="22">
-        <f>VLOOKUP(N13,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P13" s="34" t="s">
         <v>313</v>
       </c>
       <c r="Q13" s="23">
-        <f>VLOOKUP(P13,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R13" s="35" t="s">
         <v>34</v>
       </c>
       <c r="S13" s="55">
-        <f>VLOOKUP(R13,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="T13" s="36" t="s">
         <v>359</v>
       </c>
       <c r="U13" s="56">
-        <f>VLOOKUP(T13,$B$4:$H$133,7,FALSE)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -27991,7 +27992,7 @@
         <v>구교훈</v>
       </c>
       <c r="C14" s="2">
-        <f>((D14+E14+G14+H14)*0.2)+(F14*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D14" s="14">
@@ -28015,7 +28016,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f>SUM(D14:H14)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="15"/>
@@ -28026,28 +28027,28 @@
         <v>314</v>
       </c>
       <c r="M14" s="21">
-        <f>VLOOKUP(L14,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="N14" s="33" t="s">
         <v>402</v>
       </c>
       <c r="O14" s="22">
-        <f>VLOOKUP(N14,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P14" s="34" t="s">
         <v>402</v>
       </c>
       <c r="Q14" s="23">
-        <f>VLOOKUP(P14,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R14" s="55" t="s">
         <v>221</v>
       </c>
       <c r="S14" s="55">
-        <f>VLOOKUP(R14,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="T14" s="36"/>
@@ -28063,7 +28064,7 @@
         <v>권민강</v>
       </c>
       <c r="C15" s="2">
-        <f>((D15+E15+G15+H15)*0.2)+(F15*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D15" s="14">
@@ -28087,7 +28088,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f>SUM(D15:H15)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="J15" s="15"/>
@@ -28098,28 +28099,28 @@
         <v>220</v>
       </c>
       <c r="M15" s="21">
-        <f>VLOOKUP(L15,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="N15" s="33" t="s">
         <v>397</v>
       </c>
       <c r="O15" s="22">
-        <f>VLOOKUP(N15,$B$4:$H$133,4,FALSE)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P15" s="23" t="s">
         <v>382</v>
       </c>
       <c r="Q15" s="23">
-        <f>VLOOKUP(P15,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="R15" s="55" t="s">
         <v>241</v>
       </c>
       <c r="S15" s="55">
-        <f>VLOOKUP(R15,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="T15" s="56"/>
@@ -28135,7 +28136,7 @@
         <v>김기문</v>
       </c>
       <c r="C16" s="2">
-        <f>((D16+E16+G16+H16)*0.2)+(F16*0.3)</f>
+        <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
       <c r="D16" s="14">
@@ -28159,7 +28160,7 @@
         <v>2</v>
       </c>
       <c r="I16" s="14">
-        <f>SUM(D16:H16)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="J16" s="15"/>
@@ -28170,7 +28171,7 @@
         <v>460</v>
       </c>
       <c r="M16" s="21">
-        <f>VLOOKUP(L16,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="N16" s="22"/>
@@ -28179,14 +28180,14 @@
         <v>316</v>
       </c>
       <c r="Q16" s="23">
-        <f>VLOOKUP(P16,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="R16" s="55" t="s">
         <v>360</v>
       </c>
       <c r="S16" s="55">
-        <f>VLOOKUP(R16,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="T16" s="56"/>
@@ -28202,7 +28203,7 @@
         <v>김기태</v>
       </c>
       <c r="C17" s="2">
-        <f>((D17+E17+G17+H17)*0.2)+(F17*0.3)</f>
+        <f t="shared" si="0"/>
         <v>3.8000000000000003</v>
       </c>
       <c r="D17" s="14">
@@ -28226,7 +28227,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="14">
-        <f>SUM(D17:H17)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="J17" s="15"/>
@@ -28237,7 +28238,7 @@
         <v>382</v>
       </c>
       <c r="M17" s="21">
-        <f>VLOOKUP(L17,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="N17" s="22"/>
@@ -28248,7 +28249,7 @@
         <v>67</v>
       </c>
       <c r="S17" s="55">
-        <f>VLOOKUP(R17,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="T17" s="56"/>
@@ -28264,7 +28265,7 @@
         <v>김덕준</v>
       </c>
       <c r="C18" s="2">
-        <f>((D18+E18+G18+H18)*0.2)+(F18*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D18" s="14">
@@ -28288,7 +28289,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <f>SUM(D18:H18)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J18" s="15"/>
@@ -28305,7 +28306,7 @@
         <v>229</v>
       </c>
       <c r="S18" s="55">
-        <f>VLOOKUP(R18,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="T18" s="56"/>
@@ -28321,7 +28322,7 @@
         <v>김도원</v>
       </c>
       <c r="C19" s="2">
-        <f>((D19+E19+G19+H19)*0.2)+(F19*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D19" s="14">
@@ -28345,7 +28346,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <f>SUM(D19:H19)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J19" s="15"/>
@@ -28360,7 +28361,7 @@
         <v>김민섭</v>
       </c>
       <c r="C20" s="2">
-        <f>((D20+E20+G20+H20)*0.2)+(F20*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="D20" s="14">
@@ -28384,7 +28385,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f>SUM(D20:H20)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J20" s="15"/>
@@ -28399,7 +28400,7 @@
         <v>김민찬</v>
       </c>
       <c r="C21" s="2">
-        <f>((D21+E21+G21+H21)*0.2)+(F21*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D21" s="14">
@@ -28423,7 +28424,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="14">
-        <f>SUM(D21:H21)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J21" s="15"/>
@@ -28438,7 +28439,7 @@
         <v>김범기</v>
       </c>
       <c r="C22" s="2">
-        <f>((D22+E22+G22+H22)*0.2)+(F22*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D22" s="14">
@@ -28462,7 +28463,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <f>SUM(D22:H22)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J22" s="15"/>
@@ -28477,7 +28478,7 @@
         <v>김병준</v>
       </c>
       <c r="C23" s="2">
-        <f>((D23+E23+G23+H23)*0.2)+(F23*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D23" s="14">
@@ -28501,7 +28502,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="14">
-        <f>SUM(D23:H23)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J23" s="15"/>
@@ -28516,7 +28517,7 @@
         <v>김부건</v>
       </c>
       <c r="C24" s="2">
-        <f>((D24+E24+G24+H24)*0.2)+(F24*0.3)</f>
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="D24" s="14">
@@ -28540,7 +28541,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="14">
-        <f>SUM(D24:H24)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="J24" s="15"/>
@@ -28555,7 +28556,7 @@
         <v>김성수</v>
       </c>
       <c r="C25" s="2">
-        <f>((D25+E25+G25+H25)*0.2)+(F25*0.3)</f>
+        <f t="shared" si="0"/>
         <v>2.9000000000000004</v>
       </c>
       <c r="D25" s="14">
@@ -28579,7 +28580,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <f>SUM(D25:H25)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="J25" s="15"/>
@@ -28594,7 +28595,7 @@
         <v>김성준</v>
       </c>
       <c r="C26" s="2">
-        <f>((D26+E26+G26+H26)*0.2)+(F26*0.3)</f>
+        <f t="shared" si="0"/>
         <v>10.7</v>
       </c>
       <c r="D26" s="14">
@@ -28618,7 +28619,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="14">
-        <f>SUM(D26:H26)</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="J26" s="15"/>
@@ -28633,7 +28634,7 @@
         <v>김송환</v>
       </c>
       <c r="C27" s="2">
-        <f>((D27+E27+G27+H27)*0.2)+(F27*0.3)</f>
+        <f t="shared" si="0"/>
         <v>3.0999999999999996</v>
       </c>
       <c r="D27" s="14">
@@ -28657,7 +28658,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="14">
-        <f>SUM(D27:H27)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="J27" s="15"/>
@@ -28672,7 +28673,7 @@
         <v>김영태</v>
       </c>
       <c r="C28" s="2">
-        <f>((D28+E28+G28+H28)*0.2)+(F28*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D28" s="14">
@@ -28696,7 +28697,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <f>SUM(D28:H28)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J28" s="15"/>
@@ -28711,7 +28712,7 @@
         <v>김용빈</v>
       </c>
       <c r="C29" s="2">
-        <f>((D29+E29+G29+H29)*0.2)+(F29*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D29" s="14">
@@ -28735,7 +28736,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="14">
-        <f>SUM(D29:H29)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J29" s="15"/>
@@ -28750,7 +28751,7 @@
         <v>김용현</v>
       </c>
       <c r="C30" s="2">
-        <f>((D30+E30+G30+H30)*0.2)+(F30*0.3)</f>
+        <f t="shared" si="0"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="D30" s="14">
@@ -28774,7 +28775,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <f>SUM(D30:H30)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="J30" s="15"/>
@@ -28789,7 +28790,7 @@
         <v>김우인</v>
       </c>
       <c r="C31" s="2">
-        <f>((D31+E31+G31+H31)*0.2)+(F31*0.3)</f>
+        <f t="shared" si="0"/>
         <v>5.2</v>
       </c>
       <c r="D31" s="14">
@@ -28813,7 +28814,7 @@
         <v>12</v>
       </c>
       <c r="I31" s="14">
-        <f>SUM(D31:H31)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="J31" s="15"/>
@@ -28828,7 +28829,7 @@
         <v>김종준</v>
       </c>
       <c r="C32" s="2">
-        <f>((D32+E32+G32+H32)*0.2)+(F32*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
       <c r="D32" s="14">
@@ -28852,7 +28853,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="14">
-        <f>SUM(D32:H32)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J32" s="15"/>
@@ -28867,7 +28868,7 @@
         <v>김종혁</v>
       </c>
       <c r="C33" s="2">
-        <f>((D33+E33+G33+H33)*0.2)+(F33*0.3)</f>
+        <f t="shared" si="0"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="D33" s="14">
@@ -28891,7 +28892,7 @@
         <v>3</v>
       </c>
       <c r="I33" s="14">
-        <f>SUM(D33:H33)</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="J33" s="15"/>
@@ -28906,7 +28907,7 @@
         <v>김진형</v>
       </c>
       <c r="C34" s="2">
-        <f>((D34+E34+G34+H34)*0.2)+(F34*0.3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D34" s="14">
@@ -28930,7 +28931,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="14">
-        <f>SUM(D34:H34)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J34" s="15"/>
@@ -28945,7 +28946,7 @@
         <v>김진호</v>
       </c>
       <c r="C35" s="2">
-        <f>((D35+E35+G35+H35)*0.2)+(F35*0.3)</f>
+        <f t="shared" si="0"/>
         <v>6.8000000000000007</v>
       </c>
       <c r="D35" s="14">
@@ -28969,7 +28970,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="14">
-        <f>SUM(D35:H35)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="J35" s="15"/>
@@ -28984,7 +28985,7 @@
         <v>김태성</v>
       </c>
       <c r="C36" s="2">
-        <f>((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
+        <f t="shared" ref="C36:C67" si="7">((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D36" s="14">
@@ -29008,7 +29009,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="14">
-        <f>SUM(D36:H36)</f>
+        <f t="shared" ref="I36:I67" si="8">SUM(D36:H36)</f>
         <v>3</v>
       </c>
       <c r="J36" s="15"/>
@@ -29023,7 +29024,7 @@
         <v>김태양</v>
       </c>
       <c r="C37" s="2">
-        <f>((D37+E37+G37+H37)*0.2)+(F37*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D37" s="14">
@@ -29047,7 +29048,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="14">
-        <f>SUM(D37:H37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J37" s="15"/>
@@ -29062,7 +29063,7 @@
         <v>김태완</v>
       </c>
       <c r="C38" s="2">
-        <f>((D38+E38+G38+H38)*0.2)+(F38*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D38" s="14">
@@ -29086,7 +29087,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="14">
-        <f>SUM(D38:H38)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J38" s="15"/>
@@ -29101,7 +29102,7 @@
         <v>김태호</v>
       </c>
       <c r="C39" s="2">
-        <f>((D39+E39+G39+H39)*0.2)+(F39*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D39" s="14">
@@ -29125,7 +29126,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="14">
-        <f>SUM(D39:H39)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J39" s="15"/>
@@ -29140,7 +29141,7 @@
         <v>김현우</v>
       </c>
       <c r="C40" s="2">
-        <f>((D40+E40+G40+H40)*0.2)+(F40*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D40" s="14">
@@ -29164,7 +29165,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="14">
-        <f>SUM(D40:H40)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J40" s="15"/>
@@ -29179,7 +29180,7 @@
         <v>김형원</v>
       </c>
       <c r="C41" s="2">
-        <f>((D41+E41+G41+H41)*0.2)+(F41*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D41" s="14">
@@ -29203,7 +29204,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="14">
-        <f>SUM(D41:H41)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J41" s="15"/>
@@ -29218,7 +29219,7 @@
         <v>노민준</v>
       </c>
       <c r="C42" s="2">
-        <f>((D42+E42+G42+H42)*0.2)+(F42*0.3)</f>
+        <f t="shared" si="7"/>
         <v>4.6000000000000005</v>
       </c>
       <c r="D42" s="14">
@@ -29242,7 +29243,7 @@
         <v>3</v>
       </c>
       <c r="I42" s="14">
-        <f>SUM(D42:H42)</f>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
       <c r="J42" s="15"/>
@@ -29257,7 +29258,7 @@
         <v>노성호</v>
       </c>
       <c r="C43" s="2">
-        <f>((D43+E43+G43+H43)*0.2)+(F43*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="D43" s="14">
@@ -29281,7 +29282,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="14">
-        <f>SUM(D43:H43)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J43" s="15"/>
@@ -29296,7 +29297,7 @@
         <v>류서진</v>
       </c>
       <c r="C44" s="2">
-        <f>((D44+E44+G44+H44)*0.2)+(F44*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2.4</v>
       </c>
       <c r="D44" s="14">
@@ -29320,7 +29321,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="14">
-        <f>SUM(D44:H44)</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="J44" s="15"/>
@@ -29335,7 +29336,7 @@
         <v>마창기</v>
       </c>
       <c r="C45" s="2">
-        <f>((D45+E45+G45+H45)*0.2)+(F45*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D45" s="14">
@@ -29359,7 +29360,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="14">
-        <f>SUM(D45:H45)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J45" s="15"/>
@@ -29374,7 +29375,7 @@
         <v>문준수</v>
       </c>
       <c r="C46" s="2">
-        <f>((D46+E46+G46+H46)*0.2)+(F46*0.3)</f>
+        <f t="shared" si="7"/>
         <v>3.4000000000000004</v>
       </c>
       <c r="D46" s="14">
@@ -29398,7 +29399,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="14">
-        <f>SUM(D46:H46)</f>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="J46" s="15"/>
@@ -29413,7 +29414,7 @@
         <v>민건호</v>
       </c>
       <c r="C47" s="2">
-        <f>((D47+E47+G47+H47)*0.2)+(F47*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D47" s="14">
@@ -29437,7 +29438,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="14">
-        <f>SUM(D47:H47)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J47" s="15"/>
@@ -29452,7 +29453,7 @@
         <v>박수천</v>
       </c>
       <c r="C48" s="2">
-        <f>((D48+E48+G48+H48)*0.2)+(F48*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D48" s="14">
@@ -29476,7 +29477,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="14">
-        <f>SUM(D48:H48)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J48" s="15"/>
@@ -29491,7 +29492,7 @@
         <v>박정호</v>
       </c>
       <c r="C49" s="2">
-        <f>((D49+E49+G49+H49)*0.2)+(F49*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D49" s="14">
@@ -29515,7 +29516,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="14">
-        <f>SUM(D49:H49)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J49" s="15"/>
@@ -29530,7 +29531,7 @@
         <v>박주연</v>
       </c>
       <c r="C50" s="2">
-        <f>((D50+E50+G50+H50)*0.2)+(F50*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="D50" s="14">
@@ -29554,7 +29555,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="14">
-        <f>SUM(D50:H50)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="J50" s="15"/>
@@ -29569,7 +29570,7 @@
         <v>박주현</v>
       </c>
       <c r="C51" s="2">
-        <f>((D51+E51+G51+H51)*0.2)+(F51*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D51" s="14">
@@ -29593,7 +29594,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="14">
-        <f>SUM(D51:H51)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J51" s="15"/>
@@ -29608,7 +29609,7 @@
         <v>박준영</v>
       </c>
       <c r="C52" s="2">
-        <f>((D52+E52+G52+H52)*0.2)+(F52*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D52" s="14">
@@ -29632,7 +29633,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="14">
-        <f>SUM(D52:H52)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J52" s="15"/>
@@ -29647,7 +29648,7 @@
         <v>박태현</v>
       </c>
       <c r="C53" s="2">
-        <f>((D53+E53+G53+H53)*0.2)+(F53*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
       <c r="D53" s="14">
@@ -29671,7 +29672,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="14">
-        <f>SUM(D53:H53)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J53" s="15"/>
@@ -29686,7 +29687,7 @@
         <v>박하빈</v>
       </c>
       <c r="C54" s="2">
-        <f>((D54+E54+G54+H54)*0.2)+(F54*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D54" s="14">
@@ -29710,7 +29711,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="14">
-        <f>SUM(D54:H54)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J54" s="15"/>
@@ -29725,7 +29726,7 @@
         <v>박형기</v>
       </c>
       <c r="C55" s="2">
-        <f>((D55+E55+G55+H55)*0.2)+(F55*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D55" s="14">
@@ -29749,7 +29750,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="14">
-        <f>SUM(D55:H55)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J55" s="15"/>
@@ -29764,7 +29765,7 @@
         <v>손경호</v>
       </c>
       <c r="C56" s="2">
-        <f>((D56+E56+G56+H56)*0.2)+(F56*0.3)</f>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
       <c r="D56" s="14">
@@ -29788,7 +29789,7 @@
         <v>5</v>
       </c>
       <c r="I56" s="14">
-        <f>SUM(D56:H56)</f>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="J56" s="15"/>
@@ -29803,7 +29804,7 @@
         <v>송윤상</v>
       </c>
       <c r="C57" s="2">
-        <f>((D57+E57+G57+H57)*0.2)+(F57*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="D57" s="14">
@@ -29827,7 +29828,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="14">
-        <f>SUM(D57:H57)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="J57" s="15"/>
@@ -29842,7 +29843,7 @@
         <v>신기웅</v>
       </c>
       <c r="C58" s="2">
-        <f>((D58+E58+G58+H58)*0.2)+(F58*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2.1</v>
       </c>
       <c r="D58" s="14">
@@ -29866,7 +29867,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="14">
-        <f>SUM(D58:H58)</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="J58" s="15"/>
@@ -29881,7 +29882,7 @@
         <v>신종훈</v>
       </c>
       <c r="C59" s="2">
-        <f>((D59+E59+G59+H59)*0.2)+(F59*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D59" s="14">
@@ -29905,7 +29906,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="14">
-        <f>SUM(D59:H59)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J59" s="15"/>
@@ -29920,7 +29921,7 @@
         <v>안진혁</v>
       </c>
       <c r="C60" s="2">
-        <f>((D60+E60+G60+H60)*0.2)+(F60*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D60" s="14">
@@ -29944,7 +29945,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="14">
-        <f>SUM(D60:H60)</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="J60" s="15"/>
@@ -29959,7 +29960,7 @@
         <v>양진웅</v>
       </c>
       <c r="C61" s="2">
-        <f>((D61+E61+G61+H61)*0.2)+(F61*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="D61" s="14">
@@ -29983,7 +29984,7 @@
         <v>1</v>
       </c>
       <c r="I61" s="14">
-        <f>SUM(D61:H61)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="J61" s="15"/>
@@ -29998,7 +29999,7 @@
         <v>오상준</v>
       </c>
       <c r="C62" s="2">
-        <f>((D62+E62+G62+H62)*0.2)+(F62*0.3)</f>
+        <f t="shared" si="7"/>
         <v>3.7</v>
       </c>
       <c r="D62" s="14">
@@ -30022,7 +30023,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="14">
-        <f>SUM(D62:H62)</f>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="J62" s="15"/>
@@ -30037,7 +30038,7 @@
         <v>오성찬</v>
       </c>
       <c r="C63" s="2">
-        <f>((D63+E63+G63+H63)*0.2)+(F63*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0.3</v>
       </c>
       <c r="D63" s="14">
@@ -30061,7 +30062,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="14">
-        <f>SUM(D63:H63)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J63" s="15"/>
@@ -30076,7 +30077,7 @@
         <v>오우영</v>
       </c>
       <c r="C64" s="2">
-        <f>((D64+E64+G64+H64)*0.2)+(F64*0.3)</f>
+        <f t="shared" si="7"/>
         <v>2.9000000000000004</v>
       </c>
       <c r="D64" s="14">
@@ -30100,7 +30101,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="14">
-        <f>SUM(D64:H64)</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="J64" s="15"/>
@@ -30115,7 +30116,7 @@
         <v>오운용</v>
       </c>
       <c r="C65" s="2">
-        <f>((D65+E65+G65+H65)*0.2)+(F65*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D65" s="14">
@@ -30139,7 +30140,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="14">
-        <f>SUM(D65:H65)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J65" s="15"/>
@@ -30154,7 +30155,7 @@
         <v>오준서</v>
       </c>
       <c r="C66" s="2">
-        <f>((D66+E66+G66+H66)*0.2)+(F66*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D66" s="14">
@@ -30178,7 +30179,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="14">
-        <f>SUM(D66:H66)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J66" s="15"/>
@@ -30193,7 +30194,7 @@
         <v>우보광</v>
       </c>
       <c r="C67" s="2">
-        <f>((D67+E67+G67+H67)*0.2)+(F67*0.3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D67" s="14">
@@ -30217,7 +30218,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="14">
-        <f>SUM(D67:H67)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J67" s="15"/>
@@ -30232,7 +30233,7 @@
         <v>유상근</v>
       </c>
       <c r="C68" s="2">
-        <f>((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
+        <f t="shared" ref="C68:C99" si="9">((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
         <v>5</v>
       </c>
       <c r="D68" s="14">
@@ -30256,7 +30257,7 @@
         <v>1</v>
       </c>
       <c r="I68" s="14">
-        <f>SUM(D68:H68)</f>
+        <f t="shared" ref="I68:I99" si="10">SUM(D68:H68)</f>
         <v>25</v>
       </c>
       <c r="J68" s="15"/>
@@ -30271,7 +30272,7 @@
         <v>유우진</v>
       </c>
       <c r="C69" s="2">
-        <f>((D69+E69+G69+H69)*0.2)+(F69*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D69" s="14">
@@ -30295,7 +30296,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="14">
-        <f>SUM(D69:H69)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J69" s="15"/>
@@ -30310,7 +30311,7 @@
         <v>유인상</v>
       </c>
       <c r="C70" s="2">
-        <f>((D70+E70+G70+H70)*0.2)+(F70*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.8</v>
       </c>
       <c r="D70" s="14">
@@ -30334,7 +30335,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="14">
-        <f>SUM(D70:H70)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J70" s="15"/>
@@ -30349,7 +30350,7 @@
         <v>유정훈</v>
       </c>
       <c r="C71" s="2">
-        <f>((D71+E71+G71+H71)*0.2)+(F71*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.5</v>
       </c>
       <c r="D71" s="14">
@@ -30373,7 +30374,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="14">
-        <f>SUM(D71:H71)</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="J71" s="15"/>
@@ -30388,7 +30389,7 @@
         <v>유진효</v>
       </c>
       <c r="C72" s="2">
-        <f>((D72+E72+G72+H72)*0.2)+(F72*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D72" s="14">
@@ -30412,7 +30413,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="14">
-        <f>SUM(D72:H72)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J72" s="15"/>
@@ -30427,7 +30428,7 @@
         <v>윤원택</v>
       </c>
       <c r="C73" s="2">
-        <f>((D73+E73+G73+H73)*0.2)+(F73*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D73" s="14">
@@ -30451,7 +30452,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="14">
-        <f>SUM(D73:H73)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J73" s="15"/>
@@ -30466,7 +30467,7 @@
         <v>윤창현</v>
       </c>
       <c r="C74" s="2">
-        <f>((D74+E74+G74+H74)*0.2)+(F74*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.6</v>
       </c>
       <c r="D74" s="14">
@@ -30490,7 +30491,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="14">
-        <f>SUM(D74:H74)</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="J74" s="15"/>
@@ -30505,7 +30506,7 @@
         <v>윤현기</v>
       </c>
       <c r="C75" s="2">
-        <f>((D75+E75+G75+H75)*0.2)+(F75*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="D75" s="14">
@@ -30529,7 +30530,7 @@
         <v>1</v>
       </c>
       <c r="I75" s="14">
-        <f>SUM(D75:H75)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J75" s="15"/>
@@ -30544,7 +30545,7 @@
         <v>이경석</v>
       </c>
       <c r="C76" s="2">
-        <f>((D76+E76+G76+H76)*0.2)+(F76*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D76" s="14">
@@ -30568,7 +30569,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="14">
-        <f>SUM(D76:H76)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J76" s="15"/>
@@ -30583,7 +30584,7 @@
         <v>이민재</v>
       </c>
       <c r="C77" s="2">
-        <f>((D77+E77+G77+H77)*0.2)+(F77*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D77" s="14">
@@ -30607,7 +30608,7 @@
         <v>3</v>
       </c>
       <c r="I77" s="14">
-        <f>SUM(D77:H77)</f>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="J77" s="15"/>
@@ -30622,7 +30623,7 @@
         <v>이병현</v>
       </c>
       <c r="C78" s="2">
-        <f>((D78+E78+G78+H78)*0.2)+(F78*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D78" s="14">
@@ -30646,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="14">
-        <f>SUM(D78:H78)</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="J78" s="15"/>
@@ -30661,7 +30662,7 @@
         <v>이상민</v>
       </c>
       <c r="C79" s="2">
-        <f>((D79+E79+G79+H79)*0.2)+(F79*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="D79" s="14">
@@ -30685,7 +30686,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="14">
-        <f>SUM(D79:H79)</f>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="J79" s="15"/>
@@ -30700,7 +30701,7 @@
         <v>이상현</v>
       </c>
       <c r="C80" s="2">
-        <f>((D80+E80+G80+H80)*0.2)+(F80*0.3)</f>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="D80" s="14">
@@ -30724,7 +30725,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="14">
-        <f>SUM(D80:H80)</f>
+        <f t="shared" si="10"/>
         <v>16</v>
       </c>
       <c r="J80" s="15"/>
@@ -30739,7 +30740,7 @@
         <v>이새샘</v>
       </c>
       <c r="C81" s="2">
-        <f>((D81+E81+G81+H81)*0.2)+(F81*0.3)</f>
+        <f t="shared" si="9"/>
         <v>2.6</v>
       </c>
       <c r="D81" s="14">
@@ -30763,7 +30764,7 @@
         <v>2</v>
       </c>
       <c r="I81" s="14">
-        <f>SUM(D81:H81)</f>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="J81" s="15"/>
@@ -30778,7 +30779,7 @@
         <v>이성관</v>
       </c>
       <c r="C82" s="2">
-        <f>((D82+E82+G82+H82)*0.2)+(F82*0.3)</f>
+        <f t="shared" si="9"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="D82" s="14">
@@ -30802,7 +30803,7 @@
         <v>1</v>
       </c>
       <c r="I82" s="14">
-        <f>SUM(D82:H82)</f>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
       <c r="J82" s="15"/>
@@ -30817,7 +30818,7 @@
         <v>이승윤</v>
       </c>
       <c r="C83" s="2">
-        <f>((D83+E83+G83+H83)*0.2)+(F83*0.3)</f>
+        <f t="shared" si="9"/>
         <v>2.4000000000000004</v>
       </c>
       <c r="D83" s="14">
@@ -30841,7 +30842,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="14">
-        <f>SUM(D83:H83)</f>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="J83" s="15"/>
@@ -30856,7 +30857,7 @@
         <v>이연길</v>
       </c>
       <c r="C84" s="2">
-        <f>((D84+E84+G84+H84)*0.2)+(F84*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D84" s="14">
@@ -30880,7 +30881,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="14">
-        <f>SUM(D84:H84)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J84" s="15"/>
@@ -30895,7 +30896,7 @@
         <v>이영준</v>
       </c>
       <c r="C85" s="2">
-        <f>((D85+E85+G85+H85)*0.2)+(F85*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="D85" s="14">
@@ -30919,7 +30920,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="14">
-        <f>SUM(D85:H85)</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="J85" s="15"/>
@@ -30934,7 +30935,7 @@
         <v>이정범</v>
       </c>
       <c r="C86" s="2">
-        <f>((D86+E86+G86+H86)*0.2)+(F86*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="D86" s="14">
@@ -30958,7 +30959,7 @@
         <v>1</v>
       </c>
       <c r="I86" s="14">
-        <f>SUM(D86:H86)</f>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
       <c r="J86" s="15"/>
@@ -30973,7 +30974,7 @@
         <v>이종수</v>
       </c>
       <c r="C87" s="2">
-        <f>((D87+E87+G87+H87)*0.2)+(F87*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D87" s="14">
@@ -30997,7 +30998,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="14">
-        <f>SUM(D87:H87)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J87" s="15"/>
@@ -31012,7 +31013,7 @@
         <v>이찬솔</v>
       </c>
       <c r="C88" s="2">
-        <f>((D88+E88+G88+H88)*0.2)+(F88*0.3)</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="D88" s="14">
@@ -31036,7 +31037,7 @@
         <v>1</v>
       </c>
       <c r="I88" s="14">
-        <f>SUM(D88:H88)</f>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="J88" s="15"/>
@@ -31051,7 +31052,7 @@
         <v>이찬영</v>
       </c>
       <c r="C89" s="2">
-        <f>((D89+E89+G89+H89)*0.2)+(F89*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="D89" s="14">
@@ -31075,7 +31076,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="14">
-        <f>SUM(D89:H89)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
       <c r="J89" s="15"/>
@@ -31090,7 +31091,7 @@
         <v>이태한</v>
       </c>
       <c r="C90" s="2">
-        <f>((D90+E90+G90+H90)*0.2)+(F90*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D90" s="14">
@@ -31114,7 +31115,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="14">
-        <f>SUM(D90:H90)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J90" s="15"/>
@@ -31129,7 +31130,7 @@
         <v>이현택</v>
       </c>
       <c r="C91" s="2">
-        <f>((D91+E91+G91+H91)*0.2)+(F91*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D91" s="14">
@@ -31153,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="14">
-        <f>SUM(D91:H91)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J91" s="15"/>
@@ -31168,7 +31169,7 @@
         <v>이호행</v>
       </c>
       <c r="C92" s="2">
-        <f>((D92+E92+G92+H92)*0.2)+(F92*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.8</v>
       </c>
       <c r="D92" s="14">
@@ -31192,7 +31193,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="14">
-        <f>SUM(D92:H92)</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="J92" s="15"/>
@@ -31207,7 +31208,7 @@
         <v>임수철</v>
       </c>
       <c r="C93" s="2">
-        <f>((D93+E93+G93+H93)*0.2)+(F93*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D93" s="14">
@@ -31231,7 +31232,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="14">
-        <f>SUM(D93:H93)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J93" s="15"/>
@@ -31246,7 +31247,7 @@
         <v>임태환</v>
       </c>
       <c r="C94" s="2">
-        <f>((D94+E94+G94+H94)*0.2)+(F94*0.3)</f>
+        <f t="shared" si="9"/>
         <v>3.9</v>
       </c>
       <c r="D94" s="14">
@@ -31270,7 +31271,7 @@
         <v>1</v>
       </c>
       <c r="I94" s="14">
-        <f>SUM(D94:H94)</f>
+        <f t="shared" si="10"/>
         <v>18</v>
       </c>
       <c r="J94" s="15"/>
@@ -31285,7 +31286,7 @@
         <v>장희도</v>
       </c>
       <c r="C95" s="2">
-        <f>((D95+E95+G95+H95)*0.2)+(F95*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D95" s="14">
@@ -31309,7 +31310,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="14">
-        <f>SUM(D95:H95)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J95" s="15"/>
@@ -31324,7 +31325,7 @@
         <v>장희준</v>
       </c>
       <c r="C96" s="2">
-        <f>((D96+E96+G96+H96)*0.2)+(F96*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D96" s="14">
@@ -31348,7 +31349,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="14">
-        <f>SUM(D96:H96)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J96" s="15"/>
@@ -31363,7 +31364,7 @@
         <v>전나현</v>
       </c>
       <c r="C97" s="2">
-        <f>((D97+E97+G97+H97)*0.2)+(F97*0.3)</f>
+        <f t="shared" si="9"/>
         <v>2.5</v>
       </c>
       <c r="D97" s="14">
@@ -31387,7 +31388,7 @@
         <v>0</v>
       </c>
       <c r="I97" s="14">
-        <f>SUM(D97:H97)</f>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
       <c r="J97" s="15"/>
@@ -31402,7 +31403,7 @@
         <v>전성환</v>
       </c>
       <c r="C98" s="2">
-        <f>((D98+E98+G98+H98)*0.2)+(F98*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="D98" s="14">
@@ -31426,7 +31427,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="14">
-        <f>SUM(D98:H98)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J98" s="15"/>
@@ -31441,7 +31442,7 @@
         <v>전하늘</v>
       </c>
       <c r="C99" s="2">
-        <f>((D99+E99+G99+H99)*0.2)+(F99*0.3)</f>
+        <f t="shared" si="9"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="D99" s="14">
@@ -31465,7 +31466,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="14">
-        <f>SUM(D99:H99)</f>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="J99" s="15"/>
@@ -31480,7 +31481,7 @@
         <v>정민수</v>
       </c>
       <c r="C100" s="2">
-        <f>((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
+        <f t="shared" ref="C100:C131" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
         <v>5.2</v>
       </c>
       <c r="D100" s="14">
@@ -31504,7 +31505,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="14">
-        <f>SUM(D100:H100)</f>
+        <f t="shared" ref="I100:I131" si="12">SUM(D100:H100)</f>
         <v>26</v>
       </c>
       <c r="J100" s="15"/>
@@ -31519,7 +31520,7 @@
         <v>정재명</v>
       </c>
       <c r="C101" s="2">
-        <f>((D101+E101+G101+H101)*0.2)+(F101*0.3)</f>
+        <f t="shared" si="11"/>
         <v>3.6</v>
       </c>
       <c r="D101" s="14">
@@ -31543,7 +31544,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="14">
-        <f>SUM(D101:H101)</f>
+        <f t="shared" si="12"/>
         <v>18</v>
       </c>
       <c r="J101" s="15"/>
@@ -31558,7 +31559,7 @@
         <v>정현서</v>
       </c>
       <c r="C102" s="2">
-        <f>((D102+E102+G102+H102)*0.2)+(F102*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.5</v>
       </c>
       <c r="D102" s="14">
@@ -31582,7 +31583,7 @@
         <v>0</v>
       </c>
       <c r="I102" s="14">
-        <f>SUM(D102:H102)</f>
+        <f t="shared" si="12"/>
         <v>6</v>
       </c>
       <c r="J102" s="15"/>
@@ -31597,7 +31598,7 @@
         <v>조진한</v>
       </c>
       <c r="C103" s="2">
-        <f>((D103+E103+G103+H103)*0.2)+(F103*0.3)</f>
+        <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
       <c r="D103" s="14">
@@ -31621,7 +31622,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="14">
-        <f>SUM(D103:H103)</f>
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
       <c r="J103" s="15"/>
@@ -31636,7 +31637,7 @@
         <v>조현우</v>
       </c>
       <c r="C104" s="2">
-        <f>((D104+E104+G104+H104)*0.2)+(F104*0.3)</f>
+        <f t="shared" si="11"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="D104" s="14">
@@ -31660,7 +31661,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="14">
-        <f>SUM(D104:H104)</f>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="J104" s="15"/>
@@ -31675,7 +31676,7 @@
         <v>차승원</v>
       </c>
       <c r="C105" s="2">
-        <f>((D105+E105+G105+H105)*0.2)+(F105*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="D105" s="14">
@@ -31699,7 +31700,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="14">
-        <f>SUM(D105:H105)</f>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
     </row>
@@ -31713,7 +31714,7 @@
         <v>최강인</v>
       </c>
       <c r="C106" s="2">
-        <f>((D106+E106+G106+H106)*0.2)+(F106*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="D106" s="14">
@@ -31737,7 +31738,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="14">
-        <f>SUM(D106:H106)</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
     </row>
@@ -31751,7 +31752,7 @@
         <v>최령창</v>
       </c>
       <c r="C107" s="2">
-        <f>((D107+E107+G107+H107)*0.2)+(F107*0.3)</f>
+        <f t="shared" si="11"/>
         <v>4.6000000000000005</v>
       </c>
       <c r="D107" s="14">
@@ -31775,7 +31776,7 @@
         <v>2</v>
       </c>
       <c r="I107" s="14">
-        <f>SUM(D107:H107)</f>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
     </row>
@@ -31789,7 +31790,7 @@
         <v>최승훈</v>
       </c>
       <c r="C108" s="2">
-        <f>((D108+E108+G108+H108)*0.2)+(F108*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D108" s="14">
@@ -31813,7 +31814,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f>SUM(D108:H108)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -31827,7 +31828,7 @@
         <v>한상규</v>
       </c>
       <c r="C109" s="2">
-        <f>((D109+E109+G109+H109)*0.2)+(F109*0.3)</f>
+        <f t="shared" si="11"/>
         <v>3.2</v>
       </c>
       <c r="D109" s="14">
@@ -31851,7 +31852,7 @@
         <v>0</v>
       </c>
       <c r="I109" s="14">
-        <f>SUM(D109:H109)</f>
+        <f t="shared" si="12"/>
         <v>16</v>
       </c>
     </row>
@@ -31865,7 +31866,7 @@
         <v>한의현</v>
       </c>
       <c r="C110" s="2">
-        <f>((D110+E110+G110+H110)*0.2)+(F110*0.3)</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="D110" s="14">
@@ -31889,7 +31890,7 @@
         <v>1</v>
       </c>
       <c r="I110" s="14">
-        <f>SUM(D110:H110)</f>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
     </row>
@@ -31903,7 +31904,7 @@
         <v>한중희</v>
       </c>
       <c r="C111" s="2">
-        <f>((D111+E111+G111+H111)*0.2)+(F111*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.8</v>
       </c>
       <c r="D111" s="14">
@@ -31927,7 +31928,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="14">
-        <f>SUM(D111:H111)</f>
+        <f t="shared" si="12"/>
         <v>9</v>
       </c>
     </row>
@@ -31941,7 +31942,7 @@
         <v>허동혁</v>
       </c>
       <c r="C112" s="2">
-        <f>((D112+E112+G112+H112)*0.2)+(F112*0.3)</f>
+        <f t="shared" si="11"/>
         <v>2.6</v>
       </c>
       <c r="D112" s="14">
@@ -31965,7 +31966,7 @@
         <v>1</v>
       </c>
       <c r="I112" s="14">
-        <f>SUM(D112:H112)</f>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
     </row>
@@ -31979,7 +31980,7 @@
         <v>홍석준</v>
       </c>
       <c r="C113" s="2">
-        <f>((D113+E113+G113+H113)*0.2)+(F113*0.3)</f>
+        <f t="shared" si="11"/>
         <v>1.6</v>
       </c>
       <c r="D113" s="14">
@@ -32003,7 +32004,7 @@
         <v>1</v>
       </c>
       <c r="I113" s="14">
-        <f>SUM(D113:H113)</f>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
     </row>
@@ -32017,7 +32018,7 @@
         <v>홍현석</v>
       </c>
       <c r="C114" s="2">
-        <f>((D114+E114+G114+H114)*0.2)+(F114*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D114" s="14">
@@ -32041,7 +32042,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="14">
-        <f>SUM(D114:H114)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -32055,7 +32056,7 @@
         <v>황건호</v>
       </c>
       <c r="C115" s="2">
-        <f>((D115+E115+G115+H115)*0.2)+(F115*0.3)</f>
+        <f t="shared" si="11"/>
         <v>2.5</v>
       </c>
       <c r="D115" s="14">
@@ -32079,7 +32080,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="14">
-        <f>SUM(D115:H115)</f>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
     </row>
@@ -32093,7 +32094,7 @@
         <v>황석원</v>
       </c>
       <c r="C116" s="2">
-        <f>((D116+E116+G116+H116)*0.2)+(F116*0.3)</f>
+        <f t="shared" si="11"/>
         <v>3.8000000000000003</v>
       </c>
       <c r="D116" s="14">
@@ -32117,7 +32118,7 @@
         <v>1</v>
       </c>
       <c r="I116" s="14">
-        <f>SUM(D116:H116)</f>
+        <f t="shared" si="12"/>
         <v>18</v>
       </c>
     </row>
@@ -32131,7 +32132,7 @@
         <v>황재순</v>
       </c>
       <c r="C117" s="2">
-        <f>((D117+E117+G117+H117)*0.2)+(F117*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
       <c r="D117" s="14">
@@ -32155,7 +32156,7 @@
         <v>0</v>
       </c>
       <c r="I117" s="14">
-        <f>SUM(D117:H117)</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
     </row>
@@ -32169,7 +32170,7 @@
         <v>황철우</v>
       </c>
       <c r="C118" s="2">
-        <f>((D118+E118+G118+H118)*0.2)+(F118*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.4</v>
       </c>
       <c r="D118" s="14">
@@ -32193,7 +32194,7 @@
         <v>0</v>
       </c>
       <c r="I118" s="14">
-        <f>SUM(D118:H118)</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
     </row>
@@ -32207,7 +32208,7 @@
         <v>김민성</v>
       </c>
       <c r="C119" s="2">
-        <f>((D119+E119+G119+H119)*0.2)+(F119*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D119" s="14">
@@ -32231,7 +32232,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="14">
-        <f>SUM(D119:H119)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -32245,7 +32246,7 @@
         <v>송명섭</v>
       </c>
       <c r="C120" s="2">
-        <f>((D120+E120+G120+H120)*0.2)+(F120*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.2</v>
       </c>
       <c r="D120" s="14">
@@ -32269,7 +32270,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="14">
-        <f>SUM(D120:H120)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -32283,7 +32284,7 @@
         <v>최경영</v>
       </c>
       <c r="C121" s="2">
-        <f>((D121+E121+G121+H121)*0.2)+(F121*0.3)</f>
+        <f t="shared" si="11"/>
         <v>4.2</v>
       </c>
       <c r="D121" s="14">
@@ -32307,7 +32308,7 @@
         <v>15</v>
       </c>
       <c r="I121" s="14">
-        <f>SUM(D121:H121)</f>
+        <f t="shared" si="12"/>
         <v>21</v>
       </c>
     </row>
@@ -32321,7 +32322,7 @@
         <v>박지수</v>
       </c>
       <c r="C122" s="2">
-        <f>((D122+E122+G122+H122)*0.2)+(F122*0.3)</f>
+        <f t="shared" si="11"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="D122" s="14">
@@ -32345,30 +32346,30 @@
         <v>0</v>
       </c>
       <c r="I122" s="14">
-        <f>SUM(D122:H122)</f>
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:D122">
-    <cfRule type="top10" dxfId="5" priority="974" rank="7"/>
+    <cfRule type="top10" dxfId="9" priority="974" rank="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E122">
-    <cfRule type="top10" dxfId="4" priority="975" rank="7"/>
+    <cfRule type="top10" dxfId="8" priority="975" rank="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F122">
-    <cfRule type="top10" dxfId="3" priority="976" rank="7"/>
+    <cfRule type="top10" dxfId="7" priority="976" rank="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G122">
-    <cfRule type="top10" dxfId="2" priority="977" rank="7"/>
+    <cfRule type="top10" dxfId="6" priority="977" rank="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H122">
-    <cfRule type="top10" dxfId="1" priority="978" rank="3"/>
+    <cfRule type="top10" dxfId="5" priority="978" rank="3"/>
     <cfRule type="top10" priority="979" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I122">
-    <cfRule type="top10" dxfId="0" priority="980" rank="10"/>
+    <cfRule type="top10" dxfId="4" priority="980" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.39347222447395325" right="0.39347222447395325" top="0.19666667282581329" bottom="0.19666667282581329" header="0.19666667282581329" footer="0.19666667282581329"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait"/>
@@ -33932,10 +33933,10 @@
       <c r="G2" s="47" t="s">
         <v>328</v>
       </c>
-      <c r="I2" s="99" t="s">
+      <c r="I2" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="J2" s="99"/>
+      <c r="J2" s="94"/>
       <c r="K2" s="65" t="s">
         <v>276</v>
       </c>
@@ -33960,7 +33961,7 @@
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="93" t="s">
         <v>334</v>
       </c>
       <c r="C3" s="72">
@@ -34030,7 +34031,7 @@
       </c>
       <c r="G4" s="61">
         <f>VLOOKUP(F4,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I4" s="96"/>
       <c r="J4" s="66">
@@ -34058,7 +34059,7 @@
       </c>
       <c r="S4" s="63">
         <f>VLOOKUP(R4,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>26</v>
+        <v>36.700000000000003</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
@@ -34078,7 +34079,7 @@
       </c>
       <c r="G5" s="61">
         <f>VLOOKUP(F5,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>26</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="I5" s="96"/>
       <c r="J5" s="66">
@@ -34106,7 +34107,7 @@
       </c>
       <c r="S5" s="63">
         <f>VLOOKUP(R5,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>23.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
@@ -34126,7 +34127,7 @@
       </c>
       <c r="G6" s="61">
         <f>VLOOKUP(F6,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>18</v>
+        <v>21.4</v>
       </c>
       <c r="I6" s="96"/>
       <c r="J6" s="66">
@@ -34154,7 +34155,7 @@
       </c>
       <c r="S6" s="71">
         <f>VLOOKUP(R6,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>22.5</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
@@ -34174,9 +34175,9 @@
       </c>
       <c r="G7" s="61">
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>23.5</v>
-      </c>
-      <c r="I7" s="97"/>
+        <v>29.5</v>
+      </c>
+      <c r="I7" s="98"/>
       <c r="J7" s="66">
         <v>5</v>
       </c>
@@ -34202,7 +34203,7 @@
       </c>
       <c r="S7" s="71">
         <f>VLOOKUP(R7,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>17.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.25">
@@ -34240,7 +34241,7 @@
       </c>
       <c r="S8" s="71">
         <f>VLOOKUP(R8,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>12.9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.25">
@@ -34260,12 +34261,12 @@
       </c>
       <c r="G9" s="61">
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>15.4</v>
-      </c>
-      <c r="I9" s="99" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="J9" s="99"/>
+      <c r="J9" s="94"/>
       <c r="K9" s="65" t="s">
         <v>276</v>
       </c>
@@ -34288,7 +34289,7 @@
       </c>
       <c r="S9" s="71">
         <f>VLOOKUP(R9,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.25">
@@ -34308,7 +34309,7 @@
       </c>
       <c r="G10" s="61">
         <f>VLOOKUP(F10,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>14.4</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="I10" s="95" t="s">
         <v>330</v>
@@ -34338,7 +34339,7 @@
       </c>
       <c r="S10" s="71">
         <f>VLOOKUP(R10,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
@@ -34386,7 +34387,7 @@
       </c>
       <c r="S11" s="71">
         <f>VLOOKUP(R11,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.25">
@@ -34418,7 +34419,7 @@
       <c r="L12" s="65">
         <v>8</v>
       </c>
-      <c r="N12" s="98"/>
+      <c r="N12" s="101"/>
       <c r="O12" s="48">
         <v>10</v>
       </c>
@@ -34454,7 +34455,7 @@
       </c>
       <c r="G13" s="61">
         <f>VLOOKUP(F13,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>15.4</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="I13" s="96"/>
       <c r="J13" s="66">
@@ -34490,9 +34491,9 @@
       </c>
       <c r="G14" s="61">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>29.4</v>
-      </c>
-      <c r="I14" s="97"/>
+        <v>30.2</v>
+      </c>
+      <c r="I14" s="98"/>
       <c r="J14" s="66">
         <v>5</v>
       </c>
@@ -34552,13 +34553,13 @@
       </c>
       <c r="G16" s="63">
         <f>VLOOKUP(F16,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>22.5</v>
+        <v>21.2</v>
       </c>
       <c r="H16" s="37"/>
-      <c r="I16" s="99" t="s">
+      <c r="I16" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="J16" s="99"/>
+      <c r="J16" s="94"/>
       <c r="K16" s="65" t="s">
         <v>276</v>
       </c>
@@ -34581,7 +34582,7 @@
       </c>
       <c r="G17" s="63">
         <f>VLOOKUP(F17,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="H17" s="37"/>
       <c r="I17" s="95" t="s">
@@ -34619,10 +34620,10 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="99" t="s">
+      <c r="B19" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="C19" s="99"/>
+      <c r="C19" s="94"/>
       <c r="D19" s="65" t="s">
         <v>276</v>
       </c>
@@ -34673,7 +34674,7 @@
       <c r="E21" s="65" t="s">
         <v>337</v>
       </c>
-      <c r="I21" s="97"/>
+      <c r="I21" s="98"/>
       <c r="J21" s="66">
         <v>5</v>
       </c>
@@ -34685,7 +34686,7 @@
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="101"/>
+      <c r="B22" s="97"/>
       <c r="C22" s="66">
         <v>3</v>
       </c>
@@ -34697,10 +34698,10 @@
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I23" s="93" t="s">
+      <c r="I23" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="J23" s="94"/>
+      <c r="J23" s="100"/>
       <c r="K23" s="65" t="s">
         <v>276</v>
       </c>
@@ -34783,7 +34784,7 @@
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="97"/>
+      <c r="I30" s="98"/>
       <c r="J30" s="66">
         <v>7</v>
       </c>
@@ -34796,12 +34797,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B3:B17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:I21"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:I30"/>
     <mergeCell ref="N2:O2"/>
@@ -34810,6 +34805,12 @@
     <mergeCell ref="I3:I7"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:I14"/>
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:I21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34998,7 +34999,7 @@
     <row r="2" spans="1:82" x14ac:dyDescent="0.25">
       <c r="D2" s="1">
         <f>COUNTIF(D4:D55,"지급")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="1">
         <f>COUNTIF(E4:E55,"지급")</f>
@@ -36137,7 +36138,7 @@
       </c>
       <c r="D11" s="2" t="str">
         <f>VLOOKUP(B11,종합Sheet!$B$4:$F$133,3,0)</f>
-        <v>발주</v>
+        <v>지급</v>
       </c>
       <c r="E11" s="2">
         <f>VLOOKUP(B11,종합Sheet!$B$4:$F$133,4,0)</f>
@@ -39176,18 +39177,18 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:E37">
-    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="지급">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="지급">
       <formula>NOT(ISERROR(SEARCH("지급",D4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G37">
-    <cfRule type="top10" dxfId="8" priority="426" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="2" priority="426" bottom="1" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H37">
-    <cfRule type="top10" dxfId="7" priority="428" rank="10"/>
+    <cfRule type="top10" dxfId="1" priority="428" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I37">
-    <cfRule type="top10" dxfId="6" priority="430" rank="10"/>
+    <cfRule type="top10" dxfId="0" priority="430" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.39347222447395325" right="0.39347222447395325" top="0.19666667282581329" bottom="0.19666667282581329" header="0.19666667282581329" footer="0.19666667282581329"/>
   <pageSetup paperSize="9" scale="96" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcabf36b0134af82/바탕 화면/김인혁_청년축구단/1. 출석부/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1382" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0A07B7-C4E2-4499-82D0-700F96069048}"/>
+  <xr:revisionPtr revIDLastSave="1467" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42309875-AC3A-4BC5-83EE-6C35178E488A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="종합Sheet" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3045" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3102" uniqueCount="462">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -2530,10 +2530,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2542,20 +2542,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H2" s="18">
         <f>SUM(J2:AR2)/COUNTA(J2:BB2)</f>
-        <v>17.066666666666666</v>
+        <v>17.488888888888887</v>
       </c>
       <c r="I2" s="18" t="s">
         <v>83</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="AR2" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS2" s="1">
         <f t="shared" si="1"/>
@@ -3697,7 +3697,9 @@
       <c r="AQ3" s="4">
         <v>46296</v>
       </c>
-      <c r="AR3" s="4"/>
+      <c r="AR3" s="4">
+        <v>46303</v>
+      </c>
       <c r="AS3" s="4"/>
       <c r="AT3" s="4"/>
       <c r="AU3" s="4"/>
@@ -3760,11 +3762,11 @@
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>26</v>
+        <v>27.2</v>
       </c>
       <c r="I4" s="6">
         <f>(COUNTIF(J4:CD4,"출전")*1)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>348</v>
@@ -3848,7 +3850,9 @@
       <c r="AQ4" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AR4" s="2"/>
+      <c r="AR4" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -3906,7 +3910,7 @@
         <v>37</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" ref="G4:G35" si="2">RANK(H5,$H$4:$H$122,0)</f>
+        <f t="shared" ref="G5:G35" si="2">RANK(H5,$H$4:$H$122,0)</f>
         <v>53</v>
       </c>
       <c r="H5" s="6">
@@ -4451,7 +4455,7 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
@@ -4588,15 +4592,15 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
-        <v>20.3</v>
+        <v>21.6</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>348</v>
@@ -4662,7 +4666,9 @@
       <c r="AQ11" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AR11" s="2"/>
+      <c r="AR11" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -5036,7 +5042,7 @@
       </c>
       <c r="G15" s="2">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H15" s="6">
         <f>I15+개인기록Sheet!C15</f>
@@ -5147,15 +5153,15 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
-        <v>12.5</v>
+        <v>13.8</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -5209,7 +5215,9 @@
       <c r="AO16" s="2"/>
       <c r="AP16" s="2"/>
       <c r="AQ16" s="2"/>
-      <c r="AR16" s="2"/>
+      <c r="AR16" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -5268,7 +5276,7 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
@@ -6036,7 +6044,7 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="2"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C24</f>
@@ -6153,7 +6161,7 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
@@ -6284,11 +6292,11 @@
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C26</f>
-        <v>36.700000000000003</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
@@ -6376,7 +6384,9 @@
       </c>
       <c r="AP26" s="2"/>
       <c r="AQ26" s="2"/>
-      <c r="AR26" s="2"/>
+      <c r="AR26" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -6435,7 +6445,7 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C27</f>
@@ -6771,7 +6781,7 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C30</f>
@@ -6906,11 +6916,11 @@
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C31</f>
-        <v>30.2</v>
+        <v>31.6</v>
       </c>
       <c r="I31" s="6">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>348</v>
@@ -6996,7 +7006,9 @@
       <c r="AQ31" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AR31" s="2"/>
+      <c r="AR31" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -7055,7 +7067,7 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
@@ -7182,11 +7194,11 @@
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C33</f>
-        <v>22.4</v>
+        <v>23.6</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
@@ -7258,7 +7270,9 @@
       <c r="AQ33" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AR33" s="2"/>
+      <c r="AR33" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
       <c r="AU33" s="2"/>
@@ -7421,15 +7435,15 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C35</f>
-        <v>25.8</v>
+        <v>27.2</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
@@ -7503,7 +7517,9 @@
         <v>348</v>
       </c>
       <c r="AQ35" s="2"/>
-      <c r="AR35" s="2"/>
+      <c r="AR35" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS35" s="2"/>
       <c r="AT35" s="2"/>
       <c r="AU35" s="2"/>
@@ -7562,15 +7578,15 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" ref="G36:G67" si="6">RANK(H36,$H$4:$H$122,0)</f>
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C36</f>
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="I36" s="6">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
@@ -7620,7 +7636,9 @@
       <c r="AO36" s="2"/>
       <c r="AP36" s="2"/>
       <c r="AQ36" s="2"/>
-      <c r="AR36" s="2"/>
+      <c r="AR36" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS36" s="2"/>
       <c r="AT36" s="2"/>
       <c r="AU36" s="2"/>
@@ -8209,11 +8227,11 @@
       </c>
       <c r="H42" s="6">
         <f>I42+개인기록Sheet!C42</f>
-        <v>25.6</v>
+        <v>26.6</v>
       </c>
       <c r="I42" s="6">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
@@ -8291,7 +8309,9 @@
       <c r="AQ42" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AR42" s="2"/>
+      <c r="AR42" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS42" s="2"/>
       <c r="AT42" s="2"/>
       <c r="AU42" s="2"/>
@@ -8350,15 +8370,15 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H43" s="6">
         <f>I43+개인기록Sheet!C43</f>
-        <v>9.5</v>
+        <v>10.9</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -8412,7 +8432,9 @@
       <c r="AQ43" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AR43" s="2"/>
+      <c r="AR43" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS43" s="2"/>
       <c r="AT43" s="2"/>
       <c r="AU43" s="2"/>
@@ -8471,7 +8493,7 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" si="6"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H44" s="6">
         <f>I44+개인기록Sheet!C44</f>
@@ -8688,7 +8710,7 @@
       </c>
       <c r="G46" s="2">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H46" s="6">
         <f>I46+개인기록Sheet!C46</f>
@@ -9820,11 +9842,11 @@
       </c>
       <c r="H56" s="6">
         <f>I56+개인기록Sheet!C56</f>
-        <v>23.6</v>
+        <v>24.6</v>
       </c>
       <c r="I56" s="6">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -9900,7 +9922,9 @@
       <c r="AQ56" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AR56" s="2"/>
+      <c r="AR56" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS56" s="2"/>
       <c r="AT56" s="2"/>
       <c r="AU56" s="2"/>
@@ -9959,7 +9983,7 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H57" s="6">
         <f>I57+개인기록Sheet!C57</f>
@@ -10293,7 +10317,7 @@
       </c>
       <c r="G60" s="2">
         <f t="shared" si="6"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H60" s="6">
         <f>I60+개인기록Sheet!C60</f>
@@ -10525,7 +10549,7 @@
       </c>
       <c r="G62" s="2">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H62" s="6">
         <f>I62+개인기록Sheet!C62</f>
@@ -10647,7 +10671,7 @@
       </c>
       <c r="G63" s="2">
         <f t="shared" si="6"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H63" s="6">
         <f>I63+개인기록Sheet!C63</f>
@@ -11187,7 +11211,7 @@
       </c>
       <c r="G68" s="2">
         <f t="shared" ref="G68:G99" si="12">RANK(H68,$H$4:$H$122,0)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H68" s="6">
         <f>I68+개인기록Sheet!C68</f>
@@ -11323,7 +11347,7 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" si="12"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H69" s="6">
         <f>I69+개인기록Sheet!C69</f>
@@ -11549,7 +11573,7 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" si="12"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
@@ -11998,7 +12022,7 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" si="12"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
@@ -12329,7 +12353,7 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" si="12"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H78" s="6">
         <f>I78+개인기록Sheet!C78</f>
@@ -12694,7 +12718,7 @@
       </c>
       <c r="G81" s="2">
         <f t="shared" si="12"/>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H81" s="6">
         <f>I81+개인기록Sheet!C81</f>
@@ -12821,7 +12845,7 @@
       </c>
       <c r="G82" s="2">
         <f t="shared" si="12"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H82" s="6">
         <f>I82+개인기록Sheet!C82</f>
@@ -12946,15 +12970,15 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="12"/>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
-        <v>13.4</v>
+        <v>15</v>
       </c>
       <c r="I83" s="6">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
@@ -13012,7 +13036,9 @@
         <v>348</v>
       </c>
       <c r="AQ83" s="2"/>
-      <c r="AR83" s="2"/>
+      <c r="AR83" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS83" s="2"/>
       <c r="AT83" s="2"/>
       <c r="AU83" s="2"/>
@@ -13071,7 +13097,7 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" si="12"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H84" s="6">
         <f>I84+개인기록Sheet!C84</f>
@@ -13182,7 +13208,7 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" si="12"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H85" s="6">
         <f>I85+개인기록Sheet!C85</f>
@@ -13516,7 +13542,7 @@
       </c>
       <c r="G88" s="2">
         <f t="shared" si="12"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H88" s="6">
         <f>I88+개인기록Sheet!C88</f>
@@ -14504,11 +14530,11 @@
       </c>
       <c r="H97" s="6">
         <f>I97+개인기록Sheet!C97</f>
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="11"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
@@ -14566,7 +14592,9 @@
       <c r="AO97" s="2"/>
       <c r="AP97" s="2"/>
       <c r="AQ97" s="2"/>
-      <c r="AR97" s="2"/>
+      <c r="AR97" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS97" s="2"/>
       <c r="AT97" s="2"/>
       <c r="AU97" s="2"/>
@@ -14844,15 +14872,15 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" ref="G100:G122" si="15">RANK(H100,$H$4:$H$122,0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
-        <v>21.2</v>
+        <v>22.6</v>
       </c>
       <c r="I100" s="6">
         <f t="shared" si="11"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
@@ -14920,7 +14948,9 @@
       <c r="AO100" s="2"/>
       <c r="AP100" s="2"/>
       <c r="AQ100" s="2"/>
-      <c r="AR100" s="2"/>
+      <c r="AR100" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS100" s="2"/>
       <c r="AT100" s="2"/>
       <c r="AU100" s="2"/>
@@ -14979,15 +15009,15 @@
       </c>
       <c r="G101" s="2">
         <f t="shared" si="15"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
-        <v>18.600000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="I101" s="6">
         <f t="shared" si="11"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
@@ -15053,7 +15083,9 @@
       <c r="AQ101" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AR101" s="2"/>
+      <c r="AR101" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS101" s="2"/>
       <c r="AT101" s="2"/>
       <c r="AU101" s="2"/>
@@ -15112,7 +15144,7 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="15"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
@@ -15235,11 +15267,11 @@
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
-        <v>29.5</v>
+        <v>30.7</v>
       </c>
       <c r="I103" s="6">
         <f t="shared" si="11"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>348</v>
@@ -15321,7 +15353,9 @@
       <c r="AQ103" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AR103" s="2"/>
+      <c r="AR103" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS103" s="2"/>
       <c r="AT103" s="2"/>
       <c r="AU103" s="2"/>
@@ -15380,15 +15414,15 @@
       </c>
       <c r="G104" s="2">
         <f t="shared" si="15"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H104" s="6">
         <f>I104+개인기록Sheet!C104</f>
-        <v>20.8</v>
+        <v>22</v>
       </c>
       <c r="I104" s="6">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>348</v>
@@ -15460,7 +15494,9 @@
         <v>348</v>
       </c>
       <c r="AQ104" s="2"/>
-      <c r="AR104" s="2"/>
+      <c r="AR104" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS104" s="2"/>
       <c r="AT104" s="2"/>
       <c r="AU104" s="2"/>
@@ -16102,15 +16138,15 @@
       </c>
       <c r="G110" s="2">
         <f t="shared" si="15"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H110" s="6">
         <f>I110+개인기록Sheet!C110</f>
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="I110" s="6">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>348</v>
@@ -16170,7 +16206,9 @@
         <v>348</v>
       </c>
       <c r="AQ110" s="2"/>
-      <c r="AR110" s="2"/>
+      <c r="AR110" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS110" s="2"/>
       <c r="AT110" s="2"/>
       <c r="AU110" s="2"/>
@@ -16467,7 +16505,7 @@
       </c>
       <c r="G113" s="2">
         <f t="shared" si="15"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H113" s="6">
         <f>I113+개인기록Sheet!C113</f>
@@ -17353,7 +17391,7 @@
       </c>
       <c r="G121" s="2">
         <f t="shared" si="15"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H121" s="6">
         <f>I121+개인기록Sheet!C121</f>
@@ -17467,7 +17505,7 @@
       </c>
       <c r="D122" s="54">
         <f>COUNTA(AF122:AU122)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E122" s="54"/>
       <c r="F122" s="2" t="s">
@@ -17475,15 +17513,15 @@
       </c>
       <c r="G122" s="2">
         <f t="shared" si="15"/>
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H122" s="6">
         <f>I122+개인기록Sheet!C122</f>
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="I122" s="6">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
@@ -17525,7 +17563,9 @@
       <c r="AQ122" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AR122" s="2"/>
+      <c r="AR122" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AS122" s="2"/>
       <c r="AT122" s="2"/>
       <c r="AU122" s="2"/>
@@ -17590,7 +17630,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:V316"/>
+  <dimension ref="A2:V328"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.8984375" style="1" bestFit="1" customWidth="1"/>
@@ -26657,154 +26697,604 @@
       <c r="U316" s="2"/>
       <c r="V316" s="2"/>
     </row>
+    <row r="319" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B319" s="11">
+        <v>46303</v>
+      </c>
+      <c r="C319" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D319" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="E319" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="F319" s="77"/>
+      <c r="G319" s="77"/>
+      <c r="H319" s="77"/>
+      <c r="I319" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="J319" s="78"/>
+      <c r="K319" s="78"/>
+      <c r="L319" s="78"/>
+      <c r="M319" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="N319" s="79"/>
+      <c r="O319" s="79"/>
+      <c r="P319" s="79"/>
+      <c r="Q319" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="R319" s="80"/>
+      <c r="S319" s="80"/>
+      <c r="T319" s="80"/>
+      <c r="U319" s="80"/>
+      <c r="V319" s="80"/>
+    </row>
+    <row r="320" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B320" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="C320" s="75">
+        <v>1</v>
+      </c>
+      <c r="D320" s="75">
+        <v>2</v>
+      </c>
+      <c r="E320" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F320" s="7"/>
+      <c r="G320" s="7"/>
+      <c r="H320" s="7"/>
+      <c r="I320" s="8"/>
+      <c r="J320" s="8"/>
+      <c r="K320" s="8"/>
+      <c r="L320" s="8"/>
+      <c r="M320" s="20"/>
+      <c r="N320" s="20"/>
+      <c r="O320" s="20"/>
+      <c r="P320" s="20"/>
+      <c r="Q320" s="9"/>
+      <c r="R320" s="9"/>
+      <c r="S320" s="9"/>
+      <c r="T320" s="9"/>
+      <c r="U320" s="9"/>
+      <c r="V320" s="13"/>
+    </row>
+    <row r="321" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B321" s="74"/>
+      <c r="C321" s="76"/>
+      <c r="D321" s="76"/>
+      <c r="E321" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F321" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G321" s="7"/>
+      <c r="H321" s="7"/>
+      <c r="I321" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="J321" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="K321" s="8"/>
+      <c r="L321" s="8"/>
+      <c r="M321" s="20"/>
+      <c r="N321" s="20"/>
+      <c r="O321" s="20"/>
+      <c r="P321" s="20"/>
+      <c r="Q321" s="9"/>
+      <c r="R321" s="9"/>
+      <c r="S321" s="9"/>
+      <c r="T321" s="9"/>
+      <c r="U321" s="9"/>
+      <c r="V321" s="13"/>
+    </row>
+    <row r="322" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B322" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C322" s="75">
+        <v>1</v>
+      </c>
+      <c r="D322" s="75">
+        <v>1</v>
+      </c>
+      <c r="E322" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F322" s="7"/>
+      <c r="G322" s="7"/>
+      <c r="H322" s="7"/>
+      <c r="I322" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="J322" s="8"/>
+      <c r="K322" s="8"/>
+      <c r="L322" s="8"/>
+      <c r="M322" s="20"/>
+      <c r="N322" s="20"/>
+      <c r="O322" s="20"/>
+      <c r="P322" s="20"/>
+      <c r="Q322" s="9"/>
+      <c r="R322" s="9"/>
+      <c r="S322" s="9"/>
+      <c r="T322" s="9"/>
+      <c r="U322" s="9"/>
+      <c r="V322" s="13"/>
+    </row>
+    <row r="323" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B323" s="74"/>
+      <c r="C323" s="76"/>
+      <c r="D323" s="76"/>
+      <c r="E323" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F323" s="7"/>
+      <c r="G323" s="7"/>
+      <c r="H323" s="7"/>
+      <c r="I323" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="J323" s="8"/>
+      <c r="K323" s="8"/>
+      <c r="L323" s="8"/>
+      <c r="M323" s="20"/>
+      <c r="N323" s="20"/>
+      <c r="O323" s="20"/>
+      <c r="P323" s="20"/>
+      <c r="Q323" s="9"/>
+      <c r="R323" s="9"/>
+      <c r="S323" s="9"/>
+      <c r="T323" s="9"/>
+      <c r="U323" s="9"/>
+      <c r="V323" s="13"/>
+    </row>
+    <row r="324" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B324" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C324" s="75">
+        <v>0</v>
+      </c>
+      <c r="D324" s="75">
+        <v>1</v>
+      </c>
+      <c r="E324" s="7"/>
+      <c r="F324" s="7"/>
+      <c r="G324" s="7"/>
+      <c r="H324" s="7"/>
+      <c r="I324" s="8"/>
+      <c r="J324" s="8"/>
+      <c r="K324" s="8"/>
+      <c r="L324" s="8"/>
+      <c r="M324" s="20"/>
+      <c r="N324" s="20"/>
+      <c r="O324" s="20"/>
+      <c r="P324" s="20"/>
+      <c r="Q324" s="9"/>
+      <c r="R324" s="9"/>
+      <c r="S324" s="9"/>
+      <c r="T324" s="9"/>
+      <c r="U324" s="9"/>
+      <c r="V324" s="13"/>
+    </row>
+    <row r="325" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B325" s="74"/>
+      <c r="C325" s="76"/>
+      <c r="D325" s="76"/>
+      <c r="E325" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F325" s="7"/>
+      <c r="G325" s="7"/>
+      <c r="H325" s="7"/>
+      <c r="I325" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="J325" s="8"/>
+      <c r="K325" s="8"/>
+      <c r="L325" s="8"/>
+      <c r="M325" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="N325" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="O325" s="20"/>
+      <c r="P325" s="20"/>
+      <c r="Q325" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="R325" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="S325" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="T325" s="9"/>
+      <c r="U325" s="9"/>
+      <c r="V325" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="326" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B326" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C326" s="75">
+        <v>1</v>
+      </c>
+      <c r="D326" s="75">
+        <v>3</v>
+      </c>
+      <c r="E326" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="F326" s="7"/>
+      <c r="G326" s="7"/>
+      <c r="H326" s="7"/>
+      <c r="I326" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="J326" s="8"/>
+      <c r="K326" s="8"/>
+      <c r="L326" s="8"/>
+      <c r="M326" s="20"/>
+      <c r="N326" s="20"/>
+      <c r="O326" s="20"/>
+      <c r="P326" s="20"/>
+      <c r="Q326" s="9"/>
+      <c r="R326" s="9"/>
+      <c r="S326" s="9"/>
+      <c r="T326" s="9"/>
+      <c r="U326" s="9"/>
+      <c r="V326" s="13"/>
+    </row>
+    <row r="327" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B327" s="74"/>
+      <c r="C327" s="76"/>
+      <c r="D327" s="76"/>
+      <c r="E327" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="F327" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G327" s="7"/>
+      <c r="H327" s="7"/>
+      <c r="I327" s="8"/>
+      <c r="J327" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="K327" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="L327" s="8"/>
+      <c r="M327" s="20"/>
+      <c r="N327" s="20"/>
+      <c r="O327" s="20"/>
+      <c r="P327" s="20"/>
+      <c r="Q327" s="9"/>
+      <c r="R327" s="9"/>
+      <c r="S327" s="9"/>
+      <c r="T327" s="9"/>
+      <c r="U327" s="9"/>
+      <c r="V327" s="13"/>
+    </row>
+    <row r="328" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B328" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C328" s="2">
+        <f>SUM(C320:C327)</f>
+        <v>3</v>
+      </c>
+      <c r="D328" s="2">
+        <f>SUM(D320:D327)</f>
+        <v>7</v>
+      </c>
+      <c r="E328" s="2"/>
+      <c r="F328" s="2"/>
+      <c r="G328" s="2"/>
+      <c r="H328" s="2"/>
+      <c r="I328" s="2"/>
+      <c r="J328" s="2"/>
+      <c r="K328" s="2"/>
+      <c r="L328" s="2"/>
+      <c r="M328" s="2"/>
+      <c r="N328" s="2"/>
+      <c r="O328" s="2"/>
+      <c r="P328" s="2"/>
+      <c r="Q328" s="2"/>
+      <c r="R328" s="2"/>
+      <c r="S328" s="2"/>
+      <c r="T328" s="2"/>
+      <c r="U328" s="2"/>
+      <c r="V328" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="428">
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="C300:C301"/>
-    <mergeCell ref="D300:D301"/>
-    <mergeCell ref="B302:B303"/>
-    <mergeCell ref="C302:C303"/>
-    <mergeCell ref="D302:D303"/>
-    <mergeCell ref="E295:H295"/>
-    <mergeCell ref="I295:L295"/>
-    <mergeCell ref="M295:P295"/>
-    <mergeCell ref="B288:B289"/>
-    <mergeCell ref="C288:C289"/>
-    <mergeCell ref="D288:D289"/>
-    <mergeCell ref="Q295:V295"/>
-    <mergeCell ref="B296:B297"/>
-    <mergeCell ref="C296:C297"/>
-    <mergeCell ref="D296:D297"/>
-    <mergeCell ref="B298:B299"/>
-    <mergeCell ref="C298:C299"/>
-    <mergeCell ref="D298:D299"/>
-    <mergeCell ref="B290:B291"/>
-    <mergeCell ref="C290:C291"/>
-    <mergeCell ref="D290:D291"/>
-    <mergeCell ref="B282:B283"/>
-    <mergeCell ref="C282:C283"/>
-    <mergeCell ref="D282:D283"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="C284:C285"/>
-    <mergeCell ref="D284:D285"/>
-    <mergeCell ref="B286:B287"/>
-    <mergeCell ref="C286:C287"/>
-    <mergeCell ref="D286:D287"/>
-    <mergeCell ref="C272:C273"/>
-    <mergeCell ref="D272:D273"/>
-    <mergeCell ref="E279:H279"/>
-    <mergeCell ref="I279:L279"/>
-    <mergeCell ref="M279:P279"/>
-    <mergeCell ref="Q279:V279"/>
-    <mergeCell ref="B280:B281"/>
-    <mergeCell ref="C280:C281"/>
-    <mergeCell ref="D280:D281"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="C226:C227"/>
-    <mergeCell ref="D226:D227"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="C228:C229"/>
-    <mergeCell ref="D228:D229"/>
-    <mergeCell ref="E221:H221"/>
-    <mergeCell ref="I221:L221"/>
-    <mergeCell ref="M221:P221"/>
-    <mergeCell ref="Q221:V221"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="D222:D223"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="D216:D217"/>
-    <mergeCell ref="E211:H211"/>
-    <mergeCell ref="I211:L211"/>
-    <mergeCell ref="M211:P211"/>
-    <mergeCell ref="Q211:V211"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="D214:D215"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="D198:D199"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="D206:D207"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="D200:D201"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="D202:D203"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="D204:D205"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E195:H195"/>
-    <mergeCell ref="I195:L195"/>
-    <mergeCell ref="M195:P195"/>
-    <mergeCell ref="Q195:V195"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="D196:D197"/>
-    <mergeCell ref="Q183:V183"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="D184:D185"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="D190:D191"/>
-    <mergeCell ref="E183:H183"/>
-    <mergeCell ref="I183:L183"/>
-    <mergeCell ref="M183:P183"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="E113:H113"/>
-    <mergeCell ref="I113:L113"/>
-    <mergeCell ref="M113:P113"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="M77:P77"/>
-    <mergeCell ref="Q89:V89"/>
-    <mergeCell ref="M89:P89"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="Q113:V113"/>
-    <mergeCell ref="Q77:V77"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:L101"/>
-    <mergeCell ref="M101:P101"/>
-    <mergeCell ref="Q101:V101"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="D108:D109"/>
+  <mergeCells count="444">
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="C324:C325"/>
+    <mergeCell ref="D324:D325"/>
+    <mergeCell ref="B326:B327"/>
+    <mergeCell ref="C326:C327"/>
+    <mergeCell ref="D326:D327"/>
+    <mergeCell ref="E319:H319"/>
+    <mergeCell ref="I319:L319"/>
+    <mergeCell ref="M319:P319"/>
+    <mergeCell ref="Q319:V319"/>
+    <mergeCell ref="B320:B321"/>
+    <mergeCell ref="C320:C321"/>
+    <mergeCell ref="D320:D321"/>
+    <mergeCell ref="B322:B323"/>
+    <mergeCell ref="C322:C323"/>
+    <mergeCell ref="D322:D323"/>
+    <mergeCell ref="B312:B313"/>
+    <mergeCell ref="C312:C313"/>
+    <mergeCell ref="D312:D313"/>
+    <mergeCell ref="B314:B315"/>
+    <mergeCell ref="C314:C315"/>
+    <mergeCell ref="D314:D315"/>
+    <mergeCell ref="E307:H307"/>
+    <mergeCell ref="I307:L307"/>
+    <mergeCell ref="M307:P307"/>
+    <mergeCell ref="Q307:V307"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="C308:C309"/>
+    <mergeCell ref="D308:D309"/>
+    <mergeCell ref="B310:B311"/>
+    <mergeCell ref="C310:C311"/>
+    <mergeCell ref="D310:D311"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="C262:C263"/>
+    <mergeCell ref="D262:D263"/>
+    <mergeCell ref="B264:B265"/>
+    <mergeCell ref="C264:C265"/>
+    <mergeCell ref="D264:D265"/>
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="C274:C275"/>
+    <mergeCell ref="D274:D275"/>
+    <mergeCell ref="E269:H269"/>
+    <mergeCell ref="I269:L269"/>
+    <mergeCell ref="M269:P269"/>
+    <mergeCell ref="Q269:V269"/>
+    <mergeCell ref="B270:B271"/>
+    <mergeCell ref="C270:C271"/>
+    <mergeCell ref="D270:D271"/>
+    <mergeCell ref="B272:B273"/>
+    <mergeCell ref="E257:H257"/>
+    <mergeCell ref="I257:L257"/>
+    <mergeCell ref="M257:P257"/>
+    <mergeCell ref="Q257:V257"/>
+    <mergeCell ref="B258:B259"/>
+    <mergeCell ref="C258:C259"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="B260:B261"/>
+    <mergeCell ref="C260:C261"/>
+    <mergeCell ref="D260:D261"/>
+    <mergeCell ref="B252:B253"/>
+    <mergeCell ref="C252:C253"/>
+    <mergeCell ref="D252:D253"/>
+    <mergeCell ref="Q245:V245"/>
+    <mergeCell ref="B246:B247"/>
+    <mergeCell ref="C246:C247"/>
+    <mergeCell ref="D246:D247"/>
+    <mergeCell ref="B248:B249"/>
+    <mergeCell ref="C248:C249"/>
+    <mergeCell ref="D248:D249"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="C250:C251"/>
+    <mergeCell ref="D250:D251"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="C238:C239"/>
+    <mergeCell ref="D238:D239"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="C240:C241"/>
+    <mergeCell ref="D240:D241"/>
+    <mergeCell ref="E245:H245"/>
+    <mergeCell ref="I245:L245"/>
+    <mergeCell ref="M245:P245"/>
+    <mergeCell ref="E233:H233"/>
+    <mergeCell ref="I233:L233"/>
+    <mergeCell ref="M233:P233"/>
+    <mergeCell ref="Q233:V233"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="C234:C235"/>
+    <mergeCell ref="D234:D235"/>
+    <mergeCell ref="B236:B237"/>
+    <mergeCell ref="C236:C237"/>
+    <mergeCell ref="D236:D237"/>
+    <mergeCell ref="E159:H159"/>
+    <mergeCell ref="I159:L159"/>
+    <mergeCell ref="M159:P159"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="D160:D161"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="C188:C189"/>
+    <mergeCell ref="D188:D189"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="D162:D163"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="C172:C173"/>
+    <mergeCell ref="D172:D173"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="C176:C177"/>
+    <mergeCell ref="D176:D177"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="C178:C179"/>
+    <mergeCell ref="D178:D179"/>
+    <mergeCell ref="E171:H171"/>
+    <mergeCell ref="I171:L171"/>
+    <mergeCell ref="M171:P171"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="D166:D167"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="Q159:V159"/>
+    <mergeCell ref="Q171:V171"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="Q147:V147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="E147:H147"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="M147:P147"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="E135:H135"/>
+    <mergeCell ref="I135:L135"/>
+    <mergeCell ref="M135:P135"/>
+    <mergeCell ref="E125:H125"/>
+    <mergeCell ref="I125:L125"/>
+    <mergeCell ref="M125:P125"/>
+    <mergeCell ref="Q135:V135"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="Q125:V125"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="Q13:V13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="Q2:V2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:V37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="Q49:V49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="Q63:V63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="M63:P63"/>
     <mergeCell ref="B114:B115"/>
     <mergeCell ref="C114:C115"/>
     <mergeCell ref="D114:D115"/>
@@ -26829,264 +27319,152 @@
     <mergeCell ref="C104:C105"/>
     <mergeCell ref="D104:D105"/>
     <mergeCell ref="B106:B107"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="Q63:V63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="Q49:V49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:V37"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="Q13:V13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:L89"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="E135:H135"/>
-    <mergeCell ref="I135:L135"/>
-    <mergeCell ref="M135:P135"/>
-    <mergeCell ref="E125:H125"/>
-    <mergeCell ref="I125:L125"/>
-    <mergeCell ref="M125:P125"/>
-    <mergeCell ref="Q135:V135"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="Q125:V125"/>
-    <mergeCell ref="Q159:V159"/>
-    <mergeCell ref="Q171:V171"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="Q147:V147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="E147:H147"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="M147:P147"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="D166:D167"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="E159:H159"/>
-    <mergeCell ref="I159:L159"/>
-    <mergeCell ref="M159:P159"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="D160:D161"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="C188:C189"/>
-    <mergeCell ref="D188:D189"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="D162:D163"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="C172:C173"/>
-    <mergeCell ref="D172:D173"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="C176:C177"/>
-    <mergeCell ref="D176:D177"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="C178:C179"/>
-    <mergeCell ref="D178:D179"/>
-    <mergeCell ref="E171:H171"/>
-    <mergeCell ref="I171:L171"/>
-    <mergeCell ref="M171:P171"/>
-    <mergeCell ref="E233:H233"/>
-    <mergeCell ref="I233:L233"/>
-    <mergeCell ref="M233:P233"/>
-    <mergeCell ref="Q233:V233"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="C234:C235"/>
-    <mergeCell ref="D234:D235"/>
-    <mergeCell ref="B236:B237"/>
-    <mergeCell ref="C236:C237"/>
-    <mergeCell ref="D236:D237"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="C238:C239"/>
-    <mergeCell ref="D238:D239"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="C240:C241"/>
-    <mergeCell ref="D240:D241"/>
-    <mergeCell ref="E245:H245"/>
-    <mergeCell ref="I245:L245"/>
-    <mergeCell ref="M245:P245"/>
-    <mergeCell ref="B252:B253"/>
-    <mergeCell ref="C252:C253"/>
-    <mergeCell ref="D252:D253"/>
-    <mergeCell ref="Q245:V245"/>
-    <mergeCell ref="B246:B247"/>
-    <mergeCell ref="C246:C247"/>
-    <mergeCell ref="D246:D247"/>
-    <mergeCell ref="B248:B249"/>
-    <mergeCell ref="C248:C249"/>
-    <mergeCell ref="D248:D249"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="C250:C251"/>
-    <mergeCell ref="D250:D251"/>
-    <mergeCell ref="E257:H257"/>
-    <mergeCell ref="I257:L257"/>
-    <mergeCell ref="M257:P257"/>
-    <mergeCell ref="Q257:V257"/>
-    <mergeCell ref="B258:B259"/>
-    <mergeCell ref="C258:C259"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="B260:B261"/>
-    <mergeCell ref="C260:C261"/>
-    <mergeCell ref="D260:D261"/>
-    <mergeCell ref="Q307:V307"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="C308:C309"/>
-    <mergeCell ref="D308:D309"/>
-    <mergeCell ref="B310:B311"/>
-    <mergeCell ref="C310:C311"/>
-    <mergeCell ref="D310:D311"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="C262:C263"/>
-    <mergeCell ref="D262:D263"/>
-    <mergeCell ref="B264:B265"/>
-    <mergeCell ref="C264:C265"/>
-    <mergeCell ref="D264:D265"/>
-    <mergeCell ref="B274:B275"/>
-    <mergeCell ref="C274:C275"/>
-    <mergeCell ref="D274:D275"/>
-    <mergeCell ref="E269:H269"/>
-    <mergeCell ref="I269:L269"/>
-    <mergeCell ref="M269:P269"/>
-    <mergeCell ref="Q269:V269"/>
-    <mergeCell ref="B270:B271"/>
-    <mergeCell ref="C270:C271"/>
-    <mergeCell ref="D270:D271"/>
-    <mergeCell ref="B272:B273"/>
-    <mergeCell ref="B312:B313"/>
-    <mergeCell ref="C312:C313"/>
-    <mergeCell ref="D312:D313"/>
-    <mergeCell ref="B314:B315"/>
-    <mergeCell ref="C314:C315"/>
-    <mergeCell ref="D314:D315"/>
-    <mergeCell ref="E307:H307"/>
-    <mergeCell ref="I307:L307"/>
-    <mergeCell ref="M307:P307"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="M113:P113"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="M77:P77"/>
+    <mergeCell ref="Q89:V89"/>
+    <mergeCell ref="M89:P89"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="Q113:V113"/>
+    <mergeCell ref="Q77:V77"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:L101"/>
+    <mergeCell ref="M101:P101"/>
+    <mergeCell ref="Q101:V101"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E195:H195"/>
+    <mergeCell ref="I195:L195"/>
+    <mergeCell ref="M195:P195"/>
+    <mergeCell ref="Q195:V195"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="D196:D197"/>
+    <mergeCell ref="Q183:V183"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="D184:D185"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
+    <mergeCell ref="E183:H183"/>
+    <mergeCell ref="I183:L183"/>
+    <mergeCell ref="M183:P183"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="D198:D199"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="D206:D207"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="D200:D201"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="D202:D203"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="D204:D205"/>
+    <mergeCell ref="E211:H211"/>
+    <mergeCell ref="I211:L211"/>
+    <mergeCell ref="M211:P211"/>
+    <mergeCell ref="Q211:V211"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="D212:D213"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="D214:D215"/>
+    <mergeCell ref="Q221:V221"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="D222:D223"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="D216:D217"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="C226:C227"/>
+    <mergeCell ref="D226:D227"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="C228:C229"/>
+    <mergeCell ref="D228:D229"/>
+    <mergeCell ref="E221:H221"/>
+    <mergeCell ref="I221:L221"/>
+    <mergeCell ref="M221:P221"/>
+    <mergeCell ref="C272:C273"/>
+    <mergeCell ref="D272:D273"/>
+    <mergeCell ref="E279:H279"/>
+    <mergeCell ref="I279:L279"/>
+    <mergeCell ref="M279:P279"/>
+    <mergeCell ref="Q279:V279"/>
+    <mergeCell ref="B280:B281"/>
+    <mergeCell ref="C280:C281"/>
+    <mergeCell ref="D280:D281"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="C282:C283"/>
+    <mergeCell ref="D282:D283"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="C284:C285"/>
+    <mergeCell ref="D284:D285"/>
+    <mergeCell ref="B286:B287"/>
+    <mergeCell ref="C286:C287"/>
+    <mergeCell ref="D286:D287"/>
+    <mergeCell ref="B288:B289"/>
+    <mergeCell ref="C288:C289"/>
+    <mergeCell ref="D288:D289"/>
+    <mergeCell ref="Q295:V295"/>
+    <mergeCell ref="B296:B297"/>
+    <mergeCell ref="C296:C297"/>
+    <mergeCell ref="D296:D297"/>
+    <mergeCell ref="B298:B299"/>
+    <mergeCell ref="C298:C299"/>
+    <mergeCell ref="D298:D299"/>
+    <mergeCell ref="B290:B291"/>
+    <mergeCell ref="C290:C291"/>
+    <mergeCell ref="D290:D291"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="C300:C301"/>
+    <mergeCell ref="D300:D301"/>
+    <mergeCell ref="B302:B303"/>
+    <mergeCell ref="C302:C303"/>
+    <mergeCell ref="D302:D303"/>
+    <mergeCell ref="E295:H295"/>
+    <mergeCell ref="I295:L295"/>
+    <mergeCell ref="M295:P295"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -27128,19 +27506,19 @@
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="D2" s="15">
         <f>SUM(D4:D95)</f>
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E2" s="15">
         <f>SUM(E4:E95)</f>
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F2" s="15">
         <f>SUM(F4:F95)</f>
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G2" s="15">
         <f>SUM(G4:G95)</f>
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H2" s="15">
         <f>SUM(H4:H95)</f>
@@ -27222,12 +27600,12 @@
         <v>김인혁</v>
       </c>
       <c r="C4" s="2">
-        <f t="shared" ref="C4:C35" si="0">((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
-        <v>2</v>
+        <f>((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D4" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B4)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B4)</f>
@@ -27246,8 +27624,8 @@
         <v>1</v>
       </c>
       <c r="I4" s="14">
-        <f t="shared" ref="I4:I35" si="1">SUM(D4:H4)</f>
-        <v>10</v>
+        <f>SUM(D4:H4)</f>
+        <v>11</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="2">
@@ -27257,35 +27635,35 @@
         <v>350</v>
       </c>
       <c r="M4" s="21">
-        <f t="shared" ref="M4:M17" si="2">VLOOKUP(L4,$B$4:$H$133,3,FALSE)</f>
+        <f t="shared" ref="M4:M18" si="0">VLOOKUP(L4,$B$4:$H$133,3,FALSE)</f>
         <v>24</v>
       </c>
       <c r="N4" s="33" t="s">
         <v>350</v>
       </c>
       <c r="O4" s="22">
-        <f t="shared" ref="O4:O15" si="3">VLOOKUP(N4,$B$4:$H$133,4,FALSE)</f>
-        <v>10</v>
+        <f t="shared" ref="O4:O16" si="1">VLOOKUP(N4,$B$4:$H$133,4,FALSE)</f>
+        <v>12</v>
       </c>
       <c r="P4" s="34" t="s">
         <v>221</v>
       </c>
       <c r="Q4" s="23">
-        <f t="shared" ref="Q4:Q16" si="4">VLOOKUP(P4,$B$4:$H$133,5,FALSE)</f>
+        <f t="shared" ref="Q4:Q16" si="2">VLOOKUP(P4,$B$4:$H$133,5,FALSE)</f>
         <v>17</v>
       </c>
       <c r="R4" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S4" s="55">
-        <f t="shared" ref="S4:S18" si="5">VLOOKUP(R4,$B$4:$H$133,6,FALSE)</f>
+        <f t="shared" ref="S4:S18" si="3">VLOOKUP(R4,$B$4:$H$133,6,FALSE)</f>
         <v>23</v>
       </c>
       <c r="T4" s="36" t="s">
         <v>42</v>
       </c>
       <c r="U4" s="56">
-        <f t="shared" ref="U4:U13" si="6">VLOOKUP(T4,$B$4:$H$133,7,FALSE)</f>
+        <f t="shared" ref="U4:U14" si="4">VLOOKUP(T4,$B$4:$H$133,7,FALSE)</f>
         <v>15</v>
       </c>
     </row>
@@ -27299,7 +27677,7 @@
         <v>신재경</v>
       </c>
       <c r="C5" s="2">
-        <f t="shared" si="0"/>
+        <f>((D5+E5+G5+H5)*0.2)+(F5*0.3)</f>
         <v>0.90000000000000013</v>
       </c>
       <c r="D5" s="14">
@@ -27323,7 +27701,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D5:H5)</f>
         <v>4</v>
       </c>
       <c r="J5" s="15"/>
@@ -27334,35 +27712,35 @@
         <v>223</v>
       </c>
       <c r="M5" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="N5" s="33" t="s">
         <v>53</v>
       </c>
       <c r="O5" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="P5" s="34" t="s">
         <v>304</v>
       </c>
       <c r="Q5" s="23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R5" s="35" t="s">
         <v>230</v>
       </c>
       <c r="S5" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="T5" s="36" t="s">
         <v>228</v>
       </c>
       <c r="U5" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
     </row>
@@ -27376,7 +27754,7 @@
         <v>정효태</v>
       </c>
       <c r="C6" s="2">
-        <f t="shared" si="0"/>
+        <f>((D6+E6+G6+H6)*0.2)+(F6*0.3)</f>
         <v>0</v>
       </c>
       <c r="D6" s="14">
@@ -27400,7 +27778,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D6:H6)</f>
         <v>0</v>
       </c>
       <c r="J6" s="15"/>
@@ -27411,35 +27789,35 @@
         <v>397</v>
       </c>
       <c r="M6" s="21">
-        <f t="shared" si="2"/>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="N6" s="33" t="s">
         <v>356</v>
       </c>
       <c r="O6" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="P6" s="34" t="s">
         <v>64</v>
       </c>
       <c r="Q6" s="23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="R6" s="35" t="s">
         <v>353</v>
       </c>
       <c r="S6" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="T6" s="36" t="s">
         <v>220</v>
       </c>
       <c r="U6" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
     </row>
@@ -27453,7 +27831,7 @@
         <v>이승민</v>
       </c>
       <c r="C7" s="2">
-        <f t="shared" si="0"/>
+        <f>((D7+E7+G7+H7)*0.2)+(F7*0.3)</f>
         <v>0</v>
       </c>
       <c r="D7" s="14">
@@ -27477,7 +27855,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D7:H7)</f>
         <v>0</v>
       </c>
       <c r="J7" s="15"/>
@@ -27488,35 +27866,35 @@
         <v>221</v>
       </c>
       <c r="M7" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="N7" s="33" t="s">
         <v>221</v>
       </c>
       <c r="O7" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="P7" s="34" t="s">
         <v>298</v>
       </c>
       <c r="Q7" s="23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="R7" s="35" t="s">
         <v>359</v>
       </c>
       <c r="S7" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="T7" s="36" t="s">
         <v>352</v>
       </c>
       <c r="U7" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
     </row>
@@ -27530,7 +27908,7 @@
         <v>이정석</v>
       </c>
       <c r="C8" s="2">
-        <f t="shared" si="0"/>
+        <f>((D8+E8+G8+H8)*0.2)+(F8*0.3)</f>
         <v>0</v>
       </c>
       <c r="D8" s="14">
@@ -27554,7 +27932,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D8:H8)</f>
         <v>0</v>
       </c>
       <c r="J8" s="15"/>
@@ -27562,38 +27940,38 @@
         <v>5</v>
       </c>
       <c r="L8" s="32" t="s">
-        <v>231</v>
+        <v>352</v>
       </c>
       <c r="M8" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="N8" s="33" t="s">
         <v>50</v>
       </c>
       <c r="O8" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="P8" s="34" t="s">
         <v>53</v>
       </c>
       <c r="Q8" s="23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="R8" s="35" t="s">
         <v>232</v>
       </c>
       <c r="S8" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="T8" s="36" t="s">
         <v>353</v>
       </c>
       <c r="U8" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
     </row>
@@ -27607,7 +27985,7 @@
         <v>강종찬</v>
       </c>
       <c r="C9" s="2">
-        <f t="shared" si="0"/>
+        <f>((D9+E9+G9+H9)*0.2)+(F9*0.3)</f>
         <v>1</v>
       </c>
       <c r="D9" s="14">
@@ -27631,7 +28009,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D9:H9)</f>
         <v>5</v>
       </c>
       <c r="J9" s="15"/>
@@ -27639,38 +28017,38 @@
         <v>6</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>352</v>
+        <v>231</v>
       </c>
       <c r="M9" s="21">
-        <f t="shared" si="2"/>
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="N9" s="33" t="s">
         <v>223</v>
       </c>
       <c r="O9" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="P9" s="34" t="s">
         <v>7</v>
       </c>
       <c r="Q9" s="23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="R9" s="35" t="s">
-        <v>391</v>
+        <v>62</v>
       </c>
       <c r="S9" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="T9" s="36" t="s">
         <v>396</v>
       </c>
       <c r="U9" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
     </row>
@@ -27684,7 +28062,7 @@
         <v>강관석</v>
       </c>
       <c r="C10" s="2">
-        <f t="shared" si="0"/>
+        <f>((D10+E10+G10+H10)*0.2)+(F10*0.3)</f>
         <v>3.6</v>
       </c>
       <c r="D10" s="14">
@@ -27708,7 +28086,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D10:H10)</f>
         <v>14</v>
       </c>
       <c r="J10" s="15"/>
@@ -27716,38 +28094,38 @@
         <v>7</v>
       </c>
       <c r="L10" s="32" t="s">
-        <v>356</v>
+        <v>228</v>
       </c>
       <c r="M10" s="21">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="N10" s="33" t="s">
         <v>313</v>
       </c>
       <c r="O10" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="P10" s="34" t="s">
         <v>375</v>
       </c>
       <c r="Q10" s="23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="R10" s="35" t="s">
-        <v>62</v>
+        <v>391</v>
       </c>
       <c r="S10" s="55">
-        <f t="shared" si="5"/>
-        <v>14</v>
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="T10" s="36" t="s">
         <v>298</v>
       </c>
       <c r="U10" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
@@ -27761,8 +28139,8 @@
         <v>강기혁</v>
       </c>
       <c r="C11" s="2">
-        <f t="shared" si="0"/>
-        <v>5.3000000000000007</v>
+        <f>((D11+E11+G11+H11)*0.2)+(F11*0.3)</f>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D11" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B11)</f>
@@ -27774,7 +28152,7 @@
       </c>
       <c r="F11" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B11)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B11)</f>
@@ -27785,46 +28163,46 @@
         <v>0</v>
       </c>
       <c r="I11" s="14">
-        <f t="shared" si="1"/>
-        <v>25</v>
+        <f>SUM(D11:H11)</f>
+        <v>26</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="2">
         <v>8</v>
       </c>
       <c r="L11" s="32" t="s">
-        <v>228</v>
+        <v>356</v>
       </c>
       <c r="M11" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N11" s="33" t="s">
         <v>7</v>
       </c>
       <c r="O11" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="P11" s="34" t="s">
         <v>381</v>
       </c>
       <c r="Q11" s="23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="R11" s="35" t="s">
         <v>302</v>
       </c>
       <c r="S11" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="T11" s="36" t="s">
         <v>299</v>
       </c>
       <c r="U11" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
@@ -27838,7 +28216,7 @@
         <v>강도일</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" si="0"/>
+        <f>((D12+E12+G12+H12)*0.2)+(F12*0.3)</f>
         <v>0</v>
       </c>
       <c r="D12" s="14">
@@ -27862,7 +28240,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D12:H12)</f>
         <v>0</v>
       </c>
       <c r="J12" s="15"/>
@@ -27870,38 +28248,38 @@
         <v>9</v>
       </c>
       <c r="L12" s="32" t="s">
-        <v>406</v>
+        <v>304</v>
       </c>
       <c r="M12" s="21">
-        <f t="shared" si="2"/>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="N12" s="33" t="s">
-        <v>352</v>
+        <v>397</v>
       </c>
       <c r="O12" s="22">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="P12" s="34" t="s">
         <v>299</v>
       </c>
       <c r="Q12" s="23">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="R12" s="35" t="s">
         <v>308</v>
       </c>
       <c r="S12" s="55">
-        <f t="shared" si="5"/>
-        <v>11</v>
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="T12" s="36" t="s">
         <v>360</v>
       </c>
       <c r="U12" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
@@ -27915,7 +28293,7 @@
         <v>강일수</v>
       </c>
       <c r="C13" s="2">
-        <f t="shared" si="0"/>
+        <f>((D13+E13+G13+H13)*0.2)+(F13*0.3)</f>
         <v>0</v>
       </c>
       <c r="D13" s="14">
@@ -27939,7 +28317,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D13:H13)</f>
         <v>0</v>
       </c>
       <c r="J13" s="15"/>
@@ -27947,38 +28325,38 @@
         <v>10</v>
       </c>
       <c r="L13" s="32" t="s">
-        <v>304</v>
+        <v>406</v>
       </c>
       <c r="M13" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="O13" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="P13" s="34" t="s">
         <v>313</v>
       </c>
       <c r="Q13" s="23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="R13" s="35" t="s">
         <v>34</v>
       </c>
       <c r="S13" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="T13" s="36" t="s">
         <v>359</v>
       </c>
       <c r="U13" s="56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
@@ -27992,7 +28370,7 @@
         <v>구교훈</v>
       </c>
       <c r="C14" s="2">
-        <f t="shared" si="0"/>
+        <f>((D14+E14+G14+H14)*0.2)+(F14*0.3)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
@@ -28016,7 +28394,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D14:H14)</f>
         <v>0</v>
       </c>
       <c r="J14" s="15"/>
@@ -28027,32 +28405,37 @@
         <v>314</v>
       </c>
       <c r="M14" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="O14" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="P14" s="34" t="s">
         <v>402</v>
       </c>
       <c r="Q14" s="23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="R14" s="55" t="s">
         <v>221</v>
       </c>
       <c r="S14" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="T14" s="36"/>
-      <c r="U14" s="56"/>
+      <c r="T14" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="U14" s="56">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -28064,7 +28447,7 @@
         <v>권민강</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" si="0"/>
+        <f>((D15+E15+G15+H15)*0.2)+(F15*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D15" s="14">
@@ -28088,7 +28471,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D15:H15)</f>
         <v>3</v>
       </c>
       <c r="J15" s="15"/>
@@ -28099,28 +28482,28 @@
         <v>220</v>
       </c>
       <c r="M15" s="21">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="O15" s="22">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q15" s="23">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N15" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="O15" s="22">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="P15" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q15" s="23">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
       <c r="R15" s="55" t="s">
         <v>241</v>
       </c>
       <c r="S15" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T15" s="56"/>
@@ -28136,8 +28519,8 @@
         <v>김기문</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
+        <f>((D16+E16+G16+H16)*0.2)+(F16*0.3)</f>
+        <v>3.8</v>
       </c>
       <c r="D16" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B16)</f>
@@ -28149,7 +28532,7 @@
       </c>
       <c r="F16" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B16)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B16)</f>
@@ -28160,34 +28543,39 @@
         <v>2</v>
       </c>
       <c r="I16" s="14">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <f>SUM(D16:H16)</f>
+        <v>16</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="2">
         <v>13</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>460</v>
+        <v>50</v>
       </c>
       <c r="M16" s="21">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="N16" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="O16" s="22">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="P16" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q16" s="23">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q16" s="23">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
       <c r="R16" s="55" t="s">
         <v>360</v>
       </c>
       <c r="S16" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T16" s="56"/>
@@ -28203,7 +28591,7 @@
         <v>김기태</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" si="0"/>
+        <f>((D17+E17+G17+H17)*0.2)+(F17*0.3)</f>
         <v>3.8000000000000003</v>
       </c>
       <c r="D17" s="14">
@@ -28227,7 +28615,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D17:H17)</f>
         <v>19</v>
       </c>
       <c r="J17" s="15"/>
@@ -28235,21 +28623,23 @@
         <v>14</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>382</v>
+        <v>460</v>
       </c>
       <c r="M17" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="N17" s="22"/>
       <c r="O17" s="22"/>
-      <c r="P17" s="23"/>
+      <c r="P17" s="23" t="s">
+        <v>316</v>
+      </c>
       <c r="Q17" s="23"/>
       <c r="R17" s="55" t="s">
         <v>67</v>
       </c>
       <c r="S17" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="T17" s="56"/>
@@ -28265,7 +28655,7 @@
         <v>김덕준</v>
       </c>
       <c r="C18" s="2">
-        <f t="shared" si="0"/>
+        <f>((D18+E18+G18+H18)*0.2)+(F18*0.3)</f>
         <v>0</v>
       </c>
       <c r="D18" s="14">
@@ -28289,15 +28679,20 @@
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D18:H18)</f>
         <v>0</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="2">
         <v>15</v>
       </c>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
+      <c r="L18" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="M18" s="21">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
       <c r="N18" s="22"/>
       <c r="O18" s="22"/>
       <c r="P18" s="23"/>
@@ -28306,7 +28701,7 @@
         <v>229</v>
       </c>
       <c r="S18" s="55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="T18" s="56"/>
@@ -28322,7 +28717,7 @@
         <v>김도원</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" si="0"/>
+        <f>((D19+E19+G19+H19)*0.2)+(F19*0.3)</f>
         <v>0</v>
       </c>
       <c r="D19" s="14">
@@ -28346,7 +28741,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D19:H19)</f>
         <v>0</v>
       </c>
       <c r="J19" s="15"/>
@@ -28361,7 +28756,7 @@
         <v>김민섭</v>
       </c>
       <c r="C20" s="2">
-        <f t="shared" si="0"/>
+        <f>((D20+E20+G20+H20)*0.2)+(F20*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D20" s="14">
@@ -28385,7 +28780,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D20:H20)</f>
         <v>2</v>
       </c>
       <c r="J20" s="15"/>
@@ -28400,7 +28795,7 @@
         <v>김민찬</v>
       </c>
       <c r="C21" s="2">
-        <f t="shared" si="0"/>
+        <f>((D21+E21+G21+H21)*0.2)+(F21*0.3)</f>
         <v>0</v>
       </c>
       <c r="D21" s="14">
@@ -28424,7 +28819,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D21:H21)</f>
         <v>0</v>
       </c>
       <c r="J21" s="15"/>
@@ -28439,7 +28834,7 @@
         <v>김범기</v>
       </c>
       <c r="C22" s="2">
-        <f t="shared" si="0"/>
+        <f>((D22+E22+G22+H22)*0.2)+(F22*0.3)</f>
         <v>0</v>
       </c>
       <c r="D22" s="14">
@@ -28463,7 +28858,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D22:H22)</f>
         <v>0</v>
       </c>
       <c r="J22" s="15"/>
@@ -28478,7 +28873,7 @@
         <v>김병준</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" si="0"/>
+        <f>((D23+E23+G23+H23)*0.2)+(F23*0.3)</f>
         <v>0</v>
       </c>
       <c r="D23" s="14">
@@ -28502,7 +28897,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D23:H23)</f>
         <v>0</v>
       </c>
       <c r="J23" s="15"/>
@@ -28517,7 +28912,7 @@
         <v>김부건</v>
       </c>
       <c r="C24" s="2">
-        <f t="shared" si="0"/>
+        <f>((D24+E24+G24+H24)*0.2)+(F24*0.3)</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="D24" s="14">
@@ -28541,7 +28936,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D24:H24)</f>
         <v>5</v>
       </c>
       <c r="J24" s="15"/>
@@ -28556,7 +28951,7 @@
         <v>김성수</v>
       </c>
       <c r="C25" s="2">
-        <f t="shared" si="0"/>
+        <f>((D25+E25+G25+H25)*0.2)+(F25*0.3)</f>
         <v>2.9000000000000004</v>
       </c>
       <c r="D25" s="14">
@@ -28580,7 +28975,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D25:H25)</f>
         <v>11</v>
       </c>
       <c r="J25" s="15"/>
@@ -28595,7 +28990,7 @@
         <v>김성준</v>
       </c>
       <c r="C26" s="2">
-        <f t="shared" si="0"/>
+        <f>((D26+E26+G26+H26)*0.2)+(F26*0.3)</f>
         <v>10.7</v>
       </c>
       <c r="D26" s="14">
@@ -28619,7 +29014,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D26:H26)</f>
         <v>45</v>
       </c>
       <c r="J26" s="15"/>
@@ -28634,7 +29029,7 @@
         <v>김송환</v>
       </c>
       <c r="C27" s="2">
-        <f t="shared" si="0"/>
+        <f>((D27+E27+G27+H27)*0.2)+(F27*0.3)</f>
         <v>3.0999999999999996</v>
       </c>
       <c r="D27" s="14">
@@ -28658,7 +29053,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D27:H27)</f>
         <v>11</v>
       </c>
       <c r="J27" s="15"/>
@@ -28673,7 +29068,7 @@
         <v>김영태</v>
       </c>
       <c r="C28" s="2">
-        <f t="shared" si="0"/>
+        <f>((D28+E28+G28+H28)*0.2)+(F28*0.3)</f>
         <v>0</v>
       </c>
       <c r="D28" s="14">
@@ -28697,7 +29092,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D28:H28)</f>
         <v>0</v>
       </c>
       <c r="J28" s="15"/>
@@ -28712,7 +29107,7 @@
         <v>김용빈</v>
       </c>
       <c r="C29" s="2">
-        <f t="shared" si="0"/>
+        <f>((D29+E29+G29+H29)*0.2)+(F29*0.3)</f>
         <v>0</v>
       </c>
       <c r="D29" s="14">
@@ -28736,7 +29131,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D29:H29)</f>
         <v>0</v>
       </c>
       <c r="J29" s="15"/>
@@ -28751,7 +29146,7 @@
         <v>김용현</v>
       </c>
       <c r="C30" s="2">
-        <f t="shared" si="0"/>
+        <f>((D30+E30+G30+H30)*0.2)+(F30*0.3)</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="D30" s="14">
@@ -28775,7 +29170,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D30:H30)</f>
         <v>19</v>
       </c>
       <c r="J30" s="15"/>
@@ -28790,16 +29185,16 @@
         <v>김우인</v>
       </c>
       <c r="C31" s="2">
-        <f t="shared" si="0"/>
-        <v>5.2</v>
+        <f>((D31+E31+G31+H31)*0.2)+(F31*0.3)</f>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D31" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B31)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E31" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B31)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B31)</f>
@@ -28814,8 +29209,8 @@
         <v>12</v>
       </c>
       <c r="I31" s="14">
-        <f t="shared" si="1"/>
-        <v>26</v>
+        <f>SUM(D31:H31)</f>
+        <v>28</v>
       </c>
       <c r="J31" s="15"/>
     </row>
@@ -28829,7 +29224,7 @@
         <v>김종준</v>
       </c>
       <c r="C32" s="2">
-        <f t="shared" si="0"/>
+        <f>((D32+E32+G32+H32)*0.2)+(F32*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D32" s="14">
@@ -28853,7 +29248,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D32:H32)</f>
         <v>2</v>
       </c>
       <c r="J32" s="15"/>
@@ -28868,12 +29263,12 @@
         <v>김종혁</v>
       </c>
       <c r="C33" s="2">
-        <f t="shared" si="0"/>
-        <v>4.4000000000000004</v>
+        <f>((D33+E33+G33+H33)*0.2)+(F33*0.3)</f>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D33" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B33)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E33" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B33)</f>
@@ -28892,8 +29287,8 @@
         <v>3</v>
       </c>
       <c r="I33" s="14">
-        <f t="shared" si="1"/>
-        <v>21</v>
+        <f>SUM(D33:H33)</f>
+        <v>22</v>
       </c>
       <c r="J33" s="15"/>
     </row>
@@ -28907,7 +29302,7 @@
         <v>김진형</v>
       </c>
       <c r="C34" s="2">
-        <f t="shared" si="0"/>
+        <f>((D34+E34+G34+H34)*0.2)+(F34*0.3)</f>
         <v>0</v>
       </c>
       <c r="D34" s="14">
@@ -28931,7 +29326,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="14">
-        <f t="shared" si="1"/>
+        <f>SUM(D34:H34)</f>
         <v>0</v>
       </c>
       <c r="J34" s="15"/>
@@ -28946,8 +29341,8 @@
         <v>김진호</v>
       </c>
       <c r="C35" s="2">
-        <f t="shared" si="0"/>
-        <v>6.8000000000000007</v>
+        <f>((D35+E35+G35+H35)*0.2)+(F35*0.3)</f>
+        <v>7.2</v>
       </c>
       <c r="D35" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B35)</f>
@@ -28955,7 +29350,7 @@
       </c>
       <c r="E35" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B35)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F35" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B35)</f>
@@ -28970,8 +29365,8 @@
         <v>0</v>
       </c>
       <c r="I35" s="14">
-        <f t="shared" si="1"/>
-        <v>34</v>
+        <f>SUM(D35:H35)</f>
+        <v>36</v>
       </c>
       <c r="J35" s="15"/>
     </row>
@@ -28985,7 +29380,7 @@
         <v>김태성</v>
       </c>
       <c r="C36" s="2">
-        <f t="shared" ref="C36:C67" si="7">((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
+        <f>((D36+E36+G36+H36)*0.2)+(F36*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D36" s="14">
@@ -29009,7 +29404,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="14">
-        <f t="shared" ref="I36:I67" si="8">SUM(D36:H36)</f>
+        <f>SUM(D36:H36)</f>
         <v>3</v>
       </c>
       <c r="J36" s="15"/>
@@ -29024,7 +29419,7 @@
         <v>김태양</v>
       </c>
       <c r="C37" s="2">
-        <f t="shared" si="7"/>
+        <f>((D37+E37+G37+H37)*0.2)+(F37*0.3)</f>
         <v>0</v>
       </c>
       <c r="D37" s="14">
@@ -29048,7 +29443,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D37:H37)</f>
         <v>0</v>
       </c>
       <c r="J37" s="15"/>
@@ -29063,7 +29458,7 @@
         <v>김태완</v>
       </c>
       <c r="C38" s="2">
-        <f t="shared" si="7"/>
+        <f>((D38+E38+G38+H38)*0.2)+(F38*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D38" s="14">
@@ -29087,7 +29482,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D38:H38)</f>
         <v>2</v>
       </c>
       <c r="J38" s="15"/>
@@ -29102,7 +29497,7 @@
         <v>김태호</v>
       </c>
       <c r="C39" s="2">
-        <f t="shared" si="7"/>
+        <f>((D39+E39+G39+H39)*0.2)+(F39*0.3)</f>
         <v>0</v>
       </c>
       <c r="D39" s="14">
@@ -29126,7 +29521,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D39:H39)</f>
         <v>0</v>
       </c>
       <c r="J39" s="15"/>
@@ -29141,7 +29536,7 @@
         <v>김현우</v>
       </c>
       <c r="C40" s="2">
-        <f t="shared" si="7"/>
+        <f>((D40+E40+G40+H40)*0.2)+(F40*0.3)</f>
         <v>0</v>
       </c>
       <c r="D40" s="14">
@@ -29165,7 +29560,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D40:H40)</f>
         <v>0</v>
       </c>
       <c r="J40" s="15"/>
@@ -29180,7 +29575,7 @@
         <v>김형원</v>
       </c>
       <c r="C41" s="2">
-        <f t="shared" si="7"/>
+        <f>((D41+E41+G41+H41)*0.2)+(F41*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D41" s="14">
@@ -29204,7 +29599,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D41:H41)</f>
         <v>2</v>
       </c>
       <c r="J41" s="15"/>
@@ -29219,7 +29614,7 @@
         <v>노민준</v>
       </c>
       <c r="C42" s="2">
-        <f t="shared" si="7"/>
+        <f>((D42+E42+G42+H42)*0.2)+(F42*0.3)</f>
         <v>4.6000000000000005</v>
       </c>
       <c r="D42" s="14">
@@ -29243,7 +29638,7 @@
         <v>3</v>
       </c>
       <c r="I42" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D42:H42)</f>
         <v>23</v>
       </c>
       <c r="J42" s="15"/>
@@ -29258,16 +29653,16 @@
         <v>노성호</v>
       </c>
       <c r="C43" s="2">
-        <f t="shared" si="7"/>
-        <v>0.5</v>
+        <f>((D43+E43+G43+H43)*0.2)+(F43*0.3)</f>
+        <v>0.90000000000000013</v>
       </c>
       <c r="D43" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B43)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B43)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B43)</f>
@@ -29282,8 +29677,8 @@
         <v>0</v>
       </c>
       <c r="I43" s="14">
-        <f t="shared" si="8"/>
-        <v>2</v>
+        <f>SUM(D43:H43)</f>
+        <v>4</v>
       </c>
       <c r="J43" s="15"/>
     </row>
@@ -29297,7 +29692,7 @@
         <v>류서진</v>
       </c>
       <c r="C44" s="2">
-        <f t="shared" si="7"/>
+        <f>((D44+E44+G44+H44)*0.2)+(F44*0.3)</f>
         <v>2.4</v>
       </c>
       <c r="D44" s="14">
@@ -29321,7 +29716,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D44:H44)</f>
         <v>11</v>
       </c>
       <c r="J44" s="15"/>
@@ -29336,7 +29731,7 @@
         <v>마창기</v>
       </c>
       <c r="C45" s="2">
-        <f t="shared" si="7"/>
+        <f>((D45+E45+G45+H45)*0.2)+(F45*0.3)</f>
         <v>0</v>
       </c>
       <c r="D45" s="14">
@@ -29360,7 +29755,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D45:H45)</f>
         <v>0</v>
       </c>
       <c r="J45" s="15"/>
@@ -29375,7 +29770,7 @@
         <v>문준수</v>
       </c>
       <c r="C46" s="2">
-        <f t="shared" si="7"/>
+        <f>((D46+E46+G46+H46)*0.2)+(F46*0.3)</f>
         <v>3.4000000000000004</v>
       </c>
       <c r="D46" s="14">
@@ -29399,7 +29794,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D46:H46)</f>
         <v>17</v>
       </c>
       <c r="J46" s="15"/>
@@ -29414,7 +29809,7 @@
         <v>민건호</v>
       </c>
       <c r="C47" s="2">
-        <f t="shared" si="7"/>
+        <f>((D47+E47+G47+H47)*0.2)+(F47*0.3)</f>
         <v>0</v>
       </c>
       <c r="D47" s="14">
@@ -29438,7 +29833,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D47:H47)</f>
         <v>0</v>
       </c>
       <c r="J47" s="15"/>
@@ -29453,7 +29848,7 @@
         <v>박수천</v>
       </c>
       <c r="C48" s="2">
-        <f t="shared" si="7"/>
+        <f>((D48+E48+G48+H48)*0.2)+(F48*0.3)</f>
         <v>0</v>
       </c>
       <c r="D48" s="14">
@@ -29477,7 +29872,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D48:H48)</f>
         <v>0</v>
       </c>
       <c r="J48" s="15"/>
@@ -29492,7 +29887,7 @@
         <v>박정호</v>
       </c>
       <c r="C49" s="2">
-        <f t="shared" si="7"/>
+        <f>((D49+E49+G49+H49)*0.2)+(F49*0.3)</f>
         <v>0</v>
       </c>
       <c r="D49" s="14">
@@ -29516,7 +29911,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D49:H49)</f>
         <v>0</v>
       </c>
       <c r="J49" s="15"/>
@@ -29531,7 +29926,7 @@
         <v>박주연</v>
       </c>
       <c r="C50" s="2">
-        <f t="shared" si="7"/>
+        <f>((D50+E50+G50+H50)*0.2)+(F50*0.3)</f>
         <v>2.4000000000000004</v>
       </c>
       <c r="D50" s="14">
@@ -29555,7 +29950,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D50:H50)</f>
         <v>12</v>
       </c>
       <c r="J50" s="15"/>
@@ -29570,7 +29965,7 @@
         <v>박주현</v>
       </c>
       <c r="C51" s="2">
-        <f t="shared" si="7"/>
+        <f>((D51+E51+G51+H51)*0.2)+(F51*0.3)</f>
         <v>0</v>
       </c>
       <c r="D51" s="14">
@@ -29594,7 +29989,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D51:H51)</f>
         <v>0</v>
       </c>
       <c r="J51" s="15"/>
@@ -29609,7 +30004,7 @@
         <v>박준영</v>
       </c>
       <c r="C52" s="2">
-        <f t="shared" si="7"/>
+        <f>((D52+E52+G52+H52)*0.2)+(F52*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D52" s="14">
@@ -29633,7 +30028,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D52:H52)</f>
         <v>2</v>
       </c>
       <c r="J52" s="15"/>
@@ -29648,7 +30043,7 @@
         <v>박태현</v>
       </c>
       <c r="C53" s="2">
-        <f t="shared" si="7"/>
+        <f>((D53+E53+G53+H53)*0.2)+(F53*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D53" s="14">
@@ -29672,7 +30067,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D53:H53)</f>
         <v>2</v>
       </c>
       <c r="J53" s="15"/>
@@ -29687,7 +30082,7 @@
         <v>박하빈</v>
       </c>
       <c r="C54" s="2">
-        <f t="shared" si="7"/>
+        <f>((D54+E54+G54+H54)*0.2)+(F54*0.3)</f>
         <v>0</v>
       </c>
       <c r="D54" s="14">
@@ -29711,7 +30106,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D54:H54)</f>
         <v>0</v>
       </c>
       <c r="J54" s="15"/>
@@ -29726,7 +30121,7 @@
         <v>박형기</v>
       </c>
       <c r="C55" s="2">
-        <f t="shared" si="7"/>
+        <f>((D55+E55+G55+H55)*0.2)+(F55*0.3)</f>
         <v>0</v>
       </c>
       <c r="D55" s="14">
@@ -29750,7 +30145,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D55:H55)</f>
         <v>0</v>
       </c>
       <c r="J55" s="15"/>
@@ -29765,7 +30160,7 @@
         <v>손경호</v>
       </c>
       <c r="C56" s="2">
-        <f t="shared" si="7"/>
+        <f>((D56+E56+G56+H56)*0.2)+(F56*0.3)</f>
         <v>3.6</v>
       </c>
       <c r="D56" s="14">
@@ -29789,7 +30184,7 @@
         <v>5</v>
       </c>
       <c r="I56" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D56:H56)</f>
         <v>18</v>
       </c>
       <c r="J56" s="15"/>
@@ -29804,7 +30199,7 @@
         <v>송윤상</v>
       </c>
       <c r="C57" s="2">
-        <f t="shared" si="7"/>
+        <f>((D57+E57+G57+H57)*0.2)+(F57*0.3)</f>
         <v>0.6</v>
       </c>
       <c r="D57" s="14">
@@ -29828,7 +30223,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D57:H57)</f>
         <v>2</v>
       </c>
       <c r="J57" s="15"/>
@@ -29843,7 +30238,7 @@
         <v>신기웅</v>
       </c>
       <c r="C58" s="2">
-        <f t="shared" si="7"/>
+        <f>((D58+E58+G58+H58)*0.2)+(F58*0.3)</f>
         <v>2.1</v>
       </c>
       <c r="D58" s="14">
@@ -29867,7 +30262,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D58:H58)</f>
         <v>10</v>
       </c>
       <c r="J58" s="15"/>
@@ -29882,7 +30277,7 @@
         <v>신종훈</v>
       </c>
       <c r="C59" s="2">
-        <f t="shared" si="7"/>
+        <f>((D59+E59+G59+H59)*0.2)+(F59*0.3)</f>
         <v>0</v>
       </c>
       <c r="D59" s="14">
@@ -29906,7 +30301,7 @@
         <v>0</v>
       </c>
       <c r="I59" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D59:H59)</f>
         <v>0</v>
       </c>
       <c r="J59" s="15"/>
@@ -29921,7 +30316,7 @@
         <v>안진혁</v>
       </c>
       <c r="C60" s="2">
-        <f t="shared" si="7"/>
+        <f>((D60+E60+G60+H60)*0.2)+(F60*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D60" s="14">
@@ -29945,7 +30340,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D60:H60)</f>
         <v>3</v>
       </c>
       <c r="J60" s="15"/>
@@ -29960,7 +30355,7 @@
         <v>양진웅</v>
       </c>
       <c r="C61" s="2">
-        <f t="shared" si="7"/>
+        <f>((D61+E61+G61+H61)*0.2)+(F61*0.3)</f>
         <v>2</v>
       </c>
       <c r="D61" s="14">
@@ -29984,7 +30379,7 @@
         <v>1</v>
       </c>
       <c r="I61" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D61:H61)</f>
         <v>8</v>
       </c>
       <c r="J61" s="15"/>
@@ -29999,7 +30394,7 @@
         <v>오상준</v>
       </c>
       <c r="C62" s="2">
-        <f t="shared" si="7"/>
+        <f>((D62+E62+G62+H62)*0.2)+(F62*0.3)</f>
         <v>3.7</v>
       </c>
       <c r="D62" s="14">
@@ -30023,7 +30418,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D62:H62)</f>
         <v>15</v>
       </c>
       <c r="J62" s="15"/>
@@ -30038,7 +30433,7 @@
         <v>오성찬</v>
       </c>
       <c r="C63" s="2">
-        <f t="shared" si="7"/>
+        <f>((D63+E63+G63+H63)*0.2)+(F63*0.3)</f>
         <v>0.3</v>
       </c>
       <c r="D63" s="14">
@@ -30062,7 +30457,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D63:H63)</f>
         <v>1</v>
       </c>
       <c r="J63" s="15"/>
@@ -30077,7 +30472,7 @@
         <v>오우영</v>
       </c>
       <c r="C64" s="2">
-        <f t="shared" si="7"/>
+        <f>((D64+E64+G64+H64)*0.2)+(F64*0.3)</f>
         <v>2.9000000000000004</v>
       </c>
       <c r="D64" s="14">
@@ -30101,7 +30496,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D64:H64)</f>
         <v>12</v>
       </c>
       <c r="J64" s="15"/>
@@ -30116,7 +30511,7 @@
         <v>오운용</v>
       </c>
       <c r="C65" s="2">
-        <f t="shared" si="7"/>
+        <f>((D65+E65+G65+H65)*0.2)+(F65*0.3)</f>
         <v>0</v>
       </c>
       <c r="D65" s="14">
@@ -30140,7 +30535,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D65:H65)</f>
         <v>0</v>
       </c>
       <c r="J65" s="15"/>
@@ -30155,7 +30550,7 @@
         <v>오준서</v>
       </c>
       <c r="C66" s="2">
-        <f t="shared" si="7"/>
+        <f>((D66+E66+G66+H66)*0.2)+(F66*0.3)</f>
         <v>0</v>
       </c>
       <c r="D66" s="14">
@@ -30179,7 +30574,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D66:H66)</f>
         <v>0</v>
       </c>
       <c r="J66" s="15"/>
@@ -30194,7 +30589,7 @@
         <v>우보광</v>
       </c>
       <c r="C67" s="2">
-        <f t="shared" si="7"/>
+        <f>((D67+E67+G67+H67)*0.2)+(F67*0.3)</f>
         <v>0</v>
       </c>
       <c r="D67" s="14">
@@ -30218,7 +30613,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="14">
-        <f t="shared" si="8"/>
+        <f>SUM(D67:H67)</f>
         <v>0</v>
       </c>
       <c r="J67" s="15"/>
@@ -30233,7 +30628,7 @@
         <v>유상근</v>
       </c>
       <c r="C68" s="2">
-        <f t="shared" ref="C68:C99" si="9">((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
+        <f>((D68+E68+G68+H68)*0.2)+(F68*0.3)</f>
         <v>5</v>
       </c>
       <c r="D68" s="14">
@@ -30257,7 +30652,7 @@
         <v>1</v>
       </c>
       <c r="I68" s="14">
-        <f t="shared" ref="I68:I99" si="10">SUM(D68:H68)</f>
+        <f>SUM(D68:H68)</f>
         <v>25</v>
       </c>
       <c r="J68" s="15"/>
@@ -30272,7 +30667,7 @@
         <v>유우진</v>
       </c>
       <c r="C69" s="2">
-        <f t="shared" si="9"/>
+        <f>((D69+E69+G69+H69)*0.2)+(F69*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D69" s="14">
@@ -30296,7 +30691,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D69:H69)</f>
         <v>2</v>
       </c>
       <c r="J69" s="15"/>
@@ -30311,7 +30706,7 @@
         <v>유인상</v>
       </c>
       <c r="C70" s="2">
-        <f t="shared" si="9"/>
+        <f>((D70+E70+G70+H70)*0.2)+(F70*0.3)</f>
         <v>0.8</v>
       </c>
       <c r="D70" s="14">
@@ -30335,7 +30730,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D70:H70)</f>
         <v>3</v>
       </c>
       <c r="J70" s="15"/>
@@ -30350,7 +30745,7 @@
         <v>유정훈</v>
       </c>
       <c r="C71" s="2">
-        <f t="shared" si="9"/>
+        <f>((D71+E71+G71+H71)*0.2)+(F71*0.3)</f>
         <v>1.5</v>
       </c>
       <c r="D71" s="14">
@@ -30374,7 +30769,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D71:H71)</f>
         <v>6</v>
       </c>
       <c r="J71" s="15"/>
@@ -30389,7 +30784,7 @@
         <v>유진효</v>
       </c>
       <c r="C72" s="2">
-        <f t="shared" si="9"/>
+        <f>((D72+E72+G72+H72)*0.2)+(F72*0.3)</f>
         <v>0</v>
       </c>
       <c r="D72" s="14">
@@ -30413,7 +30808,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D72:H72)</f>
         <v>0</v>
       </c>
       <c r="J72" s="15"/>
@@ -30428,7 +30823,7 @@
         <v>윤원택</v>
       </c>
       <c r="C73" s="2">
-        <f t="shared" si="9"/>
+        <f>((D73+E73+G73+H73)*0.2)+(F73*0.3)</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="D73" s="14">
@@ -30452,7 +30847,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D73:H73)</f>
         <v>5</v>
       </c>
       <c r="J73" s="15"/>
@@ -30467,7 +30862,7 @@
         <v>윤창현</v>
       </c>
       <c r="C74" s="2">
-        <f t="shared" si="9"/>
+        <f>((D74+E74+G74+H74)*0.2)+(F74*0.3)</f>
         <v>1.6</v>
       </c>
       <c r="D74" s="14">
@@ -30491,7 +30886,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D74:H74)</f>
         <v>8</v>
       </c>
       <c r="J74" s="15"/>
@@ -30506,7 +30901,7 @@
         <v>윤현기</v>
       </c>
       <c r="C75" s="2">
-        <f t="shared" si="9"/>
+        <f>((D75+E75+G75+H75)*0.2)+(F75*0.3)</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="D75" s="14">
@@ -30530,7 +30925,7 @@
         <v>1</v>
       </c>
       <c r="I75" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D75:H75)</f>
         <v>5</v>
       </c>
       <c r="J75" s="15"/>
@@ -30545,7 +30940,7 @@
         <v>이경석</v>
       </c>
       <c r="C76" s="2">
-        <f t="shared" si="9"/>
+        <f>((D76+E76+G76+H76)*0.2)+(F76*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D76" s="14">
@@ -30569,7 +30964,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D76:H76)</f>
         <v>3</v>
       </c>
       <c r="J76" s="15"/>
@@ -30584,7 +30979,7 @@
         <v>이민재</v>
       </c>
       <c r="C77" s="2">
-        <f t="shared" si="9"/>
+        <f>((D77+E77+G77+H77)*0.2)+(F77*0.3)</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="D77" s="14">
@@ -30608,7 +31003,7 @@
         <v>3</v>
       </c>
       <c r="I77" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D77:H77)</f>
         <v>3</v>
       </c>
       <c r="J77" s="15"/>
@@ -30623,7 +31018,7 @@
         <v>이병현</v>
       </c>
       <c r="C78" s="2">
-        <f t="shared" si="9"/>
+        <f>((D78+E78+G78+H78)*0.2)+(F78*0.3)</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="D78" s="14">
@@ -30647,7 +31042,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D78:H78)</f>
         <v>6</v>
       </c>
       <c r="J78" s="15"/>
@@ -30662,7 +31057,7 @@
         <v>이상민</v>
       </c>
       <c r="C79" s="2">
-        <f t="shared" si="9"/>
+        <f>((D79+E79+G79+H79)*0.2)+(F79*0.3)</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="D79" s="14">
@@ -30686,7 +31081,7 @@
         <v>0</v>
       </c>
       <c r="I79" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D79:H79)</f>
         <v>6</v>
       </c>
       <c r="J79" s="15"/>
@@ -30701,7 +31096,7 @@
         <v>이상현</v>
       </c>
       <c r="C80" s="2">
-        <f t="shared" si="9"/>
+        <f>((D80+E80+G80+H80)*0.2)+(F80*0.3)</f>
         <v>4</v>
       </c>
       <c r="D80" s="14">
@@ -30725,7 +31120,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D80:H80)</f>
         <v>16</v>
       </c>
       <c r="J80" s="15"/>
@@ -30740,7 +31135,7 @@
         <v>이새샘</v>
       </c>
       <c r="C81" s="2">
-        <f t="shared" si="9"/>
+        <f>((D81+E81+G81+H81)*0.2)+(F81*0.3)</f>
         <v>2.6</v>
       </c>
       <c r="D81" s="14">
@@ -30764,7 +31159,7 @@
         <v>2</v>
       </c>
       <c r="I81" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D81:H81)</f>
         <v>13</v>
       </c>
       <c r="J81" s="15"/>
@@ -30779,7 +31174,7 @@
         <v>이성관</v>
       </c>
       <c r="C82" s="2">
-        <f t="shared" si="9"/>
+        <f>((D82+E82+G82+H82)*0.2)+(F82*0.3)</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="D82" s="14">
@@ -30803,7 +31198,7 @@
         <v>1</v>
       </c>
       <c r="I82" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D82:H82)</f>
         <v>11</v>
       </c>
       <c r="J82" s="15"/>
@@ -30818,8 +31213,8 @@
         <v>이승윤</v>
       </c>
       <c r="C83" s="2">
-        <f t="shared" si="9"/>
-        <v>2.4000000000000004</v>
+        <f>((D83+E83+G83+H83)*0.2)+(F83*0.3)</f>
+        <v>3</v>
       </c>
       <c r="D83" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B83)</f>
@@ -30827,7 +31222,7 @@
       </c>
       <c r="E83" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B83)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B83)</f>
@@ -30835,15 +31230,15 @@
       </c>
       <c r="G83" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B83)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H83" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B83)</f>
         <v>0</v>
       </c>
       <c r="I83" s="14">
-        <f t="shared" si="10"/>
-        <v>12</v>
+        <f>SUM(D83:H83)</f>
+        <v>15</v>
       </c>
       <c r="J83" s="15"/>
     </row>
@@ -30857,7 +31252,7 @@
         <v>이연길</v>
       </c>
       <c r="C84" s="2">
-        <f t="shared" si="9"/>
+        <f>((D84+E84+G84+H84)*0.2)+(F84*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D84" s="14">
@@ -30881,7 +31276,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D84:H84)</f>
         <v>2</v>
       </c>
       <c r="J84" s="15"/>
@@ -30896,7 +31291,7 @@
         <v>이영준</v>
       </c>
       <c r="C85" s="2">
-        <f t="shared" si="9"/>
+        <f>((D85+E85+G85+H85)*0.2)+(F85*0.3)</f>
         <v>0.90000000000000013</v>
       </c>
       <c r="D85" s="14">
@@ -30920,7 +31315,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D85:H85)</f>
         <v>4</v>
       </c>
       <c r="J85" s="15"/>
@@ -30935,7 +31330,7 @@
         <v>이정범</v>
       </c>
       <c r="C86" s="2">
-        <f t="shared" si="9"/>
+        <f>((D86+E86+G86+H86)*0.2)+(F86*0.3)</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="D86" s="14">
@@ -30959,7 +31354,7 @@
         <v>1</v>
       </c>
       <c r="I86" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D86:H86)</f>
         <v>7</v>
       </c>
       <c r="J86" s="15"/>
@@ -30974,7 +31369,7 @@
         <v>이종수</v>
       </c>
       <c r="C87" s="2">
-        <f t="shared" si="9"/>
+        <f>((D87+E87+G87+H87)*0.2)+(F87*0.3)</f>
         <v>0</v>
       </c>
       <c r="D87" s="14">
@@ -30998,7 +31393,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D87:H87)</f>
         <v>0</v>
       </c>
       <c r="J87" s="15"/>
@@ -31013,7 +31408,7 @@
         <v>이찬솔</v>
       </c>
       <c r="C88" s="2">
-        <f t="shared" si="9"/>
+        <f>((D88+E88+G88+H88)*0.2)+(F88*0.3)</f>
         <v>1</v>
       </c>
       <c r="D88" s="14">
@@ -31037,7 +31432,7 @@
         <v>1</v>
       </c>
       <c r="I88" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D88:H88)</f>
         <v>5</v>
       </c>
       <c r="J88" s="15"/>
@@ -31052,7 +31447,7 @@
         <v>이찬영</v>
       </c>
       <c r="C89" s="2">
-        <f t="shared" si="9"/>
+        <f>((D89+E89+G89+H89)*0.2)+(F89*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D89" s="14">
@@ -31076,7 +31471,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D89:H89)</f>
         <v>2</v>
       </c>
       <c r="J89" s="15"/>
@@ -31091,7 +31486,7 @@
         <v>이태한</v>
       </c>
       <c r="C90" s="2">
-        <f t="shared" si="9"/>
+        <f>((D90+E90+G90+H90)*0.2)+(F90*0.3)</f>
         <v>0</v>
       </c>
       <c r="D90" s="14">
@@ -31115,7 +31510,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D90:H90)</f>
         <v>0</v>
       </c>
       <c r="J90" s="15"/>
@@ -31130,7 +31525,7 @@
         <v>이현택</v>
       </c>
       <c r="C91" s="2">
-        <f t="shared" si="9"/>
+        <f>((D91+E91+G91+H91)*0.2)+(F91*0.3)</f>
         <v>0</v>
       </c>
       <c r="D91" s="14">
@@ -31154,7 +31549,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D91:H91)</f>
         <v>0</v>
       </c>
       <c r="J91" s="15"/>
@@ -31169,7 +31564,7 @@
         <v>이호행</v>
       </c>
       <c r="C92" s="2">
-        <f t="shared" si="9"/>
+        <f>((D92+E92+G92+H92)*0.2)+(F92*0.3)</f>
         <v>0.8</v>
       </c>
       <c r="D92" s="14">
@@ -31193,7 +31588,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D92:H92)</f>
         <v>4</v>
       </c>
       <c r="J92" s="15"/>
@@ -31208,7 +31603,7 @@
         <v>임수철</v>
       </c>
       <c r="C93" s="2">
-        <f t="shared" si="9"/>
+        <f>((D93+E93+G93+H93)*0.2)+(F93*0.3)</f>
         <v>0</v>
       </c>
       <c r="D93" s="14">
@@ -31232,7 +31627,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D93:H93)</f>
         <v>0</v>
       </c>
       <c r="J93" s="15"/>
@@ -31247,7 +31642,7 @@
         <v>임태환</v>
       </c>
       <c r="C94" s="2">
-        <f t="shared" si="9"/>
+        <f>((D94+E94+G94+H94)*0.2)+(F94*0.3)</f>
         <v>3.9</v>
       </c>
       <c r="D94" s="14">
@@ -31271,7 +31666,7 @@
         <v>1</v>
       </c>
       <c r="I94" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D94:H94)</f>
         <v>18</v>
       </c>
       <c r="J94" s="15"/>
@@ -31286,7 +31681,7 @@
         <v>장희도</v>
       </c>
       <c r="C95" s="2">
-        <f t="shared" si="9"/>
+        <f>((D95+E95+G95+H95)*0.2)+(F95*0.3)</f>
         <v>0</v>
       </c>
       <c r="D95" s="14">
@@ -31310,7 +31705,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D95:H95)</f>
         <v>0</v>
       </c>
       <c r="J95" s="15"/>
@@ -31325,7 +31720,7 @@
         <v>장희준</v>
       </c>
       <c r="C96" s="2">
-        <f t="shared" si="9"/>
+        <f>((D96+E96+G96+H96)*0.2)+(F96*0.3)</f>
         <v>0</v>
       </c>
       <c r="D96" s="14">
@@ -31349,7 +31744,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D96:H96)</f>
         <v>0</v>
       </c>
       <c r="J96" s="15"/>
@@ -31364,12 +31759,12 @@
         <v>전나현</v>
       </c>
       <c r="C97" s="2">
-        <f t="shared" si="9"/>
-        <v>2.5</v>
+        <f>((D97+E97+G97+H97)*0.2)+(F97*0.3)</f>
+        <v>2.7</v>
       </c>
       <c r="D97" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B97)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B97)</f>
@@ -31388,8 +31783,8 @@
         <v>0</v>
       </c>
       <c r="I97" s="14">
-        <f t="shared" si="10"/>
-        <v>10</v>
+        <f>SUM(D97:H97)</f>
+        <v>11</v>
       </c>
       <c r="J97" s="15"/>
     </row>
@@ -31403,7 +31798,7 @@
         <v>전성환</v>
       </c>
       <c r="C98" s="2">
-        <f t="shared" si="9"/>
+        <f>((D98+E98+G98+H98)*0.2)+(F98*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D98" s="14">
@@ -31427,7 +31822,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D98:H98)</f>
         <v>1</v>
       </c>
       <c r="J98" s="15"/>
@@ -31442,7 +31837,7 @@
         <v>전하늘</v>
       </c>
       <c r="C99" s="2">
-        <f t="shared" si="9"/>
+        <f>((D99+E99+G99+H99)*0.2)+(F99*0.3)</f>
         <v>0.90000000000000013</v>
       </c>
       <c r="D99" s="14">
@@ -31466,7 +31861,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="14">
-        <f t="shared" si="10"/>
+        <f>SUM(D99:H99)</f>
         <v>4</v>
       </c>
       <c r="J99" s="15"/>
@@ -31481,16 +31876,16 @@
         <v>정민수</v>
       </c>
       <c r="C100" s="2">
-        <f t="shared" ref="C100:C131" si="11">((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
-        <v>5.2</v>
+        <f>((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D100" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B100)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B100)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F100" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B100)</f>
@@ -31505,8 +31900,8 @@
         <v>0</v>
       </c>
       <c r="I100" s="14">
-        <f t="shared" ref="I100:I131" si="12">SUM(D100:H100)</f>
-        <v>26</v>
+        <f>SUM(D100:H100)</f>
+        <v>28</v>
       </c>
       <c r="J100" s="15"/>
     </row>
@@ -31520,16 +31915,16 @@
         <v>정재명</v>
       </c>
       <c r="C101" s="2">
-        <f t="shared" si="11"/>
-        <v>3.6</v>
+        <f>((D101+E101+G101+H101)*0.2)+(F101*0.3)</f>
+        <v>4.2</v>
       </c>
       <c r="D101" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B101)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E101" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B101)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F101" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B101)</f>
@@ -31544,8 +31939,8 @@
         <v>0</v>
       </c>
       <c r="I101" s="14">
-        <f t="shared" si="12"/>
-        <v>18</v>
+        <f>SUM(D101:H101)</f>
+        <v>21</v>
       </c>
       <c r="J101" s="15"/>
     </row>
@@ -31559,7 +31954,7 @@
         <v>정현서</v>
       </c>
       <c r="C102" s="2">
-        <f t="shared" si="11"/>
+        <f>((D102+E102+G102+H102)*0.2)+(F102*0.3)</f>
         <v>1.5</v>
       </c>
       <c r="D102" s="14">
@@ -31583,7 +31978,7 @@
         <v>0</v>
       </c>
       <c r="I102" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D102:H102)</f>
         <v>6</v>
       </c>
       <c r="J102" s="15"/>
@@ -31598,12 +31993,12 @@
         <v>조진한</v>
       </c>
       <c r="C103" s="2">
-        <f t="shared" si="11"/>
-        <v>6.5</v>
+        <f>((D103+E103+G103+H103)*0.2)+(F103*0.3)</f>
+        <v>6.7</v>
       </c>
       <c r="D103" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B103)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E103" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B103)</f>
@@ -31622,8 +32017,8 @@
         <v>0</v>
       </c>
       <c r="I103" s="14">
-        <f t="shared" si="12"/>
-        <v>25</v>
+        <f>SUM(D103:H103)</f>
+        <v>26</v>
       </c>
       <c r="J103" s="15"/>
     </row>
@@ -31637,8 +32032,8 @@
         <v>조현우</v>
       </c>
       <c r="C104" s="2">
-        <f t="shared" si="11"/>
-        <v>2.8000000000000003</v>
+        <f>((D104+E104+G104+H104)*0.2)+(F104*0.3)</f>
+        <v>3</v>
       </c>
       <c r="D104" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B104)</f>
@@ -31654,15 +32049,15 @@
       </c>
       <c r="G104" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B104)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H104" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B104)</f>
         <v>0</v>
       </c>
       <c r="I104" s="14">
-        <f t="shared" si="12"/>
-        <v>14</v>
+        <f>SUM(D104:H104)</f>
+        <v>15</v>
       </c>
       <c r="J104" s="15"/>
     </row>
@@ -31676,7 +32071,7 @@
         <v>차승원</v>
       </c>
       <c r="C105" s="2">
-        <f t="shared" si="11"/>
+        <f>((D105+E105+G105+H105)*0.2)+(F105*0.3)</f>
         <v>1</v>
       </c>
       <c r="D105" s="14">
@@ -31700,7 +32095,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D105:H105)</f>
         <v>5</v>
       </c>
     </row>
@@ -31714,7 +32109,7 @@
         <v>최강인</v>
       </c>
       <c r="C106" s="2">
-        <f t="shared" si="11"/>
+        <f>((D106+E106+G106+H106)*0.2)+(F106*0.3)</f>
         <v>0.5</v>
       </c>
       <c r="D106" s="14">
@@ -31738,7 +32133,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D106:H106)</f>
         <v>2</v>
       </c>
     </row>
@@ -31752,7 +32147,7 @@
         <v>최령창</v>
       </c>
       <c r="C107" s="2">
-        <f t="shared" si="11"/>
+        <f>((D107+E107+G107+H107)*0.2)+(F107*0.3)</f>
         <v>4.6000000000000005</v>
       </c>
       <c r="D107" s="14">
@@ -31776,7 +32171,7 @@
         <v>2</v>
       </c>
       <c r="I107" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D107:H107)</f>
         <v>23</v>
       </c>
     </row>
@@ -31790,7 +32185,7 @@
         <v>최승훈</v>
       </c>
       <c r="C108" s="2">
-        <f t="shared" si="11"/>
+        <f>((D108+E108+G108+H108)*0.2)+(F108*0.3)</f>
         <v>0</v>
       </c>
       <c r="D108" s="14">
@@ -31814,7 +32209,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D108:H108)</f>
         <v>0</v>
       </c>
     </row>
@@ -31828,7 +32223,7 @@
         <v>한상규</v>
       </c>
       <c r="C109" s="2">
-        <f t="shared" si="11"/>
+        <f>((D109+E109+G109+H109)*0.2)+(F109*0.3)</f>
         <v>3.2</v>
       </c>
       <c r="D109" s="14">
@@ -31852,7 +32247,7 @@
         <v>0</v>
       </c>
       <c r="I109" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D109:H109)</f>
         <v>16</v>
       </c>
     </row>
@@ -31866,8 +32261,8 @@
         <v>한의현</v>
       </c>
       <c r="C110" s="2">
-        <f t="shared" si="11"/>
-        <v>2</v>
+        <f>((D110+E110+G110+H110)*0.2)+(F110*0.3)</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D110" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B110)</f>
@@ -31887,11 +32282,11 @@
       </c>
       <c r="H110" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B110)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I110" s="14">
-        <f t="shared" si="12"/>
-        <v>10</v>
+        <f>SUM(D110:H110)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -31904,7 +32299,7 @@
         <v>한중희</v>
       </c>
       <c r="C111" s="2">
-        <f t="shared" si="11"/>
+        <f>((D111+E111+G111+H111)*0.2)+(F111*0.3)</f>
         <v>1.8</v>
       </c>
       <c r="D111" s="14">
@@ -31928,7 +32323,7 @@
         <v>1</v>
       </c>
       <c r="I111" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D111:H111)</f>
         <v>9</v>
       </c>
     </row>
@@ -31942,7 +32337,7 @@
         <v>허동혁</v>
       </c>
       <c r="C112" s="2">
-        <f t="shared" si="11"/>
+        <f>((D112+E112+G112+H112)*0.2)+(F112*0.3)</f>
         <v>2.6</v>
       </c>
       <c r="D112" s="14">
@@ -31966,7 +32361,7 @@
         <v>1</v>
       </c>
       <c r="I112" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D112:H112)</f>
         <v>12</v>
       </c>
     </row>
@@ -31980,7 +32375,7 @@
         <v>홍석준</v>
       </c>
       <c r="C113" s="2">
-        <f t="shared" si="11"/>
+        <f>((D113+E113+G113+H113)*0.2)+(F113*0.3)</f>
         <v>1.6</v>
       </c>
       <c r="D113" s="14">
@@ -32004,7 +32399,7 @@
         <v>1</v>
       </c>
       <c r="I113" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D113:H113)</f>
         <v>7</v>
       </c>
     </row>
@@ -32018,7 +32413,7 @@
         <v>홍현석</v>
       </c>
       <c r="C114" s="2">
-        <f t="shared" si="11"/>
+        <f>((D114+E114+G114+H114)*0.2)+(F114*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D114" s="14">
@@ -32042,7 +32437,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D114:H114)</f>
         <v>1</v>
       </c>
     </row>
@@ -32056,7 +32451,7 @@
         <v>황건호</v>
       </c>
       <c r="C115" s="2">
-        <f t="shared" si="11"/>
+        <f>((D115+E115+G115+H115)*0.2)+(F115*0.3)</f>
         <v>2.5</v>
       </c>
       <c r="D115" s="14">
@@ -32080,7 +32475,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D115:H115)</f>
         <v>10</v>
       </c>
     </row>
@@ -32094,7 +32489,7 @@
         <v>황석원</v>
       </c>
       <c r="C116" s="2">
-        <f t="shared" si="11"/>
+        <f>((D116+E116+G116+H116)*0.2)+(F116*0.3)</f>
         <v>3.8000000000000003</v>
       </c>
       <c r="D116" s="14">
@@ -32118,7 +32513,7 @@
         <v>1</v>
       </c>
       <c r="I116" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D116:H116)</f>
         <v>18</v>
       </c>
     </row>
@@ -32132,7 +32527,7 @@
         <v>황재순</v>
       </c>
       <c r="C117" s="2">
-        <f t="shared" si="11"/>
+        <f>((D117+E117+G117+H117)*0.2)+(F117*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D117" s="14">
@@ -32156,7 +32551,7 @@
         <v>0</v>
       </c>
       <c r="I117" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D117:H117)</f>
         <v>2</v>
       </c>
     </row>
@@ -32170,7 +32565,7 @@
         <v>황철우</v>
       </c>
       <c r="C118" s="2">
-        <f t="shared" si="11"/>
+        <f>((D118+E118+G118+H118)*0.2)+(F118*0.3)</f>
         <v>0.4</v>
       </c>
       <c r="D118" s="14">
@@ -32194,7 +32589,7 @@
         <v>0</v>
       </c>
       <c r="I118" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D118:H118)</f>
         <v>2</v>
       </c>
     </row>
@@ -32208,7 +32603,7 @@
         <v>김민성</v>
       </c>
       <c r="C119" s="2">
-        <f t="shared" si="11"/>
+        <f>((D119+E119+G119+H119)*0.2)+(F119*0.3)</f>
         <v>0</v>
       </c>
       <c r="D119" s="14">
@@ -32232,7 +32627,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D119:H119)</f>
         <v>0</v>
       </c>
     </row>
@@ -32246,7 +32641,7 @@
         <v>송명섭</v>
       </c>
       <c r="C120" s="2">
-        <f t="shared" si="11"/>
+        <f>((D120+E120+G120+H120)*0.2)+(F120*0.3)</f>
         <v>0.2</v>
       </c>
       <c r="D120" s="14">
@@ -32270,7 +32665,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D120:H120)</f>
         <v>1</v>
       </c>
     </row>
@@ -32284,7 +32679,7 @@
         <v>최경영</v>
       </c>
       <c r="C121" s="2">
-        <f t="shared" si="11"/>
+        <f>((D121+E121+G121+H121)*0.2)+(F121*0.3)</f>
         <v>4.2</v>
       </c>
       <c r="D121" s="14">
@@ -32308,7 +32703,7 @@
         <v>15</v>
       </c>
       <c r="I121" s="14">
-        <f t="shared" si="12"/>
+        <f>SUM(D121:H121)</f>
         <v>21</v>
       </c>
     </row>
@@ -32322,8 +32717,8 @@
         <v>박지수</v>
       </c>
       <c r="C122" s="2">
-        <f t="shared" si="11"/>
-        <v>0.60000000000000009</v>
+        <f>((D122+E122+G122+H122)*0.2)+(F122*0.3)</f>
+        <v>0.8</v>
       </c>
       <c r="D122" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B122)</f>
@@ -32339,18 +32734,23 @@
       </c>
       <c r="G122" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B122)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H122" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B122)</f>
         <v>0</v>
       </c>
       <c r="I122" s="14">
-        <f t="shared" si="12"/>
-        <v>3</v>
+        <f>SUM(D122:H122)</f>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:I3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I122">
+      <sortCondition ref="A3"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:D122">
     <cfRule type="top10" dxfId="9" priority="974" rank="7"/>
@@ -33933,10 +34333,10 @@
       <c r="G2" s="47" t="s">
         <v>328</v>
       </c>
-      <c r="I2" s="94" t="s">
+      <c r="I2" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="J2" s="94"/>
+      <c r="J2" s="99"/>
       <c r="K2" s="65" t="s">
         <v>276</v>
       </c>
@@ -33961,7 +34361,7 @@
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="100" t="s">
         <v>334</v>
       </c>
       <c r="C3" s="72">
@@ -34024,7 +34424,7 @@
       </c>
       <c r="E4" s="62">
         <f>VLOOKUP(D4,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="70" t="s">
         <v>224</v>
@@ -34052,14 +34452,14 @@
       </c>
       <c r="Q4" s="62">
         <f>VLOOKUP(P4,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>221</v>
       </c>
       <c r="S4" s="63">
         <f>VLOOKUP(R4,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>36.700000000000003</v>
+        <v>37.700000000000003</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.25">
@@ -34072,14 +34472,14 @@
       </c>
       <c r="E5" s="47">
         <f>VLOOKUP(D5,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="70" t="s">
         <v>221</v>
       </c>
       <c r="G5" s="61">
         <f>VLOOKUP(F5,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>36.700000000000003</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="I5" s="96"/>
       <c r="J5" s="66">
@@ -34100,14 +34500,14 @@
       </c>
       <c r="Q5" s="62">
         <f>VLOOKUP(P5,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>304</v>
       </c>
       <c r="S5" s="63">
         <f>VLOOKUP(R5,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>29.5</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
@@ -34120,7 +34520,7 @@
       </c>
       <c r="E6" s="47">
         <f>VLOOKUP(D6,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="70" t="s">
         <v>232</v>
@@ -34148,14 +34548,14 @@
       </c>
       <c r="Q6" s="69">
         <f>VLOOKUP(P6,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R6" s="65" t="s">
         <v>230</v>
       </c>
       <c r="S6" s="71">
         <f>VLOOKUP(R6,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>21.2</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
@@ -34175,9 +34575,9 @@
       </c>
       <c r="G7" s="61">
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>29.5</v>
-      </c>
-      <c r="I7" s="98"/>
+        <v>30.7</v>
+      </c>
+      <c r="I7" s="97"/>
       <c r="J7" s="66">
         <v>5</v>
       </c>
@@ -34223,7 +34623,7 @@
       </c>
       <c r="G8" s="63">
         <f>VLOOKUP(F8,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>26</v>
+        <v>27.2</v>
       </c>
       <c r="N8" s="86"/>
       <c r="O8" s="48">
@@ -34263,10 +34663,10 @@
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$121,7,0)</f>
         <v>17</v>
       </c>
-      <c r="I9" s="94" t="s">
+      <c r="I9" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="J9" s="94"/>
+      <c r="J9" s="99"/>
       <c r="K9" s="65" t="s">
         <v>276</v>
       </c>
@@ -34282,7 +34682,7 @@
       </c>
       <c r="Q9" s="69">
         <f>VLOOKUP(P9,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R9" s="65" t="s">
         <v>309</v>
@@ -34339,7 +34739,7 @@
       </c>
       <c r="S10" s="71">
         <f>VLOOKUP(R10,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>13.4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
@@ -34400,14 +34800,14 @@
       </c>
       <c r="E12" s="65">
         <f>VLOOKUP(D12,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12" s="70" t="s">
         <v>223</v>
       </c>
       <c r="G12" s="61">
         <f>VLOOKUP(F12,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>20.3</v>
+        <v>21.6</v>
       </c>
       <c r="I12" s="96"/>
       <c r="J12" s="66">
@@ -34419,7 +34819,7 @@
       <c r="L12" s="65">
         <v>8</v>
       </c>
-      <c r="N12" s="101"/>
+      <c r="N12" s="98"/>
       <c r="O12" s="48">
         <v>10</v>
       </c>
@@ -34484,16 +34884,16 @@
       </c>
       <c r="E14" s="65">
         <f>VLOOKUP(D14,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="70" t="s">
         <v>228</v>
       </c>
       <c r="G14" s="61">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>30.2</v>
-      </c>
-      <c r="I14" s="98"/>
+        <v>31.6</v>
+      </c>
+      <c r="I14" s="97"/>
       <c r="J14" s="66">
         <v>5</v>
       </c>
@@ -34527,7 +34927,7 @@
       </c>
       <c r="G15" s="63">
         <f>VLOOKUP(F15,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>12.5</v>
+        <v>13.8</v>
       </c>
       <c r="N15"/>
       <c r="O15"/>
@@ -34546,20 +34946,20 @@
       </c>
       <c r="E16" s="65">
         <f>VLOOKUP(D16,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F16" s="62" t="s">
         <v>230</v>
       </c>
       <c r="G16" s="63">
         <f>VLOOKUP(F16,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>21.2</v>
+        <v>22.6</v>
       </c>
       <c r="H16" s="37"/>
-      <c r="I16" s="94" t="s">
+      <c r="I16" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="J16" s="94"/>
+      <c r="J16" s="99"/>
       <c r="K16" s="65" t="s">
         <v>276</v>
       </c>
@@ -34582,7 +34982,7 @@
       </c>
       <c r="G17" s="63">
         <f>VLOOKUP(F17,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="H17" s="37"/>
       <c r="I17" s="95" t="s">
@@ -34620,10 +35020,10 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="94" t="s">
+      <c r="B19" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="C19" s="94"/>
+      <c r="C19" s="99"/>
       <c r="D19" s="65" t="s">
         <v>276</v>
       </c>
@@ -34674,7 +35074,7 @@
       <c r="E21" s="65" t="s">
         <v>337</v>
       </c>
-      <c r="I21" s="98"/>
+      <c r="I21" s="97"/>
       <c r="J21" s="66">
         <v>5</v>
       </c>
@@ -34686,7 +35086,7 @@
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="97"/>
+      <c r="B22" s="101"/>
       <c r="C22" s="66">
         <v>3</v>
       </c>
@@ -34698,10 +35098,10 @@
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I23" s="99" t="s">
+      <c r="I23" s="93" t="s">
         <v>248</v>
       </c>
-      <c r="J23" s="100"/>
+      <c r="J23" s="94"/>
       <c r="K23" s="65" t="s">
         <v>276</v>
       </c>
@@ -34784,7 +35184,7 @@
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="98"/>
+      <c r="I30" s="97"/>
       <c r="J30" s="66">
         <v>7</v>
       </c>
@@ -34797,6 +35197,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:I21"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:I30"/>
     <mergeCell ref="N2:O2"/>
@@ -34805,12 +35211,6 @@
     <mergeCell ref="I3:I7"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:I14"/>
-    <mergeCell ref="B3:B17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:I21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35351,11 +35751,11 @@
       </c>
       <c r="G4" s="2">
         <f t="shared" ref="G4:G37" si="2">RANK(H4,$H$4:$H$37,0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4:I28" si="3">(COUNTIF(J4:CD4,"출전")*1)</f>
@@ -35921,7 +36321,7 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C15</f>
@@ -36035,11 +36435,11 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C16</f>
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="3"/>
@@ -36149,7 +36549,7 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C17</f>
@@ -36700,7 +37100,7 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C25</f>
@@ -36928,7 +37328,7 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C29</f>
@@ -37046,7 +37446,7 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C34</f>
@@ -37945,7 +38345,7 @@
       </c>
       <c r="G27" s="2">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H27" s="6">
         <f>I27+개인기록Sheet!C62</f>
@@ -38173,7 +38573,7 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" ref="G29" si="4">RANK(H29,$H$4:$H$37,0)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C64</f>
@@ -38623,11 +39023,11 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C83</f>
-        <v>3.4000000000000004</v>
+        <v>4</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="6"/>
@@ -38847,7 +39247,7 @@
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C97</f>
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="6"/>
@@ -39075,11 +39475,11 @@
       </c>
       <c r="G37" s="2">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C104</f>
-        <v>7.8000000000000007</v>
+        <v>8</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="6"/>

--- a/김청축_2026_출석부.xlsx
+++ b/김청축_2026_출석부.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcabf36b0134af82/바탕 화면/김인혁_청년축구단/1. 출석부/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1467" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42309875-AC3A-4BC5-83EE-6C35178E488A}"/>
+  <xr:revisionPtr revIDLastSave="1563" documentId="13_ncr:1_{DC8612FD-A52F-4EAD-BD68-700165C8B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6598F0C0-BF3E-4CB0-8714-D330CE37F57A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="종합Sheet" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3102" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3172" uniqueCount="462">
   <si>
     <t>C/S DF (0.2)</t>
   </si>
@@ -2530,10 +2530,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2542,20 +2542,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AS2" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT2" s="1">
         <f t="shared" si="1"/>
@@ -3700,7 +3700,9 @@
       <c r="AR3" s="4">
         <v>46303</v>
       </c>
-      <c r="AS3" s="4"/>
+      <c r="AS3" s="4">
+        <v>46310</v>
+      </c>
       <c r="AT3" s="4"/>
       <c r="AU3" s="4"/>
       <c r="AV3" s="4"/>
@@ -3762,11 +3764,11 @@
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>27.2</v>
+        <v>28.6</v>
       </c>
       <c r="I4" s="6">
         <f>(COUNTIF(J4:CD4,"출전")*1)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>348</v>
@@ -3853,7 +3855,9 @@
       <c r="AR4" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AS4" s="2"/>
+      <c r="AS4" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
@@ -3911,7 +3915,7 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" ref="G5:G35" si="2">RANK(H5,$H$4:$H$122,0)</f>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H5" s="6">
         <f>I5+개인기록Sheet!C5</f>
@@ -4336,7 +4340,7 @@
       </c>
       <c r="G9" s="2">
         <f t="shared" si="2"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" s="6">
         <f>I9+개인기록Sheet!C9</f>
@@ -4455,7 +4459,7 @@
       </c>
       <c r="G10" s="2">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="6">
         <f>I10+개인기록Sheet!C10</f>
@@ -4592,7 +4596,7 @@
       </c>
       <c r="G11" s="2">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H11" s="6">
         <f>I11+개인기록Sheet!C11</f>
@@ -5042,7 +5046,7 @@
       </c>
       <c r="G15" s="2">
         <f t="shared" si="2"/>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H15" s="6">
         <f>I15+개인기록Sheet!C15</f>
@@ -5153,7 +5157,7 @@
       </c>
       <c r="G16" s="2">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H16" s="6">
         <f>I16+개인기록Sheet!C16</f>
@@ -5276,7 +5280,7 @@
       </c>
       <c r="G17" s="2">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" s="6">
         <f>I17+개인기록Sheet!C17</f>
@@ -5618,7 +5622,7 @@
       </c>
       <c r="G20" s="2">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H20" s="6">
         <f>I20+개인기록Sheet!C20</f>
@@ -6044,15 +6048,15 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C24</f>
-        <v>8.1</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I24" s="6">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -6103,7 +6107,9 @@
       <c r="AP24" s="2"/>
       <c r="AQ24" s="2"/>
       <c r="AR24" s="2"/>
-      <c r="AS24" s="2"/>
+      <c r="AS24" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
@@ -6161,15 +6167,15 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C25</f>
-        <v>14.9</v>
+        <v>15.9</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
@@ -6230,7 +6236,9 @@
       </c>
       <c r="AQ25" s="2"/>
       <c r="AR25" s="2"/>
-      <c r="AS25" s="2"/>
+      <c r="AS25" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
@@ -6672,7 +6680,7 @@
       </c>
       <c r="G29" s="2">
         <f t="shared" si="2"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H29" s="6">
         <f>I29+개인기록Sheet!C29</f>
@@ -6781,15 +6789,15 @@
       </c>
       <c r="G30" s="2">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H30" s="6">
         <f>I30+개인기록Sheet!C30</f>
-        <v>18.600000000000001</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="I30" s="6">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
@@ -6854,7 +6862,9 @@
       </c>
       <c r="AQ30" s="2"/>
       <c r="AR30" s="2"/>
-      <c r="AS30" s="2"/>
+      <c r="AS30" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
@@ -6916,11 +6926,11 @@
       </c>
       <c r="H31" s="6">
         <f>I31+개인기록Sheet!C31</f>
-        <v>31.6</v>
+        <v>32.6</v>
       </c>
       <c r="I31" s="6">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>348</v>
@@ -7009,7 +7019,9 @@
       <c r="AR31" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AS31" s="2"/>
+      <c r="AS31" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
@@ -7067,15 +7079,15 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C32</f>
-        <v>10.4</v>
+        <v>11.4</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
@@ -7132,7 +7144,9 @@
         <v>348</v>
       </c>
       <c r="AR32" s="2"/>
-      <c r="AS32" s="2"/>
+      <c r="AS32" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
@@ -7190,7 +7204,7 @@
       </c>
       <c r="G33" s="2">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C33</f>
@@ -7435,7 +7449,7 @@
       </c>
       <c r="G35" s="2">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H35" s="6">
         <f>I35+개인기록Sheet!C35</f>
@@ -7578,7 +7592,7 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" ref="G36:G67" si="6">RANK(H36,$H$4:$H$122,0)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C36</f>
@@ -7801,7 +7815,7 @@
       </c>
       <c r="G38" s="2">
         <f t="shared" si="6"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H38" s="6">
         <f>I38+개인기록Sheet!C38</f>
@@ -8116,7 +8130,7 @@
       </c>
       <c r="G41" s="2">
         <f t="shared" si="6"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H41" s="6">
         <f>I41+개인기록Sheet!C41</f>
@@ -8223,15 +8237,15 @@
       </c>
       <c r="G42" s="2">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H42" s="6">
         <f>I42+개인기록Sheet!C42</f>
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="I42" s="6">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
@@ -8312,7 +8326,9 @@
       <c r="AR42" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AS42" s="2"/>
+      <c r="AS42" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT42" s="2"/>
       <c r="AU42" s="2"/>
       <c r="AV42" s="2"/>
@@ -8370,7 +8386,7 @@
       </c>
       <c r="G43" s="2">
         <f t="shared" si="6"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H43" s="6">
         <f>I43+개인기록Sheet!C43</f>
@@ -8493,15 +8509,15 @@
       </c>
       <c r="G44" s="2">
         <f t="shared" si="6"/>
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H44" s="6">
         <f>I44+개인기록Sheet!C44</f>
-        <v>8.4</v>
+        <v>10.600000000000001</v>
       </c>
       <c r="I44" s="6">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -8550,7 +8566,9 @@
       </c>
       <c r="AQ44" s="2"/>
       <c r="AR44" s="2"/>
-      <c r="AS44" s="2"/>
+      <c r="AS44" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT44" s="2"/>
       <c r="AU44" s="2"/>
       <c r="AV44" s="2"/>
@@ -8710,15 +8728,15 @@
       </c>
       <c r="G46" s="2">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H46" s="6">
         <f>I46+개인기록Sheet!C46</f>
-        <v>21.4</v>
+        <v>22.6</v>
       </c>
       <c r="I46" s="6">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
@@ -8791,7 +8809,9 @@
         <v>348</v>
       </c>
       <c r="AR46" s="2"/>
-      <c r="AS46" s="2"/>
+      <c r="AS46" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT46" s="2"/>
       <c r="AU46" s="2"/>
       <c r="AV46" s="2"/>
@@ -8842,7 +8862,7 @@
       </c>
       <c r="D47" s="54">
         <f t="shared" ref="D47:D49" si="8">COUNTA(AF47:AU47)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" s="54"/>
       <c r="F47" s="2" t="s">
@@ -8850,15 +8870,15 @@
       </c>
       <c r="G47" s="2">
         <f t="shared" si="6"/>
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H47" s="6">
         <f>I47+개인기록Sheet!C47</f>
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="I47" s="6">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -8899,7 +8919,9 @@
       <c r="AP47" s="2"/>
       <c r="AQ47" s="2"/>
       <c r="AR47" s="2"/>
-      <c r="AS47" s="2"/>
+      <c r="AS47" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT47" s="2"/>
       <c r="AU47" s="2"/>
       <c r="AV47" s="2"/>
@@ -9165,7 +9187,7 @@
       </c>
       <c r="G50" s="2">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H50" s="6">
         <f>I50+개인기록Sheet!C50</f>
@@ -9403,7 +9425,7 @@
       </c>
       <c r="G52" s="2">
         <f t="shared" si="6"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H52" s="6">
         <f>I52+개인기록Sheet!C52</f>
@@ -9517,7 +9539,7 @@
       </c>
       <c r="G53" s="2">
         <f t="shared" si="6"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H53" s="6">
         <f>I53+개인기록Sheet!C53</f>
@@ -9842,11 +9864,11 @@
       </c>
       <c r="H56" s="6">
         <f>I56+개인기록Sheet!C56</f>
-        <v>24.6</v>
+        <v>25.6</v>
       </c>
       <c r="I56" s="6">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -9925,7 +9947,9 @@
       <c r="AR56" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AS56" s="2"/>
+      <c r="AS56" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT56" s="2"/>
       <c r="AU56" s="2"/>
       <c r="AV56" s="2"/>
@@ -9983,15 +10007,15 @@
       </c>
       <c r="G57" s="2">
         <f t="shared" si="6"/>
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H57" s="6">
         <f>I57+개인기록Sheet!C57</f>
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="I57" s="6">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>348</v>
@@ -10034,7 +10058,9 @@
       <c r="AP57" s="2"/>
       <c r="AQ57" s="2"/>
       <c r="AR57" s="2"/>
-      <c r="AS57" s="2"/>
+      <c r="AS57" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT57" s="2"/>
       <c r="AU57" s="2"/>
       <c r="AV57" s="2"/>
@@ -10092,7 +10118,7 @@
       </c>
       <c r="G58" s="2">
         <f t="shared" si="6"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H58" s="6">
         <f>I58+개인기록Sheet!C58</f>
@@ -10317,15 +10343,15 @@
       </c>
       <c r="G60" s="2">
         <f t="shared" si="6"/>
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H60" s="6">
         <f>I60+개인기록Sheet!C60</f>
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="I60" s="6">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
@@ -10368,7 +10394,9 @@
       <c r="AP60" s="2"/>
       <c r="AQ60" s="2"/>
       <c r="AR60" s="2"/>
-      <c r="AS60" s="2"/>
+      <c r="AS60" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT60" s="2"/>
       <c r="AU60" s="2"/>
       <c r="AV60" s="2"/>
@@ -10671,7 +10699,7 @@
       </c>
       <c r="G63" s="2">
         <f t="shared" si="6"/>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H63" s="6">
         <f>I63+개인기록Sheet!C63</f>
@@ -11211,7 +11239,7 @@
       </c>
       <c r="G68" s="2">
         <f t="shared" ref="G68:G99" si="12">RANK(H68,$H$4:$H$122,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H68" s="6">
         <f>I68+개인기록Sheet!C68</f>
@@ -11347,7 +11375,7 @@
       </c>
       <c r="G69" s="2">
         <f t="shared" si="12"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H69" s="6">
         <f>I69+개인기록Sheet!C69</f>
@@ -11458,15 +11486,15 @@
       </c>
       <c r="G70" s="2">
         <f t="shared" si="12"/>
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H70" s="6">
         <f>I70+개인기록Sheet!C70</f>
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="I70" s="6">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
@@ -11515,7 +11543,9 @@
       <c r="AP70" s="2"/>
       <c r="AQ70" s="2"/>
       <c r="AR70" s="2"/>
-      <c r="AS70" s="2"/>
+      <c r="AS70" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT70" s="2"/>
       <c r="AU70" s="2"/>
       <c r="AV70" s="2"/>
@@ -11573,7 +11603,7 @@
       </c>
       <c r="G71" s="2">
         <f t="shared" si="12"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H71" s="6">
         <f>I71+개인기록Sheet!C71</f>
@@ -11796,7 +11826,7 @@
       </c>
       <c r="G73" s="2">
         <f t="shared" si="12"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H73" s="6">
         <f>I73+개인기록Sheet!C73</f>
@@ -11909,15 +11939,15 @@
       </c>
       <c r="G74" s="2">
         <f t="shared" si="12"/>
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H74" s="6">
         <f>I74+개인기록Sheet!C74</f>
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="I74" s="6">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
@@ -11964,7 +11994,9 @@
       <c r="AP74" s="2"/>
       <c r="AQ74" s="2"/>
       <c r="AR74" s="2"/>
-      <c r="AS74" s="2"/>
+      <c r="AS74" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT74" s="2"/>
       <c r="AU74" s="2"/>
       <c r="AV74" s="2"/>
@@ -12022,7 +12054,7 @@
       </c>
       <c r="G75" s="2">
         <f t="shared" si="12"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H75" s="6">
         <f>I75+개인기록Sheet!C75</f>
@@ -12246,7 +12278,7 @@
       </c>
       <c r="G77" s="2">
         <f t="shared" si="12"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H77" s="6">
         <f>I77+개인기록Sheet!C77</f>
@@ -12353,7 +12385,7 @@
       </c>
       <c r="G78" s="2">
         <f t="shared" si="12"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H78" s="6">
         <f>I78+개인기록Sheet!C78</f>
@@ -12474,7 +12506,7 @@
       </c>
       <c r="G79" s="2">
         <f t="shared" si="12"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H79" s="6">
         <f>I79+개인기록Sheet!C79</f>
@@ -12589,15 +12621,15 @@
       </c>
       <c r="G80" s="2">
         <f t="shared" si="12"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H80" s="6">
         <f>I80+개인기록Sheet!C80</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="11"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
@@ -12660,7 +12692,9 @@
       </c>
       <c r="AQ80" s="2"/>
       <c r="AR80" s="2"/>
-      <c r="AS80" s="2"/>
+      <c r="AS80" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT80" s="2"/>
       <c r="AU80" s="2"/>
       <c r="AV80" s="2"/>
@@ -12718,15 +12752,15 @@
       </c>
       <c r="G81" s="2">
         <f t="shared" si="12"/>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H81" s="6">
         <f>I81+개인기록Sheet!C81</f>
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="I81" s="6">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
@@ -12787,7 +12821,9 @@
         <v>348</v>
       </c>
       <c r="AR81" s="2"/>
-      <c r="AS81" s="2"/>
+      <c r="AS81" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT81" s="2"/>
       <c r="AU81" s="2"/>
       <c r="AV81" s="2"/>
@@ -12845,7 +12881,7 @@
       </c>
       <c r="G82" s="2">
         <f t="shared" si="12"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H82" s="6">
         <f>I82+개인기록Sheet!C82</f>
@@ -12970,15 +13006,15 @@
       </c>
       <c r="G83" s="2">
         <f t="shared" si="12"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H83" s="6">
         <f>I83+개인기록Sheet!C83</f>
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="I83" s="6">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
@@ -13039,7 +13075,9 @@
       <c r="AR83" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AS83" s="2"/>
+      <c r="AS83" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT83" s="2"/>
       <c r="AU83" s="2"/>
       <c r="AV83" s="2"/>
@@ -13097,7 +13135,7 @@
       </c>
       <c r="G84" s="2">
         <f t="shared" si="12"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H84" s="6">
         <f>I84+개인기록Sheet!C84</f>
@@ -13208,7 +13246,7 @@
       </c>
       <c r="G85" s="2">
         <f t="shared" si="12"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H85" s="6">
         <f>I85+개인기록Sheet!C85</f>
@@ -13325,7 +13363,7 @@
       </c>
       <c r="G86" s="2">
         <f t="shared" si="12"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H86" s="6">
         <f>I86+개인기록Sheet!C86</f>
@@ -13542,7 +13580,7 @@
       </c>
       <c r="G88" s="2">
         <f t="shared" si="12"/>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H88" s="6">
         <f>I88+개인기록Sheet!C88</f>
@@ -13651,7 +13689,7 @@
       </c>
       <c r="G89" s="2">
         <f t="shared" si="12"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H89" s="6">
         <f>I89+개인기록Sheet!C89</f>
@@ -13972,7 +14010,7 @@
       </c>
       <c r="G92" s="2">
         <f t="shared" si="12"/>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H92" s="6">
         <f>I92+개인기록Sheet!C92</f>
@@ -14186,15 +14224,15 @@
       </c>
       <c r="G94" s="2">
         <f t="shared" si="12"/>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H94" s="6">
         <f>I94+개인기록Sheet!C94</f>
-        <v>15.9</v>
+        <v>17.5</v>
       </c>
       <c r="I94" s="6">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
@@ -14255,7 +14293,9 @@
         <v>348</v>
       </c>
       <c r="AR94" s="2"/>
-      <c r="AS94" s="2"/>
+      <c r="AS94" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT94" s="2"/>
       <c r="AU94" s="2"/>
       <c r="AV94" s="2"/>
@@ -14313,7 +14353,7 @@
       </c>
       <c r="G95" s="2">
         <f t="shared" si="12"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H95" s="6">
         <f>I95+개인기록Sheet!C95</f>
@@ -14526,7 +14566,7 @@
       </c>
       <c r="G97" s="2">
         <f t="shared" si="12"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H97" s="6">
         <f>I97+개인기록Sheet!C97</f>
@@ -14759,7 +14799,7 @@
       </c>
       <c r="G99" s="2">
         <f t="shared" si="12"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H99" s="6">
         <f>I99+개인기록Sheet!C99</f>
@@ -14872,15 +14912,15 @@
       </c>
       <c r="G100" s="2">
         <f t="shared" ref="G100:G122" si="15">RANK(H100,$H$4:$H$122,0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H100" s="6">
         <f>I100+개인기록Sheet!C100</f>
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
       <c r="I100" s="6">
         <f t="shared" si="11"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
@@ -14951,7 +14991,9 @@
       <c r="AR100" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AS100" s="2"/>
+      <c r="AS100" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT100" s="2"/>
       <c r="AU100" s="2"/>
       <c r="AV100" s="2"/>
@@ -15009,15 +15051,15 @@
       </c>
       <c r="G101" s="2">
         <f t="shared" si="15"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H101" s="6">
         <f>I101+개인기록Sheet!C101</f>
-        <v>20.2</v>
+        <v>21.4</v>
       </c>
       <c r="I101" s="6">
         <f t="shared" si="11"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
@@ -15086,7 +15128,9 @@
       <c r="AR101" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AS101" s="2"/>
+      <c r="AS101" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT101" s="2"/>
       <c r="AU101" s="2"/>
       <c r="AV101" s="2"/>
@@ -15144,15 +15188,15 @@
       </c>
       <c r="G102" s="2">
         <f t="shared" si="15"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H102" s="6">
         <f>I102+개인기록Sheet!C102</f>
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="I102" s="6">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
@@ -15205,7 +15249,9 @@
       <c r="AP102" s="2"/>
       <c r="AQ102" s="2"/>
       <c r="AR102" s="2"/>
-      <c r="AS102" s="2"/>
+      <c r="AS102" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT102" s="2"/>
       <c r="AU102" s="2"/>
       <c r="AV102" s="2"/>
@@ -15267,11 +15313,11 @@
       </c>
       <c r="H103" s="6">
         <f>I103+개인기록Sheet!C103</f>
-        <v>30.7</v>
+        <v>32</v>
       </c>
       <c r="I103" s="6">
         <f t="shared" si="11"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>348</v>
@@ -15356,7 +15402,9 @@
       <c r="AR103" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AS103" s="2"/>
+      <c r="AS103" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT103" s="2"/>
       <c r="AU103" s="2"/>
       <c r="AV103" s="2"/>
@@ -15418,11 +15466,11 @@
       </c>
       <c r="H104" s="6">
         <f>I104+개인기록Sheet!C104</f>
-        <v>22</v>
+        <v>23.2</v>
       </c>
       <c r="I104" s="6">
         <f t="shared" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>348</v>
@@ -15497,7 +15545,9 @@
       <c r="AR104" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AS104" s="2"/>
+      <c r="AS104" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT104" s="2"/>
       <c r="AU104" s="2"/>
       <c r="AV104" s="2"/>
@@ -15555,7 +15605,7 @@
       </c>
       <c r="G105" s="2">
         <f t="shared" si="15"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H105" s="6">
         <f>I105+개인기록Sheet!C105</f>
@@ -15669,7 +15719,7 @@
       </c>
       <c r="G106" s="2">
         <f t="shared" si="15"/>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H106" s="6">
         <f>I106+개인기록Sheet!C106</f>
@@ -15776,7 +15826,7 @@
       </c>
       <c r="G107" s="2">
         <f t="shared" si="15"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H107" s="6">
         <f>I107+개인기록Sheet!C107</f>
@@ -16007,7 +16057,7 @@
       </c>
       <c r="G109" s="2">
         <f t="shared" si="15"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H109" s="6">
         <f>I109+개인기록Sheet!C109</f>
@@ -16138,7 +16188,7 @@
       </c>
       <c r="G110" s="2">
         <f t="shared" si="15"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H110" s="6">
         <f>I110+개인기록Sheet!C110</f>
@@ -16390,7 +16440,7 @@
       </c>
       <c r="G112" s="2">
         <f t="shared" si="15"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H112" s="6">
         <f>I112+개인기록Sheet!C112</f>
@@ -16505,7 +16555,7 @@
       </c>
       <c r="G113" s="2">
         <f t="shared" si="15"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H113" s="6">
         <f>I113+개인기록Sheet!C113</f>
@@ -16620,7 +16670,7 @@
       </c>
       <c r="G114" s="2">
         <f t="shared" si="15"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H114" s="6">
         <f>I114+개인기록Sheet!C114</f>
@@ -16727,7 +16777,7 @@
       </c>
       <c r="G115" s="2">
         <f t="shared" si="15"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H115" s="6">
         <f>I115+개인기록Sheet!C115</f>
@@ -16840,7 +16890,7 @@
       </c>
       <c r="G116" s="2">
         <f t="shared" si="15"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H116" s="6">
         <f>I116+개인기록Sheet!C116</f>
@@ -17073,7 +17123,7 @@
       </c>
       <c r="G118" s="2">
         <f t="shared" si="15"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H118" s="6">
         <f>I118+개인기록Sheet!C118</f>
@@ -17391,15 +17441,15 @@
       </c>
       <c r="G121" s="2">
         <f t="shared" si="15"/>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H121" s="6">
         <f>I121+개인기록Sheet!C121</f>
-        <v>13.2</v>
+        <v>14.8</v>
       </c>
       <c r="I121" s="6">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J121" s="2"/>
       <c r="K121" s="2" t="s">
@@ -17454,7 +17504,9 @@
       </c>
       <c r="AQ121" s="2"/>
       <c r="AR121" s="2"/>
-      <c r="AS121" s="2"/>
+      <c r="AS121" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT121" s="2"/>
       <c r="AU121" s="2"/>
       <c r="AV121" s="2"/>
@@ -17505,7 +17557,7 @@
       </c>
       <c r="D122" s="54">
         <f>COUNTA(AF122:AU122)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E122" s="54"/>
       <c r="F122" s="2" t="s">
@@ -17513,15 +17565,15 @@
       </c>
       <c r="G122" s="2">
         <f t="shared" si="15"/>
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H122" s="6">
         <f>I122+개인기록Sheet!C122</f>
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="I122" s="6">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
@@ -17566,7 +17618,9 @@
       <c r="AR122" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AS122" s="2"/>
+      <c r="AS122" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="AT122" s="2"/>
       <c r="AU122" s="2"/>
       <c r="AV122" s="2"/>
@@ -17606,7 +17660,6 @@
       <c r="CD122" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:CT122" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:E122">
     <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="지급">
@@ -17630,7 +17683,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:V328"/>
+  <dimension ref="A2:V340"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.8984375" style="1" bestFit="1" customWidth="1"/>
@@ -27019,99 +27072,699 @@
       <c r="U328" s="2"/>
       <c r="V328" s="2"/>
     </row>
+    <row r="331" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B331" s="11">
+        <v>46310</v>
+      </c>
+      <c r="C331" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D331" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="E331" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="F331" s="77"/>
+      <c r="G331" s="77"/>
+      <c r="H331" s="77"/>
+      <c r="I331" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="J331" s="78"/>
+      <c r="K331" s="78"/>
+      <c r="L331" s="78"/>
+      <c r="M331" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="N331" s="79"/>
+      <c r="O331" s="79"/>
+      <c r="P331" s="79"/>
+      <c r="Q331" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="R331" s="80"/>
+      <c r="S331" s="80"/>
+      <c r="T331" s="80"/>
+      <c r="U331" s="80"/>
+      <c r="V331" s="80"/>
+    </row>
+    <row r="332" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B332" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="C332" s="75">
+        <v>0</v>
+      </c>
+      <c r="D332" s="75">
+        <v>1</v>
+      </c>
+      <c r="E332" s="7"/>
+      <c r="F332" s="7"/>
+      <c r="G332" s="7"/>
+      <c r="H332" s="7"/>
+      <c r="I332" s="8"/>
+      <c r="J332" s="8"/>
+      <c r="K332" s="8"/>
+      <c r="L332" s="8"/>
+      <c r="M332" s="20"/>
+      <c r="N332" s="20"/>
+      <c r="O332" s="20"/>
+      <c r="P332" s="20"/>
+      <c r="Q332" s="9"/>
+      <c r="R332" s="9"/>
+      <c r="S332" s="9"/>
+      <c r="T332" s="9"/>
+      <c r="U332" s="9"/>
+      <c r="V332" s="13"/>
+    </row>
+    <row r="333" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B333" s="74"/>
+      <c r="C333" s="76"/>
+      <c r="D333" s="76"/>
+      <c r="E333" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F333" s="7"/>
+      <c r="G333" s="7"/>
+      <c r="H333" s="7"/>
+      <c r="I333" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J333" s="8"/>
+      <c r="K333" s="8"/>
+      <c r="L333" s="8"/>
+      <c r="M333" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="N333" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="O333" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="P333" s="20"/>
+      <c r="Q333" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="R333" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="S333" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="T333" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="U333" s="9"/>
+      <c r="V333" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="334" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B334" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C334" s="75">
+        <v>0</v>
+      </c>
+      <c r="D334" s="75">
+        <v>0</v>
+      </c>
+      <c r="E334" s="7"/>
+      <c r="F334" s="7"/>
+      <c r="G334" s="7"/>
+      <c r="H334" s="7"/>
+      <c r="I334" s="8"/>
+      <c r="J334" s="8"/>
+      <c r="K334" s="8"/>
+      <c r="L334" s="8"/>
+      <c r="M334" s="20"/>
+      <c r="N334" s="20"/>
+      <c r="O334" s="20"/>
+      <c r="P334" s="20"/>
+      <c r="Q334" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="R334" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="S334" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="T334" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="U334" s="9"/>
+      <c r="V334" s="13" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="335" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B335" s="74"/>
+      <c r="C335" s="76"/>
+      <c r="D335" s="76"/>
+      <c r="E335" s="7"/>
+      <c r="F335" s="7"/>
+      <c r="G335" s="7"/>
+      <c r="H335" s="7"/>
+      <c r="I335" s="8"/>
+      <c r="J335" s="8"/>
+      <c r="K335" s="8"/>
+      <c r="L335" s="8"/>
+      <c r="M335" s="20"/>
+      <c r="N335" s="20"/>
+      <c r="O335" s="20"/>
+      <c r="P335" s="20"/>
+      <c r="Q335" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="R335" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="S335" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="T335" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="U335" s="9"/>
+      <c r="V335" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="336" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B336" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C336" s="75">
+        <v>2</v>
+      </c>
+      <c r="D336" s="75">
+        <v>1</v>
+      </c>
+      <c r="E336" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="F336" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G336" s="7"/>
+      <c r="H336" s="7"/>
+      <c r="I336" s="8"/>
+      <c r="J336" s="8"/>
+      <c r="K336" s="8"/>
+      <c r="L336" s="8"/>
+      <c r="M336" s="20"/>
+      <c r="N336" s="20"/>
+      <c r="O336" s="20"/>
+      <c r="P336" s="20"/>
+      <c r="Q336" s="9"/>
+      <c r="R336" s="9"/>
+      <c r="S336" s="9"/>
+      <c r="T336" s="9"/>
+      <c r="U336" s="9"/>
+      <c r="V336" s="13"/>
+    </row>
+    <row r="337" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B337" s="74"/>
+      <c r="C337" s="76"/>
+      <c r="D337" s="76"/>
+      <c r="E337" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F337" s="7"/>
+      <c r="G337" s="7"/>
+      <c r="H337" s="7"/>
+      <c r="I337" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J337" s="8"/>
+      <c r="K337" s="8"/>
+      <c r="L337" s="8"/>
+      <c r="M337" s="20"/>
+      <c r="N337" s="20"/>
+      <c r="O337" s="20"/>
+      <c r="P337" s="20"/>
+      <c r="Q337" s="9"/>
+      <c r="R337" s="9"/>
+      <c r="S337" s="9"/>
+      <c r="T337" s="9"/>
+      <c r="U337" s="9"/>
+      <c r="V337" s="13"/>
+    </row>
+    <row r="338" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B338" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="C338" s="75">
+        <v>1</v>
+      </c>
+      <c r="D338" s="75">
+        <v>4</v>
+      </c>
+      <c r="E338" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F338" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G338" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="H338" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I338" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J338" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="K338" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="L338" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="M338" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="N338" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="O338" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="P338" s="20"/>
+      <c r="Q338" s="9"/>
+      <c r="R338" s="9"/>
+      <c r="S338" s="9"/>
+      <c r="T338" s="9"/>
+      <c r="U338" s="9"/>
+      <c r="V338" s="13"/>
+    </row>
+    <row r="339" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B339" s="74"/>
+      <c r="C339" s="76"/>
+      <c r="D339" s="76"/>
+      <c r="E339" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F339" s="7"/>
+      <c r="G339" s="7"/>
+      <c r="H339" s="7"/>
+      <c r="I339" s="8"/>
+      <c r="J339" s="8"/>
+      <c r="K339" s="8"/>
+      <c r="L339" s="8"/>
+      <c r="M339" s="20"/>
+      <c r="N339" s="20"/>
+      <c r="O339" s="20"/>
+      <c r="P339" s="20"/>
+      <c r="Q339" s="9"/>
+      <c r="R339" s="9"/>
+      <c r="S339" s="9"/>
+      <c r="T339" s="9"/>
+      <c r="U339" s="9"/>
+      <c r="V339" s="13"/>
+    </row>
+    <row r="340" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B340" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C340" s="2">
+        <f>SUM(C332:C339)</f>
+        <v>3</v>
+      </c>
+      <c r="D340" s="2">
+        <f>SUM(D332:D339)</f>
+        <v>6</v>
+      </c>
+      <c r="E340" s="2"/>
+      <c r="F340" s="2"/>
+      <c r="G340" s="2"/>
+      <c r="H340" s="2"/>
+      <c r="I340" s="2"/>
+      <c r="J340" s="2"/>
+      <c r="K340" s="2"/>
+      <c r="L340" s="2"/>
+      <c r="M340" s="2"/>
+      <c r="N340" s="2"/>
+      <c r="O340" s="2"/>
+      <c r="P340" s="2"/>
+      <c r="Q340" s="2"/>
+      <c r="R340" s="2"/>
+      <c r="S340" s="2"/>
+      <c r="T340" s="2"/>
+      <c r="U340" s="2"/>
+      <c r="V340" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="444">
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="C324:C325"/>
-    <mergeCell ref="D324:D325"/>
-    <mergeCell ref="B326:B327"/>
-    <mergeCell ref="C326:C327"/>
-    <mergeCell ref="D326:D327"/>
-    <mergeCell ref="E319:H319"/>
-    <mergeCell ref="I319:L319"/>
-    <mergeCell ref="M319:P319"/>
-    <mergeCell ref="Q319:V319"/>
-    <mergeCell ref="B320:B321"/>
-    <mergeCell ref="C320:C321"/>
-    <mergeCell ref="D320:D321"/>
-    <mergeCell ref="B322:B323"/>
-    <mergeCell ref="C322:C323"/>
-    <mergeCell ref="D322:D323"/>
-    <mergeCell ref="B312:B313"/>
-    <mergeCell ref="C312:C313"/>
-    <mergeCell ref="D312:D313"/>
-    <mergeCell ref="B314:B315"/>
-    <mergeCell ref="C314:C315"/>
-    <mergeCell ref="D314:D315"/>
-    <mergeCell ref="E307:H307"/>
-    <mergeCell ref="I307:L307"/>
-    <mergeCell ref="M307:P307"/>
-    <mergeCell ref="Q307:V307"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="C308:C309"/>
-    <mergeCell ref="D308:D309"/>
-    <mergeCell ref="B310:B311"/>
-    <mergeCell ref="C310:C311"/>
-    <mergeCell ref="D310:D311"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="C262:C263"/>
-    <mergeCell ref="D262:D263"/>
-    <mergeCell ref="B264:B265"/>
-    <mergeCell ref="C264:C265"/>
-    <mergeCell ref="D264:D265"/>
-    <mergeCell ref="B274:B275"/>
-    <mergeCell ref="C274:C275"/>
-    <mergeCell ref="D274:D275"/>
-    <mergeCell ref="E269:H269"/>
-    <mergeCell ref="I269:L269"/>
-    <mergeCell ref="M269:P269"/>
-    <mergeCell ref="Q269:V269"/>
-    <mergeCell ref="B270:B271"/>
-    <mergeCell ref="C270:C271"/>
-    <mergeCell ref="D270:D271"/>
-    <mergeCell ref="B272:B273"/>
-    <mergeCell ref="E257:H257"/>
-    <mergeCell ref="I257:L257"/>
-    <mergeCell ref="M257:P257"/>
-    <mergeCell ref="Q257:V257"/>
-    <mergeCell ref="B258:B259"/>
-    <mergeCell ref="C258:C259"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="B260:B261"/>
-    <mergeCell ref="C260:C261"/>
-    <mergeCell ref="D260:D261"/>
-    <mergeCell ref="B252:B253"/>
-    <mergeCell ref="C252:C253"/>
-    <mergeCell ref="D252:D253"/>
-    <mergeCell ref="Q245:V245"/>
-    <mergeCell ref="B246:B247"/>
-    <mergeCell ref="C246:C247"/>
-    <mergeCell ref="D246:D247"/>
-    <mergeCell ref="B248:B249"/>
-    <mergeCell ref="C248:C249"/>
-    <mergeCell ref="D248:D249"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="C250:C251"/>
-    <mergeCell ref="D250:D251"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="C238:C239"/>
-    <mergeCell ref="D238:D239"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="C240:C241"/>
-    <mergeCell ref="D240:D241"/>
-    <mergeCell ref="E245:H245"/>
-    <mergeCell ref="I245:L245"/>
-    <mergeCell ref="M245:P245"/>
-    <mergeCell ref="E233:H233"/>
-    <mergeCell ref="I233:L233"/>
-    <mergeCell ref="M233:P233"/>
-    <mergeCell ref="Q233:V233"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="C234:C235"/>
-    <mergeCell ref="D234:D235"/>
-    <mergeCell ref="B236:B237"/>
-    <mergeCell ref="C236:C237"/>
-    <mergeCell ref="D236:D237"/>
+  <mergeCells count="460">
+    <mergeCell ref="B336:B337"/>
+    <mergeCell ref="C336:C337"/>
+    <mergeCell ref="D336:D337"/>
+    <mergeCell ref="B338:B339"/>
+    <mergeCell ref="C338:C339"/>
+    <mergeCell ref="D338:D339"/>
+    <mergeCell ref="E331:H331"/>
+    <mergeCell ref="I331:L331"/>
+    <mergeCell ref="M331:P331"/>
+    <mergeCell ref="Q331:V331"/>
+    <mergeCell ref="B332:B333"/>
+    <mergeCell ref="C332:C333"/>
+    <mergeCell ref="D332:D333"/>
+    <mergeCell ref="B334:B335"/>
+    <mergeCell ref="C334:C335"/>
+    <mergeCell ref="D334:D335"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="C300:C301"/>
+    <mergeCell ref="D300:D301"/>
+    <mergeCell ref="B302:B303"/>
+    <mergeCell ref="C302:C303"/>
+    <mergeCell ref="D302:D303"/>
+    <mergeCell ref="E295:H295"/>
+    <mergeCell ref="I295:L295"/>
+    <mergeCell ref="M295:P295"/>
+    <mergeCell ref="Q295:V295"/>
+    <mergeCell ref="B296:B297"/>
+    <mergeCell ref="C296:C297"/>
+    <mergeCell ref="D296:D297"/>
+    <mergeCell ref="B298:B299"/>
+    <mergeCell ref="C298:C299"/>
+    <mergeCell ref="D298:D299"/>
+    <mergeCell ref="B290:B291"/>
+    <mergeCell ref="C290:C291"/>
+    <mergeCell ref="D290:D291"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="C284:C285"/>
+    <mergeCell ref="D284:D285"/>
+    <mergeCell ref="B286:B287"/>
+    <mergeCell ref="C286:C287"/>
+    <mergeCell ref="D286:D287"/>
+    <mergeCell ref="B288:B289"/>
+    <mergeCell ref="C288:C289"/>
+    <mergeCell ref="D288:D289"/>
+    <mergeCell ref="E279:H279"/>
+    <mergeCell ref="I279:L279"/>
+    <mergeCell ref="M279:P279"/>
+    <mergeCell ref="Q279:V279"/>
+    <mergeCell ref="B280:B281"/>
+    <mergeCell ref="C280:C281"/>
+    <mergeCell ref="D280:D281"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="C282:C283"/>
+    <mergeCell ref="D282:D283"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="C226:C227"/>
+    <mergeCell ref="D226:D227"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="C228:C229"/>
+    <mergeCell ref="D228:D229"/>
+    <mergeCell ref="E221:H221"/>
+    <mergeCell ref="I221:L221"/>
+    <mergeCell ref="M221:P221"/>
+    <mergeCell ref="Q221:V221"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="D222:D223"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="C216:C217"/>
+    <mergeCell ref="D216:D217"/>
+    <mergeCell ref="E211:H211"/>
+    <mergeCell ref="I211:L211"/>
+    <mergeCell ref="M211:P211"/>
+    <mergeCell ref="Q211:V211"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="D212:D213"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="D214:D215"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="D198:D199"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="D206:D207"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="D200:D201"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="D202:D203"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="C204:C205"/>
+    <mergeCell ref="D204:D205"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E195:H195"/>
+    <mergeCell ref="I195:L195"/>
+    <mergeCell ref="M195:P195"/>
+    <mergeCell ref="Q195:V195"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="D196:D197"/>
+    <mergeCell ref="Q183:V183"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="D184:D185"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
+    <mergeCell ref="E183:H183"/>
+    <mergeCell ref="I183:L183"/>
+    <mergeCell ref="M183:P183"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="C126:C127"/>
+    <mergeCell ref="D126:D127"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="E113:H113"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="M113:P113"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="M77:P77"/>
+    <mergeCell ref="Q89:V89"/>
+    <mergeCell ref="M89:P89"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="Q113:V113"/>
+    <mergeCell ref="Q77:V77"/>
+    <mergeCell ref="E101:H101"/>
+    <mergeCell ref="I101:L101"/>
+    <mergeCell ref="M101:P101"/>
+    <mergeCell ref="Q101:V101"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:C109"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="Q63:V63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="Q49:V49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:V37"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:V24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="Q2:V2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="Q13:V13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="E135:H135"/>
+    <mergeCell ref="I135:L135"/>
+    <mergeCell ref="M135:P135"/>
+    <mergeCell ref="E125:H125"/>
+    <mergeCell ref="I125:L125"/>
+    <mergeCell ref="M125:P125"/>
+    <mergeCell ref="Q135:V135"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="Q125:V125"/>
+    <mergeCell ref="Q159:V159"/>
+    <mergeCell ref="Q171:V171"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="Q147:V147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D148:D149"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="E147:H147"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="M147:P147"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="C164:C165"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="C152:C153"/>
+    <mergeCell ref="D152:D153"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="C166:C167"/>
+    <mergeCell ref="D166:D167"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
     <mergeCell ref="E159:H159"/>
     <mergeCell ref="I159:L159"/>
     <mergeCell ref="M159:P159"/>
@@ -27136,335 +27789,99 @@
     <mergeCell ref="E171:H171"/>
     <mergeCell ref="I171:L171"/>
     <mergeCell ref="M171:P171"/>
-    <mergeCell ref="C152:C153"/>
-    <mergeCell ref="D152:D153"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="C166:C167"/>
-    <mergeCell ref="D166:D167"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="Q159:V159"/>
-    <mergeCell ref="Q171:V171"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="Q147:V147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D148:D149"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="E147:H147"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="M147:P147"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="E135:H135"/>
-    <mergeCell ref="I135:L135"/>
-    <mergeCell ref="M135:P135"/>
-    <mergeCell ref="E125:H125"/>
-    <mergeCell ref="I125:L125"/>
-    <mergeCell ref="M125:P125"/>
-    <mergeCell ref="Q135:V135"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="Q125:V125"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="I89:L89"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="Q13:V13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q24:V24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:V37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="Q49:V49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="Q63:V63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="E113:H113"/>
-    <mergeCell ref="I113:L113"/>
-    <mergeCell ref="M113:P113"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="M77:P77"/>
-    <mergeCell ref="Q89:V89"/>
-    <mergeCell ref="M89:P89"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="Q113:V113"/>
-    <mergeCell ref="Q77:V77"/>
-    <mergeCell ref="E101:H101"/>
-    <mergeCell ref="I101:L101"/>
-    <mergeCell ref="M101:P101"/>
-    <mergeCell ref="Q101:V101"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:C109"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="C120:C121"/>
-    <mergeCell ref="D120:D121"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="C126:C127"/>
-    <mergeCell ref="D126:D127"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E195:H195"/>
-    <mergeCell ref="I195:L195"/>
-    <mergeCell ref="M195:P195"/>
-    <mergeCell ref="Q195:V195"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="D196:D197"/>
-    <mergeCell ref="Q183:V183"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="D184:D185"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="D190:D191"/>
-    <mergeCell ref="E183:H183"/>
-    <mergeCell ref="I183:L183"/>
-    <mergeCell ref="M183:P183"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="D198:D199"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="C206:C207"/>
-    <mergeCell ref="D206:D207"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:C201"/>
-    <mergeCell ref="D200:D201"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="D202:D203"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="C204:C205"/>
-    <mergeCell ref="D204:D205"/>
-    <mergeCell ref="E211:H211"/>
-    <mergeCell ref="I211:L211"/>
-    <mergeCell ref="M211:P211"/>
-    <mergeCell ref="Q211:V211"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="D214:D215"/>
-    <mergeCell ref="Q221:V221"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="D222:D223"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="C216:C217"/>
-    <mergeCell ref="D216:D217"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="C226:C227"/>
-    <mergeCell ref="D226:D227"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="C228:C229"/>
-    <mergeCell ref="D228:D229"/>
-    <mergeCell ref="E221:H221"/>
-    <mergeCell ref="I221:L221"/>
-    <mergeCell ref="M221:P221"/>
+    <mergeCell ref="E233:H233"/>
+    <mergeCell ref="I233:L233"/>
+    <mergeCell ref="M233:P233"/>
+    <mergeCell ref="Q233:V233"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="C234:C235"/>
+    <mergeCell ref="D234:D235"/>
+    <mergeCell ref="B236:B237"/>
+    <mergeCell ref="C236:C237"/>
+    <mergeCell ref="D236:D237"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="C238:C239"/>
+    <mergeCell ref="D238:D239"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="C240:C241"/>
+    <mergeCell ref="D240:D241"/>
+    <mergeCell ref="E245:H245"/>
+    <mergeCell ref="I245:L245"/>
+    <mergeCell ref="M245:P245"/>
+    <mergeCell ref="B252:B253"/>
+    <mergeCell ref="C252:C253"/>
+    <mergeCell ref="D252:D253"/>
+    <mergeCell ref="Q245:V245"/>
+    <mergeCell ref="B246:B247"/>
+    <mergeCell ref="C246:C247"/>
+    <mergeCell ref="D246:D247"/>
+    <mergeCell ref="B248:B249"/>
+    <mergeCell ref="C248:C249"/>
+    <mergeCell ref="D248:D249"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="C250:C251"/>
+    <mergeCell ref="D250:D251"/>
+    <mergeCell ref="E269:H269"/>
+    <mergeCell ref="I269:L269"/>
+    <mergeCell ref="M269:P269"/>
+    <mergeCell ref="Q269:V269"/>
+    <mergeCell ref="B270:B271"/>
+    <mergeCell ref="C270:C271"/>
+    <mergeCell ref="D270:D271"/>
+    <mergeCell ref="B272:B273"/>
+    <mergeCell ref="E257:H257"/>
+    <mergeCell ref="I257:L257"/>
+    <mergeCell ref="M257:P257"/>
+    <mergeCell ref="Q257:V257"/>
+    <mergeCell ref="B258:B259"/>
+    <mergeCell ref="C258:C259"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="B260:B261"/>
+    <mergeCell ref="C260:C261"/>
+    <mergeCell ref="D260:D261"/>
     <mergeCell ref="C272:C273"/>
     <mergeCell ref="D272:D273"/>
-    <mergeCell ref="E279:H279"/>
-    <mergeCell ref="I279:L279"/>
-    <mergeCell ref="M279:P279"/>
-    <mergeCell ref="Q279:V279"/>
-    <mergeCell ref="B280:B281"/>
-    <mergeCell ref="C280:C281"/>
-    <mergeCell ref="D280:D281"/>
-    <mergeCell ref="B282:B283"/>
-    <mergeCell ref="C282:C283"/>
-    <mergeCell ref="D282:D283"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="C284:C285"/>
-    <mergeCell ref="D284:D285"/>
-    <mergeCell ref="B286:B287"/>
-    <mergeCell ref="C286:C287"/>
-    <mergeCell ref="D286:D287"/>
-    <mergeCell ref="B288:B289"/>
-    <mergeCell ref="C288:C289"/>
-    <mergeCell ref="D288:D289"/>
-    <mergeCell ref="Q295:V295"/>
-    <mergeCell ref="B296:B297"/>
-    <mergeCell ref="C296:C297"/>
-    <mergeCell ref="D296:D297"/>
-    <mergeCell ref="B298:B299"/>
-    <mergeCell ref="C298:C299"/>
-    <mergeCell ref="D298:D299"/>
-    <mergeCell ref="B290:B291"/>
-    <mergeCell ref="C290:C291"/>
-    <mergeCell ref="D290:D291"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="C300:C301"/>
-    <mergeCell ref="D300:D301"/>
-    <mergeCell ref="B302:B303"/>
-    <mergeCell ref="C302:C303"/>
-    <mergeCell ref="D302:D303"/>
-    <mergeCell ref="E295:H295"/>
-    <mergeCell ref="I295:L295"/>
-    <mergeCell ref="M295:P295"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="C262:C263"/>
+    <mergeCell ref="D262:D263"/>
+    <mergeCell ref="B264:B265"/>
+    <mergeCell ref="C264:C265"/>
+    <mergeCell ref="D264:D265"/>
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="C274:C275"/>
+    <mergeCell ref="D274:D275"/>
+    <mergeCell ref="E307:H307"/>
+    <mergeCell ref="I307:L307"/>
+    <mergeCell ref="M307:P307"/>
+    <mergeCell ref="Q307:V307"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="C308:C309"/>
+    <mergeCell ref="D308:D309"/>
+    <mergeCell ref="B310:B311"/>
+    <mergeCell ref="C310:C311"/>
+    <mergeCell ref="D310:D311"/>
+    <mergeCell ref="Q319:V319"/>
+    <mergeCell ref="B320:B321"/>
+    <mergeCell ref="C320:C321"/>
+    <mergeCell ref="D320:D321"/>
+    <mergeCell ref="B322:B323"/>
+    <mergeCell ref="C322:C323"/>
+    <mergeCell ref="D322:D323"/>
+    <mergeCell ref="B312:B313"/>
+    <mergeCell ref="C312:C313"/>
+    <mergeCell ref="D312:D313"/>
+    <mergeCell ref="B314:B315"/>
+    <mergeCell ref="C314:C315"/>
+    <mergeCell ref="D314:D315"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="C324:C325"/>
+    <mergeCell ref="D324:D325"/>
+    <mergeCell ref="B326:B327"/>
+    <mergeCell ref="C326:C327"/>
+    <mergeCell ref="D326:D327"/>
+    <mergeCell ref="E319:H319"/>
+    <mergeCell ref="I319:L319"/>
+    <mergeCell ref="M319:P319"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
@@ -27506,23 +27923,23 @@
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="D2" s="15">
         <f>SUM(D4:D95)</f>
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E2" s="15">
         <f>SUM(E4:E95)</f>
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F2" s="15">
         <f>SUM(F4:F95)</f>
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G2" s="15">
         <f>SUM(G4:G95)</f>
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="H2" s="15">
         <f>SUM(H4:H95)</f>
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -27601,7 +28018,7 @@
       </c>
       <c r="C4" s="2">
         <f>((D4+E4+G4+H4)*0.2)+(F4*0.3)</f>
-        <v>2.2000000000000002</v>
+        <v>2.6</v>
       </c>
       <c r="D4" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B4)</f>
@@ -27609,7 +28026,7 @@
       </c>
       <c r="E4" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B4)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B4)</f>
@@ -27625,7 +28042,7 @@
       </c>
       <c r="I4" s="14">
         <f>SUM(D4:H4)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="2">
@@ -27664,7 +28081,7 @@
       </c>
       <c r="U4" s="56">
         <f t="shared" ref="U4:U14" si="4">VLOOKUP(T4,$B$4:$H$133,7,FALSE)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -27727,14 +28144,14 @@
       </c>
       <c r="Q5" s="23">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R5" s="35" t="s">
         <v>230</v>
       </c>
       <c r="S5" s="55">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T5" s="36" t="s">
         <v>228</v>
@@ -27790,10 +28207,10 @@
       </c>
       <c r="M6" s="21">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>356</v>
+        <v>50</v>
       </c>
       <c r="O6" s="22">
         <f t="shared" si="1"/>
@@ -27863,18 +28280,18 @@
         <v>4</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="M7" s="21">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>221</v>
+        <v>356</v>
       </c>
       <c r="O7" s="22">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P7" s="34" t="s">
         <v>298</v>
@@ -27884,18 +28301,18 @@
         <v>8</v>
       </c>
       <c r="R7" s="35" t="s">
-        <v>359</v>
+        <v>232</v>
       </c>
       <c r="S7" s="55">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="T7" s="36" t="s">
-        <v>352</v>
+        <v>181</v>
       </c>
       <c r="U7" s="56">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -27940,18 +28357,18 @@
         <v>5</v>
       </c>
       <c r="L8" s="32" t="s">
-        <v>352</v>
+        <v>221</v>
       </c>
       <c r="M8" s="21">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="O8" s="22">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P8" s="34" t="s">
         <v>53</v>
@@ -27961,14 +28378,14 @@
         <v>8</v>
       </c>
       <c r="R8" s="35" t="s">
-        <v>232</v>
+        <v>62</v>
       </c>
       <c r="S8" s="55">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T8" s="36" t="s">
-        <v>353</v>
+        <v>311</v>
       </c>
       <c r="U8" s="56">
         <f t="shared" si="4"/>
@@ -28017,7 +28434,7 @@
         <v>6</v>
       </c>
       <c r="L9" s="32" t="s">
-        <v>231</v>
+        <v>352</v>
       </c>
       <c r="M9" s="21">
         <f t="shared" si="0"/>
@@ -28038,11 +28455,11 @@
         <v>8</v>
       </c>
       <c r="R9" s="35" t="s">
-        <v>62</v>
+        <v>359</v>
       </c>
       <c r="S9" s="55">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T9" s="36" t="s">
         <v>396</v>
@@ -28192,7 +28609,7 @@
         <v>7</v>
       </c>
       <c r="R11" s="35" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="S11" s="55">
         <f t="shared" si="3"/>
@@ -28248,11 +28665,11 @@
         <v>9</v>
       </c>
       <c r="L12" s="32" t="s">
-        <v>304</v>
+        <v>406</v>
       </c>
       <c r="M12" s="21">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="33" t="s">
         <v>397</v>
@@ -28269,11 +28686,11 @@
         <v>6</v>
       </c>
       <c r="R12" s="35" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="S12" s="55">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T12" s="36" t="s">
         <v>360</v>
@@ -28325,11 +28742,11 @@
         <v>10</v>
       </c>
       <c r="L13" s="32" t="s">
-        <v>406</v>
+        <v>304</v>
       </c>
       <c r="M13" s="21">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N13" s="33" t="s">
         <v>352</v>
@@ -28346,11 +28763,11 @@
         <v>5</v>
       </c>
       <c r="R13" s="35" t="s">
-        <v>34</v>
+        <v>360</v>
       </c>
       <c r="S13" s="55">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" s="36" t="s">
         <v>359</v>
@@ -28423,11 +28840,11 @@
         <v>5</v>
       </c>
       <c r="R14" s="55" t="s">
-        <v>221</v>
+        <v>34</v>
       </c>
       <c r="S14" s="55">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" s="36" t="s">
         <v>229</v>
@@ -28500,7 +28917,7 @@
         <v>5</v>
       </c>
       <c r="R15" s="55" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="S15" s="55">
         <f t="shared" si="3"/>
@@ -28564,15 +28981,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="P16" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q16" s="23">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
       <c r="R16" s="55" t="s">
-        <v>360</v>
+        <v>241</v>
       </c>
       <c r="S16" s="55">
         <f t="shared" si="3"/>
@@ -28631,9 +29043,7 @@
       </c>
       <c r="N17" s="22"/>
       <c r="O17" s="22"/>
-      <c r="P17" s="23" t="s">
-        <v>316</v>
-      </c>
+      <c r="P17" s="23"/>
       <c r="Q17" s="23"/>
       <c r="R17" s="55" t="s">
         <v>67</v>
@@ -28697,13 +29107,8 @@
       <c r="O18" s="22"/>
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
-      <c r="R18" s="55" t="s">
-        <v>229</v>
-      </c>
-      <c r="S18" s="55">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
+      <c r="R18" s="55"/>
+      <c r="S18" s="55"/>
       <c r="T18" s="56"/>
       <c r="U18" s="56"/>
     </row>
@@ -28913,7 +29318,7 @@
       </c>
       <c r="C24" s="2">
         <f>((D24+E24+G24+H24)*0.2)+(F24*0.3)</f>
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="D24" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B24)</f>
@@ -28933,11 +29338,11 @@
       </c>
       <c r="H24" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="14">
         <f>SUM(D24:H24)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J24" s="15"/>
     </row>
@@ -29615,7 +30020,7 @@
       </c>
       <c r="C42" s="2">
         <f>((D42+E42+G42+H42)*0.2)+(F42*0.3)</f>
-        <v>4.6000000000000005</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="D42" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B42)</f>
@@ -29635,11 +30040,11 @@
       </c>
       <c r="H42" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B42)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42" s="14">
         <f>SUM(D42:H42)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J42" s="15"/>
     </row>
@@ -29693,19 +30098,19 @@
       </c>
       <c r="C44" s="2">
         <f>((D44+E44+G44+H44)*0.2)+(F44*0.3)</f>
-        <v>2.4</v>
+        <v>3.6000000000000005</v>
       </c>
       <c r="D44" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B44)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E44" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B44)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B44)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B44)</f>
@@ -29717,7 +30122,7 @@
       </c>
       <c r="I44" s="14">
         <f>SUM(D44:H44)</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J44" s="15"/>
     </row>
@@ -29771,7 +30176,7 @@
       </c>
       <c r="C46" s="2">
         <f>((D46+E46+G46+H46)*0.2)+(F46*0.3)</f>
-        <v>3.4000000000000004</v>
+        <v>3.6</v>
       </c>
       <c r="D46" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B46)</f>
@@ -29787,7 +30192,7 @@
       </c>
       <c r="G46" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B46)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H46" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B46)</f>
@@ -29795,7 +30200,7 @@
       </c>
       <c r="I46" s="14">
         <f>SUM(D46:H46)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J46" s="15"/>
     </row>
@@ -29810,7 +30215,7 @@
       </c>
       <c r="C47" s="2">
         <f>((D47+E47+G47+H47)*0.2)+(F47*0.3)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D47" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B47)</f>
@@ -29822,11 +30227,11 @@
       </c>
       <c r="F47" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B47)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B47)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B47)</f>
@@ -29834,7 +30239,7 @@
       </c>
       <c r="I47" s="14">
         <f>SUM(D47:H47)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J47" s="15"/>
     </row>
@@ -30200,7 +30605,7 @@
       </c>
       <c r="C57" s="2">
         <f>((D57+E57+G57+H57)*0.2)+(F57*0.3)</f>
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D57" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B57)</f>
@@ -30212,7 +30617,7 @@
       </c>
       <c r="F57" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B57)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G57" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B57)</f>
@@ -30224,7 +30629,7 @@
       </c>
       <c r="I57" s="14">
         <f>SUM(D57:H57)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J57" s="15"/>
     </row>
@@ -30317,7 +30722,7 @@
       </c>
       <c r="C60" s="2">
         <f>((D60+E60+G60+H60)*0.2)+(F60*0.3)</f>
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
       <c r="D60" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B60)</f>
@@ -30333,7 +30738,7 @@
       </c>
       <c r="G60" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B60)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H60" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B60)</f>
@@ -30341,7 +30746,7 @@
       </c>
       <c r="I60" s="14">
         <f>SUM(D60:H60)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J60" s="15"/>
     </row>
@@ -30707,7 +31112,7 @@
       </c>
       <c r="C70" s="2">
         <f>((D70+E70+G70+H70)*0.2)+(F70*0.3)</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D70" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B70)</f>
@@ -30715,7 +31120,7 @@
       </c>
       <c r="E70" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B70)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B70)</f>
@@ -30731,7 +31136,7 @@
       </c>
       <c r="I70" s="14">
         <f>SUM(D70:H70)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J70" s="15"/>
     </row>
@@ -30863,7 +31268,7 @@
       </c>
       <c r="C74" s="2">
         <f>((D74+E74+G74+H74)*0.2)+(F74*0.3)</f>
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="D74" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B74)</f>
@@ -30879,7 +31284,7 @@
       </c>
       <c r="G74" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B74)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H74" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B74)</f>
@@ -30887,7 +31292,7 @@
       </c>
       <c r="I74" s="14">
         <f>SUM(D74:H74)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J74" s="15"/>
     </row>
@@ -31136,7 +31541,7 @@
       </c>
       <c r="C81" s="2">
         <f>((D81+E81+G81+H81)*0.2)+(F81*0.3)</f>
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="D81" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B81)</f>
@@ -31152,7 +31557,7 @@
       </c>
       <c r="G81" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B81)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H81" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B81)</f>
@@ -31160,7 +31565,7 @@
       </c>
       <c r="I81" s="14">
         <f>SUM(D81:H81)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J81" s="15"/>
     </row>
@@ -31214,7 +31619,7 @@
       </c>
       <c r="C83" s="2">
         <f>((D83+E83+G83+H83)*0.2)+(F83*0.3)</f>
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D83" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B83)</f>
@@ -31230,7 +31635,7 @@
       </c>
       <c r="G83" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B83)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H83" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B83)</f>
@@ -31238,7 +31643,7 @@
       </c>
       <c r="I83" s="14">
         <f>SUM(D83:H83)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J83" s="15"/>
     </row>
@@ -31643,11 +32048,11 @@
       </c>
       <c r="C94" s="2">
         <f>((D94+E94+G94+H94)*0.2)+(F94*0.3)</f>
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="D94" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B94)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E94" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B94)</f>
@@ -31667,7 +32072,7 @@
       </c>
       <c r="I94" s="14">
         <f>SUM(D94:H94)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J94" s="15"/>
     </row>
@@ -31877,7 +32282,7 @@
       </c>
       <c r="C100" s="2">
         <f>((D100+E100+G100+H100)*0.2)+(F100*0.3)</f>
-        <v>5.6000000000000005</v>
+        <v>5.8000000000000007</v>
       </c>
       <c r="D100" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B100)</f>
@@ -31893,7 +32298,7 @@
       </c>
       <c r="G100" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B100)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H100" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B100)</f>
@@ -31901,7 +32306,7 @@
       </c>
       <c r="I100" s="14">
         <f>SUM(D100:H100)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J100" s="15"/>
     </row>
@@ -31916,11 +32321,11 @@
       </c>
       <c r="C101" s="2">
         <f>((D101+E101+G101+H101)*0.2)+(F101*0.3)</f>
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D101" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B101)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E101" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B101)</f>
@@ -31940,7 +32345,7 @@
       </c>
       <c r="I101" s="14">
         <f>SUM(D101:H101)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J101" s="15"/>
     </row>
@@ -31955,11 +32360,11 @@
       </c>
       <c r="C102" s="2">
         <f>((D102+E102+G102+H102)*0.2)+(F102*0.3)</f>
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="D102" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B102)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B102)</f>
@@ -31979,7 +32384,7 @@
       </c>
       <c r="I102" s="14">
         <f>SUM(D102:H102)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J102" s="15"/>
     </row>
@@ -31994,7 +32399,7 @@
       </c>
       <c r="C103" s="2">
         <f>((D103+E103+G103+H103)*0.2)+(F103*0.3)</f>
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="D103" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B103)</f>
@@ -32006,7 +32411,7 @@
       </c>
       <c r="F103" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B103)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G103" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B103)</f>
@@ -32018,7 +32423,7 @@
       </c>
       <c r="I103" s="14">
         <f>SUM(D103:H103)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J103" s="15"/>
     </row>
@@ -32033,7 +32438,7 @@
       </c>
       <c r="C104" s="2">
         <f>((D104+E104+G104+H104)*0.2)+(F104*0.3)</f>
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D104" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B104)</f>
@@ -32049,7 +32454,7 @@
       </c>
       <c r="G104" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B104)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H104" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B104)</f>
@@ -32057,7 +32462,7 @@
       </c>
       <c r="I104" s="14">
         <f>SUM(D104:H104)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J104" s="15"/>
     </row>
@@ -32680,7 +33085,7 @@
       </c>
       <c r="C121" s="2">
         <f>((D121+E121+G121+H121)*0.2)+(F121*0.3)</f>
-        <v>4.2</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="D121" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B121)</f>
@@ -32688,7 +33093,7 @@
       </c>
       <c r="E121" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B121)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B121)</f>
@@ -32696,15 +33101,15 @@
       </c>
       <c r="G121" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B121)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H121" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B121)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I121" s="14">
         <f>SUM(D121:H121)</f>
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -32718,15 +33123,15 @@
       </c>
       <c r="C122" s="2">
         <f>((D122+E122+G122+H122)*0.2)+(F122*0.3)</f>
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="D122" s="14">
         <f>COUNTIF(경기기록Sheet!$E:$H,B122)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" s="14">
         <f>COUNTIF(경기기록Sheet!$I:$L,B122)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="14">
         <f>COUNTIF(경기기록Sheet!$M:$P,B122)</f>
@@ -32734,7 +33139,7 @@
       </c>
       <c r="G122" s="14">
         <f>COUNTIF(경기기록Sheet!$Q:$U,B122)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H122" s="14">
         <f>COUNTIF(경기기록Sheet!$V:$V,B122)</f>
@@ -32742,15 +33147,10 @@
       </c>
       <c r="I122" s="14">
         <f>SUM(D122:H122)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I122">
-      <sortCondition ref="A3"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D4:D122">
     <cfRule type="top10" dxfId="9" priority="974" rank="7"/>
@@ -34333,10 +34733,10 @@
       <c r="G2" s="47" t="s">
         <v>328</v>
       </c>
-      <c r="I2" s="99" t="s">
+      <c r="I2" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="J2" s="99"/>
+      <c r="J2" s="94"/>
       <c r="K2" s="65" t="s">
         <v>276</v>
       </c>
@@ -34361,7 +34761,7 @@
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="93" t="s">
         <v>334</v>
       </c>
       <c r="C3" s="72">
@@ -34424,7 +34824,7 @@
       </c>
       <c r="E4" s="62">
         <f>VLOOKUP(D4,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="70" t="s">
         <v>224</v>
@@ -34500,14 +34900,14 @@
       </c>
       <c r="Q5" s="62">
         <f>VLOOKUP(P5,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>304</v>
       </c>
       <c r="S5" s="63">
         <f>VLOOKUP(R5,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>30.7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.25">
@@ -34520,14 +34920,14 @@
       </c>
       <c r="E6" s="47">
         <f>VLOOKUP(D6,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6" s="70" t="s">
         <v>232</v>
       </c>
       <c r="G6" s="61">
         <f>VLOOKUP(F6,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>21.4</v>
+        <v>22.6</v>
       </c>
       <c r="I6" s="96"/>
       <c r="J6" s="66">
@@ -34548,14 +34948,14 @@
       </c>
       <c r="Q6" s="69">
         <f>VLOOKUP(P6,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R6" s="65" t="s">
         <v>230</v>
       </c>
       <c r="S6" s="71">
         <f>VLOOKUP(R6,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.25">
@@ -34568,16 +34968,16 @@
       </c>
       <c r="E7" s="47">
         <f>VLOOKUP(D7,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="70" t="s">
         <v>304</v>
       </c>
       <c r="G7" s="61">
         <f>VLOOKUP(F7,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>30.7</v>
-      </c>
-      <c r="I7" s="97"/>
+        <v>32</v>
+      </c>
+      <c r="I7" s="98"/>
       <c r="J7" s="66">
         <v>5</v>
       </c>
@@ -34623,7 +35023,7 @@
       </c>
       <c r="G8" s="63">
         <f>VLOOKUP(F8,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>27.2</v>
+        <v>28.6</v>
       </c>
       <c r="N8" s="86"/>
       <c r="O8" s="48">
@@ -34661,12 +35061,12 @@
       </c>
       <c r="G9" s="61">
         <f>VLOOKUP(F9,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>17</v>
-      </c>
-      <c r="I9" s="99" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="J9" s="99"/>
+      <c r="J9" s="94"/>
       <c r="K9" s="65" t="s">
         <v>276</v>
       </c>
@@ -34682,7 +35082,7 @@
       </c>
       <c r="Q9" s="69">
         <f>VLOOKUP(P9,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R9" s="65" t="s">
         <v>309</v>
@@ -34702,14 +35102,14 @@
       </c>
       <c r="E10" s="64">
         <f>VLOOKUP(D10,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="70" t="s">
         <v>53</v>
       </c>
       <c r="G10" s="61">
         <f>VLOOKUP(F10,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>18.600000000000001</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="I10" s="95" t="s">
         <v>330</v>
@@ -34739,7 +35139,7 @@
       </c>
       <c r="S10" s="71">
         <f>VLOOKUP(R10,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>15</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.25">
@@ -34752,7 +35152,7 @@
       </c>
       <c r="E11" s="65">
         <f>VLOOKUP(D11,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="70" t="s">
         <v>48</v>
@@ -34819,7 +35219,7 @@
       <c r="L12" s="65">
         <v>8</v>
       </c>
-      <c r="N12" s="98"/>
+      <c r="N12" s="101"/>
       <c r="O12" s="48">
         <v>10</v>
       </c>
@@ -34848,7 +35248,7 @@
       </c>
       <c r="E13" s="65">
         <f>VLOOKUP(D13,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" s="70" t="s">
         <v>241</v>
@@ -34884,16 +35284,16 @@
       </c>
       <c r="E14" s="65">
         <f>VLOOKUP(D14,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="70" t="s">
         <v>228</v>
       </c>
       <c r="G14" s="61">
         <f>VLOOKUP(F14,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>31.6</v>
-      </c>
-      <c r="I14" s="97"/>
+        <v>32.6</v>
+      </c>
+      <c r="I14" s="98"/>
       <c r="J14" s="66">
         <v>5</v>
       </c>
@@ -34946,20 +35346,20 @@
       </c>
       <c r="E16" s="65">
         <f>VLOOKUP(D16,종합Sheet!$B$3:$I$121,8,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F16" s="62" t="s">
         <v>230</v>
       </c>
       <c r="G16" s="63">
         <f>VLOOKUP(F16,종합Sheet!$B$3:$I$121,7,0)</f>
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
       <c r="H16" s="37"/>
-      <c r="I16" s="99" t="s">
+      <c r="I16" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="J16" s="99"/>
+      <c r="J16" s="94"/>
       <c r="K16" s="65" t="s">
         <v>276</v>
       </c>
@@ -35020,10 +35420,10 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="99" t="s">
+      <c r="B19" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="C19" s="99"/>
+      <c r="C19" s="94"/>
       <c r="D19" s="65" t="s">
         <v>276</v>
       </c>
@@ -35074,7 +35474,7 @@
       <c r="E21" s="65" t="s">
         <v>337</v>
       </c>
-      <c r="I21" s="97"/>
+      <c r="I21" s="98"/>
       <c r="J21" s="66">
         <v>5</v>
       </c>
@@ -35086,7 +35486,7 @@
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="101"/>
+      <c r="B22" s="97"/>
       <c r="C22" s="66">
         <v>3</v>
       </c>
@@ -35098,10 +35498,10 @@
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I23" s="93" t="s">
+      <c r="I23" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="J23" s="94"/>
+      <c r="J23" s="100"/>
       <c r="K23" s="65" t="s">
         <v>276</v>
       </c>
@@ -35184,7 +35584,7 @@
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I30" s="97"/>
+      <c r="I30" s="98"/>
       <c r="J30" s="66">
         <v>7</v>
       </c>
@@ -35197,12 +35597,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B3:B17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:I21"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:I30"/>
     <mergeCell ref="N2:O2"/>
@@ -35211,6 +35605,12 @@
     <mergeCell ref="I3:I7"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I10:I14"/>
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:I21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35751,11 +36151,11 @@
       </c>
       <c r="G4" s="2">
         <f t="shared" ref="G4:G37" si="2">RANK(H4,$H$4:$H$37,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="6">
         <f>I4+개인기록Sheet!C4</f>
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4:I28" si="3">(COUNTIF(J4:CD4,"출전")*1)</f>
@@ -36665,7 +37065,7 @@
       </c>
       <c r="G12" s="2">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="6">
         <f>I12+개인기록Sheet!C18</f>
@@ -37328,7 +37728,7 @@
       </c>
       <c r="G18" s="2">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" s="6">
         <f>I18+개인기록Sheet!C29</f>
@@ -37446,7 +37846,7 @@
       </c>
       <c r="G19" s="2">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H19" s="6">
         <f>I19+개인기록Sheet!C34</f>
@@ -37676,11 +38076,11 @@
       </c>
       <c r="G21" s="2">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H21" s="6">
         <f>I21+개인기록Sheet!C44</f>
-        <v>4.4000000000000004</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="I21" s="6">
         <f t="shared" si="3"/>
@@ -37777,7 +38177,7 @@
       </c>
       <c r="D22" s="2">
         <f>VLOOKUP(B22,종합Sheet!$B$4:$F$133,3,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
         <f>VLOOKUP(B22,종합Sheet!$B$4:$F$133,4,0)</f>
@@ -37887,7 +38287,7 @@
       </c>
       <c r="G23" s="2">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H23" s="6">
         <f>I23+개인기록Sheet!C49</f>
@@ -38003,11 +38403,11 @@
       </c>
       <c r="G24" s="2">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H24" s="6">
         <f>I24+개인기록Sheet!C57</f>
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="I24" s="6">
         <f t="shared" si="3"/>
@@ -38115,7 +38515,7 @@
       </c>
       <c r="G25" s="2">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="6">
         <f>I25+개인기록Sheet!C59</f>
@@ -38229,11 +38629,11 @@
       </c>
       <c r="G26" s="2">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" s="6">
         <f>I26+개인기록Sheet!C60</f>
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="3"/>
@@ -38907,7 +39307,7 @@
       </c>
       <c r="G32" s="2">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H32" s="6">
         <f>I32+개인기록Sheet!C79</f>
@@ -39027,7 +39427,7 @@
       </c>
       <c r="H33" s="6">
         <f>I33+개인기록Sheet!C83</f>
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="6"/>
@@ -39361,11 +39761,11 @@
       </c>
       <c r="G36" s="2">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H36" s="6">
         <f>I36+개인기록Sheet!C102</f>
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I36" s="6">
         <f t="shared" si="6"/>
@@ -39479,7 +39879,7 @@
       </c>
       <c r="H37" s="6">
         <f>I37+개인기록Sheet!C104</f>
-        <v>8</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="6"/>
